--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F139D2-E493-5F48-919C-8D1671F02DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81F938F-CD76-C846-8210-14F4E0829026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -626,9 +626,6 @@
     <t>#! DUMP_COLS x.actions</t>
   </si>
   <si>
-    <t xml:space="preserve">         Extracteur De Données D'Effectifs</t>
-  </si>
-  <si>
     <t>#` ${arrondissement}</t>
   </si>
   <si>
@@ -672,6 +669,9 @@
   </si>
   <si>
     <t xml:space="preserve">         Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Extracteur de données d'effectifs</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1548,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1858,7 +1858,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1927,10 +1927,10 @@
   <sheetData>
     <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" s="56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="46" t="e">
         <f>VLOOKUP(A2,'codage tribunal'!A:B,2,FALSE)</f>
@@ -1959,37 +1959,37 @@
       <c r="C4" s="39"/>
       <c r="D4" s="40"/>
       <c r="E4" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="G4" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="H4" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="I4" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="J4" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="K4" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="43" t="s">
-        <v>80</v>
-      </c>
       <c r="L4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="44"/>
       <c r="C5" s="48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="51" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
@@ -2020,7 +2020,7 @@
         <v>#N/A</v>
       </c>
       <c r="L5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA05D1ED-D4C7-1C41-A54A-DAB6911B620F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E054AD9C-5FEE-444C-AC9A-C915ED0C461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -784,7 +784,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -868,29 +868,35 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -899,21 +905,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6FC886D6-2077-B34D-B1DF-739B068A66D1}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1834,7 +1826,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:K150">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ISBLANK($C5)=FALSE,ISBLANK($D5)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1865,26 +1857,28 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="71.1640625" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="36" customWidth="1"/>
+    <col min="3" max="9" width="10.83203125" style="36"/>
+    <col min="10" max="10" width="71.1640625" style="36" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-    </row>
-    <row r="2" spans="1:10" s="15" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10" s="32" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
         <v>7</v>
       </c>
@@ -1900,71 +1894,71 @@
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
     </row>
-    <row r="3" spans="1:10" s="15" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="32" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="30"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-    </row>
-    <row r="4" spans="1:10" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35" t="s">
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+    </row>
+    <row r="4" spans="1:10" s="32" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30"/>
+      <c r="B4" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35" t="s">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+    </row>
+    <row r="5" spans="1:10" s="32" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="30"/>
+      <c r="B5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-    </row>
-    <row r="6" spans="1:10" s="15" customFormat="1" ht="32.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" spans="1:10" s="32" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-    </row>
-    <row r="7" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+    </row>
+    <row r="7" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="30"/>
       <c r="B7" s="31" t="s">
         <v>47</v>
@@ -1978,143 +1972,151 @@
       <c r="I7" s="31"/>
       <c r="J7" s="31"/>
     </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="36" t="s">
+    <row r="8" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-    </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="36" t="s">
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+    </row>
+    <row r="9" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-    </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="36" t="s">
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+    </row>
+    <row r="10" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-    </row>
-    <row r="11" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="36" t="s">
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-    </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+    </row>
+    <row r="12" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="32" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="32" t="s">
+    <row r="13" spans="1:10" s="32" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="32" t="s">
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" spans="1:10" s="32" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-    </row>
-    <row r="15" spans="1:10" s="15" customFormat="1" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="32" t="s">
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+    </row>
+    <row r="15" spans="1:10" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="32" t="s">
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" spans="1:10" s="32" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-    </row>
-    <row r="18" spans="1:10" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29" t="s">
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+    </row>
+    <row r="18" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="B6:J6"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B8:J8"/>
@@ -2123,12 +2125,6 @@
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E054AD9C-5FEE-444C-AC9A-C915ED0C461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFA25C5-CCD6-A14E-8507-17C853FC29DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -784,7 +784,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -868,36 +868,37 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1615,7 +1616,7 @@
       <c r="E4"/>
     </row>
     <row r="5" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B5" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C5"/>
@@ -1693,7 +1694,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B5" s="39" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1706,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -1721,7 +1722,7 @@
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>35</v>
       </c>
@@ -1732,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>22</v>
       </c>
@@ -1744,13 +1745,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="9"/>
     </row>
-    <row r="4" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -1779,7 +1780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="C5" s="19" t="s">
         <v>34</v>
@@ -1819,8 +1820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="M6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1857,258 +1858,268 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" style="36" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="36" customWidth="1"/>
-    <col min="3" max="9" width="10.83203125" style="36"/>
-    <col min="10" max="10" width="71.1640625" style="36" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="36"/>
+    <col min="1" max="1" width="8.1640625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="24" customWidth="1"/>
+    <col min="3" max="9" width="10.83203125" style="24"/>
+    <col min="10" max="10" width="71.1640625" style="24" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-    </row>
-    <row r="2" spans="1:10" s="32" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-    </row>
-    <row r="3" spans="1:10" s="32" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="30"/>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-    </row>
-    <row r="4" spans="1:10" s="32" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+    </row>
+    <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30"/>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-    </row>
-    <row r="5" spans="1:10" s="32" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="30"/>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-    </row>
-    <row r="6" spans="1:10" s="32" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+    </row>
+    <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-    </row>
-    <row r="7" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+    </row>
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="30"/>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-    </row>
-    <row r="8" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="35" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-    </row>
-    <row r="9" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="35" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+    </row>
+    <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-    </row>
-    <row r="10" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="35" t="s">
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+    </row>
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-    </row>
-    <row r="11" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="35" t="s">
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+    </row>
+    <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-    </row>
-    <row r="12" spans="1:10" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+    </row>
+    <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="30" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" s="32" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="33" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-    </row>
-    <row r="14" spans="1:10" s="32" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="33" t="s">
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+    </row>
+    <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-    </row>
-    <row r="15" spans="1:10" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="33" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-    </row>
-    <row r="16" spans="1:10" s="32" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="s">
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+    </row>
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="18" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
@@ -2124,7 +2135,6 @@
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFA25C5-CCD6-A14E-8507-17C853FC29DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F89413-D477-E346-84BF-35A1BA14109B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="2" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Fonctionnaires placés de substitution</t>
   </si>
   <si>
-    <t>Contractuels</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -570,6 +567,24 @@
   </si>
   <si>
     <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
+  </si>
+  <si>
+    <t>SIEGE</t>
+  </si>
+  <si>
+    <t>GREFFE</t>
+  </si>
+  <si>
+    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
+  </si>
+  <si>
+    <t>Contractuels et vacataires</t>
+  </si>
+  <si>
+    <t>TOTAL SIEGE</t>
+  </si>
+  <si>
+    <t>TOTAL GREFFE</t>
   </si>
 </sst>
 </file>
@@ -583,7 +598,7 @@
     <numFmt numFmtId="166" formatCode="General;General;\-"/>
     <numFmt numFmtId="167" formatCode="0.###;0.###;\-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -660,6 +675,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -705,7 +728,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -777,6 +800,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -784,7 +883,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -825,9 +924,6 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -877,6 +973,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -892,13 +992,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -906,7 +1026,22 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6FC886D6-2077-B34D-B1DF-739B068A66D1}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1345,7 +1480,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1360,131 +1495,131 @@
       </c>
     </row>
     <row r="2" spans="1:118" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
-      <c r="AQ2" s="24"/>
-      <c r="AR2" s="24"/>
-      <c r="AS2" s="24"/>
-      <c r="AT2" s="24"/>
-      <c r="AU2" s="24"/>
-      <c r="AV2" s="24"/>
-      <c r="AW2" s="24"/>
-      <c r="AX2" s="24"/>
-      <c r="AY2" s="24"/>
-      <c r="AZ2" s="24"/>
-      <c r="BA2" s="24"/>
-      <c r="BB2" s="24"/>
-      <c r="BC2" s="24"/>
-      <c r="BD2" s="24"/>
-      <c r="BE2" s="24"/>
-      <c r="BF2" s="24"/>
-      <c r="BG2" s="24"/>
-      <c r="BH2" s="24"/>
-      <c r="BI2" s="24"/>
-      <c r="BJ2" s="24"/>
-      <c r="BK2" s="24"/>
-      <c r="BL2" s="24"/>
-      <c r="BM2" s="24"/>
-      <c r="BN2" s="24"/>
-      <c r="BO2" s="24"/>
-      <c r="BP2" s="24"/>
-      <c r="BQ2" s="24"/>
-      <c r="BR2" s="24"/>
-      <c r="BS2" s="24"/>
-      <c r="BT2" s="24"/>
-      <c r="BU2" s="24"/>
-      <c r="BV2" s="24"/>
-      <c r="BW2" s="24"/>
-      <c r="BX2" s="24"/>
-      <c r="BY2" s="24"/>
-      <c r="BZ2" s="24"/>
-      <c r="CA2" s="24"/>
-      <c r="CB2" s="24"/>
-      <c r="CC2" s="24"/>
-      <c r="CD2" s="24"/>
-      <c r="CE2" s="24"/>
-      <c r="CF2" s="24"/>
-      <c r="CG2" s="24"/>
-      <c r="CH2" s="24"/>
-      <c r="CI2" s="24"/>
-      <c r="CJ2" s="24"/>
-      <c r="CK2" s="24"/>
-      <c r="CL2" s="24"/>
-      <c r="CM2" s="24"/>
-      <c r="CN2" s="24"/>
-      <c r="CO2" s="24"/>
-      <c r="CP2" s="24"/>
-      <c r="CQ2" s="24"/>
-      <c r="CR2" s="24"/>
-      <c r="CS2" s="24"/>
-      <c r="CT2" s="24"/>
-      <c r="CU2" s="24"/>
-      <c r="CV2" s="24"/>
-      <c r="CW2" s="24"/>
-      <c r="CX2" s="24"/>
-      <c r="CY2" s="24"/>
-      <c r="CZ2" s="24"/>
-      <c r="DA2" s="24"/>
-      <c r="DB2" s="24"/>
-      <c r="DC2" s="24"/>
-      <c r="DD2" s="24"/>
-      <c r="DE2" s="24"/>
-      <c r="DF2" s="24"/>
-      <c r="DG2" s="24"/>
-      <c r="DH2" s="24"/>
-      <c r="DI2" s="24"/>
-      <c r="DJ2" s="24"/>
-      <c r="DK2" s="24"/>
-      <c r="DL2" s="24"/>
-      <c r="DM2" s="24"/>
-      <c r="DN2" s="24"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="23"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="23"/>
+      <c r="AV2" s="23"/>
+      <c r="AW2" s="23"/>
+      <c r="AX2" s="23"/>
+      <c r="AY2" s="23"/>
+      <c r="AZ2" s="23"/>
+      <c r="BA2" s="23"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="23"/>
+      <c r="BD2" s="23"/>
+      <c r="BE2" s="23"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="23"/>
+      <c r="BH2" s="23"/>
+      <c r="BI2" s="23"/>
+      <c r="BJ2" s="23"/>
+      <c r="BK2" s="23"/>
+      <c r="BL2" s="23"/>
+      <c r="BM2" s="23"/>
+      <c r="BN2" s="23"/>
+      <c r="BO2" s="23"/>
+      <c r="BP2" s="23"/>
+      <c r="BQ2" s="23"/>
+      <c r="BR2" s="23"/>
+      <c r="BS2" s="23"/>
+      <c r="BT2" s="23"/>
+      <c r="BU2" s="23"/>
+      <c r="BV2" s="23"/>
+      <c r="BW2" s="23"/>
+      <c r="BX2" s="23"/>
+      <c r="BY2" s="23"/>
+      <c r="BZ2" s="23"/>
+      <c r="CA2" s="23"/>
+      <c r="CB2" s="23"/>
+      <c r="CC2" s="23"/>
+      <c r="CD2" s="23"/>
+      <c r="CE2" s="23"/>
+      <c r="CF2" s="23"/>
+      <c r="CG2" s="23"/>
+      <c r="CH2" s="23"/>
+      <c r="CI2" s="23"/>
+      <c r="CJ2" s="23"/>
+      <c r="CK2" s="23"/>
+      <c r="CL2" s="23"/>
+      <c r="CM2" s="23"/>
+      <c r="CN2" s="23"/>
+      <c r="CO2" s="23"/>
+      <c r="CP2" s="23"/>
+      <c r="CQ2" s="23"/>
+      <c r="CR2" s="23"/>
+      <c r="CS2" s="23"/>
+      <c r="CT2" s="23"/>
+      <c r="CU2" s="23"/>
+      <c r="CV2" s="23"/>
+      <c r="CW2" s="23"/>
+      <c r="CX2" s="23"/>
+      <c r="CY2" s="23"/>
+      <c r="CZ2" s="23"/>
+      <c r="DA2" s="23"/>
+      <c r="DB2" s="23"/>
+      <c r="DC2" s="23"/>
+      <c r="DD2" s="23"/>
+      <c r="DE2" s="23"/>
+      <c r="DF2" s="23"/>
+      <c r="DG2" s="23"/>
+      <c r="DH2" s="23"/>
+      <c r="DI2" s="23"/>
+      <c r="DJ2" s="23"/>
+      <c r="DK2" s="23"/>
+      <c r="DL2" s="23"/>
+      <c r="DM2" s="23"/>
+      <c r="DN2" s="23"/>
     </row>
     <row r="3" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
@@ -1493,119 +1628,119 @@
       <c r="C3"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="26"/>
-      <c r="BT3" s="26"/>
-      <c r="BU3" s="26"/>
-      <c r="BV3" s="26"/>
-      <c r="BW3" s="26"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="26"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="26"/>
-      <c r="CB3" s="26"/>
-      <c r="CC3" s="26"/>
-      <c r="CD3" s="26"/>
-      <c r="CE3" s="26"/>
-      <c r="CF3" s="26"/>
-      <c r="CG3" s="26"/>
-      <c r="CH3" s="26"/>
-      <c r="CI3" s="26"/>
-      <c r="CJ3" s="26"/>
-      <c r="CK3" s="26"/>
-      <c r="CL3" s="26"/>
-      <c r="CM3" s="26"/>
-      <c r="CN3" s="26"/>
-      <c r="CO3" s="26"/>
-      <c r="CP3" s="26"/>
-      <c r="CQ3" s="26"/>
-      <c r="CR3" s="26"/>
-      <c r="CS3" s="26"/>
-      <c r="CT3" s="26"/>
-      <c r="CU3" s="26"/>
-      <c r="CV3" s="26"/>
-      <c r="CW3" s="26"/>
-      <c r="CX3" s="26"/>
-      <c r="CY3" s="26"/>
-      <c r="CZ3" s="26"/>
-      <c r="DA3" s="26"/>
-      <c r="DB3" s="26"/>
-      <c r="DC3" s="26"/>
-      <c r="DD3" s="26"/>
-      <c r="DE3" s="26"/>
-      <c r="DF3" s="26"/>
-      <c r="DG3" s="26"/>
-      <c r="DH3" s="26"/>
-      <c r="DI3" s="26"/>
-      <c r="DJ3" s="26"/>
-      <c r="DK3" s="26"/>
-      <c r="DL3" s="26"/>
-      <c r="DM3" s="26"/>
-      <c r="DN3" s="26"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="25"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="25"/>
+      <c r="BL3" s="25"/>
+      <c r="BM3" s="25"/>
+      <c r="BN3" s="25"/>
+      <c r="BO3" s="25"/>
+      <c r="BP3" s="25"/>
+      <c r="BQ3" s="25"/>
+      <c r="BR3" s="25"/>
+      <c r="BS3" s="25"/>
+      <c r="BT3" s="25"/>
+      <c r="BU3" s="25"/>
+      <c r="BV3" s="25"/>
+      <c r="BW3" s="25"/>
+      <c r="BX3" s="25"/>
+      <c r="BY3" s="25"/>
+      <c r="BZ3" s="25"/>
+      <c r="CA3" s="25"/>
+      <c r="CB3" s="25"/>
+      <c r="CC3" s="25"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="25"/>
+      <c r="CF3" s="25"/>
+      <c r="CG3" s="25"/>
+      <c r="CH3" s="25"/>
+      <c r="CI3" s="25"/>
+      <c r="CJ3" s="25"/>
+      <c r="CK3" s="25"/>
+      <c r="CL3" s="25"/>
+      <c r="CM3" s="25"/>
+      <c r="CN3" s="25"/>
+      <c r="CO3" s="25"/>
+      <c r="CP3" s="25"/>
+      <c r="CQ3" s="25"/>
+      <c r="CR3" s="25"/>
+      <c r="CS3" s="25"/>
+      <c r="CT3" s="25"/>
+      <c r="CU3" s="25"/>
+      <c r="CV3" s="25"/>
+      <c r="CW3" s="25"/>
+      <c r="CX3" s="25"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="25"/>
+      <c r="DA3" s="25"/>
+      <c r="DB3" s="25"/>
+      <c r="DC3" s="25"/>
+      <c r="DD3" s="25"/>
+      <c r="DE3" s="25"/>
+      <c r="DF3" s="25"/>
+      <c r="DG3" s="25"/>
+      <c r="DH3" s="25"/>
+      <c r="DI3" s="25"/>
+      <c r="DJ3" s="25"/>
+      <c r="DK3" s="25"/>
+      <c r="DL3" s="25"/>
+      <c r="DM3" s="25"/>
+      <c r="DN3" s="25"/>
     </row>
     <row r="4" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1616,7 +1751,7 @@
       <c r="E4"/>
     </row>
     <row r="5" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="31" t="s">
         <v>15</v>
       </c>
       <c r="C5"/>
@@ -1655,7 +1790,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1670,7 +1805,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
@@ -1678,7 +1813,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
@@ -1686,7 +1821,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
@@ -1694,7 +1829,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="31" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1707,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -1720,24 +1855,25 @@
     <col min="9" max="9" width="18.33203125" customWidth="1"/>
     <col min="10" max="10" width="20.5" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>30</v>
+    <row r="1" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="17" t="e">
+      <c r="B2" s="16" t="e">
         <f>VLOOKUP(A2,'codage tribunal'!A:B,2,FALSE)</f>
         <v>#N/A</v>
       </c>
@@ -1745,13 +1881,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
+      <c r="C3" s="9"/>
+      <c r="E3" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9"/>
-    </row>
-    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -1764,70 +1917,126 @@
       <c r="G4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="K4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="L4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
-      <c r="C5" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="M4" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" s="14"/>
+      <c r="C5" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="22" t="e">
+      <c r="D5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="21" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="F5" s="20" t="e">
+      <c r="F5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="20" t="e">
+      <c r="G5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="20" t="e">
+      <c r="H5" s="19" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,
+IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+),'ETPT Format DDG'!$I:$I,"C",
+'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$G:$G,"Magistrat")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I5" s="46" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,
+IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+),
+'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$G:$G,"Magistrat")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="I5" s="20" t="e">
+      <c r="K5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="20" t="e">
+      <c r="L5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="K5" s="21" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="M5" s="20" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$2,'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L6" t="s">
+      <c r="N5" s="46" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,
+IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+),
+'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$G:$G,"Greffe")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O5" s="20" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,
+IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+),'ETPT Format DDG'!$I:$I,"C",
+'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$G:$G,"Autour du magistrat")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P6" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:K150">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <mergeCells count="2">
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="J3:N3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:O150">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ISBLANK($C5)=FALSE,ISBLANK($D5)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1858,124 +2067,124 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" style="24" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="24" customWidth="1"/>
-    <col min="3" max="9" width="10.83203125" style="24"/>
-    <col min="10" max="10" width="71.1640625" style="24" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="24"/>
+    <col min="1" max="1" width="8.1640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="23" customWidth="1"/>
+    <col min="3" max="9" width="10.83203125" style="23"/>
+    <col min="10" max="10" width="71.1640625" style="23" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:10" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-    </row>
-    <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31" t="s">
+      <c r="C3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31" t="s">
+      <c r="C4" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31" t="s">
+      <c r="C5" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-    </row>
-    <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="37" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-    </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
@@ -2001,7 +2210,7 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
@@ -2014,7 +2223,7 @@
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -2026,98 +2235,99 @@
       <c r="J11" s="38"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="37" t="s">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+    </row>
+    <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-    </row>
-    <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="37" t="s">
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="37" t="s">
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-    </row>
-    <row r="16" spans="1:10" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="37" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+    </row>
+    <row r="18" spans="1:10" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-    </row>
-    <row r="18" spans="1:10" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
@@ -2134,7 +2344,6 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C13:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F89413-D477-E346-84BF-35A1BA14109B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24816E1E-27A1-9147-92A5-D82FD9079116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="2" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/Desktop/Betagouv/a-just/front/src/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24816E1E-27A1-9147-92A5-D82FD9079116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C34238-0F47-A349-9585-09C806FD1DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24580" windowHeight="14560" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22480" windowHeight="17620" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
@@ -592,11 +592,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="General;General;\-"/>
-    <numFmt numFmtId="167" formatCode="0.###;0.###;\-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="General;General;\-"/>
+    <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -880,8 +880,8 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -918,10 +918,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -933,19 +933,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -957,11 +951,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -974,6 +968,30 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -995,53 +1013,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{C877C5E8-FCBF-114F-9ECB-F75EF7C9C0EB}"/>
+    <cellStyle name="Milliers" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6FC886D6-2077-B34D-B1DF-739B068A66D1}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79998168889431442"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1169,7 +1154,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1495,131 +1480,131 @@
       </c>
     </row>
     <row r="2" spans="1:118" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="23"/>
-      <c r="AD2" s="23"/>
-      <c r="AE2" s="23"/>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="23"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="23"/>
-      <c r="AS2" s="23"/>
-      <c r="AT2" s="23"/>
-      <c r="AU2" s="23"/>
-      <c r="AV2" s="23"/>
-      <c r="AW2" s="23"/>
-      <c r="AX2" s="23"/>
-      <c r="AY2" s="23"/>
-      <c r="AZ2" s="23"/>
-      <c r="BA2" s="23"/>
-      <c r="BB2" s="23"/>
-      <c r="BC2" s="23"/>
-      <c r="BD2" s="23"/>
-      <c r="BE2" s="23"/>
-      <c r="BF2" s="23"/>
-      <c r="BG2" s="23"/>
-      <c r="BH2" s="23"/>
-      <c r="BI2" s="23"/>
-      <c r="BJ2" s="23"/>
-      <c r="BK2" s="23"/>
-      <c r="BL2" s="23"/>
-      <c r="BM2" s="23"/>
-      <c r="BN2" s="23"/>
-      <c r="BO2" s="23"/>
-      <c r="BP2" s="23"/>
-      <c r="BQ2" s="23"/>
-      <c r="BR2" s="23"/>
-      <c r="BS2" s="23"/>
-      <c r="BT2" s="23"/>
-      <c r="BU2" s="23"/>
-      <c r="BV2" s="23"/>
-      <c r="BW2" s="23"/>
-      <c r="BX2" s="23"/>
-      <c r="BY2" s="23"/>
-      <c r="BZ2" s="23"/>
-      <c r="CA2" s="23"/>
-      <c r="CB2" s="23"/>
-      <c r="CC2" s="23"/>
-      <c r="CD2" s="23"/>
-      <c r="CE2" s="23"/>
-      <c r="CF2" s="23"/>
-      <c r="CG2" s="23"/>
-      <c r="CH2" s="23"/>
-      <c r="CI2" s="23"/>
-      <c r="CJ2" s="23"/>
-      <c r="CK2" s="23"/>
-      <c r="CL2" s="23"/>
-      <c r="CM2" s="23"/>
-      <c r="CN2" s="23"/>
-      <c r="CO2" s="23"/>
-      <c r="CP2" s="23"/>
-      <c r="CQ2" s="23"/>
-      <c r="CR2" s="23"/>
-      <c r="CS2" s="23"/>
-      <c r="CT2" s="23"/>
-      <c r="CU2" s="23"/>
-      <c r="CV2" s="23"/>
-      <c r="CW2" s="23"/>
-      <c r="CX2" s="23"/>
-      <c r="CY2" s="23"/>
-      <c r="CZ2" s="23"/>
-      <c r="DA2" s="23"/>
-      <c r="DB2" s="23"/>
-      <c r="DC2" s="23"/>
-      <c r="DD2" s="23"/>
-      <c r="DE2" s="23"/>
-      <c r="DF2" s="23"/>
-      <c r="DG2" s="23"/>
-      <c r="DH2" s="23"/>
-      <c r="DI2" s="23"/>
-      <c r="DJ2" s="23"/>
-      <c r="DK2" s="23"/>
-      <c r="DL2" s="23"/>
-      <c r="DM2" s="23"/>
-      <c r="DN2" s="23"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="21"/>
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="21"/>
+      <c r="AT2" s="21"/>
+      <c r="AU2" s="21"/>
+      <c r="AV2" s="21"/>
+      <c r="AW2" s="21"/>
+      <c r="AX2" s="21"/>
+      <c r="AY2" s="21"/>
+      <c r="AZ2" s="21"/>
+      <c r="BA2" s="21"/>
+      <c r="BB2" s="21"/>
+      <c r="BC2" s="21"/>
+      <c r="BD2" s="21"/>
+      <c r="BE2" s="21"/>
+      <c r="BF2" s="21"/>
+      <c r="BG2" s="21"/>
+      <c r="BH2" s="21"/>
+      <c r="BI2" s="21"/>
+      <c r="BJ2" s="21"/>
+      <c r="BK2" s="21"/>
+      <c r="BL2" s="21"/>
+      <c r="BM2" s="21"/>
+      <c r="BN2" s="21"/>
+      <c r="BO2" s="21"/>
+      <c r="BP2" s="21"/>
+      <c r="BQ2" s="21"/>
+      <c r="BR2" s="21"/>
+      <c r="BS2" s="21"/>
+      <c r="BT2" s="21"/>
+      <c r="BU2" s="21"/>
+      <c r="BV2" s="21"/>
+      <c r="BW2" s="21"/>
+      <c r="BX2" s="21"/>
+      <c r="BY2" s="21"/>
+      <c r="BZ2" s="21"/>
+      <c r="CA2" s="21"/>
+      <c r="CB2" s="21"/>
+      <c r="CC2" s="21"/>
+      <c r="CD2" s="21"/>
+      <c r="CE2" s="21"/>
+      <c r="CF2" s="21"/>
+      <c r="CG2" s="21"/>
+      <c r="CH2" s="21"/>
+      <c r="CI2" s="21"/>
+      <c r="CJ2" s="21"/>
+      <c r="CK2" s="21"/>
+      <c r="CL2" s="21"/>
+      <c r="CM2" s="21"/>
+      <c r="CN2" s="21"/>
+      <c r="CO2" s="21"/>
+      <c r="CP2" s="21"/>
+      <c r="CQ2" s="21"/>
+      <c r="CR2" s="21"/>
+      <c r="CS2" s="21"/>
+      <c r="CT2" s="21"/>
+      <c r="CU2" s="21"/>
+      <c r="CV2" s="21"/>
+      <c r="CW2" s="21"/>
+      <c r="CX2" s="21"/>
+      <c r="CY2" s="21"/>
+      <c r="CZ2" s="21"/>
+      <c r="DA2" s="21"/>
+      <c r="DB2" s="21"/>
+      <c r="DC2" s="21"/>
+      <c r="DD2" s="21"/>
+      <c r="DE2" s="21"/>
+      <c r="DF2" s="21"/>
+      <c r="DG2" s="21"/>
+      <c r="DH2" s="21"/>
+      <c r="DI2" s="21"/>
+      <c r="DJ2" s="21"/>
+      <c r="DK2" s="21"/>
+      <c r="DL2" s="21"/>
+      <c r="DM2" s="21"/>
+      <c r="DN2" s="21"/>
     </row>
     <row r="3" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
@@ -1628,119 +1613,119 @@
       <c r="C3"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="25"/>
-      <c r="BB3" s="25"/>
-      <c r="BC3" s="25"/>
-      <c r="BD3" s="25"/>
-      <c r="BE3" s="25"/>
-      <c r="BF3" s="25"/>
-      <c r="BG3" s="25"/>
-      <c r="BH3" s="25"/>
-      <c r="BI3" s="25"/>
-      <c r="BJ3" s="25"/>
-      <c r="BK3" s="25"/>
-      <c r="BL3" s="25"/>
-      <c r="BM3" s="25"/>
-      <c r="BN3" s="25"/>
-      <c r="BO3" s="25"/>
-      <c r="BP3" s="25"/>
-      <c r="BQ3" s="25"/>
-      <c r="BR3" s="25"/>
-      <c r="BS3" s="25"/>
-      <c r="BT3" s="25"/>
-      <c r="BU3" s="25"/>
-      <c r="BV3" s="25"/>
-      <c r="BW3" s="25"/>
-      <c r="BX3" s="25"/>
-      <c r="BY3" s="25"/>
-      <c r="BZ3" s="25"/>
-      <c r="CA3" s="25"/>
-      <c r="CB3" s="25"/>
-      <c r="CC3" s="25"/>
-      <c r="CD3" s="25"/>
-      <c r="CE3" s="25"/>
-      <c r="CF3" s="25"/>
-      <c r="CG3" s="25"/>
-      <c r="CH3" s="25"/>
-      <c r="CI3" s="25"/>
-      <c r="CJ3" s="25"/>
-      <c r="CK3" s="25"/>
-      <c r="CL3" s="25"/>
-      <c r="CM3" s="25"/>
-      <c r="CN3" s="25"/>
-      <c r="CO3" s="25"/>
-      <c r="CP3" s="25"/>
-      <c r="CQ3" s="25"/>
-      <c r="CR3" s="25"/>
-      <c r="CS3" s="25"/>
-      <c r="CT3" s="25"/>
-      <c r="CU3" s="25"/>
-      <c r="CV3" s="25"/>
-      <c r="CW3" s="25"/>
-      <c r="CX3" s="25"/>
-      <c r="CY3" s="25"/>
-      <c r="CZ3" s="25"/>
-      <c r="DA3" s="25"/>
-      <c r="DB3" s="25"/>
-      <c r="DC3" s="25"/>
-      <c r="DD3" s="25"/>
-      <c r="DE3" s="25"/>
-      <c r="DF3" s="25"/>
-      <c r="DG3" s="25"/>
-      <c r="DH3" s="25"/>
-      <c r="DI3" s="25"/>
-      <c r="DJ3" s="25"/>
-      <c r="DK3" s="25"/>
-      <c r="DL3" s="25"/>
-      <c r="DM3" s="25"/>
-      <c r="DN3" s="25"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
+      <c r="BM3" s="23"/>
+      <c r="BN3" s="23"/>
+      <c r="BO3" s="23"/>
+      <c r="BP3" s="23"/>
+      <c r="BQ3" s="23"/>
+      <c r="BR3" s="23"/>
+      <c r="BS3" s="23"/>
+      <c r="BT3" s="23"/>
+      <c r="BU3" s="23"/>
+      <c r="BV3" s="23"/>
+      <c r="BW3" s="23"/>
+      <c r="BX3" s="23"/>
+      <c r="BY3" s="23"/>
+      <c r="BZ3" s="23"/>
+      <c r="CA3" s="23"/>
+      <c r="CB3" s="23"/>
+      <c r="CC3" s="23"/>
+      <c r="CD3" s="23"/>
+      <c r="CE3" s="23"/>
+      <c r="CF3" s="23"/>
+      <c r="CG3" s="23"/>
+      <c r="CH3" s="23"/>
+      <c r="CI3" s="23"/>
+      <c r="CJ3" s="23"/>
+      <c r="CK3" s="23"/>
+      <c r="CL3" s="23"/>
+      <c r="CM3" s="23"/>
+      <c r="CN3" s="23"/>
+      <c r="CO3" s="23"/>
+      <c r="CP3" s="23"/>
+      <c r="CQ3" s="23"/>
+      <c r="CR3" s="23"/>
+      <c r="CS3" s="23"/>
+      <c r="CT3" s="23"/>
+      <c r="CU3" s="23"/>
+      <c r="CV3" s="23"/>
+      <c r="CW3" s="23"/>
+      <c r="CX3" s="23"/>
+      <c r="CY3" s="23"/>
+      <c r="CZ3" s="23"/>
+      <c r="DA3" s="23"/>
+      <c r="DB3" s="23"/>
+      <c r="DC3" s="23"/>
+      <c r="DD3" s="23"/>
+      <c r="DE3" s="23"/>
+      <c r="DF3" s="23"/>
+      <c r="DG3" s="23"/>
+      <c r="DH3" s="23"/>
+      <c r="DI3" s="23"/>
+      <c r="DJ3" s="23"/>
+      <c r="DK3" s="23"/>
+      <c r="DL3" s="23"/>
+      <c r="DM3" s="23"/>
+      <c r="DN3" s="23"/>
     </row>
     <row r="4" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1751,7 +1736,7 @@
       <c r="E4"/>
     </row>
     <row r="5" spans="1:118" x14ac:dyDescent="0.2">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C5"/>
@@ -1805,7 +1790,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
@@ -1813,7 +1798,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
@@ -1821,7 +1806,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
@@ -1829,7 +1814,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1848,18 +1833,19 @@
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="21.33203125" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" customWidth="1"/>
     <col min="7" max="8" width="16.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" customWidth="1"/>
     <col min="10" max="10" width="20.5" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" customWidth="1"/>
+    <col min="12" max="13" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="15" t="s">
@@ -1870,7 +1856,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="16" t="e">
@@ -1883,28 +1869,28 @@
     </row>
     <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="39" t="s">
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="42" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="30" t="s">
         <v>58</v>
       </c>
       <c r="P3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -1917,10 +1903,10 @@
       <c r="G4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="32" t="s">
         <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
@@ -1932,40 +1918,40 @@
       <c r="L4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="43" t="s">
+      <c r="M4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="N4" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="33" t="s">
         <v>59</v>
       </c>
       <c r="P4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="21" t="e">
+      <c r="E5" s="19" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="F5" s="19" t="e">
+      <c r="F5" s="17" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="19" t="e">
+      <c r="G5" s="17" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="19" t="e">
+      <c r="H5" s="17" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
@@ -1975,7 +1961,7 @@
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="I5" s="46" t="e">
+      <c r="I5" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
@@ -1985,23 +1971,23 @@
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="19" t="e">
+      <c r="J5" s="17" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="K5" s="19" t="e">
+      <c r="K5" s="17" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" s="19" t="e">
+      <c r="L5" s="17" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
         <v>#N/A</v>
       </c>
-      <c r="M5" s="20" t="e">
+      <c r="M5" s="18" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$2,'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="N5" s="46" t="e">
+      <c r="N5" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
@@ -2011,7 +1997,7 @@
 'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="O5" s="20" t="e">
+      <c r="O5" s="18" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
@@ -2036,7 +2022,7 @@
     <mergeCell ref="J3:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:O150">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ISBLANK($C5)=FALSE,ISBLANK($D5)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2067,276 +2053,266 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="23" customWidth="1"/>
-    <col min="3" max="9" width="10.83203125" style="23"/>
-    <col min="10" max="10" width="71.1640625" style="23" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="23"/>
+    <col min="1" max="1" width="8.1640625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="21" customWidth="1"/>
+    <col min="3" max="9" width="10.83203125" style="21"/>
+    <col min="10" max="10" width="71.1640625" style="21" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29"/>
-      <c r="B5" s="30" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
     </row>
     <row r="16" spans="1:10" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-    </row>
-    <row r="18" spans="1:10" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+    </row>
+    <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C5:J5"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="B16:J16"/>
@@ -2344,6 +2320,16 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A18:J18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C34238-0F47-A349-9585-09C806FD1DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B14F26-027E-9F4C-A957-F1AF0E6DE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="22480" windowHeight="17620" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -983,6 +983,12 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -995,29 +1001,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1869,20 +1869,20 @@
     </row>
     <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="35" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="37"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="39"/>
       <c r="O3" s="30" t="s">
         <v>58</v>
       </c>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="36" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="19" t="e">
@@ -2078,224 +2078,224 @@
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-    </row>
-    <row r="16" spans="1:10" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+    </row>
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42" t="s">
@@ -2313,6 +2313,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="B16:J16"/>
@@ -2320,16 +2326,10 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C5:J5"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
-    <mergeCell ref="A18:J18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B14F26-027E-9F4C-A957-F1AF0E6DE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5149D40B-076D-2842-AB9D-6E40C934E9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22480" windowHeight="17620" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="1" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
     <sheet name="ETPT Format DDG" sheetId="9" r:id="rId2"/>
-    <sheet name="Agrégats DDG" sheetId="10" r:id="rId3"/>
-    <sheet name="codage tribunal" sheetId="12" state="hidden" r:id="rId4"/>
-    <sheet name="codage fonction" sheetId="13" state="hidden" r:id="rId5"/>
-    <sheet name="NOTICE et COMMENTAIRES" sheetId="4" r:id="rId6"/>
+    <sheet name="codage condition" sheetId="14" r:id="rId3"/>
+    <sheet name="Agrégats DDG" sheetId="10" r:id="rId4"/>
+    <sheet name="codage tribunal" sheetId="12" r:id="rId5"/>
+    <sheet name="codage fonction" sheetId="13" state="hidden" r:id="rId6"/>
+    <sheet name="NOTICE et COMMENTAIRES" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
+    <definedName name="J">'codage condition'!$B$2:$B$4</definedName>
+    <definedName name="JA">'codage condition'!$A$2:$A$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -998,19 +1001,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1826,6 +1829,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF251994-7598-1648-8DDF-3EC3EBC896DA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
   <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2030,7 +2045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AF7A98-8726-2B45-9E0D-08F39416C73F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2039,7 +2054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D177071-EB91-3A4C-8FA0-97E070BB3BA4}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2048,7 +2063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C706A55-5422-5B42-B9B4-A00444FB459D}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2061,164 +2076,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
@@ -2240,79 +2255,80 @@
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
     </row>
     <row r="16" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
@@ -2329,7 +2345,6 @@
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B14F26-027E-9F4C-A957-F1AF0E6DE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E1AF8-A48F-1F46-ABB5-81C69BA0C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="22480" windowHeight="17620" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -301,6 +301,267 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Précisions nécessaires aux DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tribunal d'affectation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La colonne "Code fonction"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> est remplie automatiquement mais </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> car elle permet de distinguer</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> les placés de substitution des placés additionnels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Par défaut, tous les placés ont été codés en "M-PLAC-ADD" (Magistrat placé additionnel) ou "F-PLAC-ADD" (Fonctionnaire placé additionnel). Si des Placés étaient des effectifs de substitution, les recoder "M-PLAC-SUB" pour les magistrats ou "F-PLAC-SUB" pour les fonctionnaires, à l'aide du menu déroulant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les éventuels </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ont été répartis entre les CET de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> moins d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> plus d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dans l'onglet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Agrégats DDG"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
+    </r>
+  </si>
+  <si>
+    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
+  </si>
+  <si>
+    <t>SIEGE</t>
+  </si>
+  <si>
+    <t>GREFFE</t>
+  </si>
+  <si>
+    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
+  </si>
+  <si>
+    <t>Contractuels et vacataires</t>
+  </si>
+  <si>
+    <t>TOTAL SIEGE</t>
+  </si>
+  <si>
+    <t>TOTAL GREFFE</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Un </t>
     </r>
     <r>
@@ -324,267 +585,16 @@
       </rPr>
       <t>appelle une vérification. Soit l'agent était effectivement absent pendant toute la période (en CLM par ex.), soit il n'a pas été ventilé.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Précisions nécessaires aux DDG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tribunal d'affectation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>La colonne "Code fonction"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> est remplie automatiquement mais </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> car elle permet de distinguer</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> les placés de substitution des placés additionnels</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Par défaut, tous les placés ont été codés en "M-PLAC-ADD" (Magistrat placé additionnel) ou "F-PLAC-ADD" (Fonctionnaire placé additionnel). Si des Placés étaient des effectifs de substitution, les recoder "M-PLAC-SUB" pour les magistrats ou "F-PLAC-SUB" pour les fonctionnaires, à l'aide du menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Les éventuels </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CET</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ont été répartis entre les CET de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> moins d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> plus d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dans l'onglet </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Agrégats DDG"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, il convient de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
-    </r>
-  </si>
-  <si>
-    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
-  </si>
-  <si>
-    <t>SIEGE</t>
-  </si>
-  <si>
-    <t>GREFFE</t>
-  </si>
-  <si>
-    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
-  </si>
-  <si>
-    <t>Contractuels et vacataires</t>
-  </si>
-  <si>
-    <t>TOTAL SIEGE</t>
-  </si>
-  <si>
-    <t>TOTAL GREFFE</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Il est nécessaire de ventiler durant les temps d'indisponibilité.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -883,7 +893,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -998,26 +1008,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1870,21 +1883,21 @@
     <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
       <c r="E3" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="39"/>
       <c r="J3" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K3" s="38"/>
       <c r="L3" s="38"/>
       <c r="M3" s="38"/>
       <c r="N3" s="39"/>
       <c r="O3" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P3" t="s">
         <v>0</v>
@@ -1904,10 +1917,10 @@
         <v>25</v>
       </c>
       <c r="H4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>59</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>26</v>
@@ -1919,13 +1932,13 @@
         <v>28</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
         <v>30</v>
@@ -2061,171 +2074,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-    </row>
-    <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+    </row>
+    <row r="11" spans="1:10" s="10" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46"/>
@@ -2240,79 +2253,80 @@
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="C13" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
+      <c r="C14" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
+      <c r="C15" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
     </row>
     <row r="16" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+    </row>
+    <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
@@ -2329,7 +2343,6 @@
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,24 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5149D40B-076D-2842-AB9D-6E40C934E9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D7AC2-D774-DD4B-B142-54A1DADF6667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="1" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
     <sheet name="ETPT Format DDG" sheetId="9" r:id="rId2"/>
-    <sheet name="codage condition" sheetId="14" r:id="rId3"/>
-    <sheet name="Agrégats DDG" sheetId="10" r:id="rId4"/>
-    <sheet name="codage tribunal" sheetId="12" r:id="rId5"/>
-    <sheet name="codage fonction" sheetId="13" state="hidden" r:id="rId6"/>
-    <sheet name="NOTICE et COMMENTAIRES" sheetId="4" r:id="rId7"/>
+    <sheet name="Agrégats DDG" sheetId="10" r:id="rId3"/>
+    <sheet name="codage tribunal" sheetId="12" state="hidden" r:id="rId4"/>
+    <sheet name="codage fonction" sheetId="13" state="hidden" r:id="rId5"/>
+    <sheet name="NOTICE et COMMENTAIRES" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
-    <definedName name="J">'codage condition'!$B$2:$B$4</definedName>
-    <definedName name="JA">'codage condition'!$A$2:$A$4</definedName>
+    <definedName name="J">#REF!</definedName>
+    <definedName name="JA">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -155,12 +154,6 @@
     <t>Selectionner une juridiction</t>
   </si>
   <si>
-    <t xml:space="preserve">         Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         Extracteur de données d'effectifs</t>
-  </si>
-  <si>
     <t xml:space="preserve">        EXPLICATIONS ET CONTROLES A EFFECTUER</t>
   </si>
   <si>
@@ -588,6 +581,15 @@
   </si>
   <si>
     <t>TOTAL GREFFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Agrégats DDG</t>
   </si>
 </sst>
 </file>
@@ -601,7 +603,7 @@
     <numFmt numFmtId="167" formatCode="General;General;\-"/>
     <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -686,6 +688,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -886,7 +903,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1001,6 +1018,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1008,9 +1028,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1021,6 +1038,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1063,15 +1086,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>46180</xdr:colOff>
+      <xdr:colOff>103906</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>23090</xdr:rowOff>
+      <xdr:rowOff>57725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>542634</xdr:colOff>
+      <xdr:colOff>923635</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>476535</xdr:rowOff>
+      <xdr:rowOff>806439</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1094,8 +1117,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46180" y="23090"/>
-          <a:ext cx="496454" cy="453445"/>
+          <a:off x="103906" y="57725"/>
+          <a:ext cx="819729" cy="748714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1112,22 +1135,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>46180</xdr:colOff>
+      <xdr:colOff>103905</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>23090</xdr:rowOff>
+      <xdr:rowOff>57725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>542634</xdr:colOff>
+      <xdr:colOff>923634</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>476535</xdr:rowOff>
+      <xdr:rowOff>806439</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CD8D5B3-C3E9-E94E-BD8C-2EF269EA8931}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D7A5D8C-BE33-ED45-A77A-8F455267161F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1143,8 +1166,106 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46180" y="23090"/>
-          <a:ext cx="496454" cy="453445"/>
+          <a:off x="103905" y="57725"/>
+          <a:ext cx="819729" cy="748714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>98777</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>84665</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1114778</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1012648</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD1D57F9-87BD-BD45-83E9-42F2487B9728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="98777" y="84665"/>
+          <a:ext cx="1016001" cy="927983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>103910</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69271</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>300184</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>817985</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC1CFF2-AC52-DD4F-9E83-87135FE34159}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="103910" y="69271"/>
+          <a:ext cx="819729" cy="748714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1456,7 +1577,7 @@
   <dimension ref="A1:DN8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
@@ -1466,9 +1587,9 @@
     <col min="8" max="8" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:118" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1776,9 +1897,9 @@
     <col min="2" max="2" width="71.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1829,20 +1950,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF251994-7598-1648-8DDF-3EC3EBC896DA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="10.83203125" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -1859,193 +1968,219 @@
     <col min="15" max="15" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+    </row>
+    <row r="2" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B2" s="15" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="16" t="e">
-        <f>VLOOKUP(A2,'codage tribunal'!A:B,2,FALSE)</f>
-        <v>#N/A</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
-      <c r="C3" s="9"/>
-      <c r="E3" s="37" t="s">
+    <row r="3" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="16" t="e">
+        <f>VLOOKUP(A3,'codage tribunal'!A:B,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
+      <c r="C4" s="9"/>
+      <c r="E4" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="37" t="s">
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="30" t="s">
+      <c r="I5" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="P3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="31" t="s">
+      <c r="J5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="O5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="C5" s="35" t="s">
+    <row r="6" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14"/>
+      <c r="C6" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D6" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="19" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="E6" s="19" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$3)</f>
         <v>#N/A</v>
       </c>
-      <c r="F5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="F6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*ADDITIONNEL*")</f>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="G6" s="17" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*SUBSTITUTION*")</f>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="17" t="e">
+      <c r="H6" s="17" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),'ETPT Format DDG'!$I:$I,"C",
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="I5" s="34" t="e">
+      <c r="I6" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="J6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$3)</f>
         <v>#N/A</v>
       </c>
-      <c r="K5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="K6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*ADDITIONNEL*")</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="L6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*SUBSTITUTION*")</f>
         <v>#N/A</v>
       </c>
-      <c r="M5" s="18" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$2,'ETPT Format DDG'!$G:$G,"Greffe")</f>
+      <c r="M6" s="18" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="N5" s="34" t="e">
+      <c r="N6" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="O5" s="18" t="e">
+      <c r="O6" s="18" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),'ETPT Format DDG'!$I:$I,"C",
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Autour du magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="P6" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:O150">
+  <conditionalFormatting sqref="C6:O151">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(ISBLANK($C5)=FALSE,ISBLANK($D5)=TRUE)</formula>
+      <formula>AND(ISBLANK($C6)=FALSE,ISBLANK($D6)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AF7A98-8726-2B45-9E0D-08F39416C73F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2054,7 +2189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D177071-EB91-3A4C-8FA0-97E070BB3BA4}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2063,7 +2198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C706A55-5422-5B42-B9B4-A00444FB459D}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2075,43 +2210,43 @@
     <col min="11" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+    <row r="1" spans="1:10" s="26" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="B2" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
@@ -2124,10 +2259,10 @@
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="43"/>
       <c r="E4" s="43"/>
@@ -2140,10 +2275,10 @@
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -2158,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="43"/>
@@ -2171,21 +2306,21 @@
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
+      <c r="B7" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
@@ -2211,7 +2346,7 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
@@ -2224,7 +2359,7 @@
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
@@ -2240,7 +2375,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46"/>
@@ -2256,7 +2391,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="43"/>
       <c r="E13" s="43"/>
@@ -2271,7 +2406,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="43"/>
@@ -2286,7 +2421,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
@@ -2301,7 +2436,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -2313,21 +2448,22 @@
       <c r="J16" s="43"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
+      <c r="A18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
@@ -2344,9 +2480,9 @@
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B12:J12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D7AC2-D774-DD4B-B142-54A1DADF6667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA203BC9-F64E-6A46-951B-47BBC64CF6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -297,6 +297,211 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Précisions nécessaires aux DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tribunal d'affectation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les éventuels </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ont été répartis entre les CET de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> moins d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> plus d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dans l'onglet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Agrégats DDG"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
+    </r>
+  </si>
+  <si>
+    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
+  </si>
+  <si>
+    <t>SIEGE</t>
+  </si>
+  <si>
+    <t>GREFFE</t>
+  </si>
+  <si>
+    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
+  </si>
+  <si>
+    <t>Contractuels et vacataires</t>
+  </si>
+  <si>
+    <t>TOTAL SIEGE</t>
+  </si>
+  <si>
+    <t>TOTAL GREFFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Agrégats DDG</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Un </t>
     </r>
     <r>
@@ -320,114 +525,64 @@
       </rPr>
       <t>appelle une vérification. Soit l'agent était effectivement absent pendant toute la période (en CLM par ex.), soit il n'a pas été ventilé.</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Il est nécessaire de ventiler durant les temps d'indisponibilité.</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Précisions nécessaires aux DDG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La colonne "Fonction"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> est remplie automatiquement mais </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tribunal d'affectation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> car elle permet de distinguer</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>La colonne "Code fonction"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> est remplie automatiquement mais </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> car elle permet de distinguer</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -443,153 +598,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Par défaut, tous les placés ont été codés en "M-PLAC-ADD" (Magistrat placé additionnel) ou "F-PLAC-ADD" (Fonctionnaire placé additionnel). Si des Placés étaient des effectifs de substitution, les recoder "M-PLAC-SUB" pour les magistrats ou "F-PLAC-SUB" pour les fonctionnaires, à l'aide du menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Les éventuels </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CET</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ont été répartis entre les CET de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> moins d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> plus d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dans l'onglet </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Agrégats DDG"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, il convient de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
-    </r>
-  </si>
-  <si>
-    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
-  </si>
-  <si>
-    <t>SIEGE</t>
-  </si>
-  <si>
-    <t>GREFFE</t>
-  </si>
-  <si>
-    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
-  </si>
-  <si>
-    <t>Contractuels et vacataires</t>
-  </si>
-  <si>
-    <t>TOTAL SIEGE</t>
-  </si>
-  <si>
-    <t>TOTAL GREFFE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Extracteur de données d'effectifs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Agrégats DDG</t>
+      <t>. Par défaut, tous les placés sont "* PLACÉ ADDITIONNEL". Si des Placés étaient des effectifs de substitution, il faut les renseigner en "* PLACÉ SUBSTITUTION", à l'aide du menu déroulant.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -903,7 +913,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1019,6 +1029,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1027,23 +1046,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1589,7 +1605,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1899,7 +1915,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1970,7 +1986,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2017,21 +2033,21 @@
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
       <c r="E4" s="37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="38"/>
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
       <c r="I4" s="39"/>
       <c r="J4" s="37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K4" s="38"/>
       <c r="L4" s="38"/>
       <c r="M4" s="38"/>
       <c r="N4" s="39"/>
       <c r="O4" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P4" t="s">
         <v>0</v>
@@ -2051,10 +2067,10 @@
         <v>25</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>26</v>
@@ -2066,13 +2082,13 @@
         <v>28</v>
       </c>
       <c r="M5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="32" t="s">
-        <v>59</v>
-      </c>
       <c r="O5" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
         <v>30</v>
@@ -2211,258 +2227,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="26" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="B11" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="B12" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
+      <c r="C13" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
+      <c r="C14" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
+      <c r="C15" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
+      <c r="B16" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
+      <c r="A18" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
@@ -2478,8 +2496,6 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B14F26-027E-9F4C-A957-F1AF0E6DE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA203BC9-F64E-6A46-951B-47BBC64CF6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22480" windowHeight="17620" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
+    <definedName name="J">#REF!</definedName>
+    <definedName name="JA">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -152,12 +154,6 @@
     <t>Selectionner une juridiction</t>
   </si>
   <si>
-    <t xml:space="preserve">         Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         Extracteur de données d'effectifs</t>
-  </si>
-  <si>
     <t xml:space="preserve">        EXPLICATIONS ET CONTROLES A EFFECTUER</t>
   </si>
   <si>
@@ -301,6 +297,211 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Précisions nécessaires aux DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tribunal d'affectation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les éventuels </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ont été répartis entre les CET de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> moins d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> plus d'un mois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dans l'onglet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Agrégats DDG"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, il convient de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
+    </r>
+  </si>
+  <si>
+    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
+  </si>
+  <si>
+    <t>SIEGE</t>
+  </si>
+  <si>
+    <t>GREFFE</t>
+  </si>
+  <si>
+    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
+  </si>
+  <si>
+    <t>Contractuels et vacataires</t>
+  </si>
+  <si>
+    <t>TOTAL SIEGE</t>
+  </si>
+  <si>
+    <t>TOTAL GREFFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Agrégats DDG</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Un </t>
     </r>
     <r>
@@ -324,114 +525,64 @@
       </rPr>
       <t>appelle une vérification. Soit l'agent était effectivement absent pendant toute la période (en CLM par ex.), soit il n'a pas été ventilé.</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Il est nécessaire de ventiler durant les temps d'indisponibilité.</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Précisions nécessaires aux DDG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (dans l'onglet "ETPT Format DDG"):</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La colonne "JURIDICTION" permet de préciser le </t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La colonne "Fonction"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> est remplie automatiquement mais </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tribunal d'affectation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (TJ / TPRX) -&gt; les données ont été prérenseignées à partir des éléments présents dans A-JUST. LEs magistrats sont, par défaut, affectés au TJ. Il convient de </t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> car elle permet de distinguer</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>contrôler ces renseignements et de réaffecter, au besoin, les agents dans l'un des TPRX proposés dans le menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>La colonne "Code fonction"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> est remplie automatiquement mais </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>doit être contrôlée et, au besoin, corrigée pour les agents placés</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> car elle permet de distinguer</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -447,144 +598,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Par défaut, tous les placés ont été codés en "M-PLAC-ADD" (Magistrat placé additionnel) ou "F-PLAC-ADD" (Fonctionnaire placé additionnel). Si des Placés étaient des effectifs de substitution, les recoder "M-PLAC-SUB" pour les magistrats ou "F-PLAC-SUB" pour les fonctionnaires, à l'aide du menu déroulant.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Les éventuels </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CET</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ont été répartis entre les CET de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> moins d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DS), qui sont considérés, lors des DDG, comme de l'absentéisme et ceux de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> plus d'un mois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (colonne DR) qui déduisent de l'ETPT (action 99).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dans l'onglet </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Agrégats DDG"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, il convient de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">sélectionner le tribunal voulu dans le menu déroulant </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(case en bleu) pour que s'affiche une synthèse montrant, pour le tribunal sélectionné (TJ ou TPRX), les ETPT affectés à chaque activité ou contentieux, ainsi que les indisponibilités déduisant de l'ETPT (action 99) et celles qui ont été réintégrées (absentéisme).</t>
-    </r>
-  </si>
-  <si>
-    <t>Pour toute question, n'hésitez pas à contacter l'équipe A-JUST : support-utilisateurs@a-just.fr</t>
-  </si>
-  <si>
-    <t>SIEGE</t>
-  </si>
-  <si>
-    <t>GREFFE</t>
-  </si>
-  <si>
-    <t>EQUIPE AUTOUR DU MAGISTRAT</t>
-  </si>
-  <si>
-    <t>Contractuels et vacataires</t>
-  </si>
-  <si>
-    <t>TOTAL SIEGE</t>
-  </si>
-  <si>
-    <t>TOTAL GREFFE</t>
+      <t>. Par défaut, tous les placés sont "* PLACÉ ADDITIONNEL". Si des Placés étaient des effectifs de substitution, il faut les renseigner en "* PLACÉ SUBSTITUTION", à l'aide du menu déroulant.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -598,7 +613,7 @@
     <numFmt numFmtId="167" formatCode="General;General;\-"/>
     <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +698,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -883,7 +913,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1001,23 +1031,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1060,15 +1102,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>46180</xdr:colOff>
+      <xdr:colOff>103906</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>23090</xdr:rowOff>
+      <xdr:rowOff>57725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>542634</xdr:colOff>
+      <xdr:colOff>923635</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>476535</xdr:rowOff>
+      <xdr:rowOff>806439</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1091,8 +1133,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46180" y="23090"/>
-          <a:ext cx="496454" cy="453445"/>
+          <a:off x="103906" y="57725"/>
+          <a:ext cx="819729" cy="748714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1109,22 +1151,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>46180</xdr:colOff>
+      <xdr:colOff>103905</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>23090</xdr:rowOff>
+      <xdr:rowOff>57725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>542634</xdr:colOff>
+      <xdr:colOff>923634</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>476535</xdr:rowOff>
+      <xdr:rowOff>806439</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CD8D5B3-C3E9-E94E-BD8C-2EF269EA8931}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D7A5D8C-BE33-ED45-A77A-8F455267161F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,8 +1182,106 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46180" y="23090"/>
-          <a:ext cx="496454" cy="453445"/>
+          <a:off x="103905" y="57725"/>
+          <a:ext cx="819729" cy="748714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>98777</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>84665</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1114778</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1012648</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD1D57F9-87BD-BD45-83E9-42F2487B9728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="98777" y="84665"/>
+          <a:ext cx="1016001" cy="927983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>103910</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69271</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>300184</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>817985</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC1CFF2-AC52-DD4F-9E83-87135FE34159}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="103910" y="69271"/>
+          <a:ext cx="819729" cy="748714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1453,7 +1593,7 @@
   <dimension ref="A1:DN8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
@@ -1463,9 +1603,9 @@
     <col min="8" max="8" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:118" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1773,9 +1913,9 @@
     <col min="2" max="2" width="71.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1827,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -1844,189 +1984,215 @@
     <col min="15" max="15" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+    </row>
+    <row r="2" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B2" s="15" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="16" t="e">
-        <f>VLOOKUP(A2,'codage tribunal'!A:B,2,FALSE)</f>
-        <v>#N/A</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="40" x14ac:dyDescent="0.2">
-      <c r="C3" s="9"/>
-      <c r="E3" s="37" t="s">
+    <row r="3" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="16" t="e">
+        <f>VLOOKUP(A3,'codage tribunal'!A:B,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
+      <c r="C4" s="9"/>
+      <c r="E4" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="37" t="s">
+      <c r="J5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="O5" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="C5" s="35" t="s">
+    <row r="6" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14"/>
+      <c r="C6" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D6" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="19" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="E6" s="19" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$3)</f>
         <v>#N/A</v>
       </c>
-      <c r="F5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="F6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*ADDITIONNEL*")</f>
         <v>#N/A</v>
       </c>
-      <c r="G5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="G6" s="17" t="e">
+        <f>SUMIFS(
+INDEX('ETPT Format DDG'!$A:$DU,
+,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*SUBSTITUTION*")</f>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="17" t="e">
+      <c r="H6" s="17" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),'ETPT Format DDG'!$I:$I,"C",
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="I5" s="34" t="e">
+      <c r="I6" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="J5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="J6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-TIT",'ETPT Format DDG'!$C:$C,$A$3)</f>
         <v>#N/A</v>
       </c>
-      <c r="K5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="K6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*ADDITIONNEL*")</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" s="17" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-SUB",'ETPT Format DDG'!$C:$C,$A$2)</f>
+      <c r="L6" s="17" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"F-PLAC-ADD",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$H:$H,"*SUBSTITUTION*")</f>
         <v>#N/A</v>
       </c>
-      <c r="M5" s="18" t="e">
-        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$2,'ETPT Format DDG'!$G:$G,"Greffe")</f>
+      <c r="M6" s="18" t="e">
+        <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"C",'ETPT Format DDG'!$C:$C,$A$3,'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="N5" s="34" t="e">
+      <c r="N6" s="34" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="O5" s="18" t="e">
+      <c r="O6" s="18" t="e">
         <f>SUMIFS(
 INDEX('ETPT Format DDG'!$A:$DU,
 ,
-IFERROR(MATCH(D5,'ETPT Format DDG'!$2:$2,0),MATCH(C5,'ETPT Format DDG'!$2:$2,0))
+IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))
 ),'ETPT Format DDG'!$I:$I,"C",
-'ETPT Format DDG'!$C:$C,$A$2,
+'ETPT Format DDG'!$C:$C,$A$3,
 'ETPT Format DDG'!$G:$G,"Autour du magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="P6" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:O150">
+  <conditionalFormatting sqref="C6:O151">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(ISBLANK($C5)=FALSE,ISBLANK($D5)=TRUE)</formula>
+      <formula>AND(ISBLANK($C6)=FALSE,ISBLANK($D6)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2060,43 +2226,43 @@
     <col min="11" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+    <row r="1" spans="1:10" s="26" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="40"/>
@@ -2109,10 +2275,10 @@
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40"/>
@@ -2125,10 +2291,10 @@
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="40"/>
@@ -2143,7 +2309,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -2156,92 +2322,92 @@
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+    </row>
+    <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+    </row>
+    <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-    </row>
-    <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-    </row>
-    <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-    </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
+      <c r="B11" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="B12" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
@@ -2255,8 +2421,8 @@
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="40" t="s">
-        <v>52</v>
+      <c r="C14" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
@@ -2271,7 +2437,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
@@ -2286,7 +2452,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="40"/>
@@ -2298,21 +2464,25 @@
       <c r="J16" s="40"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
+      <c r="A18" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
@@ -2326,12 +2496,9 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA203BC9-F64E-6A46-951B-47BBC64CF6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0EC40A-8235-D541-872B-E56B25ACA821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" activeTab="5" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ETPT A-JUST" sheetId="1" r:id="rId1"/>
@@ -492,12 +492,6 @@
     <t>TOTAL GREFFE</t>
   </si>
   <si>
-    <t xml:space="preserve">                Extracteur de données d'effectifs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme)</t>
-  </si>
-  <si>
     <t xml:space="preserve">                Agrégats DDG</t>
   </si>
   <si>
@@ -600,6 +594,12 @@
       </rPr>
       <t>. Par défaut, tous les placés sont "* PLACÉ ADDITIONNEL". Si des Placés étaient des effectifs de substitution, il faut les renseigner en "* PLACÉ SUBSTITUTION", à l'aide du menu déroulant.</t>
     </r>
+  </si>
+  <si>
+    <t>#`                Extracteur de données d'effectifs - Format DDG (avec réintégration de l'absentéisme) ${daydate}</t>
+  </si>
+  <si>
+    <t>#`                Extracteur de données d'effectifs ${daydate}</t>
   </si>
 </sst>
 </file>
@@ -1028,38 +1028,38 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1605,7 +1605,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1915,7 +1915,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="4" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1986,7 +1986,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2227,261 +2227,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="26" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
     </row>
     <row r="8" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
+      <c r="B11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
     </row>
     <row r="13" spans="1:10" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
     </row>
     <row r="14" spans="1:10" s="10" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
+      <c r="C14" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
     </row>
     <row r="16" spans="1:10" s="10" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="18" spans="1:10" s="26" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B12:J12"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
@@ -2496,6 +2493,9 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B11:J11"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B12:J12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E73E9-22DA-CD4D-A450-626969BDFFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA858C80-C3E3-5745-AD6A-7B4D1C9BEFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA858C80-C3E3-5745-AD6A-7B4D1C9BEFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD9AE63-F50C-8349-B7B0-208DEB503AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="520">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -2966,6 +2966,9 @@
   <si>
     <t>RECAPITULATIF</t>
   </si>
+  <si>
+    <t>CPH détachés</t>
+  </si>
 </sst>
 </file>
 
@@ -2977,7 +2980,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="General;General;\-"/>
     <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="39" x14ac:knownFonts="1">
     <font>
@@ -3632,7 +3635,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3830,12 +3833,12 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3850,14 +3853,14 @@
     <xf numFmtId="49" fontId="23" fillId="9" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3866,49 +3869,49 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3950,20 +3953,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyProtection="1">
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -3978,13 +3981,13 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="26" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3999,35 +4002,35 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="26" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4038,61 +4041,61 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="13" borderId="15" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -4148,15 +4151,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="29" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4175,7 +4178,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="34" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4186,13 +4189,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="19" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="34" fillId="19" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="34" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="34" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="18" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4219,7 +4222,7 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -4231,26 +4234,26 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -4272,6 +4275,30 @@
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4280,27 +4307,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4320,9 +4326,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{C877C5E8-FCBF-114F-9ECB-F75EF7C9C0EB}"/>
@@ -5254,18 +5258,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="197" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
       <c r="K1" s="28" t="s">
         <v>0</v>
       </c>
@@ -5274,17 +5278,17 @@
       <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="204" t="s">
+      <c r="B2" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="199"/>
       <c r="K2" s="10" t="s">
         <v>0</v>
       </c>
@@ -5367,17 +5371,17 @@
     </row>
     <row r="7" spans="1:11" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="29"/>
-      <c r="B7" s="204" t="s">
+      <c r="B7" s="199" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="204"/>
-      <c r="D7" s="204"/>
-      <c r="E7" s="204"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="204"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="199"/>
       <c r="K7" s="10" t="s">
         <v>0</v>
       </c>
@@ -5450,17 +5454,17 @@
       <c r="A12" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="205" t="s">
+      <c r="B12" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="206"/>
-      <c r="D12" s="206"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="206"/>
-      <c r="G12" s="206"/>
-      <c r="H12" s="206"/>
-      <c r="I12" s="206"/>
-      <c r="J12" s="206"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="203"/>
+      <c r="I12" s="203"/>
+      <c r="J12" s="203"/>
       <c r="K12" s="10" t="s">
         <v>0</v>
       </c>
@@ -5544,29 +5548,30 @@
       </c>
     </row>
     <row r="18" spans="1:11" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="202" t="s">
+      <c r="A18" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="203"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
+      <c r="B18" s="198"/>
+      <c r="C18" s="198"/>
+      <c r="D18" s="198"/>
+      <c r="E18" s="198"/>
+      <c r="F18" s="198"/>
+      <c r="G18" s="198"/>
+      <c r="H18" s="198"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="198"/>
       <c r="K18" s="28" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
@@ -5583,7 +5588,6 @@
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5605,16 +5609,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="212" t="s">
         <v>509</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
       <c r="I1" s="114"/>
       <c r="J1" s="114"/>
       <c r="K1" s="114"/>
@@ -5653,7 +5657,7 @@
       <c r="G2" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="157" t="s">
@@ -5686,13 +5690,13 @@
       <c r="R2" s="157" t="s">
         <v>462</v>
       </c>
-      <c r="S2" s="209" t="s">
+      <c r="S2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="T2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="U2" s="209" t="s">
+      <c r="U2" s="210" t="s">
         <v>460</v>
       </c>
       <c r="V2" s="157" t="s">
@@ -5722,7 +5726,7 @@
       <c r="AD2" s="157" t="s">
         <v>459</v>
       </c>
-      <c r="AE2" s="209" t="s">
+      <c r="AE2" s="210" t="s">
         <v>508</v>
       </c>
       <c r="AF2" s="157" t="s">
@@ -5734,7 +5738,7 @@
       <c r="AH2" s="157" t="s">
         <v>507</v>
       </c>
-      <c r="AI2" s="209" t="s">
+      <c r="AI2" s="210" t="s">
         <v>506</v>
       </c>
     </row>
@@ -5748,7 +5752,7 @@
       <c r="G3" s="157" t="s">
         <v>453</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="157" t="s">
         <v>505</v>
       </c>
@@ -5779,11 +5783,11 @@
       <c r="R3" s="157" t="s">
         <v>440</v>
       </c>
-      <c r="S3" s="209"/>
+      <c r="S3" s="210"/>
       <c r="T3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="U3" s="209"/>
+      <c r="U3" s="210"/>
       <c r="V3" s="157" t="s">
         <v>496</v>
       </c>
@@ -5811,7 +5815,7 @@
       <c r="AD3" s="157" t="s">
         <v>488</v>
       </c>
-      <c r="AE3" s="209"/>
+      <c r="AE3" s="210"/>
       <c r="AF3" s="157" t="s">
         <v>487</v>
       </c>
@@ -5821,7 +5825,7 @@
       <c r="AH3" s="157" t="s">
         <v>417</v>
       </c>
-      <c r="AI3" s="209"/>
+      <c r="AI3" s="210"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="160"/>
@@ -5843,7 +5847,7 @@
       <c r="G4" s="157" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="157" t="s">
         <v>486</v>
       </c>
@@ -5874,11 +5878,11 @@
       <c r="R4" s="157" t="s">
         <v>389</v>
       </c>
-      <c r="S4" s="209"/>
+      <c r="S4" s="210"/>
       <c r="T4" s="157" t="s">
         <v>385</v>
       </c>
-      <c r="U4" s="209"/>
+      <c r="U4" s="210"/>
       <c r="V4" s="157" t="s">
         <v>477</v>
       </c>
@@ -5906,7 +5910,7 @@
       <c r="AD4" s="157" t="s">
         <v>469</v>
       </c>
-      <c r="AE4" s="209"/>
+      <c r="AE4" s="210"/>
       <c r="AF4" s="157" t="s">
         <v>468</v>
       </c>
@@ -5916,7 +5920,7 @@
       <c r="AH4" s="157" t="s">
         <v>364</v>
       </c>
-      <c r="AI4" s="209"/>
+      <c r="AI4" s="210"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="163" t="s">
@@ -7020,13 +7024,13 @@
       <c r="G2" s="157" t="s">
         <v>462</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="I2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="209" t="s">
+      <c r="J2" s="210" t="s">
         <v>460</v>
       </c>
     </row>
@@ -7040,11 +7044,11 @@
       <c r="G3" s="157" t="s">
         <v>440</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="J3" s="209"/>
+      <c r="J3" s="210"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="179"/>
@@ -7066,11 +7070,11 @@
       <c r="G4" s="157" t="s">
         <v>389</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="157" t="s">
         <v>385</v>
       </c>
-      <c r="J4" s="209"/>
+      <c r="J4" s="210"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="173" t="s">
@@ -7469,7 +7473,7 @@
       <c r="G2" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="156" t="s">
@@ -7514,7 +7518,7 @@
       <c r="V2" s="156" t="s">
         <v>462</v>
       </c>
-      <c r="W2" s="209" t="s">
+      <c r="W2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="X2" s="157" t="s">
@@ -7529,7 +7533,7 @@
       <c r="AA2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="AB2" s="209" t="s">
+      <c r="AB2" s="210" t="s">
         <v>460</v>
       </c>
       <c r="AC2" s="154" t="s">
@@ -7559,7 +7563,7 @@
       <c r="AK2" s="154" t="s">
         <v>459</v>
       </c>
-      <c r="AL2" s="209" t="s">
+      <c r="AL2" s="210" t="s">
         <v>458</v>
       </c>
       <c r="AM2" s="154" t="s">
@@ -7601,7 +7605,7 @@
       <c r="AY2" s="154" t="s">
         <v>457</v>
       </c>
-      <c r="AZ2" s="209" t="s">
+      <c r="AZ2" s="210" t="s">
         <v>456</v>
       </c>
       <c r="BA2" s="153" t="s">
@@ -7631,7 +7635,7 @@
       <c r="BI2" s="153" t="s">
         <v>455</v>
       </c>
-      <c r="BJ2" s="209" t="s">
+      <c r="BJ2" s="210" t="s">
         <v>454</v>
       </c>
       <c r="BK2"/>
@@ -7646,7 +7650,7 @@
       <c r="G3" s="157" t="s">
         <v>453</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="156" t="s">
         <v>452</v>
       </c>
@@ -7687,7 +7691,7 @@
       <c r="V3" s="156" t="s">
         <v>440</v>
       </c>
-      <c r="W3" s="209"/>
+      <c r="W3" s="210"/>
       <c r="X3" s="152"/>
       <c r="Y3" s="157" t="s">
         <v>439</v>
@@ -7698,7 +7702,7 @@
       <c r="AA3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="AB3" s="209"/>
+      <c r="AB3" s="210"/>
       <c r="AC3" s="154" t="s">
         <v>436</v>
       </c>
@@ -7726,7 +7730,7 @@
       <c r="AK3" s="154" t="s">
         <v>430</v>
       </c>
-      <c r="AL3" s="209"/>
+      <c r="AL3" s="210"/>
       <c r="AM3" s="154" t="s">
         <v>429</v>
       </c>
@@ -7766,7 +7770,7 @@
       <c r="AY3" s="154" t="s">
         <v>417</v>
       </c>
-      <c r="AZ3" s="209"/>
+      <c r="AZ3" s="210"/>
       <c r="BA3" s="153" t="s">
         <v>416</v>
       </c>
@@ -7794,7 +7798,7 @@
       <c r="BI3" s="153" t="s">
         <v>408</v>
       </c>
-      <c r="BJ3" s="209"/>
+      <c r="BJ3" s="210"/>
     </row>
     <row r="4" spans="1:63" s="114" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="159"/>
@@ -7816,7 +7820,7 @@
       <c r="G4" s="157" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="156" t="s">
         <v>402</v>
       </c>
@@ -7859,7 +7863,7 @@
       <c r="V4" s="156" t="s">
         <v>389</v>
       </c>
-      <c r="W4" s="209"/>
+      <c r="W4" s="210"/>
       <c r="X4" s="155" t="s">
         <v>388</v>
       </c>
@@ -7872,7 +7876,7 @@
       <c r="AA4" s="155" t="s">
         <v>385</v>
       </c>
-      <c r="AB4" s="209"/>
+      <c r="AB4" s="210"/>
       <c r="AC4" s="154" t="s">
         <v>384</v>
       </c>
@@ -7900,7 +7904,7 @@
       <c r="AK4" s="154" t="s">
         <v>377</v>
       </c>
-      <c r="AL4" s="209"/>
+      <c r="AL4" s="210"/>
       <c r="AM4" s="154" t="s">
         <v>376</v>
       </c>
@@ -7940,7 +7944,7 @@
       <c r="AY4" s="154" t="s">
         <v>364</v>
       </c>
-      <c r="AZ4" s="209"/>
+      <c r="AZ4" s="210"/>
       <c r="BA4" s="153" t="s">
         <v>363</v>
       </c>
@@ -7968,7 +7972,7 @@
       <c r="BI4" s="153" t="s">
         <v>355</v>
       </c>
-      <c r="BJ4" s="209"/>
+      <c r="BJ4" s="210"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="114" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -10739,7 +10743,7 @@
       <c r="G2" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="157" t="s">
@@ -10772,13 +10776,13 @@
       <c r="R2" s="157" t="s">
         <v>462</v>
       </c>
-      <c r="S2" s="209" t="s">
+      <c r="S2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="T2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="U2" s="209" t="s">
+      <c r="U2" s="210" t="s">
         <v>460</v>
       </c>
       <c r="V2" s="157" t="s">
@@ -10808,7 +10812,7 @@
       <c r="AD2" s="157" t="s">
         <v>459</v>
       </c>
-      <c r="AE2" s="209" t="s">
+      <c r="AE2" s="210" t="s">
         <v>508</v>
       </c>
       <c r="AF2" s="157" t="s">
@@ -10820,7 +10824,7 @@
       <c r="AH2" s="157" t="s">
         <v>507</v>
       </c>
-      <c r="AI2" s="209" t="s">
+      <c r="AI2" s="210" t="s">
         <v>506</v>
       </c>
     </row>
@@ -10834,7 +10838,7 @@
       <c r="G3" s="157" t="s">
         <v>453</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="157" t="s">
         <v>505</v>
       </c>
@@ -10865,11 +10869,11 @@
       <c r="R3" s="157" t="s">
         <v>440</v>
       </c>
-      <c r="S3" s="209"/>
+      <c r="S3" s="210"/>
       <c r="T3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="U3" s="209"/>
+      <c r="U3" s="210"/>
       <c r="V3" s="157" t="s">
         <v>496</v>
       </c>
@@ -10897,7 +10901,7 @@
       <c r="AD3" s="157" t="s">
         <v>488</v>
       </c>
-      <c r="AE3" s="209"/>
+      <c r="AE3" s="210"/>
       <c r="AF3" s="157" t="s">
         <v>487</v>
       </c>
@@ -10907,7 +10911,7 @@
       <c r="AH3" s="157" t="s">
         <v>417</v>
       </c>
-      <c r="AI3" s="209"/>
+      <c r="AI3" s="210"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="160"/>
@@ -10929,7 +10933,7 @@
       <c r="G4" s="157" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="157" t="s">
         <v>486</v>
       </c>
@@ -10960,11 +10964,11 @@
       <c r="R4" s="157" t="s">
         <v>389</v>
       </c>
-      <c r="S4" s="209"/>
+      <c r="S4" s="210"/>
       <c r="T4" s="157" t="s">
         <v>385</v>
       </c>
-      <c r="U4" s="209"/>
+      <c r="U4" s="210"/>
       <c r="V4" s="157" t="s">
         <v>477</v>
       </c>
@@ -10992,7 +10996,7 @@
       <c r="AD4" s="157" t="s">
         <v>469</v>
       </c>
-      <c r="AE4" s="209"/>
+      <c r="AE4" s="210"/>
       <c r="AF4" s="157" t="s">
         <v>468</v>
       </c>
@@ -11002,7 +11006,7 @@
       <c r="AH4" s="157" t="s">
         <v>364</v>
       </c>
-      <c r="AI4" s="209"/>
+      <c r="AI4" s="210"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="163" t="s">
@@ -12704,13 +12708,13 @@
       <c r="G2" s="157" t="s">
         <v>462</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="I2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="209" t="s">
+      <c r="J2" s="210" t="s">
         <v>460</v>
       </c>
     </row>
@@ -12724,11 +12728,11 @@
       <c r="G3" s="157" t="s">
         <v>440</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="J3" s="209"/>
+      <c r="J3" s="210"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="179"/>
@@ -12750,11 +12754,11 @@
       <c r="G4" s="157" t="s">
         <v>389</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="157" t="s">
         <v>385</v>
       </c>
-      <c r="J4" s="209"/>
+      <c r="J4" s="210"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="173" t="s">
@@ -13445,14 +13449,14 @@
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="EA1" s="212" t="s">
+      <c r="EA1" s="204" t="s">
         <v>518</v>
       </c>
-      <c r="EB1" s="212"/>
-      <c r="EC1" s="212"/>
-      <c r="ED1" s="212"/>
-      <c r="EE1" s="212"/>
-      <c r="EF1" s="212"/>
+      <c r="EB1" s="204"/>
+      <c r="EC1" s="204"/>
+      <c r="ED1" s="204"/>
+      <c r="EE1" s="204"/>
+      <c r="EF1" s="204"/>
     </row>
     <row r="2" spans="1:136" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
@@ -13574,20 +13578,20 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="205" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="198"/>
-      <c r="I4" s="199"/>
-      <c r="J4" s="197" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="207"/>
       <c r="O4" s="32" t="s">
         <v>55</v>
       </c>
@@ -13760,7 +13764,9 @@
     <col min="6" max="6" width="11" style="37"/>
     <col min="7" max="7" width="12" style="37" customWidth="1"/>
     <col min="8" max="8" width="27.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="37"/>
+    <col min="9" max="9" width="12.1640625" style="37" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="37" customWidth="1"/>
+    <col min="11" max="16384" width="11" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="41" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -13776,7 +13782,9 @@
         <v>161</v>
       </c>
       <c r="H1"/>
-      <c r="I1"/>
+      <c r="I1" s="213" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B2"/>
@@ -15182,16 +15190,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="66" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="109"/>
-      <c r="B1" s="208" t="s">
+      <c r="B1" s="209" t="s">
         <v>465</v>
       </c>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
       <c r="AC1" s="108"/>
       <c r="AD1" s="108"/>
       <c r="AE1" s="108"/>
@@ -15212,7 +15220,7 @@
       <c r="G2" s="104" t="s">
         <v>464</v>
       </c>
-      <c r="H2" s="207" t="s">
+      <c r="H2" s="208" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="103" t="s">
@@ -15257,7 +15265,7 @@
       <c r="V2" s="103" t="s">
         <v>462</v>
       </c>
-      <c r="W2" s="207" t="s">
+      <c r="W2" s="208" t="s">
         <v>461</v>
       </c>
       <c r="X2" s="104" t="s">
@@ -15272,7 +15280,7 @@
       <c r="AA2" s="104" t="s">
         <v>178</v>
       </c>
-      <c r="AB2" s="207" t="s">
+      <c r="AB2" s="208" t="s">
         <v>460</v>
       </c>
       <c r="AC2" s="100" t="s">
@@ -15302,7 +15310,7 @@
       <c r="AK2" s="100" t="s">
         <v>459</v>
       </c>
-      <c r="AL2" s="207" t="s">
+      <c r="AL2" s="208" t="s">
         <v>458</v>
       </c>
       <c r="AM2" s="100" t="s">
@@ -15344,7 +15352,7 @@
       <c r="AY2" s="100" t="s">
         <v>457</v>
       </c>
-      <c r="AZ2" s="207" t="s">
+      <c r="AZ2" s="208" t="s">
         <v>456</v>
       </c>
       <c r="BA2" s="99" t="s">
@@ -15374,7 +15382,7 @@
       <c r="BI2" s="99" t="s">
         <v>455</v>
       </c>
-      <c r="BJ2" s="207" t="s">
+      <c r="BJ2" s="208" t="s">
         <v>454</v>
       </c>
     </row>
@@ -15388,7 +15396,7 @@
       <c r="G3" s="104" t="s">
         <v>453</v>
       </c>
-      <c r="H3" s="207"/>
+      <c r="H3" s="208"/>
       <c r="I3" s="103" t="s">
         <v>452</v>
       </c>
@@ -15429,7 +15437,7 @@
       <c r="V3" s="103" t="s">
         <v>440</v>
       </c>
-      <c r="W3" s="207"/>
+      <c r="W3" s="208"/>
       <c r="X3" s="98"/>
       <c r="Y3" s="104" t="s">
         <v>439</v>
@@ -15440,7 +15448,7 @@
       <c r="AA3" s="104" t="s">
         <v>437</v>
       </c>
-      <c r="AB3" s="207"/>
+      <c r="AB3" s="208"/>
       <c r="AC3" s="100" t="s">
         <v>436</v>
       </c>
@@ -15468,7 +15476,7 @@
       <c r="AK3" s="100" t="s">
         <v>430</v>
       </c>
-      <c r="AL3" s="207"/>
+      <c r="AL3" s="208"/>
       <c r="AM3" s="100" t="s">
         <v>429</v>
       </c>
@@ -15508,7 +15516,7 @@
       <c r="AY3" s="100" t="s">
         <v>417</v>
       </c>
-      <c r="AZ3" s="207"/>
+      <c r="AZ3" s="208"/>
       <c r="BA3" s="99" t="s">
         <v>416</v>
       </c>
@@ -15536,7 +15544,7 @@
       <c r="BI3" s="99" t="s">
         <v>408</v>
       </c>
-      <c r="BJ3" s="207"/>
+      <c r="BJ3" s="208"/>
     </row>
     <row r="4" spans="1:62" s="66" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="106"/>
@@ -15558,7 +15566,7 @@
       <c r="G4" s="104" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="207"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="103" t="s">
         <v>402</v>
       </c>
@@ -15601,7 +15609,7 @@
       <c r="V4" s="102" t="s">
         <v>389</v>
       </c>
-      <c r="W4" s="207"/>
+      <c r="W4" s="208"/>
       <c r="X4" s="101" t="s">
         <v>388</v>
       </c>
@@ -15614,7 +15622,7 @@
       <c r="AA4" s="101" t="s">
         <v>385</v>
       </c>
-      <c r="AB4" s="207"/>
+      <c r="AB4" s="208"/>
       <c r="AC4" s="100" t="s">
         <v>384</v>
       </c>
@@ -15642,7 +15650,7 @@
       <c r="AK4" s="100" t="s">
         <v>377</v>
       </c>
-      <c r="AL4" s="207"/>
+      <c r="AL4" s="208"/>
       <c r="AM4" s="100" t="s">
         <v>376</v>
       </c>
@@ -15682,7 +15690,7 @@
       <c r="AY4" s="100" t="s">
         <v>364</v>
       </c>
-      <c r="AZ4" s="207"/>
+      <c r="AZ4" s="208"/>
       <c r="BA4" s="99" t="s">
         <v>363</v>
       </c>
@@ -15710,7 +15718,7 @@
       <c r="BI4" s="99" t="s">
         <v>355</v>
       </c>
-      <c r="BJ4" s="207"/>
+      <c r="BJ4" s="208"/>
     </row>
     <row r="5" spans="1:62" s="66" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="74" t="s">
@@ -16688,7 +16696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="74" t="s">
         <v>259</v>
       </c>
@@ -17400,16 +17408,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="114" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="210" t="s">
+      <c r="B1" s="211" t="s">
         <v>465</v>
       </c>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
     </row>
     <row r="2" spans="1:62" s="114" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="160"/>
@@ -17421,7 +17429,7 @@
       <c r="G2" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="210" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="156" t="s">
@@ -17466,7 +17474,7 @@
       <c r="V2" s="156" t="s">
         <v>462</v>
       </c>
-      <c r="W2" s="209" t="s">
+      <c r="W2" s="210" t="s">
         <v>461</v>
       </c>
       <c r="X2" s="157" t="s">
@@ -17481,7 +17489,7 @@
       <c r="AA2" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="AB2" s="209" t="s">
+      <c r="AB2" s="210" t="s">
         <v>460</v>
       </c>
       <c r="AC2" s="154" t="s">
@@ -17511,7 +17519,7 @@
       <c r="AK2" s="154" t="s">
         <v>459</v>
       </c>
-      <c r="AL2" s="209" t="s">
+      <c r="AL2" s="210" t="s">
         <v>458</v>
       </c>
       <c r="AM2" s="154" t="s">
@@ -17553,7 +17561,7 @@
       <c r="AY2" s="154" t="s">
         <v>457</v>
       </c>
-      <c r="AZ2" s="209" t="s">
+      <c r="AZ2" s="210" t="s">
         <v>456</v>
       </c>
       <c r="BA2" s="153" t="s">
@@ -17583,7 +17591,7 @@
       <c r="BI2" s="153" t="s">
         <v>455</v>
       </c>
-      <c r="BJ2" s="209" t="s">
+      <c r="BJ2" s="210" t="s">
         <v>454</v>
       </c>
     </row>
@@ -17597,7 +17605,7 @@
       <c r="G3" s="157" t="s">
         <v>453</v>
       </c>
-      <c r="H3" s="209"/>
+      <c r="H3" s="210"/>
       <c r="I3" s="156" t="s">
         <v>452</v>
       </c>
@@ -17638,7 +17646,7 @@
       <c r="V3" s="156" t="s">
         <v>440</v>
       </c>
-      <c r="W3" s="209"/>
+      <c r="W3" s="210"/>
       <c r="X3" s="152"/>
       <c r="Y3" s="157" t="s">
         <v>439</v>
@@ -17649,7 +17657,7 @@
       <c r="AA3" s="157" t="s">
         <v>437</v>
       </c>
-      <c r="AB3" s="209"/>
+      <c r="AB3" s="210"/>
       <c r="AC3" s="154" t="s">
         <v>436</v>
       </c>
@@ -17677,7 +17685,7 @@
       <c r="AK3" s="154" t="s">
         <v>430</v>
       </c>
-      <c r="AL3" s="209"/>
+      <c r="AL3" s="210"/>
       <c r="AM3" s="154" t="s">
         <v>429</v>
       </c>
@@ -17717,7 +17725,7 @@
       <c r="AY3" s="154" t="s">
         <v>417</v>
       </c>
-      <c r="AZ3" s="209"/>
+      <c r="AZ3" s="210"/>
       <c r="BA3" s="153" t="s">
         <v>416</v>
       </c>
@@ -17745,7 +17753,7 @@
       <c r="BI3" s="153" t="s">
         <v>408</v>
       </c>
-      <c r="BJ3" s="209"/>
+      <c r="BJ3" s="210"/>
     </row>
     <row r="4" spans="1:62" s="114" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="159"/>
@@ -17767,7 +17775,7 @@
       <c r="G4" s="157" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="209"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="156" t="s">
         <v>402</v>
       </c>
@@ -17810,7 +17818,7 @@
       <c r="V4" s="156" t="s">
         <v>389</v>
       </c>
-      <c r="W4" s="209"/>
+      <c r="W4" s="210"/>
       <c r="X4" s="155" t="s">
         <v>388</v>
       </c>
@@ -17823,7 +17831,7 @@
       <c r="AA4" s="155" t="s">
         <v>385</v>
       </c>
-      <c r="AB4" s="209"/>
+      <c r="AB4" s="210"/>
       <c r="AC4" s="154" t="s">
         <v>384</v>
       </c>
@@ -17851,7 +17859,7 @@
       <c r="AK4" s="154" t="s">
         <v>377</v>
       </c>
-      <c r="AL4" s="209"/>
+      <c r="AL4" s="210"/>
       <c r="AM4" s="154" t="s">
         <v>376</v>
       </c>
@@ -17891,7 +17899,7 @@
       <c r="AY4" s="154" t="s">
         <v>364</v>
       </c>
-      <c r="AZ4" s="209"/>
+      <c r="AZ4" s="210"/>
       <c r="BA4" s="153" t="s">
         <v>363</v>
       </c>
@@ -17919,7 +17927,7 @@
       <c r="BI4" s="153" t="s">
         <v>355</v>
       </c>
-      <c r="BJ4" s="209"/>
+      <c r="BJ4" s="210"/>
     </row>
     <row r="5" spans="1:62" s="114" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="124" t="s">

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F327840D-70B6-7B48-B14F-7A0BA89B1209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1867FA-6BD2-604C-AC39-EE3945E7A4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -3210,7 +3210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -3553,19 +3553,6 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color rgb="FF333F4F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF333F4F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF333F4F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thick">
         <color rgb="FFFF0000"/>
@@ -3685,6 +3672,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF333F4F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF333F4F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF333F4F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF333F4F"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF333F4F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3695,7 +3733,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4367,19 +4405,10 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="4" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="4" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4393,13 +4422,58 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="40" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4408,11 +4482,35 @@
     <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4444,14 +4542,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4461,60 +4559,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="41" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -4654,9 +4698,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>13121</xdr:colOff>
+      <xdr:colOff>227016</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>81478</xdr:rowOff>
+      <xdr:rowOff>14635</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="960661" cy="902640"/>
     <xdr:pic>
@@ -4680,7 +4724,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="838621" y="81478"/>
+          <a:off x="320595" y="14635"/>
           <a:ext cx="960661" cy="902640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5305,11 +5349,11 @@
       <c r="B1" s="197" t="s">
         <v>494</v>
       </c>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="225" t="s">
         <v>495</v>
       </c>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
       <c r="F1" s="198"/>
       <c r="H1" s="28" t="s">
         <v>0</v>
@@ -5318,11 +5362,11 @@
     <row r="2" spans="1:8" s="202" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>496</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
       <c r="F2" s="201"/>
       <c r="H2" s="28" t="s">
         <v>0</v>
@@ -5346,156 +5390,163 @@
       <c r="D4" s="207" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="232" t="s">
         <v>500</v>
       </c>
-      <c r="F4" s="221"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="221"/>
       <c r="H4" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
-      <c r="B5" s="240" t="s">
+      <c r="B5" s="214" t="s">
         <v>501</v>
       </c>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="215" t="s">
         <v>502</v>
       </c>
-      <c r="D5" s="241" t="s">
+      <c r="D5" s="215" t="s">
         <v>503</v>
       </c>
-      <c r="E5" s="242" t="s">
+      <c r="E5" s="234" t="s">
         <v>518</v>
       </c>
-      <c r="F5" s="243"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="220"/>
       <c r="H5" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
-      <c r="B6" s="244" t="s">
+      <c r="B6" s="216" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="C6" s="217" t="s">
         <v>505</v>
       </c>
-      <c r="D6" s="245" t="s">
+      <c r="D6" s="217" t="s">
         <v>506</v>
       </c>
-      <c r="E6" s="246" t="s">
+      <c r="E6" s="236" t="s">
         <v>519</v>
       </c>
-      <c r="F6" s="247"/>
+      <c r="F6" s="237"/>
+      <c r="G6" s="220"/>
       <c r="H6" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
-      <c r="B7" s="244" t="s">
+      <c r="B7" s="216" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="245" t="s">
+      <c r="C7" s="217" t="s">
         <v>508</v>
       </c>
-      <c r="D7" s="245" t="s">
+      <c r="D7" s="217" t="s">
         <v>509</v>
       </c>
-      <c r="E7" s="246" t="s">
+      <c r="E7" s="236" t="s">
         <v>518</v>
       </c>
-      <c r="F7" s="247"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="220"/>
       <c r="H7" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
-      <c r="B8" s="248" t="s">
+      <c r="B8" s="218" t="s">
         <v>510</v>
       </c>
-      <c r="C8" s="249" t="s">
+      <c r="C8" s="227" t="s">
         <v>511</v>
       </c>
-      <c r="D8" s="249" t="s">
+      <c r="D8" s="227" t="s">
         <v>512</v>
       </c>
-      <c r="E8" s="250" t="s">
+      <c r="E8" s="238" t="s">
         <v>520</v>
       </c>
-      <c r="F8" s="251"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="220"/>
       <c r="H8" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
-      <c r="B9" s="248" t="s">
+      <c r="B9" s="218" t="s">
         <v>513</v>
       </c>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="253"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="220"/>
       <c r="H9" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
-      <c r="B10" s="254" t="s">
+      <c r="B10" s="219" t="s">
         <v>514</v>
       </c>
-      <c r="C10" s="255"/>
-      <c r="D10" s="255"/>
-      <c r="E10" s="256"/>
-      <c r="F10" s="257"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="220"/>
       <c r="H10" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="28" customFormat="1" ht="5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="203"/>
-      <c r="B11" s="209"/>
-      <c r="C11" s="209"/>
-      <c r="D11" s="209"/>
-      <c r="E11" s="209"/>
-      <c r="F11" s="209"/>
+      <c r="B11" s="224"/>
+      <c r="C11" s="224"/>
+      <c r="D11" s="224"/>
+      <c r="E11" s="224"/>
+      <c r="F11" s="224"/>
       <c r="H11" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="28" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="203"/>
-      <c r="B12" s="210"/>
-      <c r="C12" s="219" t="s">
+      <c r="B12" s="222"/>
+      <c r="C12" s="231" t="s">
         <v>515</v>
       </c>
-      <c r="D12" s="219"/>
-      <c r="E12" s="219"/>
-      <c r="F12" s="211"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="223"/>
       <c r="H12" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="212"/>
+      <c r="A13" s="209"/>
       <c r="F13" s="204"/>
       <c r="H13" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="217" t="s">
+      <c r="A14" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="218"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="230"/>
       <c r="H14" s="28" t="s">
         <v>0</v>
       </c>
@@ -5548,16 +5599,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="232" t="s">
+      <c r="A1" s="252" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="252"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
       <c r="I1" s="112"/>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -5596,7 +5647,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -5629,13 +5680,13 @@
       <c r="R2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="230" t="s">
+      <c r="U2" s="250" t="s">
         <v>434</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -5665,7 +5716,7 @@
       <c r="AD2" s="155" t="s">
         <v>433</v>
       </c>
-      <c r="AE2" s="230" t="s">
+      <c r="AE2" s="250" t="s">
         <v>482</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -5677,7 +5728,7 @@
       <c r="AH2" s="155" t="s">
         <v>481</v>
       </c>
-      <c r="AI2" s="230" t="s">
+      <c r="AI2" s="250" t="s">
         <v>480</v>
       </c>
     </row>
@@ -5691,7 +5742,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="155" t="s">
         <v>479</v>
       </c>
@@ -5722,11 +5773,11 @@
       <c r="R3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="S3" s="230"/>
+      <c r="S3" s="250"/>
       <c r="T3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="U3" s="230"/>
+      <c r="U3" s="250"/>
       <c r="V3" s="155" t="s">
         <v>470</v>
       </c>
@@ -5754,7 +5805,7 @@
       <c r="AD3" s="155" t="s">
         <v>462</v>
       </c>
-      <c r="AE3" s="230"/>
+      <c r="AE3" s="250"/>
       <c r="AF3" s="155" t="s">
         <v>461</v>
       </c>
@@ -5764,7 +5815,7 @@
       <c r="AH3" s="155" t="s">
         <v>391</v>
       </c>
-      <c r="AI3" s="230"/>
+      <c r="AI3" s="250"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -5786,7 +5837,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="155" t="s">
         <v>460</v>
       </c>
@@ -5817,11 +5868,11 @@
       <c r="R4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="S4" s="230"/>
+      <c r="S4" s="250"/>
       <c r="T4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="U4" s="230"/>
+      <c r="U4" s="250"/>
       <c r="V4" s="155" t="s">
         <v>451</v>
       </c>
@@ -5849,7 +5900,7 @@
       <c r="AD4" s="155" t="s">
         <v>443</v>
       </c>
-      <c r="AE4" s="230"/>
+      <c r="AE4" s="250"/>
       <c r="AF4" s="155" t="s">
         <v>442</v>
       </c>
@@ -5859,7 +5910,7 @@
       <c r="AH4" s="155" t="s">
         <v>338</v>
       </c>
-      <c r="AI4" s="230"/>
+      <c r="AI4" s="250"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -6963,13 +7014,13 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="230" t="s">
+      <c r="J2" s="250" t="s">
         <v>434</v>
       </c>
     </row>
@@ -6983,11 +7034,11 @@
       <c r="G3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="J3" s="230"/>
+      <c r="J3" s="250"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -7009,11 +7060,11 @@
       <c r="G4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="J4" s="230"/>
+      <c r="J4" s="250"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -7412,7 +7463,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -7457,7 +7508,7 @@
       <c r="V2" s="154" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="230" t="s">
+      <c r="W2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -7472,7 +7523,7 @@
       <c r="AA2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="230" t="s">
+      <c r="AB2" s="250" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -7502,7 +7553,7 @@
       <c r="AK2" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="230" t="s">
+      <c r="AL2" s="250" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -7544,7 +7595,7 @@
       <c r="AY2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="230" t="s">
+      <c r="AZ2" s="250" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -7574,7 +7625,7 @@
       <c r="BI2" s="151" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="230" t="s">
+      <c r="BJ2" s="250" t="s">
         <v>428</v>
       </c>
       <c r="BK2"/>
@@ -7589,7 +7640,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="154" t="s">
         <v>426</v>
       </c>
@@ -7630,7 +7681,7 @@
       <c r="V3" s="154" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="230"/>
+      <c r="W3" s="250"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>413</v>
@@ -7641,7 +7692,7 @@
       <c r="AA3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="230"/>
+      <c r="AB3" s="250"/>
       <c r="AC3" s="152" t="s">
         <v>410</v>
       </c>
@@ -7669,7 +7720,7 @@
       <c r="AK3" s="152" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="230"/>
+      <c r="AL3" s="250"/>
       <c r="AM3" s="152" t="s">
         <v>403</v>
       </c>
@@ -7709,7 +7760,7 @@
       <c r="AY3" s="152" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="230"/>
+      <c r="AZ3" s="250"/>
       <c r="BA3" s="151" t="s">
         <v>390</v>
       </c>
@@ -7737,7 +7788,7 @@
       <c r="BI3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="230"/>
+      <c r="BJ3" s="250"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
@@ -7759,7 +7810,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="154" t="s">
         <v>376</v>
       </c>
@@ -7802,7 +7853,7 @@
       <c r="V4" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="230"/>
+      <c r="W4" s="250"/>
       <c r="X4" s="153" t="s">
         <v>362</v>
       </c>
@@ -7815,7 +7866,7 @@
       <c r="AA4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="230"/>
+      <c r="AB4" s="250"/>
       <c r="AC4" s="152" t="s">
         <v>358</v>
       </c>
@@ -7843,7 +7894,7 @@
       <c r="AK4" s="152" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="230"/>
+      <c r="AL4" s="250"/>
       <c r="AM4" s="152" t="s">
         <v>350</v>
       </c>
@@ -7883,7 +7934,7 @@
       <c r="AY4" s="152" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="230"/>
+      <c r="AZ4" s="250"/>
       <c r="BA4" s="151" t="s">
         <v>337</v>
       </c>
@@ -7911,7 +7962,7 @@
       <c r="BI4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="230"/>
+      <c r="BJ4" s="250"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -7920,7 +7971,7 @@
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
-      <c r="D5" s="215"/>
+      <c r="D5" s="212"/>
       <c r="E5" s="132" t="s">
         <v>328</v>
       </c>
@@ -8132,7 +8183,7 @@
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
-      <c r="D6" s="216" t="str">
+      <c r="D6" s="213" t="str">
         <f t="shared" ref="D6:D15" si="6">IF(ISBLANK($D$5),"",$D$5)</f>
         <v/>
       </c>
@@ -8346,7 +8397,7 @@
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
-      <c r="D7" s="216" t="str">
+      <c r="D7" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8560,7 +8611,7 @@
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
-      <c r="D8" s="216" t="str">
+      <c r="D8" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8774,7 +8825,7 @@
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
-      <c r="D9" s="216" t="str">
+      <c r="D9" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8988,7 +9039,7 @@
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
-      <c r="D10" s="216" t="str">
+      <c r="D10" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9202,7 +9253,7 @@
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
-      <c r="D11" s="216" t="str">
+      <c r="D11" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9416,7 +9467,7 @@
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
-      <c r="D12" s="216" t="str">
+      <c r="D12" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9630,7 +9681,7 @@
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
-      <c r="D13" s="216" t="str">
+      <c r="D13" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9844,7 +9895,7 @@
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
-      <c r="D14" s="216" t="str">
+      <c r="D14" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10058,7 +10109,7 @@
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
-      <c r="D15" s="216" t="str">
+      <c r="D15" s="213" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10569,17 +10620,17 @@
       <c r="AZ18" s="111"/>
     </row>
     <row r="19" spans="1:62" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="233" t="s">
+      <c r="E19" s="253" t="s">
         <v>440</v>
       </c>
-      <c r="F19" s="234"/>
-      <c r="G19" s="234"/>
-      <c r="H19" s="234"/>
-      <c r="I19" s="234"/>
-      <c r="J19" s="234"/>
-      <c r="K19" s="234"/>
-      <c r="L19" s="234"/>
-      <c r="M19" s="235"/>
+      <c r="F19" s="254"/>
+      <c r="G19" s="254"/>
+      <c r="H19" s="254"/>
+      <c r="I19" s="254"/>
+      <c r="J19" s="254"/>
+      <c r="K19" s="254"/>
+      <c r="L19" s="254"/>
+      <c r="M19" s="255"/>
     </row>
     <row r="20" spans="1:62" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:62" x14ac:dyDescent="0.2">
@@ -10695,7 +10746,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -10728,13 +10779,13 @@
       <c r="R2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="230" t="s">
+      <c r="U2" s="250" t="s">
         <v>434</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -10764,7 +10815,7 @@
       <c r="AD2" s="155" t="s">
         <v>433</v>
       </c>
-      <c r="AE2" s="230" t="s">
+      <c r="AE2" s="250" t="s">
         <v>482</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -10776,7 +10827,7 @@
       <c r="AH2" s="155" t="s">
         <v>481</v>
       </c>
-      <c r="AI2" s="230" t="s">
+      <c r="AI2" s="250" t="s">
         <v>480</v>
       </c>
     </row>
@@ -10790,7 +10841,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="155" t="s">
         <v>479</v>
       </c>
@@ -10821,11 +10872,11 @@
       <c r="R3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="S3" s="230"/>
+      <c r="S3" s="250"/>
       <c r="T3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="U3" s="230"/>
+      <c r="U3" s="250"/>
       <c r="V3" s="155" t="s">
         <v>470</v>
       </c>
@@ -10853,7 +10904,7 @@
       <c r="AD3" s="155" t="s">
         <v>462</v>
       </c>
-      <c r="AE3" s="230"/>
+      <c r="AE3" s="250"/>
       <c r="AF3" s="155" t="s">
         <v>461</v>
       </c>
@@ -10863,7 +10914,7 @@
       <c r="AH3" s="155" t="s">
         <v>391</v>
       </c>
-      <c r="AI3" s="230"/>
+      <c r="AI3" s="250"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -10885,7 +10936,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="155" t="s">
         <v>460</v>
       </c>
@@ -10916,11 +10967,11 @@
       <c r="R4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="S4" s="230"/>
+      <c r="S4" s="250"/>
       <c r="T4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="U4" s="230"/>
+      <c r="U4" s="250"/>
       <c r="V4" s="155" t="s">
         <v>451</v>
       </c>
@@ -10948,7 +10999,7 @@
       <c r="AD4" s="155" t="s">
         <v>443</v>
       </c>
-      <c r="AE4" s="230"/>
+      <c r="AE4" s="250"/>
       <c r="AF4" s="155" t="s">
         <v>442</v>
       </c>
@@ -10958,7 +11009,7 @@
       <c r="AH4" s="155" t="s">
         <v>338</v>
       </c>
-      <c r="AI4" s="230"/>
+      <c r="AI4" s="250"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -12550,32 +12601,32 @@
       <c r="S17" s="111"/>
     </row>
     <row r="18" spans="5:19" ht="21" x14ac:dyDescent="0.25">
-      <c r="E18" s="236" t="s">
+      <c r="E18" s="256" t="s">
         <v>517</v>
       </c>
-      <c r="F18" s="237"/>
-      <c r="G18" s="237"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="237"/>
-      <c r="K18" s="237"/>
-      <c r="L18" s="237"/>
-      <c r="M18" s="237"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
+      <c r="M18" s="257"/>
     </row>
     <row r="19" spans="5:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="5:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="233" t="s">
+      <c r="E20" s="253" t="s">
         <v>440</v>
       </c>
-      <c r="F20" s="234"/>
-      <c r="G20" s="234"/>
-      <c r="H20" s="234"/>
-      <c r="I20" s="234"/>
-      <c r="J20" s="234"/>
-      <c r="K20" s="234"/>
-      <c r="L20" s="234"/>
-      <c r="M20" s="234"/>
-      <c r="N20" s="213"/>
+      <c r="F20" s="254"/>
+      <c r="G20" s="254"/>
+      <c r="H20" s="254"/>
+      <c r="I20" s="254"/>
+      <c r="J20" s="254"/>
+      <c r="K20" s="254"/>
+      <c r="L20" s="254"/>
+      <c r="M20" s="254"/>
+      <c r="N20" s="210"/>
     </row>
     <row r="21" spans="5:19" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="5:19" x14ac:dyDescent="0.2">
@@ -12689,13 +12740,13 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="230" t="s">
+      <c r="J2" s="250" t="s">
         <v>434</v>
       </c>
     </row>
@@ -12709,11 +12760,11 @@
       <c r="G3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="J3" s="230"/>
+      <c r="J3" s="250"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -12735,11 +12786,11 @@
       <c r="G4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="J4" s="230"/>
+      <c r="J4" s="250"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -13062,23 +13113,23 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="E16" s="238" t="s">
+      <c r="E16" s="258" t="s">
         <v>516</v>
       </c>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
+      <c r="F16" s="259"/>
+      <c r="G16" s="259"/>
+      <c r="H16" s="259"/>
+      <c r="I16" s="259"/>
+      <c r="J16" s="259"/>
     </row>
     <row r="17" spans="4:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="110"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
+      <c r="E17" s="259"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
+      <c r="J17" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -13447,14 +13498,14 @@
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="EA1" s="224" t="s">
+      <c r="EA1" s="244" t="s">
         <v>492</v>
       </c>
-      <c r="EB1" s="224"/>
-      <c r="EC1" s="224"/>
-      <c r="ED1" s="224"/>
-      <c r="EE1" s="224"/>
-      <c r="EF1" s="224"/>
+      <c r="EB1" s="244"/>
+      <c r="EC1" s="244"/>
+      <c r="ED1" s="244"/>
+      <c r="EE1" s="244"/>
+      <c r="EF1" s="244"/>
     </row>
     <row r="2" spans="1:136" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
@@ -13531,7 +13582,7 @@
     <row r="1" spans="1:16" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="214" t="s">
+      <c r="C1" s="211" t="s">
         <v>507</v>
       </c>
       <c r="D1" s="7"/>
@@ -13576,20 +13627,20 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="245" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="227"/>
-      <c r="J4" s="225" t="s">
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="245" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="M4" s="226"/>
-      <c r="N4" s="227"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="247"/>
       <c r="O4" s="30" t="s">
         <v>29</v>
       </c>
@@ -15188,16 +15239,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
-      <c r="B1" s="229" t="s">
+      <c r="B1" s="249" t="s">
         <v>439</v>
       </c>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
+      <c r="C1" s="249"/>
+      <c r="D1" s="249"/>
+      <c r="E1" s="249"/>
+      <c r="F1" s="249"/>
+      <c r="G1" s="249"/>
+      <c r="H1" s="249"/>
+      <c r="I1" s="249"/>
       <c r="AC1" s="106"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
@@ -15218,7 +15269,7 @@
       <c r="G2" s="102" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="228" t="s">
+      <c r="H2" s="248" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="101" t="s">
@@ -15263,7 +15314,7 @@
       <c r="V2" s="101" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="228" t="s">
+      <c r="W2" s="248" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="102" t="s">
@@ -15278,7 +15329,7 @@
       <c r="AA2" s="102" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="228" t="s">
+      <c r="AB2" s="248" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="98" t="s">
@@ -15308,7 +15359,7 @@
       <c r="AK2" s="98" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="228" t="s">
+      <c r="AL2" s="248" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="98" t="s">
@@ -15350,7 +15401,7 @@
       <c r="AY2" s="98" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="228" t="s">
+      <c r="AZ2" s="248" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="97" t="s">
@@ -15380,7 +15431,7 @@
       <c r="BI2" s="97" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="228" t="s">
+      <c r="BJ2" s="248" t="s">
         <v>428</v>
       </c>
     </row>
@@ -15394,7 +15445,7 @@
       <c r="G3" s="102" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="228"/>
+      <c r="H3" s="248"/>
       <c r="I3" s="101" t="s">
         <v>426</v>
       </c>
@@ -15435,7 +15486,7 @@
       <c r="V3" s="101" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="228"/>
+      <c r="W3" s="248"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
         <v>413</v>
@@ -15446,7 +15497,7 @@
       <c r="AA3" s="102" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="228"/>
+      <c r="AB3" s="248"/>
       <c r="AC3" s="98" t="s">
         <v>410</v>
       </c>
@@ -15474,7 +15525,7 @@
       <c r="AK3" s="98" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="228"/>
+      <c r="AL3" s="248"/>
       <c r="AM3" s="98" t="s">
         <v>403</v>
       </c>
@@ -15514,7 +15565,7 @@
       <c r="AY3" s="98" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="228"/>
+      <c r="AZ3" s="248"/>
       <c r="BA3" s="97" t="s">
         <v>390</v>
       </c>
@@ -15542,7 +15593,7 @@
       <c r="BI3" s="97" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="228"/>
+      <c r="BJ3" s="248"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
@@ -15564,7 +15615,7 @@
       <c r="G4" s="102" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="228"/>
+      <c r="H4" s="248"/>
       <c r="I4" s="101" t="s">
         <v>376</v>
       </c>
@@ -15607,7 +15658,7 @@
       <c r="V4" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="228"/>
+      <c r="W4" s="248"/>
       <c r="X4" s="99" t="s">
         <v>362</v>
       </c>
@@ -15620,7 +15671,7 @@
       <c r="AA4" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="228"/>
+      <c r="AB4" s="248"/>
       <c r="AC4" s="98" t="s">
         <v>358</v>
       </c>
@@ -15648,7 +15699,7 @@
       <c r="AK4" s="98" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="228"/>
+      <c r="AL4" s="248"/>
       <c r="AM4" s="98" t="s">
         <v>350</v>
       </c>
@@ -15688,7 +15739,7 @@
       <c r="AY4" s="98" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="228"/>
+      <c r="AZ4" s="248"/>
       <c r="BA4" s="97" t="s">
         <v>337</v>
       </c>
@@ -15716,7 +15767,7 @@
       <c r="BI4" s="97" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="228"/>
+      <c r="BJ4" s="248"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
@@ -16694,7 +16745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
         <v>233</v>
       </c>
@@ -17406,16 +17457,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="231" t="s">
+      <c r="B1" s="251" t="s">
         <v>439</v>
       </c>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
+      <c r="G1" s="251"/>
+      <c r="H1" s="251"/>
+      <c r="I1" s="251"/>
     </row>
     <row r="2" spans="1:62" s="112" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="158"/>
@@ -17427,7 +17478,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="250" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -17472,7 +17523,7 @@
       <c r="V2" s="154" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="230" t="s">
+      <c r="W2" s="250" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -17487,7 +17538,7 @@
       <c r="AA2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="230" t="s">
+      <c r="AB2" s="250" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -17517,7 +17568,7 @@
       <c r="AK2" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="230" t="s">
+      <c r="AL2" s="250" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -17559,7 +17610,7 @@
       <c r="AY2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="230" t="s">
+      <c r="AZ2" s="250" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -17589,7 +17640,7 @@
       <c r="BI2" s="151" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="230" t="s">
+      <c r="BJ2" s="250" t="s">
         <v>428</v>
       </c>
     </row>
@@ -17603,7 +17654,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="230"/>
+      <c r="H3" s="250"/>
       <c r="I3" s="154" t="s">
         <v>426</v>
       </c>
@@ -17644,7 +17695,7 @@
       <c r="V3" s="154" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="230"/>
+      <c r="W3" s="250"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>413</v>
@@ -17655,7 +17706,7 @@
       <c r="AA3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="230"/>
+      <c r="AB3" s="250"/>
       <c r="AC3" s="152" t="s">
         <v>410</v>
       </c>
@@ -17683,7 +17734,7 @@
       <c r="AK3" s="152" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="230"/>
+      <c r="AL3" s="250"/>
       <c r="AM3" s="152" t="s">
         <v>403</v>
       </c>
@@ -17723,7 +17774,7 @@
       <c r="AY3" s="152" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="230"/>
+      <c r="AZ3" s="250"/>
       <c r="BA3" s="151" t="s">
         <v>390</v>
       </c>
@@ -17751,7 +17802,7 @@
       <c r="BI3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="230"/>
+      <c r="BJ3" s="250"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
@@ -17773,7 +17824,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="230"/>
+      <c r="H4" s="250"/>
       <c r="I4" s="154" t="s">
         <v>376</v>
       </c>
@@ -17816,7 +17867,7 @@
       <c r="V4" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="230"/>
+      <c r="W4" s="250"/>
       <c r="X4" s="153" t="s">
         <v>362</v>
       </c>
@@ -17829,7 +17880,7 @@
       <c r="AA4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="230"/>
+      <c r="AB4" s="250"/>
       <c r="AC4" s="152" t="s">
         <v>358</v>
       </c>
@@ -17857,7 +17908,7 @@
       <c r="AK4" s="152" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="230"/>
+      <c r="AL4" s="250"/>
       <c r="AM4" s="152" t="s">
         <v>350</v>
       </c>
@@ -17897,7 +17948,7 @@
       <c r="AY4" s="152" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="230"/>
+      <c r="AZ4" s="250"/>
       <c r="BA4" s="151" t="s">
         <v>337</v>
       </c>
@@ -17925,7 +17976,7 @@
       <c r="BI4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="230"/>
+      <c r="BJ4" s="250"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1867FA-6BD2-604C-AC39-EE3945E7A4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E1AFE1-6CA2-E94C-AACA-7E3E27C0DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -2688,16 +2688,76 @@
     </r>
   </si>
   <si>
-    <t>→ Sélectionner la juridiction souhaitée à partir du menu déroulant qui se trouve dans la cellule D5 identifiée en orange.</t>
+    <t>#! HYPERLINK firstLink.label firstLink.url</t>
+  </si>
+  <si>
+    <t>#! HYPERLINK secondLink.label secondLink.url</t>
+  </si>
+  <si>
+    <t>#! HYPERLINK thirdLink.label thirdLink.url</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">→ Sélectionner la juridiction souhaitée à partir du menu déroulant qui se trouve dans la cellule D5 identifiée en </t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2D46E0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→ Sélectionner la juridiction souhaitée à partir du menu déroulant qui se trouve dans la cellule D5 identifiée en</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
+        <sz val="12"/>
+        <color rgb="FF860000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>orange.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2D46E0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→ Sélectionner la juridiction souhaitée à partir du menu déroulant qui se trouve dans la cellule D5 identifiée en</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF860000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <color theme="5"/>
         <rFont val="Calibri (Corps)"/>
       </rPr>
@@ -2706,7 +2766,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
+        <sz val="12"/>
         <color rgb="FF860000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -2714,15 +2774,6 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <t>#! HYPERLINK firstLink.label firstLink.url</t>
-  </si>
-  <si>
-    <t>#! HYPERLINK secondLink.label secondLink.url</t>
-  </si>
-  <si>
-    <t>#! HYPERLINK thirdLink.label thirdLink.url</t>
   </si>
 </sst>
 </file>
@@ -2737,9 +2788,16 @@
     <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
     <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3009,14 +3067,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="22"/>
       <color theme="0"/>
@@ -3037,20 +3087,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF860000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="5"/>
-      <name val="Calibri (Corps)"/>
     </font>
     <font>
       <b/>
@@ -3075,8 +3111,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF860000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2D46E0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri (Corps)"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3209,8 +3290,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE64B85"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D46E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B0B97"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F02D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B252"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="46">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -3576,15 +3693,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color rgb="FFFF0000"/>
@@ -3724,16 +3832,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3741,7 +3848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3750,61 +3857,61 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3817,287 +3924,520 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="9" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyProtection="1">
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="9" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="9" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="9" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="19" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="18" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
@@ -4105,269 +4445,36 @@
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="13" borderId="15" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="37" fillId="20" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="28" fillId="10" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="11" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="19" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="18" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="9" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="9" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="8" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="20" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4393,66 +4500,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="4" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="40" xfId="6" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4464,106 +4556,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{C877C5E8-FCBF-114F-9ECB-F75EF7C9C0EB}"/>
-    <cellStyle name="Lien hypertexte" xfId="6" builtinId="8"/>
     <cellStyle name="Milliers" xfId="3" builtinId="3"/>
     <cellStyle name="Milliers 2" xfId="5" xr:uid="{C98A9282-6AC5-784B-80AA-54BB74A59302}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4588,6 +4706,16 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF01A94F"/>
+      <color rgb="FFF7EF2D"/>
+      <color rgb="FFFE0000"/>
+      <color rgb="FF0B0B97"/>
+      <color rgb="FF2C45E0"/>
+      <color rgb="FFCE4275"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -5349,11 +5477,11 @@
       <c r="B1" s="197" t="s">
         <v>494</v>
       </c>
-      <c r="C1" s="225" t="s">
+      <c r="C1" s="220" t="s">
         <v>495</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
       <c r="F1" s="198"/>
       <c r="H1" s="28" t="s">
         <v>0</v>
@@ -5362,11 +5490,11 @@
     <row r="2" spans="1:8" s="202" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="221" t="s">
         <v>496</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
       <c r="F2" s="201"/>
       <c r="H2" s="28" t="s">
         <v>0</v>
@@ -5390,143 +5518,143 @@
       <c r="D4" s="207" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="232" t="s">
+      <c r="E4" s="227" t="s">
         <v>500</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="221"/>
+      <c r="F4" s="228"/>
+      <c r="G4" s="216"/>
       <c r="H4" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="248" t="s">
         <v>501</v>
       </c>
-      <c r="C5" s="215" t="s">
+      <c r="C5" s="213" t="s">
         <v>502</v>
       </c>
-      <c r="D5" s="215" t="s">
+      <c r="D5" s="213" t="s">
         <v>503</v>
       </c>
-      <c r="E5" s="234" t="s">
-        <v>518</v>
-      </c>
-      <c r="F5" s="235"/>
-      <c r="G5" s="220"/>
+      <c r="E5" s="229" t="s">
+        <v>516</v>
+      </c>
+      <c r="F5" s="230"/>
+      <c r="G5" s="215"/>
       <c r="H5" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
-      <c r="B6" s="216" t="s">
+      <c r="B6" s="249" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="217" t="s">
+      <c r="C6" s="214" t="s">
         <v>505</v>
       </c>
-      <c r="D6" s="217" t="s">
+      <c r="D6" s="214" t="s">
         <v>506</v>
       </c>
-      <c r="E6" s="236" t="s">
-        <v>519</v>
-      </c>
-      <c r="F6" s="237"/>
-      <c r="G6" s="220"/>
+      <c r="E6" s="231" t="s">
+        <v>517</v>
+      </c>
+      <c r="F6" s="232"/>
+      <c r="G6" s="215"/>
       <c r="H6" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="250" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="217" t="s">
+      <c r="C7" s="214" t="s">
         <v>508</v>
       </c>
-      <c r="D7" s="217" t="s">
+      <c r="D7" s="214" t="s">
         <v>509</v>
       </c>
-      <c r="E7" s="236" t="s">
-        <v>518</v>
-      </c>
-      <c r="F7" s="237"/>
-      <c r="G7" s="220"/>
+      <c r="E7" s="231" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" s="232"/>
+      <c r="G7" s="215"/>
       <c r="H7" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
-      <c r="B8" s="218" t="s">
+      <c r="B8" s="251" t="s">
         <v>510</v>
       </c>
-      <c r="C8" s="227" t="s">
+      <c r="C8" s="222" t="s">
         <v>511</v>
       </c>
-      <c r="D8" s="227" t="s">
+      <c r="D8" s="222" t="s">
         <v>512</v>
       </c>
-      <c r="E8" s="238" t="s">
-        <v>520</v>
-      </c>
-      <c r="F8" s="239"/>
-      <c r="G8" s="220"/>
+      <c r="E8" s="233" t="s">
+        <v>518</v>
+      </c>
+      <c r="F8" s="234"/>
+      <c r="G8" s="215"/>
       <c r="H8" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
-      <c r="B9" s="218" t="s">
+      <c r="B9" s="252" t="s">
         <v>513</v>
       </c>
-      <c r="C9" s="227"/>
-      <c r="D9" s="227"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="220"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="215"/>
       <c r="H9" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
-      <c r="B10" s="219" t="s">
+      <c r="B10" s="253" t="s">
         <v>514</v>
       </c>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="220"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="215"/>
       <c r="H10" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="28" customFormat="1" ht="5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="203"/>
-      <c r="B11" s="224"/>
-      <c r="C11" s="224"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="224"/>
+      <c r="B11" s="219"/>
+      <c r="C11" s="219"/>
+      <c r="D11" s="219"/>
+      <c r="E11" s="219"/>
+      <c r="F11" s="219"/>
       <c r="H11" s="28" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="28" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="203"/>
-      <c r="B12" s="222"/>
-      <c r="C12" s="231" t="s">
+      <c r="B12" s="217"/>
+      <c r="C12" s="226" t="s">
         <v>515</v>
       </c>
-      <c r="D12" s="231"/>
-      <c r="E12" s="231"/>
-      <c r="F12" s="223"/>
+      <c r="D12" s="226"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="218"/>
       <c r="H12" s="28" t="s">
         <v>0</v>
       </c>
@@ -5539,14 +5667,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="229" t="s">
+      <c r="A14" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="229"/>
-      <c r="C14" s="229"/>
-      <c r="D14" s="229"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="230"/>
+      <c r="B14" s="224"/>
+      <c r="C14" s="224"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="225"/>
       <c r="H14" s="28" t="s">
         <v>0</v>
       </c>
@@ -5570,14 +5698,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F10"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B5" location="'ETPT A-JUST'!A1" display="ETPT A-JUST" xr:uid="{A4B55920-38FE-8C44-A223-5786C8919747}"/>
-    <hyperlink ref="B6" location="'ETPT Format DDG'!A1" display="ETPT Format DDG" xr:uid="{79FC5922-FC41-BA4A-995C-9841D25952FF}"/>
-    <hyperlink ref="B7" location="'Agrégats DDG'!A1" display="Agrégats DDG" xr:uid="{81D3F220-88AB-F743-B1AC-13451DEA3C28}"/>
-    <hyperlink ref="B8" location="ETPT_TJ_DDG!A1" display="ETPT_TJ_DDG" xr:uid="{43523AD2-5123-C849-8EFA-27E13C4C136A}"/>
-    <hyperlink ref="B9" location="ETPT_TPRX_DDG!A1" display="ETPT_TPRX-DDG" xr:uid="{97476A23-C1B3-284C-B5B5-53A729579959}"/>
-    <hyperlink ref="B10" location="ETPT_CPH_DDG!A1" display="ETPT_CPH_DDG" xr:uid="{1F598F93-AFA2-E243-9BD5-6F6F6C8A32A5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <drawing r:id="rId1"/>
@@ -5599,16 +5719,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="252" t="s">
+      <c r="A1" s="247" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="252"/>
-      <c r="C1" s="252"/>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="252"/>
-      <c r="H1" s="252"/>
+      <c r="B1" s="247"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="247"/>
+      <c r="E1" s="247"/>
+      <c r="F1" s="247"/>
+      <c r="G1" s="247"/>
+      <c r="H1" s="247"/>
       <c r="I1" s="112"/>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -5647,7 +5767,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -5680,13 +5800,13 @@
       <c r="R2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="S2" s="250" t="s">
+      <c r="S2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="250" t="s">
+      <c r="U2" s="245" t="s">
         <v>434</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -5716,7 +5836,7 @@
       <c r="AD2" s="155" t="s">
         <v>433</v>
       </c>
-      <c r="AE2" s="250" t="s">
+      <c r="AE2" s="245" t="s">
         <v>482</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -5728,7 +5848,7 @@
       <c r="AH2" s="155" t="s">
         <v>481</v>
       </c>
-      <c r="AI2" s="250" t="s">
+      <c r="AI2" s="245" t="s">
         <v>480</v>
       </c>
     </row>
@@ -5742,7 +5862,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="155" t="s">
         <v>479</v>
       </c>
@@ -5773,11 +5893,11 @@
       <c r="R3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="S3" s="250"/>
+      <c r="S3" s="245"/>
       <c r="T3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="U3" s="250"/>
+      <c r="U3" s="245"/>
       <c r="V3" s="155" t="s">
         <v>470</v>
       </c>
@@ -5805,7 +5925,7 @@
       <c r="AD3" s="155" t="s">
         <v>462</v>
       </c>
-      <c r="AE3" s="250"/>
+      <c r="AE3" s="245"/>
       <c r="AF3" s="155" t="s">
         <v>461</v>
       </c>
@@ -5815,7 +5935,7 @@
       <c r="AH3" s="155" t="s">
         <v>391</v>
       </c>
-      <c r="AI3" s="250"/>
+      <c r="AI3" s="245"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -5837,7 +5957,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="155" t="s">
         <v>460</v>
       </c>
@@ -5868,11 +5988,11 @@
       <c r="R4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="S4" s="250"/>
+      <c r="S4" s="245"/>
       <c r="T4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="U4" s="250"/>
+      <c r="U4" s="245"/>
       <c r="V4" s="155" t="s">
         <v>451</v>
       </c>
@@ -5900,7 +6020,7 @@
       <c r="AD4" s="155" t="s">
         <v>443</v>
       </c>
-      <c r="AE4" s="250"/>
+      <c r="AE4" s="245"/>
       <c r="AF4" s="155" t="s">
         <v>442</v>
       </c>
@@ -5910,7 +6030,7 @@
       <c r="AH4" s="155" t="s">
         <v>338</v>
       </c>
-      <c r="AI4" s="250"/>
+      <c r="AI4" s="245"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -7014,13 +7134,13 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="250" t="s">
+      <c r="J2" s="245" t="s">
         <v>434</v>
       </c>
     </row>
@@ -7034,11 +7154,11 @@
       <c r="G3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="J3" s="250"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -7060,11 +7180,11 @@
       <c r="G4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="J4" s="250"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -7363,9 +7483,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2925AE-B1C3-2143-BED8-865F5DD872E0}">
   <sheetPr codeName="Feuil9">
-    <tabColor rgb="FFC00000"/>
+    <tabColor rgb="FFFE0000"/>
   </sheetPr>
-  <dimension ref="A1:BK23"/>
+  <dimension ref="A1:BK21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="108" hidden="1" customWidth="1"/>
@@ -7463,7 +7583,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -7508,7 +7628,7 @@
       <c r="V2" s="154" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="250" t="s">
+      <c r="W2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -7523,7 +7643,7 @@
       <c r="AA2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="250" t="s">
+      <c r="AB2" s="245" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -7553,7 +7673,7 @@
       <c r="AK2" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="250" t="s">
+      <c r="AL2" s="245" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -7595,7 +7715,7 @@
       <c r="AY2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="250" t="s">
+      <c r="AZ2" s="245" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -7625,7 +7745,7 @@
       <c r="BI2" s="151" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="250" t="s">
+      <c r="BJ2" s="245" t="s">
         <v>428</v>
       </c>
       <c r="BK2"/>
@@ -7640,7 +7760,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="154" t="s">
         <v>426</v>
       </c>
@@ -7681,7 +7801,7 @@
       <c r="V3" s="154" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="250"/>
+      <c r="W3" s="245"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>413</v>
@@ -7692,7 +7812,7 @@
       <c r="AA3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="250"/>
+      <c r="AB3" s="245"/>
       <c r="AC3" s="152" t="s">
         <v>410</v>
       </c>
@@ -7720,7 +7840,7 @@
       <c r="AK3" s="152" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="250"/>
+      <c r="AL3" s="245"/>
       <c r="AM3" s="152" t="s">
         <v>403</v>
       </c>
@@ -7760,7 +7880,7 @@
       <c r="AY3" s="152" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="250"/>
+      <c r="AZ3" s="245"/>
       <c r="BA3" s="151" t="s">
         <v>390</v>
       </c>
@@ -7788,7 +7908,7 @@
       <c r="BI3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="250"/>
+      <c r="BJ3" s="245"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
@@ -7810,7 +7930,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="154" t="s">
         <v>376</v>
       </c>
@@ -7853,7 +7973,7 @@
       <c r="V4" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="250"/>
+      <c r="W4" s="245"/>
       <c r="X4" s="153" t="s">
         <v>362</v>
       </c>
@@ -7866,7 +7986,7 @@
       <c r="AA4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="250"/>
+      <c r="AB4" s="245"/>
       <c r="AC4" s="152" t="s">
         <v>358</v>
       </c>
@@ -7894,7 +8014,7 @@
       <c r="AK4" s="152" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="250"/>
+      <c r="AL4" s="245"/>
       <c r="AM4" s="152" t="s">
         <v>350</v>
       </c>
@@ -7934,7 +8054,7 @@
       <c r="AY4" s="152" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="250"/>
+      <c r="AZ4" s="245"/>
       <c r="BA4" s="151" t="s">
         <v>337</v>
       </c>
@@ -7962,7 +8082,7 @@
       <c r="BI4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="250"/>
+      <c r="BJ4" s="245"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -7971,7 +8091,7 @@
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
-      <c r="D5" s="212"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
         <v>328</v>
       </c>
@@ -8183,7 +8303,7 @@
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
-      <c r="D6" s="213" t="str">
+      <c r="D6" s="212" t="str">
         <f t="shared" ref="D6:D15" si="6">IF(ISBLANK($D$5),"",$D$5)</f>
         <v/>
       </c>
@@ -8397,7 +8517,7 @@
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
-      <c r="D7" s="213" t="str">
+      <c r="D7" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8611,7 +8731,7 @@
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
-      <c r="D8" s="213" t="str">
+      <c r="D8" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8825,7 +8945,7 @@
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
-      <c r="D9" s="213" t="str">
+      <c r="D9" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9039,7 +9159,7 @@
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
-      <c r="D10" s="213" t="str">
+      <c r="D10" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9253,7 +9373,7 @@
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
-      <c r="D11" s="213" t="str">
+      <c r="D11" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9467,7 +9587,7 @@
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
-      <c r="D12" s="213" t="str">
+      <c r="D12" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9681,7 +9801,7 @@
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
-      <c r="D13" s="213" t="str">
+      <c r="D13" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -9895,7 +10015,7 @@
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
-      <c r="D14" s="213" t="str">
+      <c r="D14" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10109,7 +10229,7 @@
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
-      <c r="D15" s="213" t="str">
+      <c r="D15" s="212" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10551,97 +10671,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:62" s="112" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="116"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="113"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113"/>
-      <c r="O17" s="113"/>
-      <c r="P17" s="113"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="113"/>
-      <c r="S17" s="113"/>
-      <c r="T17" s="113"/>
-      <c r="U17" s="113"/>
-      <c r="V17" s="113"/>
-      <c r="W17" s="113"/>
-      <c r="X17" s="113"/>
-      <c r="Y17" s="113"/>
-      <c r="Z17" s="113"/>
-      <c r="AA17" s="113"/>
-      <c r="AB17" s="113"/>
-      <c r="AC17" s="113"/>
-      <c r="AD17" s="113"/>
-      <c r="AE17" s="113"/>
-      <c r="AF17" s="113"/>
-      <c r="AG17" s="113"/>
-      <c r="AH17" s="113"/>
-      <c r="AI17" s="113"/>
-      <c r="AJ17" s="113"/>
-      <c r="AK17" s="113"/>
-      <c r="AL17" s="113"/>
-      <c r="AM17" s="113"/>
-      <c r="AN17" s="113"/>
-      <c r="AO17" s="113"/>
-      <c r="AP17" s="113"/>
-      <c r="AQ17" s="113"/>
-      <c r="AR17" s="113"/>
-      <c r="AS17" s="113"/>
-      <c r="AT17" s="113"/>
-      <c r="AU17" s="113"/>
-      <c r="AV17" s="113"/>
-      <c r="AW17" s="113"/>
-      <c r="AX17" s="113"/>
-      <c r="AY17" s="113"/>
-      <c r="AZ17" s="113"/>
-      <c r="BA17" s="113"/>
-      <c r="BB17" s="113"/>
-      <c r="BC17" s="113"/>
-      <c r="BD17" s="113"/>
-      <c r="BE17" s="113"/>
-      <c r="BF17" s="113"/>
-      <c r="BG17" s="113"/>
-      <c r="BH17" s="113"/>
-      <c r="BI17" s="113"/>
-      <c r="BJ17" s="113"/>
-    </row>
-    <row r="18" spans="1:62" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="W18" s="111"/>
-      <c r="AZ18" s="111"/>
-    </row>
-    <row r="19" spans="1:62" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="253" t="s">
+    <row r="17" spans="4:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="W17" s="111"/>
+      <c r="AZ17" s="111"/>
+    </row>
+    <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="258" t="s">
         <v>440</v>
       </c>
-      <c r="F19" s="254"/>
-      <c r="G19" s="254"/>
-      <c r="H19" s="254"/>
-      <c r="I19" s="254"/>
-      <c r="J19" s="254"/>
-      <c r="K19" s="254"/>
-      <c r="L19" s="254"/>
-      <c r="M19" s="255"/>
-    </row>
-    <row r="20" spans="1:62" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="AH22" s="109"/>
-    </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="E23" s="110"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="261"/>
+    </row>
+    <row r="19" spans="4:52" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="4:52" x14ac:dyDescent="0.2">
+      <c r="AH20" s="109"/>
+    </row>
+    <row r="21" spans="4:52" x14ac:dyDescent="0.2">
+      <c r="E21" s="110"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E19:M19"/>
+  <mergeCells count="6">
     <mergeCell ref="BJ2:BJ4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="W2:W4"/>
@@ -10657,9 +10709,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B695F461-4586-D34F-8E14-1071CB20CB72}">
   <sheetPr codeName="Feuil15">
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FFF7EF2D"/>
   </sheetPr>
-  <dimension ref="A1:BJ23"/>
+  <dimension ref="A1:BJ21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="11" style="108" hidden="1" customWidth="1"/>
@@ -10746,7 +10798,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -10779,13 +10831,13 @@
       <c r="R2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="S2" s="250" t="s">
+      <c r="S2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="250" t="s">
+      <c r="U2" s="245" t="s">
         <v>434</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -10815,7 +10867,7 @@
       <c r="AD2" s="155" t="s">
         <v>433</v>
       </c>
-      <c r="AE2" s="250" t="s">
+      <c r="AE2" s="245" t="s">
         <v>482</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -10827,7 +10879,7 @@
       <c r="AH2" s="155" t="s">
         <v>481</v>
       </c>
-      <c r="AI2" s="250" t="s">
+      <c r="AI2" s="245" t="s">
         <v>480</v>
       </c>
     </row>
@@ -10841,7 +10893,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="155" t="s">
         <v>479</v>
       </c>
@@ -10872,11 +10924,11 @@
       <c r="R3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="S3" s="250"/>
+      <c r="S3" s="245"/>
       <c r="T3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="U3" s="250"/>
+      <c r="U3" s="245"/>
       <c r="V3" s="155" t="s">
         <v>470</v>
       </c>
@@ -10904,7 +10956,7 @@
       <c r="AD3" s="155" t="s">
         <v>462</v>
       </c>
-      <c r="AE3" s="250"/>
+      <c r="AE3" s="245"/>
       <c r="AF3" s="155" t="s">
         <v>461</v>
       </c>
@@ -10914,7 +10966,7 @@
       <c r="AH3" s="155" t="s">
         <v>391</v>
       </c>
-      <c r="AI3" s="250"/>
+      <c r="AI3" s="245"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -10936,7 +10988,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="155" t="s">
         <v>460</v>
       </c>
@@ -10967,11 +11019,11 @@
       <c r="R4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="S4" s="250"/>
+      <c r="S4" s="245"/>
       <c r="T4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="U4" s="250"/>
+      <c r="U4" s="245"/>
       <c r="V4" s="155" t="s">
         <v>451</v>
       </c>
@@ -10999,7 +11051,7 @@
       <c r="AD4" s="155" t="s">
         <v>443</v>
       </c>
-      <c r="AE4" s="250"/>
+      <c r="AE4" s="245"/>
       <c r="AF4" s="155" t="s">
         <v>442</v>
       </c>
@@ -11009,7 +11061,7 @@
       <c r="AH4" s="155" t="s">
         <v>338</v>
       </c>
-      <c r="AI4" s="250"/>
+      <c r="AI4" s="245"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -12597,45 +12649,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:19" x14ac:dyDescent="0.2">
       <c r="S17" s="111"/>
     </row>
-    <row r="18" spans="5:19" ht="21" x14ac:dyDescent="0.25">
-      <c r="E18" s="256" t="s">
-        <v>517</v>
-      </c>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
-      <c r="M18" s="257"/>
-    </row>
-    <row r="19" spans="5:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="5:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="253" t="s">
+    <row r="18" spans="4:19" x14ac:dyDescent="0.2">
+      <c r="D18" s="255" t="s">
+        <v>520</v>
+      </c>
+      <c r="E18" s="256"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="4:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="257"/>
+      <c r="E19" s="256"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="256"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="256"/>
+      <c r="J19" s="256"/>
+      <c r="K19" s="256"/>
+    </row>
+    <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="258" t="s">
         <v>440</v>
       </c>
-      <c r="F20" s="254"/>
-      <c r="G20" s="254"/>
-      <c r="H20" s="254"/>
-      <c r="I20" s="254"/>
-      <c r="J20" s="254"/>
-      <c r="K20" s="254"/>
-      <c r="L20" s="254"/>
-      <c r="M20" s="254"/>
-      <c r="N20" s="210"/>
-    </row>
-    <row r="21" spans="5:19" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.2">
-      <c r="F23" s="110"/>
-    </row>
+      <c r="E20" s="259"/>
+      <c r="F20" s="260"/>
+      <c r="G20" s="260"/>
+      <c r="H20" s="260"/>
+      <c r="I20" s="260"/>
+      <c r="J20" s="261"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="4:19" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E20:M20"/>
+  <mergeCells count="5">
     <mergeCell ref="AI2:AI4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="S2:S4"/>
@@ -12650,7 +12703,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70C2B6A9-5FC7-3A43-BF37-0B81E3F33F51}">
   <sheetPr codeName="Feuil16">
-    <tabColor rgb="FF92D050"/>
+    <tabColor rgb="FF01A94F"/>
   </sheetPr>
   <dimension ref="A1:BJ17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -12740,13 +12793,13 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="250" t="s">
+      <c r="J2" s="245" t="s">
         <v>434</v>
       </c>
     </row>
@@ -12760,11 +12813,11 @@
       <c r="G3" s="155" t="s">
         <v>414</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="J3" s="250"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -12786,11 +12839,11 @@
       <c r="G4" s="155" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="155" t="s">
         <v>359</v>
       </c>
-      <c r="J4" s="250"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -13113,29 +13166,29 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="E16" s="258" t="s">
-        <v>516</v>
-      </c>
-      <c r="F16" s="259"/>
-      <c r="G16" s="259"/>
-      <c r="H16" s="259"/>
-      <c r="I16" s="259"/>
-      <c r="J16" s="259"/>
+      <c r="D16" s="255" t="s">
+        <v>519</v>
+      </c>
+      <c r="E16" s="256"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="4:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="110"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
-      <c r="J17" s="259"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="E16:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13145,7 +13198,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3674A8A-13E9-4EDB-B294-D1FF8F18362C}">
   <sheetPr codeName="Feuil4">
-    <tabColor theme="0"/>
+    <tabColor rgb="FFCE4275"/>
   </sheetPr>
   <dimension ref="A1:DN8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13464,7 +13517,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B89445B-6ECC-4440-B85C-E593AE209933}">
   <sheetPr codeName="Feuil13">
-    <tabColor theme="0"/>
+    <tabColor rgb="FF2C45E0"/>
   </sheetPr>
   <dimension ref="A1:EF4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13498,14 +13551,14 @@
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="EA1" s="244" t="s">
+      <c r="EA1" s="239" t="s">
         <v>492</v>
       </c>
-      <c r="EB1" s="244"/>
-      <c r="EC1" s="244"/>
-      <c r="ED1" s="244"/>
-      <c r="EE1" s="244"/>
-      <c r="EF1" s="244"/>
+      <c r="EB1" s="239"/>
+      <c r="EC1" s="239"/>
+      <c r="ED1" s="239"/>
+      <c r="EE1" s="239"/>
+      <c r="EF1" s="239"/>
     </row>
     <row r="2" spans="1:136" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
@@ -13561,7 +13614,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E893F90-1EC7-764C-B747-7920FCEC73CB}">
   <sheetPr codeName="Feuil18">
-    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
+    <tabColor rgb="FF0B0B97"/>
   </sheetPr>
   <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13582,7 +13635,7 @@
     <row r="1" spans="1:16" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="211" t="s">
+      <c r="C1" s="210" t="s">
         <v>507</v>
       </c>
       <c r="D1" s="7"/>
@@ -13627,20 +13680,20 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="245" t="s">
+      <c r="E4" s="240" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="245" t="s">
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="240" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="246"/>
-      <c r="N4" s="247"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="241"/>
+      <c r="N4" s="242"/>
       <c r="O4" s="30" t="s">
         <v>29</v>
       </c>
@@ -15239,16 +15292,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
-      <c r="B1" s="249" t="s">
+      <c r="B1" s="244" t="s">
         <v>439</v>
       </c>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
-      <c r="G1" s="249"/>
-      <c r="H1" s="249"/>
-      <c r="I1" s="249"/>
+      <c r="C1" s="244"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="244"/>
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
       <c r="AC1" s="106"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
@@ -15269,7 +15322,7 @@
       <c r="G2" s="102" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="248" t="s">
+      <c r="H2" s="243" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="101" t="s">
@@ -15314,7 +15367,7 @@
       <c r="V2" s="101" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="248" t="s">
+      <c r="W2" s="243" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="102" t="s">
@@ -15329,7 +15382,7 @@
       <c r="AA2" s="102" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="248" t="s">
+      <c r="AB2" s="243" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="98" t="s">
@@ -15359,7 +15412,7 @@
       <c r="AK2" s="98" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="248" t="s">
+      <c r="AL2" s="243" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="98" t="s">
@@ -15401,7 +15454,7 @@
       <c r="AY2" s="98" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="248" t="s">
+      <c r="AZ2" s="243" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="97" t="s">
@@ -15431,7 +15484,7 @@
       <c r="BI2" s="97" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="248" t="s">
+      <c r="BJ2" s="243" t="s">
         <v>428</v>
       </c>
     </row>
@@ -15445,7 +15498,7 @@
       <c r="G3" s="102" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="248"/>
+      <c r="H3" s="243"/>
       <c r="I3" s="101" t="s">
         <v>426</v>
       </c>
@@ -15486,7 +15539,7 @@
       <c r="V3" s="101" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="248"/>
+      <c r="W3" s="243"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
         <v>413</v>
@@ -15497,7 +15550,7 @@
       <c r="AA3" s="102" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="248"/>
+      <c r="AB3" s="243"/>
       <c r="AC3" s="98" t="s">
         <v>410</v>
       </c>
@@ -15525,7 +15578,7 @@
       <c r="AK3" s="98" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="248"/>
+      <c r="AL3" s="243"/>
       <c r="AM3" s="98" t="s">
         <v>403</v>
       </c>
@@ -15565,7 +15618,7 @@
       <c r="AY3" s="98" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="248"/>
+      <c r="AZ3" s="243"/>
       <c r="BA3" s="97" t="s">
         <v>390</v>
       </c>
@@ -15593,7 +15646,7 @@
       <c r="BI3" s="97" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="248"/>
+      <c r="BJ3" s="243"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
@@ -15615,7 +15668,7 @@
       <c r="G4" s="102" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="248"/>
+      <c r="H4" s="243"/>
       <c r="I4" s="101" t="s">
         <v>376</v>
       </c>
@@ -15658,7 +15711,7 @@
       <c r="V4" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="248"/>
+      <c r="W4" s="243"/>
       <c r="X4" s="99" t="s">
         <v>362</v>
       </c>
@@ -15671,7 +15724,7 @@
       <c r="AA4" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="248"/>
+      <c r="AB4" s="243"/>
       <c r="AC4" s="98" t="s">
         <v>358</v>
       </c>
@@ -15699,7 +15752,7 @@
       <c r="AK4" s="98" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="248"/>
+      <c r="AL4" s="243"/>
       <c r="AM4" s="98" t="s">
         <v>350</v>
       </c>
@@ -15739,7 +15792,7 @@
       <c r="AY4" s="98" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="248"/>
+      <c r="AZ4" s="243"/>
       <c r="BA4" s="97" t="s">
         <v>337</v>
       </c>
@@ -15767,7 +15820,7 @@
       <c r="BI4" s="97" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="248"/>
+      <c r="BJ4" s="243"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
@@ -17457,16 +17510,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="251" t="s">
+      <c r="B1" s="246" t="s">
         <v>439</v>
       </c>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
     </row>
     <row r="2" spans="1:62" s="112" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="158"/>
@@ -17478,7 +17531,7 @@
       <c r="G2" s="155" t="s">
         <v>438</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -17523,7 +17576,7 @@
       <c r="V2" s="154" t="s">
         <v>436</v>
       </c>
-      <c r="W2" s="250" t="s">
+      <c r="W2" s="245" t="s">
         <v>435</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -17538,7 +17591,7 @@
       <c r="AA2" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="AB2" s="250" t="s">
+      <c r="AB2" s="245" t="s">
         <v>434</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -17568,7 +17621,7 @@
       <c r="AK2" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="AL2" s="250" t="s">
+      <c r="AL2" s="245" t="s">
         <v>432</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -17610,7 +17663,7 @@
       <c r="AY2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AZ2" s="250" t="s">
+      <c r="AZ2" s="245" t="s">
         <v>430</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -17640,7 +17693,7 @@
       <c r="BI2" s="151" t="s">
         <v>429</v>
       </c>
-      <c r="BJ2" s="250" t="s">
+      <c r="BJ2" s="245" t="s">
         <v>428</v>
       </c>
     </row>
@@ -17654,7 +17707,7 @@
       <c r="G3" s="155" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="250"/>
+      <c r="H3" s="245"/>
       <c r="I3" s="154" t="s">
         <v>426</v>
       </c>
@@ -17695,7 +17748,7 @@
       <c r="V3" s="154" t="s">
         <v>414</v>
       </c>
-      <c r="W3" s="250"/>
+      <c r="W3" s="245"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>413</v>
@@ -17706,7 +17759,7 @@
       <c r="AA3" s="155" t="s">
         <v>411</v>
       </c>
-      <c r="AB3" s="250"/>
+      <c r="AB3" s="245"/>
       <c r="AC3" s="152" t="s">
         <v>410</v>
       </c>
@@ -17734,7 +17787,7 @@
       <c r="AK3" s="152" t="s">
         <v>404</v>
       </c>
-      <c r="AL3" s="250"/>
+      <c r="AL3" s="245"/>
       <c r="AM3" s="152" t="s">
         <v>403</v>
       </c>
@@ -17774,7 +17827,7 @@
       <c r="AY3" s="152" t="s">
         <v>391</v>
       </c>
-      <c r="AZ3" s="250"/>
+      <c r="AZ3" s="245"/>
       <c r="BA3" s="151" t="s">
         <v>390</v>
       </c>
@@ -17802,7 +17855,7 @@
       <c r="BI3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="BJ3" s="250"/>
+      <c r="BJ3" s="245"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
@@ -17824,7 +17877,7 @@
       <c r="G4" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="H4" s="250"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="154" t="s">
         <v>376</v>
       </c>
@@ -17867,7 +17920,7 @@
       <c r="V4" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="W4" s="250"/>
+      <c r="W4" s="245"/>
       <c r="X4" s="153" t="s">
         <v>362</v>
       </c>
@@ -17880,7 +17933,7 @@
       <c r="AA4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="AB4" s="250"/>
+      <c r="AB4" s="245"/>
       <c r="AC4" s="152" t="s">
         <v>358</v>
       </c>
@@ -17908,7 +17961,7 @@
       <c r="AK4" s="152" t="s">
         <v>351</v>
       </c>
-      <c r="AL4" s="250"/>
+      <c r="AL4" s="245"/>
       <c r="AM4" s="152" t="s">
         <v>350</v>
       </c>
@@ -17948,7 +18001,7 @@
       <c r="AY4" s="152" t="s">
         <v>338</v>
       </c>
-      <c r="AZ4" s="250"/>
+      <c r="AZ4" s="245"/>
       <c r="BA4" s="151" t="s">
         <v>337</v>
       </c>
@@ -17976,7 +18029,7 @@
       <c r="BI4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="BJ4" s="250"/>
+      <c r="BJ4" s="245"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E1AFE1-6CA2-E94C-AACA-7E3E27C0DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14291D7F-E60F-9247-B097-E13377546AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="520">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>#! DUMP_COLS days1</t>
-  </si>
-  <si>
-    <t>#! DUMP_COLS subtitles1</t>
   </si>
   <si>
     <t>#! FOR_EACH x stats1</t>
@@ -3840,7 +3837,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4547,6 +4544,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4633,51 +4672,6 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="28" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4870,15 +4864,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>80818</xdr:colOff>
+      <xdr:colOff>92364</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>34637</xdr:rowOff>
+      <xdr:rowOff>48382</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1041499</xdr:colOff>
+      <xdr:colOff>1027546</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>912092</xdr:rowOff>
+      <xdr:rowOff>923637</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4901,8 +4895,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="80818" y="34637"/>
-          <a:ext cx="960681" cy="877455"/>
+          <a:off x="92364" y="48382"/>
+          <a:ext cx="935182" cy="875255"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4919,22 +4913,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>40404</xdr:colOff>
+      <xdr:colOff>92360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>34635</xdr:rowOff>
+      <xdr:rowOff>46180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>520744</xdr:colOff>
+      <xdr:colOff>1027043</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>912090</xdr:rowOff>
+      <xdr:rowOff>935179</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 5">
+        <xdr:cNvPr id="11" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92CAA262-EE87-1645-B3B3-39A2AC20B813}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{972ABFF3-CF12-FB44-AC70-9373B08ED323}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4950,8 +4944,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="80808" y="34635"/>
-          <a:ext cx="960680" cy="877455"/>
+          <a:off x="184721" y="46180"/>
+          <a:ext cx="1869366" cy="888999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4968,15 +4962,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>324555</xdr:colOff>
+      <xdr:colOff>239888</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>70555</xdr:rowOff>
+      <xdr:rowOff>28222</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1285236</xdr:colOff>
+      <xdr:colOff>1326444</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>948010</xdr:rowOff>
+      <xdr:rowOff>976232</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4999,8 +4993,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="324555" y="70555"/>
-          <a:ext cx="960681" cy="877455"/>
+          <a:off x="239888" y="28222"/>
+          <a:ext cx="1086556" cy="948010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5475,13 +5469,13 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1" s="233" t="s">
         <v>494</v>
       </c>
-      <c r="C1" s="220" t="s">
-        <v>495</v>
-      </c>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
       <c r="F1" s="198"/>
       <c r="H1" s="28" t="s">
         <v>0</v>
@@ -5490,11 +5484,11 @@
     <row r="2" spans="1:8" s="202" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
-      <c r="C2" s="221" t="s">
-        <v>496</v>
-      </c>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
+      <c r="C2" s="234" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
       <c r="F2" s="201"/>
       <c r="H2" s="28" t="s">
         <v>0</v>
@@ -5510,18 +5504,18 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" s="207" t="s">
         <v>497</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="D4" s="207" t="s">
         <v>498</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="E4" s="240" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="227" t="s">
-        <v>500</v>
-      </c>
-      <c r="F4" s="228"/>
+      <c r="F4" s="241"/>
       <c r="G4" s="216"/>
       <c r="H4" s="28" t="s">
         <v>0</v>
@@ -5529,19 +5523,19 @@
     </row>
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
-      <c r="B5" s="248" t="s">
+      <c r="B5" s="220" t="s">
+        <v>500</v>
+      </c>
+      <c r="C5" s="213" t="s">
         <v>501</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="D5" s="213" t="s">
         <v>502</v>
       </c>
-      <c r="D5" s="213" t="s">
-        <v>503</v>
-      </c>
-      <c r="E5" s="229" t="s">
-        <v>516</v>
-      </c>
-      <c r="F5" s="230"/>
+      <c r="E5" s="242" t="s">
+        <v>515</v>
+      </c>
+      <c r="F5" s="243"/>
       <c r="G5" s="215"/>
       <c r="H5" s="28" t="s">
         <v>0</v>
@@ -5549,19 +5543,19 @@
     </row>
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
-      <c r="B6" s="249" t="s">
+      <c r="B6" s="221" t="s">
+        <v>503</v>
+      </c>
+      <c r="C6" s="214" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="214" t="s">
+      <c r="D6" s="214" t="s">
         <v>505</v>
       </c>
-      <c r="D6" s="214" t="s">
-        <v>506</v>
-      </c>
-      <c r="E6" s="231" t="s">
-        <v>517</v>
-      </c>
-      <c r="F6" s="232"/>
+      <c r="E6" s="244" t="s">
+        <v>516</v>
+      </c>
+      <c r="F6" s="245"/>
       <c r="G6" s="215"/>
       <c r="H6" s="28" t="s">
         <v>0</v>
@@ -5569,19 +5563,19 @@
     </row>
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
-      <c r="B7" s="250" t="s">
+      <c r="B7" s="222" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" s="214" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="214" t="s">
+      <c r="D7" s="214" t="s">
         <v>508</v>
       </c>
-      <c r="D7" s="214" t="s">
-        <v>509</v>
-      </c>
-      <c r="E7" s="231" t="s">
-        <v>516</v>
-      </c>
-      <c r="F7" s="232"/>
+      <c r="E7" s="244" t="s">
+        <v>515</v>
+      </c>
+      <c r="F7" s="245"/>
       <c r="G7" s="215"/>
       <c r="H7" s="28" t="s">
         <v>0</v>
@@ -5589,19 +5583,19 @@
     </row>
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
-      <c r="B8" s="251" t="s">
+      <c r="B8" s="223" t="s">
+        <v>509</v>
+      </c>
+      <c r="C8" s="235" t="s">
         <v>510</v>
       </c>
-      <c r="C8" s="222" t="s">
+      <c r="D8" s="235" t="s">
         <v>511</v>
       </c>
-      <c r="D8" s="222" t="s">
-        <v>512</v>
-      </c>
-      <c r="E8" s="233" t="s">
-        <v>518</v>
-      </c>
-      <c r="F8" s="234"/>
+      <c r="E8" s="246" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" s="247"/>
       <c r="G8" s="215"/>
       <c r="H8" s="28" t="s">
         <v>0</v>
@@ -5609,13 +5603,13 @@
     </row>
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
-      <c r="B9" s="252" t="s">
-        <v>513</v>
-      </c>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="236"/>
+      <c r="B9" s="224" t="s">
+        <v>512</v>
+      </c>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="249"/>
       <c r="G9" s="215"/>
       <c r="H9" s="28" t="s">
         <v>0</v>
@@ -5623,13 +5617,13 @@
     </row>
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
-      <c r="B10" s="253" t="s">
-        <v>514</v>
-      </c>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="238"/>
+      <c r="B10" s="225" t="s">
+        <v>513</v>
+      </c>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="251"/>
       <c r="G10" s="215"/>
       <c r="H10" s="28" t="s">
         <v>0</v>
@@ -5649,11 +5643,11 @@
     <row r="12" spans="1:8" s="28" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
-      <c r="C12" s="226" t="s">
-        <v>515</v>
-      </c>
-      <c r="D12" s="226"/>
-      <c r="E12" s="226"/>
+      <c r="C12" s="239" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="239"/>
+      <c r="E12" s="239"/>
       <c r="F12" s="218"/>
       <c r="H12" s="28" t="s">
         <v>0</v>
@@ -5667,14 +5661,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="224" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="224"/>
-      <c r="C14" s="224"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="224"/>
-      <c r="F14" s="225"/>
+      <c r="A14" s="237" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="237"/>
+      <c r="C14" s="237"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="237"/>
+      <c r="F14" s="238"/>
       <c r="H14" s="28" t="s">
         <v>0</v>
       </c>
@@ -5719,16 +5713,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="247" t="s">
-        <v>483</v>
-      </c>
-      <c r="B1" s="247"/>
-      <c r="C1" s="247"/>
-      <c r="D1" s="247"/>
-      <c r="E1" s="247"/>
-      <c r="F1" s="247"/>
-      <c r="G1" s="247"/>
-      <c r="H1" s="247"/>
+      <c r="A1" s="260" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
       <c r="I1" s="112"/>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -5765,91 +5759,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>436</v>
+      </c>
       <c r="I2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="S2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="S2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="T2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="U2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="U2" s="258" t="s">
+        <v>433</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>433</v>
-      </c>
-      <c r="AE2" s="245" t="s">
-        <v>482</v>
+        <v>432</v>
+      </c>
+      <c r="AE2" s="258" t="s">
+        <v>481</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>481</v>
-      </c>
-      <c r="AI2" s="245" t="s">
         <v>480</v>
+      </c>
+      <c r="AI2" s="258" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5860,181 +5854,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>426</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>414</v>
-      </c>
-      <c r="S3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="U3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>462</v>
-      </c>
-      <c r="AE3" s="245"/>
+        <v>461</v>
+      </c>
+      <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="AI3" s="245"/>
+        <v>390</v>
+      </c>
+      <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>377</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>376</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>363</v>
-      </c>
-      <c r="S4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>359</v>
-      </c>
-      <c r="U4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>443</v>
-      </c>
-      <c r="AE4" s="245"/>
+        <v>442</v>
+      </c>
+      <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>338</v>
-      </c>
-      <c r="AI4" s="245"/>
+        <v>337</v>
+      </c>
+      <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6043,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6150,7 +6144,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6159,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6211,7 +6205,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6220,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6272,7 +6266,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6281,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6345,7 +6339,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6354,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6427,7 +6421,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6436,10 +6430,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6500,7 +6494,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6509,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6573,7 +6567,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6582,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6649,7 +6643,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6658,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6719,7 +6713,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6728,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6832,7 +6826,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6841,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6950,7 +6944,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -7080,7 +7074,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -7115,7 +7109,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7132,16 +7126,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="I2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="J2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="J2" s="258" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7152,43 +7146,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>414</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="J3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>363</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>359</v>
-      </c>
-      <c r="J4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7197,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7221,7 +7215,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7230,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7248,7 +7242,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7257,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7275,7 +7269,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7284,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7302,7 +7296,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7311,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7329,7 +7323,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7338,10 +7332,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7356,7 +7350,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7365,10 +7359,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7383,7 +7377,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7392,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7413,7 +7407,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7422,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7448,7 +7442,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7507,12 +7501,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7581,172 +7575,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>436</v>
+      </c>
       <c r="I2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>436</v>
-      </c>
-      <c r="W2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="W2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="X2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="AB2" s="258" t="s">
+        <v>433</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>433</v>
-      </c>
-      <c r="AL2" s="245" t="s">
         <v>432</v>
       </c>
+      <c r="AL2" s="258" t="s">
+        <v>431</v>
+      </c>
       <c r="AM2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>431</v>
-      </c>
-      <c r="AZ2" s="245" t="s">
         <v>430</v>
       </c>
+      <c r="AZ2" s="258" t="s">
+        <v>429</v>
+      </c>
       <c r="BA2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>429</v>
-      </c>
-      <c r="BJ2" s="245" t="s">
         <v>428</v>
+      </c>
+      <c r="BJ2" s="258" t="s">
+        <v>427</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7758,345 +7752,345 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>426</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>414</v>
-      </c>
-      <c r="W3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AI3" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ3" s="152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>404</v>
-      </c>
-      <c r="AL3" s="245"/>
+        <v>403</v>
+      </c>
+      <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>391</v>
-      </c>
-      <c r="AZ3" s="245"/>
+        <v>390</v>
+      </c>
+      <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>382</v>
-      </c>
-      <c r="BJ3" s="245"/>
+        <v>381</v>
+      </c>
+      <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>377</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>376</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>363</v>
-      </c>
-      <c r="W4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AI4" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>351</v>
-      </c>
-      <c r="AL4" s="245"/>
+        <v>350</v>
+      </c>
+      <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>338</v>
-      </c>
-      <c r="AZ4" s="245"/>
+        <v>337</v>
+      </c>
+      <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>329</v>
-      </c>
-      <c r="BJ4" s="245"/>
+        <v>328</v>
+      </c>
+      <c r="BJ4" s="258"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8299,7 +8293,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8308,10 +8302,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8513,7 +8507,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8522,10 +8516,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8727,7 +8721,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8736,10 +8730,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8941,7 +8935,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8950,10 +8944,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -9155,7 +9149,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -9164,10 +9158,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9369,7 +9363,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9378,10 +9372,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9583,7 +9577,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9592,10 +9586,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9797,7 +9791,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9806,10 +9800,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -10011,7 +10005,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -10020,10 +10014,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10225,7 +10219,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10234,10 +10228,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10444,7 +10438,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10676,14 +10670,14 @@
       <c r="AZ17" s="111"/>
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="258" t="s">
-        <v>440</v>
-      </c>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="261"/>
+      <c r="D18" s="229" t="s">
+        <v>439</v>
+      </c>
+      <c r="E18" s="231"/>
+      <c r="F18" s="231"/>
+      <c r="G18" s="231"/>
+      <c r="H18" s="231"/>
+      <c r="I18" s="232"/>
     </row>
     <row r="19" spans="4:52" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="4:52" x14ac:dyDescent="0.2">
@@ -10722,12 +10716,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10796,91 +10790,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>436</v>
+      </c>
       <c r="I2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="S2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="S2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="T2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="U2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="U2" s="258" t="s">
+        <v>433</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>433</v>
-      </c>
-      <c r="AE2" s="245" t="s">
-        <v>482</v>
+        <v>432</v>
+      </c>
+      <c r="AE2" s="258" t="s">
+        <v>481</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>481</v>
-      </c>
-      <c r="AI2" s="245" t="s">
         <v>480</v>
+      </c>
+      <c r="AI2" s="258" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10891,190 +10885,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>426</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>414</v>
-      </c>
-      <c r="S3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="U3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>462</v>
-      </c>
-      <c r="AE3" s="245"/>
+        <v>461</v>
+      </c>
+      <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="AI3" s="245"/>
+        <v>390</v>
+      </c>
+      <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>377</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>376</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>363</v>
-      </c>
-      <c r="S4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>359</v>
-      </c>
-      <c r="U4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>443</v>
-      </c>
-      <c r="AE4" s="245"/>
+        <v>442</v>
+      </c>
+      <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>338</v>
-      </c>
-      <c r="AI4" s="245"/>
+        <v>337</v>
+      </c>
+      <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11195,7 +11189,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11204,10 +11198,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11328,7 +11322,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11337,10 +11331,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11461,7 +11455,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11470,10 +11464,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11594,7 +11588,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11603,10 +11597,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11727,7 +11721,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11736,10 +11730,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11860,7 +11854,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11869,10 +11863,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -11993,7 +11987,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -12002,10 +11996,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -12126,7 +12120,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12135,10 +12129,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12259,7 +12253,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12268,10 +12262,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12392,7 +12386,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12401,10 +12395,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12530,7 +12524,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12653,10 +12647,10 @@
       <c r="S17" s="111"/>
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
-      <c r="D18" s="255" t="s">
-        <v>520</v>
-      </c>
-      <c r="E18" s="256"/>
+      <c r="D18" s="226" t="s">
+        <v>519</v>
+      </c>
+      <c r="E18" s="227"/>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
@@ -12665,25 +12659,25 @@
       <c r="K18"/>
     </row>
     <row r="19" spans="4:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="257"/>
-      <c r="E19" s="256"/>
-      <c r="F19" s="256"/>
-      <c r="G19" s="256"/>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
+      <c r="D19" s="228"/>
+      <c r="E19" s="227"/>
+      <c r="F19" s="227"/>
+      <c r="G19" s="227"/>
+      <c r="H19" s="227"/>
+      <c r="I19" s="227"/>
+      <c r="J19" s="227"/>
+      <c r="K19" s="227"/>
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="258" t="s">
-        <v>440</v>
-      </c>
-      <c r="E20" s="259"/>
-      <c r="F20" s="260"/>
-      <c r="G20" s="260"/>
-      <c r="H20" s="260"/>
-      <c r="I20" s="260"/>
-      <c r="J20" s="261"/>
+      <c r="D20" s="229" t="s">
+        <v>439</v>
+      </c>
+      <c r="E20" s="230"/>
+      <c r="F20" s="231"/>
+      <c r="G20" s="231"/>
+      <c r="H20" s="231"/>
+      <c r="I20" s="231"/>
+      <c r="J20" s="232"/>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="4:19" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
@@ -12717,12 +12711,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12791,16 +12785,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="I2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="J2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="J2" s="258" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12811,52 +12805,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>414</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="J3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>363</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>359</v>
-      </c>
-      <c r="J4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12877,7 +12871,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12886,10 +12880,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12910,7 +12904,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12919,10 +12913,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12943,7 +12937,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12952,10 +12946,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12976,7 +12970,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12985,10 +12979,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -13009,7 +13003,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13018,10 +13012,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -13042,7 +13036,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13051,10 +13045,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -13075,7 +13069,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13084,10 +13078,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -13108,7 +13102,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13117,10 +13111,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -13146,7 +13140,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -13166,10 +13160,10 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="D16" s="255" t="s">
-        <v>519</v>
-      </c>
-      <c r="E16" s="256"/>
+      <c r="D16" s="226" t="s">
+        <v>518</v>
+      </c>
+      <c r="E16" s="227"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
@@ -13177,7 +13171,7 @@
       <c r="J16" s="23"/>
     </row>
     <row r="17" spans="4:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="254"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
@@ -13215,7 +13209,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13519,11 +13513,11 @@
   <sheetPr codeName="Feuil13">
     <tabColor rgb="FF2C45E0"/>
   </sheetPr>
-  <dimension ref="A1:EF4"/>
+  <dimension ref="A1:EG4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.5" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="126" max="126" width="13.5" customWidth="1"/>
     <col min="127" max="127" width="15.83203125" customWidth="1"/>
     <col min="128" max="128" width="36.1640625" customWidth="1"/>
@@ -13536,9 +13530,9 @@
     <col min="144" max="144" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:136" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13546,55 +13540,55 @@
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="EA1" s="239" t="s">
-        <v>492</v>
-      </c>
-      <c r="EB1" s="239"/>
-      <c r="EC1" s="239"/>
-      <c r="ED1" s="239"/>
-      <c r="EE1" s="239"/>
-      <c r="EF1" s="239"/>
-    </row>
-    <row r="2" spans="1:136" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="EA1" s="252" t="s">
+        <v>491</v>
+      </c>
+      <c r="EB1" s="252"/>
+      <c r="EC1" s="252"/>
+      <c r="ED1" s="252"/>
+      <c r="EE1" s="252"/>
+      <c r="EF1" s="252"/>
+      <c r="EG1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:137" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="EA2" s="194" t="s">
+        <v>34</v>
+      </c>
+      <c r="EB2" s="194" t="s">
+        <v>35</v>
+      </c>
+      <c r="EC2" s="194" t="s">
+        <v>36</v>
+      </c>
+      <c r="ED2" s="194" t="s">
+        <v>37</v>
+      </c>
+      <c r="EE2" s="194" t="s">
+        <v>42</v>
+      </c>
+      <c r="EF2" s="194" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:137" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="EA2" s="194" t="s">
-        <v>35</v>
-      </c>
-      <c r="EB2" s="194" t="s">
-        <v>36</v>
-      </c>
-      <c r="EC2" s="194" t="s">
-        <v>37</v>
-      </c>
-      <c r="ED2" s="194" t="s">
-        <v>38</v>
-      </c>
-      <c r="EE2" s="194" t="s">
-        <v>43</v>
-      </c>
-      <c r="EF2" s="194" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:136" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:136" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:137" x14ac:dyDescent="0.2">
       <c r="B4" s="29" t="s">
         <v>7</v>
       </c>
@@ -13636,7 +13630,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13657,10 +13651,10 @@
     </row>
     <row r="2" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -13668,7 +13662,7 @@
     </row>
     <row r="3" spans="1:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16" t="e">
         <f>VLOOKUP(A3,'codage tribunal'!A:B,2,FALSE)</f>
@@ -13680,22 +13674,22 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="240" t="s">
+      <c r="E4" s="253" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="253" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="240" t="s">
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="255"/>
+      <c r="O4" s="30" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="241"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="30" t="s">
-        <v>29</v>
       </c>
       <c r="P4" t="s">
         <v>0</v>
@@ -13706,49 +13700,49 @@
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
       <c r="E5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="32" t="s">
+      <c r="K5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>32</v>
-      </c>
       <c r="O5" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
       <c r="C6" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="21" t="e">
         <f>SUMIFS(INDEX('ETPT Format DDG'!$A:$DU,,IFERROR(MATCH(D6,'ETPT Format DDG'!$2:$2,0),MATCH(C6,'ETPT Format DDG'!$2:$2,0))),'ETPT Format DDG'!$I:$I,"M-TIT",'ETPT Format DDG'!$C:$C,$A$3)</f>
@@ -13819,7 +13813,7 @@
         <v>#N/A</v>
       </c>
       <c r="P6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -13873,19 +13867,19 @@
   <sheetData>
     <row r="1" spans="1:9" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1"/>
       <c r="D1" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E1"/>
       <c r="G1" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13945,1310 +13939,1310 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B1" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="F1" s="59" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" s="60" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>200</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C2" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="58" t="s">
+      <c r="F2" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E3" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C5" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="41" t="s">
         <v>51</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E7" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E8" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E11" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E17" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="41" t="s">
         <v>47</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="48" t="s">
+      <c r="F22" s="48" t="s">
         <v>70</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E23" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="48" t="s">
         <v>70</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C24" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="E24" s="48" t="s">
+      <c r="F24" s="48" t="s">
         <v>74</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E25" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="48" t="s">
         <v>74</v>
-      </c>
-      <c r="F25" s="48" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="41" t="s">
+      <c r="F26" s="41" t="s">
         <v>78</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E27" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="41" t="s">
         <v>78</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B28" s="41" t="s">
-        <v>172</v>
-      </c>
       <c r="C28" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C29" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="54" t="s">
         <v>82</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="54" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="E30" s="41" t="s">
+      <c r="F30" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="F30" s="46" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E31" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="F31" s="46" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E32" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="F32" s="46" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E33" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="F33" s="46" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E34" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="F34" s="46" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="41" t="s">
         <v>91</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B36" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E36" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="41" t="s">
+      <c r="F36" s="41" t="s">
         <v>94</v>
-      </c>
-      <c r="F36" s="41" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E37" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="41" t="s">
         <v>94</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E38" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="41" t="s">
         <v>94</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E39" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="41" t="s">
         <v>94</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B40" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="41" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="E41" s="48" t="s">
+      <c r="F41" s="48" t="s">
         <v>102</v>
-      </c>
-      <c r="F41" s="48" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C42" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E42" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" s="48" t="s">
         <v>102</v>
-      </c>
-      <c r="F42" s="48" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" s="48" t="s">
         <v>102</v>
-      </c>
-      <c r="F43" s="48" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E44" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="48" t="s">
         <v>102</v>
-      </c>
-      <c r="F44" s="48" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" s="48" t="s">
         <v>107</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="F45" s="48" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C46" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D46" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" s="48" t="s">
+      <c r="F46" s="41" t="s">
         <v>110</v>
-      </c>
-      <c r="F46" s="41" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F47" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B52" s="41" t="s">
-        <v>157</v>
-      </c>
       <c r="C52" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="41" t="s">
         <v>117</v>
-      </c>
-      <c r="D52" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="41" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C53" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E53" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F53" s="42" t="s">
         <v>119</v>
-      </c>
-      <c r="D53" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F53" s="42" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F57" s="41" t="s">
         <v>124</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="E57" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="F57" s="41" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E58" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C59" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F59" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="D59" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F59" s="48" t="s">
-        <v>127</v>
-      </c>
       <c r="G59" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C60" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D60" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E60" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F60" s="48" t="s">
-        <v>129</v>
-      </c>
       <c r="G60" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C61" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D61" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F61" s="48" t="s">
-        <v>131</v>
-      </c>
       <c r="G61" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C62" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E62" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C63" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F63" s="48" t="s">
         <v>133</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E63" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F63" s="48" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>143</v>
-      </c>
       <c r="D64" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E64" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F64" s="46"/>
       <c r="G64" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -15292,16 +15286,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
-      <c r="B1" s="244" t="s">
-        <v>439</v>
-      </c>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
-      <c r="E1" s="244"/>
-      <c r="F1" s="244"/>
-      <c r="G1" s="244"/>
-      <c r="H1" s="244"/>
-      <c r="I1" s="244"/>
+      <c r="B1" s="257" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+      <c r="H1" s="257"/>
+      <c r="I1" s="257"/>
       <c r="AC1" s="106"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
@@ -15320,172 +15314,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" s="243" t="s">
         <v>437</v>
       </c>
+      <c r="H2" s="256" t="s">
+        <v>436</v>
+      </c>
       <c r="I2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>436</v>
-      </c>
-      <c r="W2" s="243" t="s">
         <v>435</v>
       </c>
+      <c r="W2" s="256" t="s">
+        <v>434</v>
+      </c>
       <c r="X2" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB2" s="243" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="AB2" s="256" t="s">
+        <v>433</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>433</v>
-      </c>
-      <c r="AL2" s="243" t="s">
         <v>432</v>
       </c>
+      <c r="AL2" s="256" t="s">
+        <v>431</v>
+      </c>
       <c r="AM2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>431</v>
-      </c>
-      <c r="AZ2" s="243" t="s">
         <v>430</v>
       </c>
+      <c r="AZ2" s="256" t="s">
+        <v>429</v>
+      </c>
       <c r="BA2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>429</v>
-      </c>
-      <c r="BJ2" s="243" t="s">
         <v>428</v>
+      </c>
+      <c r="BJ2" s="256" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15496,360 +15490,360 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="243"/>
+        <v>426</v>
+      </c>
+      <c r="H3" s="256"/>
       <c r="I3" s="101" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="W3" s="243"/>
+        <v>413</v>
+      </c>
+      <c r="W3" s="256"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB3" s="243"/>
+        <v>410</v>
+      </c>
+      <c r="AB3" s="256"/>
       <c r="AC3" s="98" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AI3" s="98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ3" s="98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>404</v>
-      </c>
-      <c r="AL3" s="243"/>
+        <v>403</v>
+      </c>
+      <c r="AL3" s="256"/>
       <c r="AM3" s="98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>391</v>
-      </c>
-      <c r="AZ3" s="243"/>
+        <v>390</v>
+      </c>
+      <c r="AZ3" s="256"/>
       <c r="BA3" s="97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>382</v>
-      </c>
-      <c r="BJ3" s="243"/>
+        <v>381</v>
+      </c>
+      <c r="BJ3" s="256"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>377</v>
-      </c>
-      <c r="H4" s="243"/>
+        <v>376</v>
+      </c>
+      <c r="H4" s="256"/>
       <c r="I4" s="101" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>363</v>
-      </c>
-      <c r="W4" s="243"/>
+        <v>362</v>
+      </c>
+      <c r="W4" s="256"/>
       <c r="X4" s="99" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB4" s="243"/>
+        <v>358</v>
+      </c>
+      <c r="AB4" s="256"/>
       <c r="AC4" s="98" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AI4" s="98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>351</v>
-      </c>
-      <c r="AL4" s="243"/>
+        <v>350</v>
+      </c>
+      <c r="AL4" s="256"/>
       <c r="AM4" s="98" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>338</v>
-      </c>
-      <c r="AZ4" s="243"/>
+        <v>337</v>
+      </c>
+      <c r="AZ4" s="256"/>
       <c r="BA4" s="97" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>329</v>
-      </c>
-      <c r="BJ4" s="243"/>
+        <v>328</v>
+      </c>
+      <c r="BJ4" s="256"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="94"/>
       <c r="K5" s="93"/>
@@ -15858,51 +15852,51 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q5" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S5" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="T5" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="T5" s="74" t="s">
-        <v>209</v>
-      </c>
       <c r="U5" s="74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
         <v>0</v>
       </c>
       <c r="X5" s="74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y5" s="74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA5" s="74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB5" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G5:AA5)</f>
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15910,10 +15904,10 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
@@ -15926,25 +15920,25 @@
       <c r="AQ5" s="92"/>
       <c r="AR5" s="92"/>
       <c r="AS5" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AT5" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AU5" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AV5" s="74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AW5" s="74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AX5" s="74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AY5" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -15966,25 +15960,25 @@
     </row>
     <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -15992,49 +15986,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16043,47 +16037,47 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AN6" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AO6" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AP6" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AQ6" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AR6" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AS6" s="92"/>
       <c r="AT6" s="92"/>
@@ -16091,10 +16085,10 @@
       <c r="AV6" s="92"/>
       <c r="AW6" s="92"/>
       <c r="AX6" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AY6" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16116,22 +16110,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16166,22 +16160,22 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
@@ -16200,7 +16194,7 @@
       <c r="AW7" s="75"/>
       <c r="AX7" s="75"/>
       <c r="AY7" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16222,25 +16216,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16260,23 +16254,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16328,25 +16322,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16366,23 +16360,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16390,22 +16384,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16424,7 +16418,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16446,25 +16440,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16484,23 +16478,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16508,22 +16502,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16542,7 +16536,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16564,25 +16558,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16602,23 +16596,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16626,22 +16620,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16660,7 +16654,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16682,25 +16676,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16720,23 +16714,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16744,22 +16738,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16778,7 +16772,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16800,25 +16794,25 @@
     </row>
     <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16838,23 +16832,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16906,71 +16900,71 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="77" t="s">
         <v>233</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>232</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="77" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>234</v>
-      </c>
       <c r="G14" s="74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
         <v>0</v>
       </c>
       <c r="I14" s="74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K14" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P14" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q14" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="R14" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="S14" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="T14" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="U14" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="V14" s="74" t="s">
         <v>224</v>
-      </c>
-      <c r="Q14" s="74" t="s">
-        <v>227</v>
-      </c>
-      <c r="R14" s="74" t="s">
-        <v>226</v>
-      </c>
-      <c r="S14" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="T14" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="U14" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="V14" s="74" t="s">
-        <v>225</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -16985,72 +16979,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AE14" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AF14" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AH14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AI14" s="74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AN14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AO14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AP14" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AQ14" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR14" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AS14" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AT14" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AU14" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AV14" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AW14" s="74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -17072,71 +17066,71 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
         <v>0</v>
       </c>
       <c r="I15" s="74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K15" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M15" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P15" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q15" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="R15" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="S15" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="T15" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="U15" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="V15" s="74" t="s">
         <v>224</v>
-      </c>
-      <c r="Q15" s="74" t="s">
-        <v>227</v>
-      </c>
-      <c r="R15" s="74" t="s">
-        <v>226</v>
-      </c>
-      <c r="S15" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="T15" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="U15" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="V15" s="74" t="s">
-        <v>225</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17151,72 +17145,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AE15" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AF15" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AH15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AI15" s="74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AN15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AO15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AP15" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AQ15" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR15" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AS15" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AT15" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AU15" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AV15" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AW15" s="74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17243,7 +17237,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17510,16 +17504,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="246" t="s">
-        <v>439</v>
-      </c>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
+      <c r="B1" s="259" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
     </row>
     <row r="2" spans="1:62" s="112" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="158"/>
@@ -17529,172 +17523,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" s="245" t="s">
         <v>437</v>
       </c>
+      <c r="H2" s="258" t="s">
+        <v>436</v>
+      </c>
       <c r="I2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>436</v>
-      </c>
-      <c r="W2" s="245" t="s">
         <v>435</v>
       </c>
+      <c r="W2" s="258" t="s">
+        <v>434</v>
+      </c>
       <c r="X2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB2" s="245" t="s">
-        <v>434</v>
+        <v>151</v>
+      </c>
+      <c r="AB2" s="258" t="s">
+        <v>433</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>433</v>
-      </c>
-      <c r="AL2" s="245" t="s">
         <v>432</v>
       </c>
+      <c r="AL2" s="258" t="s">
+        <v>431</v>
+      </c>
       <c r="AM2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>431</v>
-      </c>
-      <c r="AZ2" s="245" t="s">
         <v>430</v>
       </c>
+      <c r="AZ2" s="258" t="s">
+        <v>429</v>
+      </c>
       <c r="BA2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>429</v>
-      </c>
-      <c r="BJ2" s="245" t="s">
         <v>428</v>
+      </c>
+      <c r="BJ2" s="258" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17705,335 +17699,335 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="245"/>
+        <v>426</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>414</v>
-      </c>
-      <c r="W3" s="245"/>
+        <v>413</v>
+      </c>
+      <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB3" s="245"/>
+        <v>410</v>
+      </c>
+      <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AI3" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ3" s="152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>404</v>
-      </c>
-      <c r="AL3" s="245"/>
+        <v>403</v>
+      </c>
+      <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>391</v>
-      </c>
-      <c r="AZ3" s="245"/>
+        <v>390</v>
+      </c>
+      <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>382</v>
-      </c>
-      <c r="BJ3" s="245"/>
+        <v>381</v>
+      </c>
+      <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>377</v>
-      </c>
-      <c r="H4" s="245"/>
+        <v>376</v>
+      </c>
+      <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>363</v>
-      </c>
-      <c r="W4" s="245"/>
+        <v>362</v>
+      </c>
+      <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB4" s="245"/>
+        <v>358</v>
+      </c>
+      <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AI4" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>351</v>
-      </c>
-      <c r="AL4" s="245"/>
+        <v>350</v>
+      </c>
+      <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>338</v>
-      </c>
-      <c r="AZ4" s="245"/>
+        <v>337</v>
+      </c>
+      <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>329</v>
-      </c>
-      <c r="BJ4" s="245"/>
+        <v>328</v>
+      </c>
+      <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -18042,10 +18036,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18226,7 +18220,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18235,10 +18229,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18438,7 +18432,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18447,10 +18441,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18556,7 +18550,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18565,10 +18559,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18665,7 +18659,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18674,10 +18668,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18844,7 +18838,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18853,10 +18847,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18980,7 +18974,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -18989,10 +18983,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19116,7 +19110,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -19125,10 +19119,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19258,7 +19252,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19267,10 +19261,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19367,7 +19361,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19376,10 +19370,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19589,7 +19583,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19598,10 +19592,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19816,7 +19810,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -20119,7 +20113,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14291D7F-E60F-9247-B097-E13377546AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07F5CDD-D549-6647-BCEA-0EBCBF0F4466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -450,9 +450,6 @@
   </si>
   <si>
     <t>PPI</t>
-  </si>
-  <si>
-    <t>CONT A JP Autour du magistrat</t>
   </si>
   <si>
     <t>CONT A JP Autour du Juge</t>
@@ -2771,6 +2768,9 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>JA JP</t>
   </si>
 </sst>
 </file>
@@ -5469,10 +5469,10 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
+        <v>492</v>
+      </c>
+      <c r="C1" s="233" t="s">
         <v>493</v>
-      </c>
-      <c r="C1" s="233" t="s">
-        <v>494</v>
       </c>
       <c r="D1" s="233"/>
       <c r="E1" s="233"/>
@@ -5485,7 +5485,7 @@
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
       <c r="C2" s="234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D2" s="234"/>
       <c r="E2" s="234"/>
@@ -5504,16 +5504,16 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="207" t="s">
         <v>496</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="D4" s="207" t="s">
         <v>497</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="E4" s="240" t="s">
         <v>498</v>
-      </c>
-      <c r="E4" s="240" t="s">
-        <v>499</v>
       </c>
       <c r="F4" s="241"/>
       <c r="G4" s="216"/>
@@ -5524,16 +5524,16 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" s="213" t="s">
         <v>500</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="D5" s="213" t="s">
         <v>501</v>
       </c>
-      <c r="D5" s="213" t="s">
-        <v>502</v>
-      </c>
       <c r="E5" s="242" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F5" s="243"/>
       <c r="G5" s="215"/>
@@ -5544,16 +5544,16 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="214" t="s">
         <v>503</v>
       </c>
-      <c r="C6" s="214" t="s">
+      <c r="D6" s="214" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="214" t="s">
-        <v>505</v>
-      </c>
       <c r="E6" s="244" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F6" s="245"/>
       <c r="G6" s="215"/>
@@ -5564,16 +5564,16 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="214" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="214" t="s">
+      <c r="D7" s="214" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="214" t="s">
-        <v>508</v>
-      </c>
       <c r="E7" s="244" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F7" s="245"/>
       <c r="G7" s="215"/>
@@ -5584,16 +5584,16 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
+        <v>508</v>
+      </c>
+      <c r="C8" s="235" t="s">
         <v>509</v>
       </c>
-      <c r="C8" s="235" t="s">
+      <c r="D8" s="235" t="s">
         <v>510</v>
       </c>
-      <c r="D8" s="235" t="s">
-        <v>511</v>
-      </c>
       <c r="E8" s="246" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F8" s="247"/>
       <c r="G8" s="215"/>
@@ -5604,7 +5604,7 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C9" s="235"/>
       <c r="D9" s="235"/>
@@ -5618,7 +5618,7 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="236"/>
@@ -5644,7 +5644,7 @@
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
       <c r="C12" s="239" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
@@ -5714,7 +5714,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="260" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -5759,91 +5759,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5854,181 +5854,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6144,7 +6144,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6153,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6205,7 +6205,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6214,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6266,7 +6266,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6339,7 +6339,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6421,7 +6421,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6430,10 +6430,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6503,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6576,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6643,7 +6643,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6652,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6722,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6835,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6944,7 +6944,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -7109,7 +7109,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7126,16 +7126,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7146,43 +7146,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7191,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7215,7 +7215,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7224,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7242,7 +7242,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7251,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7269,7 +7269,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7278,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7296,7 +7296,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7305,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7323,7 +7323,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7332,10 +7332,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7350,7 +7350,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7359,10 +7359,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7377,7 +7377,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7442,7 +7442,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7501,12 +7501,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7575,172 +7575,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7752,78 +7752,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7832,265 +7832,265 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="258"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8293,7 +8293,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8302,10 +8302,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8516,10 +8516,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8721,7 +8721,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8730,10 +8730,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8944,10 +8944,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -9149,7 +9149,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -9158,10 +9158,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9363,7 +9363,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9372,10 +9372,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9586,10 +9586,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9791,7 +9791,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9800,10 +9800,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -10014,10 +10014,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10228,10 +10228,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10438,7 +10438,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10671,7 +10671,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10716,12 +10716,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10790,91 +10790,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10885,190 +10885,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11189,7 +11189,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11198,10 +11198,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11331,10 +11331,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11455,7 +11455,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11464,10 +11464,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11597,10 +11597,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11721,7 +11721,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11730,10 +11730,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11863,10 +11863,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -11987,7 +11987,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -11996,10 +11996,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12129,10 +12129,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12253,7 +12253,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12262,10 +12262,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12395,10 +12395,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12524,7 +12524,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12648,7 +12648,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12670,7 +12670,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12711,12 +12711,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12785,16 +12785,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12805,52 +12805,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12871,7 +12871,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12880,10 +12880,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12913,10 +12913,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12937,7 +12937,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12946,10 +12946,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12979,10 +12979,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -13003,7 +13003,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13012,10 +13012,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -13036,7 +13036,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13045,10 +13045,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -13069,7 +13069,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13078,10 +13078,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -13102,7 +13102,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13111,10 +13111,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -13140,7 +13140,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -13161,7 +13161,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13209,7 +13209,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13532,7 +13532,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13543,7 +13543,7 @@
         <v>6</v>
       </c>
       <c r="EA1" s="252" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="EB1" s="252"/>
       <c r="EC1" s="252"/>
@@ -13630,7 +13630,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13871,15 +13871,15 @@
       </c>
       <c r="B1"/>
       <c r="D1" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E1"/>
       <c r="G1" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13939,19 +13939,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F1" s="59" t="s">
         <v>34</v>
@@ -13959,16 +13959,16 @@
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>46</v>
@@ -13979,16 +13979,16 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>46</v>
@@ -13999,16 +13999,16 @@
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>46</v>
@@ -14019,16 +14019,16 @@
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>46</v>
@@ -14039,16 +14039,16 @@
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>46</v>
@@ -14059,16 +14059,16 @@
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>46</v>
@@ -14079,16 +14079,16 @@
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>46</v>
@@ -14099,16 +14099,16 @@
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>46</v>
@@ -14119,16 +14119,16 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>46</v>
@@ -14139,16 +14139,16 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>46</v>
@@ -14159,16 +14159,16 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>46</v>
@@ -14179,16 +14179,16 @@
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>46</v>
@@ -14199,16 +14199,16 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>46</v>
@@ -14219,16 +14219,16 @@
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>46</v>
@@ -14239,16 +14239,16 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>46</v>
@@ -14259,16 +14259,16 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>46</v>
@@ -14279,16 +14279,16 @@
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>46</v>
@@ -14299,16 +14299,16 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>46</v>
@@ -14319,16 +14319,16 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>46</v>
@@ -14339,16 +14339,16 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>46</v>
@@ -14359,16 +14359,16 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>69</v>
@@ -14379,16 +14379,16 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C23" s="57" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>69</v>
@@ -14399,16 +14399,16 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>73</v>
@@ -14419,16 +14419,16 @@
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>73</v>
@@ -14439,16 +14439,16 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>77</v>
@@ -14459,16 +14459,16 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>77</v>
@@ -14479,16 +14479,16 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>170</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>171</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E28" s="41" t="s">
         <v>77</v>
@@ -14499,16 +14499,16 @@
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="54" t="s">
         <v>81</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>77</v>
@@ -14519,7 +14519,7 @@
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
@@ -14528,7 +14528,7 @@
         <v>83</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>84</v>
@@ -14539,16 +14539,16 @@
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>84</v>
@@ -14559,16 +14559,16 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>84</v>
@@ -14579,7 +14579,7 @@
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>88</v>
@@ -14588,7 +14588,7 @@
         <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>84</v>
@@ -14599,7 +14599,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>89</v>
@@ -14608,7 +14608,7 @@
         <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>84</v>
@@ -14619,7 +14619,7 @@
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>90</v>
@@ -14628,7 +14628,7 @@
         <v>90</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>84</v>
@@ -14639,7 +14639,7 @@
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>92</v>
@@ -14648,7 +14648,7 @@
         <v>92</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>93</v>
@@ -14659,16 +14659,16 @@
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>93</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>96</v>
@@ -14688,7 +14688,7 @@
         <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>93</v>
@@ -14699,7 +14699,7 @@
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>97</v>
@@ -14708,7 +14708,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>93</v>
@@ -14719,7 +14719,7 @@
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>98</v>
@@ -14728,7 +14728,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>93</v>
@@ -14739,7 +14739,7 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>100</v>
@@ -14748,7 +14748,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="48" t="s">
         <v>101</v>
@@ -14759,16 +14759,16 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="48" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" s="48" t="s">
         <v>101</v>
@@ -14779,7 +14779,7 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>104</v>
@@ -14788,7 +14788,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E43" s="48" t="s">
         <v>101</v>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>105</v>
@@ -14808,7 +14808,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" s="48" t="s">
         <v>101</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>106</v>
@@ -14828,7 +14828,7 @@
         <v>106</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>101</v>
@@ -14839,16 +14839,16 @@
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C46" s="48" t="s">
         <v>108</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E46" s="48" t="s">
         <v>109</v>
@@ -14859,16 +14859,16 @@
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C47" s="48" t="s">
         <v>111</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E47" s="48" t="s">
         <v>109</v>
@@ -14879,16 +14879,16 @@
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="48" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E48" s="48" t="s">
         <v>109</v>
@@ -14899,16 +14899,16 @@
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C49" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E49" s="48" t="s">
         <v>109</v>
@@ -14919,16 +14919,16 @@
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E50" s="48" t="s">
         <v>109</v>
@@ -14939,16 +14939,16 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>109</v>
@@ -14959,16 +14959,16 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="41" t="s">
         <v>155</v>
-      </c>
-      <c r="B52" s="41" t="s">
-        <v>156</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>116</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>109</v>
@@ -14979,16 +14979,16 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>118</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>109</v>
@@ -14999,16 +14999,16 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C54" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>109</v>
@@ -15019,16 +15019,16 @@
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C55" s="54" t="s">
         <v>121</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E55" s="53" t="s">
         <v>109</v>
@@ -15039,36 +15039,36 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>122</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E56" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>109</v>
@@ -15079,33 +15079,33 @@
     </row>
     <row r="58" spans="1:7" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>125</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>109</v>
@@ -15114,21 +15114,21 @@
         <v>126</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>127</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>109</v>
@@ -15137,21 +15137,21 @@
         <v>128</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" s="48" t="s">
         <v>129</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>109</v>
@@ -15160,89 +15160,89 @@
         <v>130</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C62" s="48" t="s">
         <v>131</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>109</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>132</v>
+        <v>519</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>142</v>
-      </c>
       <c r="D64" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E64" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F64" s="46"/>
       <c r="G64" s="42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E65" s="44" t="s">
         <v>109</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -15287,7 +15287,7 @@
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
       <c r="B1" s="257" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C1" s="257"/>
       <c r="D1" s="257"/>
@@ -15314,172 +15314,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="256" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="256" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="256" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="256" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="256" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="256" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15490,78 +15490,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="256"/>
       <c r="I3" s="101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="256"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="256"/>
       <c r="AC3" s="98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15570,273 +15570,273 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="256"/>
       <c r="AM3" s="98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="256"/>
       <c r="BA3" s="97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="256"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="256"/>
       <c r="I4" s="101" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="256"/>
       <c r="X4" s="99" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="256"/>
       <c r="AC4" s="98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="256"/>
       <c r="AM4" s="98" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="256"/>
       <c r="BA4" s="97" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="256"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
@@ -15852,25 +15852,25 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q5" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S5" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T5" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T5" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U5" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15893,10 +15893,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15904,10 +15904,10 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
@@ -15920,25 +15920,25 @@
       <c r="AQ5" s="92"/>
       <c r="AR5" s="92"/>
       <c r="AS5" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AT5" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AU5" s="74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AV5" s="74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AW5" s="74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AX5" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AY5" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -15960,25 +15960,25 @@
     </row>
     <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -15986,49 +15986,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16037,47 +16037,47 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AN6" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO6" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AP6" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AQ6" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AR6" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AS6" s="92"/>
       <c r="AT6" s="92"/>
@@ -16085,10 +16085,10 @@
       <c r="AV6" s="92"/>
       <c r="AW6" s="92"/>
       <c r="AX6" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AY6" s="74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16110,22 +16110,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16160,22 +16160,22 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
@@ -16194,7 +16194,7 @@
       <c r="AW7" s="75"/>
       <c r="AX7" s="75"/>
       <c r="AY7" s="74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16216,25 +16216,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16254,23 +16254,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16322,25 +16322,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16360,23 +16360,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16384,22 +16384,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16418,7 +16418,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16440,25 +16440,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16478,23 +16478,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16502,22 +16502,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16536,7 +16536,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16558,25 +16558,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16596,23 +16596,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16620,22 +16620,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16654,7 +16654,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16676,25 +16676,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16714,23 +16714,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16738,22 +16738,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16772,7 +16772,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16794,25 +16794,25 @@
     </row>
     <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16832,23 +16832,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16900,25 +16900,25 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="77" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>233</v>
-      </c>
       <c r="G14" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
@@ -16928,43 +16928,43 @@
         <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q14" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R14" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S14" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T14" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T14" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U14" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V14" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -16979,72 +16979,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AD14" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE14" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI14" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AO14" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AP14" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AQ14" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AR14" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AS14" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AT14" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU14" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV14" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AW14" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -17066,25 +17066,25 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
@@ -17094,43 +17094,43 @@
         <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q15" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R15" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S15" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T15" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T15" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U15" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V15" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17145,72 +17145,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AD15" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE15" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI15" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AO15" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AP15" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AQ15" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AR15" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AS15" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AT15" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU15" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV15" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AW15" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17237,7 +17237,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17505,7 +17505,7 @@
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="259" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C1" s="259"/>
       <c r="D1" s="259"/>
@@ -17523,172 +17523,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17699,78 +17699,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17779,255 +17779,255 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -18036,10 +18036,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18220,7 +18220,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18229,10 +18229,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18432,7 +18432,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18441,10 +18441,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18550,7 +18550,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18559,10 +18559,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18659,7 +18659,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18668,10 +18668,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18838,7 +18838,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18847,10 +18847,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18974,7 +18974,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -18983,10 +18983,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -19119,10 +19119,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19252,7 +19252,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19261,10 +19261,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19361,7 +19361,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19370,10 +19370,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19583,7 +19583,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19592,10 +19592,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19810,7 +19810,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -20113,7 +20113,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14291D7F-E60F-9247-B097-E13377546AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96EFCC9-952B-9C47-8418-74278CEBA416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -450,9 +450,6 @@
   </si>
   <si>
     <t>PPI</t>
-  </si>
-  <si>
-    <t>CONT A JP Autour du magistrat</t>
   </si>
   <si>
     <t>CONT A JP Autour du Juge</t>
@@ -2771,6 +2768,9 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>JA JP</t>
   </si>
 </sst>
 </file>
@@ -5469,10 +5469,10 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
+        <v>492</v>
+      </c>
+      <c r="C1" s="233" t="s">
         <v>493</v>
-      </c>
-      <c r="C1" s="233" t="s">
-        <v>494</v>
       </c>
       <c r="D1" s="233"/>
       <c r="E1" s="233"/>
@@ -5485,7 +5485,7 @@
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
       <c r="C2" s="234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D2" s="234"/>
       <c r="E2" s="234"/>
@@ -5504,16 +5504,16 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="207" t="s">
         <v>496</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="D4" s="207" t="s">
         <v>497</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="E4" s="240" t="s">
         <v>498</v>
-      </c>
-      <c r="E4" s="240" t="s">
-        <v>499</v>
       </c>
       <c r="F4" s="241"/>
       <c r="G4" s="216"/>
@@ -5524,16 +5524,16 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" s="213" t="s">
         <v>500</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="D5" s="213" t="s">
         <v>501</v>
       </c>
-      <c r="D5" s="213" t="s">
-        <v>502</v>
-      </c>
       <c r="E5" s="242" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F5" s="243"/>
       <c r="G5" s="215"/>
@@ -5544,16 +5544,16 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="214" t="s">
         <v>503</v>
       </c>
-      <c r="C6" s="214" t="s">
+      <c r="D6" s="214" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="214" t="s">
-        <v>505</v>
-      </c>
       <c r="E6" s="244" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F6" s="245"/>
       <c r="G6" s="215"/>
@@ -5564,16 +5564,16 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="214" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="214" t="s">
+      <c r="D7" s="214" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="214" t="s">
-        <v>508</v>
-      </c>
       <c r="E7" s="244" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F7" s="245"/>
       <c r="G7" s="215"/>
@@ -5584,16 +5584,16 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
+        <v>508</v>
+      </c>
+      <c r="C8" s="235" t="s">
         <v>509</v>
       </c>
-      <c r="C8" s="235" t="s">
+      <c r="D8" s="235" t="s">
         <v>510</v>
       </c>
-      <c r="D8" s="235" t="s">
-        <v>511</v>
-      </c>
       <c r="E8" s="246" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F8" s="247"/>
       <c r="G8" s="215"/>
@@ -5604,7 +5604,7 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C9" s="235"/>
       <c r="D9" s="235"/>
@@ -5618,7 +5618,7 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="236"/>
@@ -5644,7 +5644,7 @@
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
       <c r="C12" s="239" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
@@ -5714,7 +5714,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="260" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -5759,91 +5759,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5854,181 +5854,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6144,7 +6144,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6153,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6205,7 +6205,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6214,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6266,7 +6266,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6339,7 +6339,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6421,7 +6421,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6430,10 +6430,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6503,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6576,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6643,7 +6643,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6652,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6722,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6835,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6944,7 +6944,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -7109,7 +7109,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7126,16 +7126,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7146,43 +7146,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7191,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7215,7 +7215,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7224,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7242,7 +7242,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7251,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7269,7 +7269,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7278,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7296,7 +7296,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7305,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7323,7 +7323,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7332,10 +7332,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7350,7 +7350,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7359,10 +7359,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7377,7 +7377,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7442,7 +7442,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7501,12 +7501,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7575,172 +7575,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7752,78 +7752,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7832,265 +7832,265 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="258"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8293,7 +8293,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8302,10 +8302,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8516,10 +8516,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8721,7 +8721,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8730,10 +8730,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8944,10 +8944,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -9149,7 +9149,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -9158,10 +9158,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9363,7 +9363,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9372,10 +9372,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9586,10 +9586,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9791,7 +9791,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9800,10 +9800,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -10014,10 +10014,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10228,10 +10228,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10438,7 +10438,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10671,7 +10671,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10716,12 +10716,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10790,91 +10790,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10885,190 +10885,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11189,7 +11189,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11198,10 +11198,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11331,10 +11331,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11455,7 +11455,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11464,10 +11464,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11597,10 +11597,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11721,7 +11721,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11730,10 +11730,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11863,10 +11863,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -11987,7 +11987,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -11996,10 +11996,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12129,10 +12129,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12253,7 +12253,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12262,10 +12262,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12395,10 +12395,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12524,7 +12524,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12648,7 +12648,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12670,7 +12670,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12711,12 +12711,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12785,16 +12785,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12805,52 +12805,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12871,7 +12871,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12880,10 +12880,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12913,10 +12913,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12937,7 +12937,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12946,10 +12946,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12979,10 +12979,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -13003,7 +13003,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13012,10 +13012,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -13036,7 +13036,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13045,10 +13045,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -13069,7 +13069,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13078,10 +13078,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -13102,7 +13102,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13111,10 +13111,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -13140,7 +13140,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -13161,7 +13161,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13209,7 +13209,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13532,7 +13532,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13543,7 +13543,7 @@
         <v>6</v>
       </c>
       <c r="EA1" s="252" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="EB1" s="252"/>
       <c r="EC1" s="252"/>
@@ -13630,7 +13630,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13871,15 +13871,15 @@
       </c>
       <c r="B1"/>
       <c r="D1" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E1"/>
       <c r="G1" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13939,19 +13939,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F1" s="59" t="s">
         <v>34</v>
@@ -13959,16 +13959,16 @@
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>46</v>
@@ -13979,16 +13979,16 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>46</v>
@@ -13999,16 +13999,16 @@
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>46</v>
@@ -14019,16 +14019,16 @@
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>46</v>
@@ -14039,16 +14039,16 @@
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>46</v>
@@ -14059,16 +14059,16 @@
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>46</v>
@@ -14079,16 +14079,16 @@
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>46</v>
@@ -14099,16 +14099,16 @@
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>46</v>
@@ -14119,16 +14119,16 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>46</v>
@@ -14139,16 +14139,16 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>46</v>
@@ -14159,16 +14159,16 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>46</v>
@@ -14179,16 +14179,16 @@
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>46</v>
@@ -14199,16 +14199,16 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>46</v>
@@ -14219,16 +14219,16 @@
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>46</v>
@@ -14239,16 +14239,16 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>46</v>
@@ -14259,16 +14259,16 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>46</v>
@@ -14279,16 +14279,16 @@
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>46</v>
@@ -14299,16 +14299,16 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>46</v>
@@ -14319,16 +14319,16 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>46</v>
@@ -14339,16 +14339,16 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>46</v>
@@ -14359,16 +14359,16 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>69</v>
@@ -14379,16 +14379,16 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C23" s="57" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>69</v>
@@ -14399,16 +14399,16 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>73</v>
@@ -14419,16 +14419,16 @@
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>73</v>
@@ -14439,16 +14439,16 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>77</v>
@@ -14459,16 +14459,16 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>77</v>
@@ -14479,16 +14479,16 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>170</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>171</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E28" s="41" t="s">
         <v>77</v>
@@ -14499,16 +14499,16 @@
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="54" t="s">
         <v>81</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>77</v>
@@ -14519,7 +14519,7 @@
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
@@ -14528,7 +14528,7 @@
         <v>83</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>84</v>
@@ -14539,16 +14539,16 @@
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>84</v>
@@ -14559,16 +14559,16 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>84</v>
@@ -14579,7 +14579,7 @@
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>88</v>
@@ -14588,7 +14588,7 @@
         <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>84</v>
@@ -14599,7 +14599,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>89</v>
@@ -14608,7 +14608,7 @@
         <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>84</v>
@@ -14619,7 +14619,7 @@
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>90</v>
@@ -14628,7 +14628,7 @@
         <v>90</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>84</v>
@@ -14639,7 +14639,7 @@
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>92</v>
@@ -14648,7 +14648,7 @@
         <v>92</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>93</v>
@@ -14659,16 +14659,16 @@
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>93</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>96</v>
@@ -14688,7 +14688,7 @@
         <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>93</v>
@@ -14699,7 +14699,7 @@
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>97</v>
@@ -14708,7 +14708,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>93</v>
@@ -14719,7 +14719,7 @@
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>98</v>
@@ -14728,7 +14728,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>93</v>
@@ -14739,7 +14739,7 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>100</v>
@@ -14748,7 +14748,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="48" t="s">
         <v>101</v>
@@ -14759,16 +14759,16 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="48" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" s="48" t="s">
         <v>101</v>
@@ -14779,7 +14779,7 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>104</v>
@@ -14788,7 +14788,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E43" s="48" t="s">
         <v>101</v>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>105</v>
@@ -14808,7 +14808,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" s="48" t="s">
         <v>101</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>106</v>
@@ -14828,7 +14828,7 @@
         <v>106</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>101</v>
@@ -14839,16 +14839,16 @@
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C46" s="48" t="s">
         <v>108</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E46" s="48" t="s">
         <v>109</v>
@@ -14859,16 +14859,16 @@
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C47" s="48" t="s">
         <v>111</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E47" s="48" t="s">
         <v>109</v>
@@ -14879,16 +14879,16 @@
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="48" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E48" s="48" t="s">
         <v>109</v>
@@ -14899,16 +14899,16 @@
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C49" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E49" s="48" t="s">
         <v>109</v>
@@ -14919,16 +14919,16 @@
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E50" s="48" t="s">
         <v>109</v>
@@ -14939,16 +14939,16 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>109</v>
@@ -14959,16 +14959,16 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="41" t="s">
         <v>155</v>
-      </c>
-      <c r="B52" s="41" t="s">
-        <v>156</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>116</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>109</v>
@@ -14979,16 +14979,16 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>118</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>109</v>
@@ -14999,16 +14999,16 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C54" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>109</v>
@@ -15019,16 +15019,16 @@
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C55" s="54" t="s">
         <v>121</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E55" s="53" t="s">
         <v>109</v>
@@ -15039,36 +15039,36 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>122</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E56" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>109</v>
@@ -15079,33 +15079,33 @@
     </row>
     <row r="58" spans="1:7" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>125</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>109</v>
@@ -15114,21 +15114,21 @@
         <v>126</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>127</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>109</v>
@@ -15137,21 +15137,21 @@
         <v>128</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" s="48" t="s">
         <v>129</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>109</v>
@@ -15160,89 +15160,89 @@
         <v>130</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C62" s="48" t="s">
         <v>131</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>109</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>132</v>
+        <v>519</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>142</v>
-      </c>
       <c r="D64" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E64" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F64" s="46"/>
       <c r="G64" s="42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E65" s="44" t="s">
         <v>109</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -15287,7 +15287,7 @@
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
       <c r="B1" s="257" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C1" s="257"/>
       <c r="D1" s="257"/>
@@ -15314,172 +15314,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="256" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="256" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="256" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="256" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="256" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="256" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15490,78 +15490,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="256"/>
       <c r="I3" s="101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="256"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="256"/>
       <c r="AC3" s="98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15570,273 +15570,273 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="256"/>
       <c r="AM3" s="98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="256"/>
       <c r="BA3" s="97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="256"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="256"/>
       <c r="I4" s="101" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="256"/>
       <c r="X4" s="99" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="256"/>
       <c r="AC4" s="98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="256"/>
       <c r="AM4" s="98" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="256"/>
       <c r="BA4" s="97" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="256"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
@@ -15852,25 +15852,25 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q5" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S5" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T5" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T5" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U5" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15893,10 +15893,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15904,10 +15904,10 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
@@ -15920,25 +15920,25 @@
       <c r="AQ5" s="92"/>
       <c r="AR5" s="92"/>
       <c r="AS5" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AT5" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AU5" s="74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AV5" s="74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AW5" s="74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AX5" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AY5" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -15960,25 +15960,25 @@
     </row>
     <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -15986,49 +15986,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16037,47 +16037,47 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AN6" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO6" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AP6" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AQ6" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AR6" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AS6" s="92"/>
       <c r="AT6" s="92"/>
@@ -16085,10 +16085,10 @@
       <c r="AV6" s="92"/>
       <c r="AW6" s="92"/>
       <c r="AX6" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AY6" s="74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16110,22 +16110,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16160,22 +16160,22 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
@@ -16194,7 +16194,7 @@
       <c r="AW7" s="75"/>
       <c r="AX7" s="75"/>
       <c r="AY7" s="74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16216,25 +16216,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16254,23 +16254,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16322,25 +16322,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16360,23 +16360,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16384,22 +16384,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16418,7 +16418,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16440,25 +16440,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16478,23 +16478,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16502,22 +16502,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16536,7 +16536,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16558,25 +16558,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16596,23 +16596,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16620,22 +16620,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16654,7 +16654,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16676,25 +16676,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16714,23 +16714,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16738,22 +16738,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16772,7 +16772,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16794,25 +16794,25 @@
     </row>
     <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16832,23 +16832,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16900,25 +16900,25 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="77" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>233</v>
-      </c>
       <c r="G14" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
@@ -16928,43 +16928,43 @@
         <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q14" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R14" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S14" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T14" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T14" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U14" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V14" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -16979,72 +16979,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AD14" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE14" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI14" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AO14" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AP14" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AQ14" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AR14" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AS14" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AT14" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU14" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV14" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AW14" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -17066,25 +17066,25 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
@@ -17094,43 +17094,43 @@
         <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q15" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R15" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S15" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="T15" s="74" t="s">
         <v>207</v>
-      </c>
-      <c r="T15" s="74" t="s">
-        <v>208</v>
       </c>
       <c r="U15" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V15" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17145,72 +17145,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AD15" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE15" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI15" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AO15" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AP15" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AQ15" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AR15" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AS15" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AT15" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU15" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV15" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AW15" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17237,7 +17237,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17505,7 +17505,7 @@
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="259" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C1" s="259"/>
       <c r="D1" s="259"/>
@@ -17523,172 +17523,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17699,78 +17699,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17779,255 +17779,255 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -18036,10 +18036,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18220,7 +18220,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18229,10 +18229,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18432,7 +18432,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18441,10 +18441,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18550,7 +18550,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18559,10 +18559,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18659,7 +18659,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18668,10 +18668,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18838,7 +18838,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18847,10 +18847,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18974,7 +18974,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -18983,10 +18983,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -19119,10 +19119,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19252,7 +19252,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19261,10 +19261,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19361,7 +19361,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19370,10 +19370,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19583,7 +19583,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19592,10 +19592,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19810,7 +19810,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -20113,7 +20113,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07F5CDD-D549-6647-BCEA-0EBCBF0F4466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C175DC4F-D524-694E-A1E8-046EB5A40464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="522">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -2771,6 +2771,12 @@
   </si>
   <si>
     <t>JA JP</t>
+  </si>
+  <si>
+    <t>JURISTE ASSISTANT Vif</t>
+  </si>
+  <si>
+    <t>JA VIF</t>
   </si>
 </sst>
 </file>
@@ -3837,7 +3843,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4672,6 +4678,12 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -13924,7 +13936,7 @@
   <sheetPr codeName="Feuil14">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" style="41" bestFit="1" customWidth="1"/>
@@ -15164,34 +15176,35 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62" s="48" t="s">
+      <c r="B62" s="262" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" s="262" t="s">
+        <v>521</v>
+      </c>
+      <c r="D62" s="262" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="262" t="s">
         <v>109</v>
       </c>
-      <c r="G62" s="42" t="s">
-        <v>144</v>
-      </c>
+      <c r="F62" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="42"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
         <v>140</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>519</v>
+        <v>131</v>
       </c>
       <c r="D63" s="48" t="s">
         <v>137</v>
@@ -15199,54 +15212,74 @@
       <c r="E63" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="F63" s="48" t="s">
+      <c r="G63" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="48" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="47" t="s">
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="42" t="s">
+      <c r="B65" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C65" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="D64" s="42" t="s">
+      <c r="D65" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="42" t="s">
+      <c r="E65" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="F64" s="46"/>
-      <c r="G64" s="42" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="D65" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E65" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F65" s="43"/>
+      <c r="F65" s="46"/>
       <c r="G65" s="42" t="s">
         <v>136</v>
       </c>
     </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="43"/>
+      <c r="G66" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F65" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:F66" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="74" orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96EFCC9-952B-9C47-8418-74278CEBA416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747CEEAA-2D6B-7D4C-8FEC-C5ACAC0255E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="521">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -2771,6 +2771,9 @@
   </si>
   <si>
     <t>JA JP</t>
+  </si>
+  <si>
+    <t>JA VIF</t>
   </si>
 </sst>
 </file>
@@ -13924,7 +13927,7 @@
   <sheetPr codeName="Feuil14">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" style="41" bestFit="1" customWidth="1"/>
@@ -15191,7 +15194,7 @@
         <v>143</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D63" s="48" t="s">
         <v>137</v>
@@ -15202,51 +15205,72 @@
       <c r="F63" s="48" t="s">
         <v>132</v>
       </c>
+      <c r="G63" s="42"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="47" t="s">
+      <c r="A64" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="42" t="s">
+      <c r="B64" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C65" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="D64" s="42" t="s">
+      <c r="D65" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="42" t="s">
+      <c r="E65" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="F64" s="46"/>
-      <c r="G64" s="42" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="D65" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E65" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F65" s="43"/>
+      <c r="F65" s="46"/>
       <c r="G65" s="42" t="s">
         <v>136</v>
       </c>
     </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="43"/>
+      <c r="G66" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F65" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:F66" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="74" orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747CEEAA-2D6B-7D4C-8FEC-C5ACAC0255E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7161F2AA-EFD1-F948-B7A2-01F41596DC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ACCUEIL" sheetId="33" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="520">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -410,16 +410,7 @@
     <t>VACATAIRES</t>
   </si>
   <si>
-    <t>CONT A JP</t>
-  </si>
-  <si>
     <t>CONT A JP Greffe</t>
-  </si>
-  <si>
-    <t>CONT B JP</t>
-  </si>
-  <si>
-    <t>CONT C JP</t>
   </si>
   <si>
     <t>AS</t>
@@ -2774,6 +2765,12 @@
   </si>
   <si>
     <t>JA VIF</t>
+  </si>
+  <si>
+    <t>CONT B JP Greffe</t>
+  </si>
+  <si>
+    <t>CONT C JP Greffe</t>
   </si>
 </sst>
 </file>
@@ -5157,9 +5154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5197,7 +5194,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5303,7 +5300,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5445,7 +5442,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5472,10 +5469,10 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C1" s="233" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D1" s="233"/>
       <c r="E1" s="233"/>
@@ -5488,7 +5485,7 @@
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
       <c r="C2" s="234" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D2" s="234"/>
       <c r="E2" s="234"/>
@@ -5507,16 +5504,16 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
+        <v>492</v>
+      </c>
+      <c r="C4" s="207" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" s="207" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" s="240" t="s">
         <v>495</v>
-      </c>
-      <c r="C4" s="207" t="s">
-        <v>496</v>
-      </c>
-      <c r="D4" s="207" t="s">
-        <v>497</v>
-      </c>
-      <c r="E4" s="240" t="s">
-        <v>498</v>
       </c>
       <c r="F4" s="241"/>
       <c r="G4" s="216"/>
@@ -5527,16 +5524,16 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C5" s="213" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D5" s="213" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E5" s="242" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F5" s="243"/>
       <c r="G5" s="215"/>
@@ -5547,16 +5544,16 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C6" s="214" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D6" s="214" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E6" s="244" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F6" s="245"/>
       <c r="G6" s="215"/>
@@ -5567,16 +5564,16 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C7" s="214" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D7" s="214" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E7" s="244" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F7" s="245"/>
       <c r="G7" s="215"/>
@@ -5587,16 +5584,16 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C8" s="235" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D8" s="235" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E8" s="246" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F8" s="247"/>
       <c r="G8" s="215"/>
@@ -5607,7 +5604,7 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C9" s="235"/>
       <c r="D9" s="235"/>
@@ -5621,7 +5618,7 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="236"/>
@@ -5647,7 +5644,7 @@
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
       <c r="C12" s="239" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
@@ -5717,7 +5714,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="260" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -5762,91 +5759,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5857,181 +5854,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6040,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6147,7 +6144,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6156,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6208,7 +6205,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6217,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6269,7 +6266,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6278,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6342,7 +6339,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6351,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6424,7 +6421,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6433,10 +6430,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6497,7 +6494,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6506,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6570,7 +6567,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6579,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6646,7 +6643,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6655,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6716,7 +6713,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6725,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6829,7 +6826,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6838,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6947,7 +6944,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -7077,7 +7074,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -7112,7 +7109,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7129,16 +7126,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7149,43 +7146,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7194,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7218,7 +7215,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7227,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7245,7 +7242,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7254,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7272,7 +7269,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7281,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7299,7 +7296,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7308,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7326,7 +7323,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7335,10 +7332,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7353,7 +7350,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7362,10 +7359,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7380,7 +7377,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7389,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7410,7 +7407,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7419,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7445,7 +7442,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7504,12 +7501,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7578,172 +7575,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7755,78 +7752,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7835,265 +7832,265 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="BJ4" s="258"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8296,7 +8293,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8305,10 +8302,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8510,7 +8507,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8519,10 +8516,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8724,7 +8721,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8733,10 +8730,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8938,7 +8935,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8947,10 +8944,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -9161,10 +9158,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9366,7 +9363,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9375,10 +9372,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9580,7 +9577,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9589,10 +9586,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9794,7 +9791,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9803,10 +9800,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -10008,7 +10005,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -10017,10 +10014,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10222,7 +10219,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10231,10 +10228,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10441,7 +10438,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10674,7 +10671,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10719,12 +10716,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10793,91 +10790,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10888,190 +10885,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11192,7 +11189,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11201,10 +11198,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11325,7 +11322,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11334,10 +11331,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11458,7 +11455,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11467,10 +11464,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11591,7 +11588,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11600,10 +11597,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11724,7 +11721,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11733,10 +11730,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11857,7 +11854,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11866,10 +11863,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -11990,7 +11987,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -11999,10 +11996,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -12123,7 +12120,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12132,10 +12129,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12256,7 +12253,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12265,10 +12262,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12389,7 +12386,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12398,10 +12395,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12527,7 +12524,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12651,7 +12648,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12673,7 +12670,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12714,12 +12711,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12788,16 +12785,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12808,52 +12805,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12874,7 +12871,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12883,10 +12880,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12907,7 +12904,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12916,10 +12913,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12940,7 +12937,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12949,10 +12946,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12973,7 +12970,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12982,10 +12979,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -13006,7 +13003,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13015,10 +13012,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -13039,7 +13036,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13048,10 +13045,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -13072,7 +13069,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13081,10 +13078,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -13105,7 +13102,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13114,10 +13111,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -13143,7 +13140,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -13164,7 +13161,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13212,7 +13209,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13535,7 +13532,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13546,7 +13543,7 @@
         <v>6</v>
       </c>
       <c r="EA1" s="252" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="EB1" s="252"/>
       <c r="EC1" s="252"/>
@@ -13633,7 +13630,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13874,15 +13871,15 @@
       </c>
       <c r="B1"/>
       <c r="D1" s="40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E1"/>
       <c r="G1" s="40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13942,19 +13939,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F1" s="59" t="s">
         <v>34</v>
@@ -13962,16 +13959,16 @@
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>46</v>
@@ -13982,16 +13979,16 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>46</v>
@@ -14002,16 +13999,16 @@
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>46</v>
@@ -14022,16 +14019,16 @@
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>46</v>
@@ -14042,16 +14039,16 @@
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>46</v>
@@ -14062,16 +14059,16 @@
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>46</v>
@@ -14082,16 +14079,16 @@
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>46</v>
@@ -14102,16 +14099,16 @@
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>46</v>
@@ -14122,16 +14119,16 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>46</v>
@@ -14142,16 +14139,16 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>46</v>
@@ -14162,16 +14159,16 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>46</v>
@@ -14182,16 +14179,16 @@
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>46</v>
@@ -14202,16 +14199,16 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>46</v>
@@ -14222,16 +14219,16 @@
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>46</v>
@@ -14242,16 +14239,16 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>46</v>
@@ -14262,16 +14259,16 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>46</v>
@@ -14282,16 +14279,16 @@
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>46</v>
@@ -14302,16 +14299,16 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>46</v>
@@ -14322,16 +14319,16 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>46</v>
@@ -14342,16 +14339,16 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>46</v>
@@ -14362,16 +14359,16 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>69</v>
@@ -14382,16 +14379,16 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C23" s="57" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>69</v>
@@ -14402,16 +14399,16 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C24" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>73</v>
@@ -14422,16 +14419,16 @@
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C25" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>73</v>
@@ -14442,16 +14439,16 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="41" t="s">
         <v>169</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>172</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>77</v>
@@ -14462,16 +14459,16 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>77</v>
@@ -14482,16 +14479,16 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E28" s="41" t="s">
         <v>77</v>
@@ -14502,16 +14499,16 @@
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C29" s="54" t="s">
         <v>81</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>77</v>
@@ -14522,7 +14519,7 @@
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
@@ -14531,7 +14528,7 @@
         <v>83</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>84</v>
@@ -14542,16 +14539,16 @@
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>84</v>
@@ -14562,16 +14559,16 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>84</v>
@@ -14582,7 +14579,7 @@
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>88</v>
@@ -14591,7 +14588,7 @@
         <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>84</v>
@@ -14602,7 +14599,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>89</v>
@@ -14611,7 +14608,7 @@
         <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>84</v>
@@ -14622,7 +14619,7 @@
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>90</v>
@@ -14631,7 +14628,7 @@
         <v>90</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>84</v>
@@ -14642,7 +14639,7 @@
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>92</v>
@@ -14651,7 +14648,7 @@
         <v>92</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>93</v>
@@ -14662,16 +14659,16 @@
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>93</v>
@@ -14682,7 +14679,7 @@
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>96</v>
@@ -14691,7 +14688,7 @@
         <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>93</v>
@@ -14702,7 +14699,7 @@
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>97</v>
@@ -14711,7 +14708,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>93</v>
@@ -14722,7 +14719,7 @@
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>98</v>
@@ -14731,7 +14728,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>93</v>
@@ -14742,7 +14739,7 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>100</v>
@@ -14751,7 +14748,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E41" s="48" t="s">
         <v>101</v>
@@ -14762,16 +14759,16 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C42" s="48" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E42" s="48" t="s">
         <v>101</v>
@@ -14782,7 +14779,7 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>104</v>
@@ -14791,7 +14788,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E43" s="48" t="s">
         <v>101</v>
@@ -14802,7 +14799,7 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>105</v>
@@ -14811,7 +14808,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E44" s="48" t="s">
         <v>101</v>
@@ -14822,7 +14819,7 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>106</v>
@@ -14831,7 +14828,7 @@
         <v>106</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>101</v>
@@ -14842,16 +14839,16 @@
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C46" s="48" t="s">
         <v>108</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E46" s="48" t="s">
         <v>109</v>
@@ -14862,16 +14859,16 @@
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C47" s="48" t="s">
         <v>111</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E47" s="48" t="s">
         <v>109</v>
@@ -14882,16 +14879,16 @@
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C48" s="48" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E48" s="48" t="s">
         <v>109</v>
@@ -14902,16 +14899,16 @@
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C49" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E49" s="48" t="s">
         <v>109</v>
@@ -14922,16 +14919,16 @@
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="48" t="s">
         <v>154</v>
-      </c>
-      <c r="B50" s="48" t="s">
-        <v>157</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E50" s="48" t="s">
         <v>109</v>
@@ -14942,16 +14939,16 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>109</v>
@@ -14962,16 +14959,16 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>116</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>109</v>
@@ -14982,36 +14979,36 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>118</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>120</v>
+        <v>518</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>109</v>
@@ -15022,16 +15019,16 @@
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>121</v>
+        <v>519</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E55" s="53" t="s">
         <v>109</v>
@@ -15042,231 +15039,231 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E56" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C57" s="41" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>109</v>
       </c>
       <c r="F57" s="41" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E58" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F59" s="48" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F60" s="48" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F61" s="48" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C62" s="48" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>109</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="48" t="s">
-        <v>143</v>
-      </c>
       <c r="C63" s="48" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G63" s="42"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="48" t="s">
-        <v>143</v>
-      </c>
       <c r="C64" s="48" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E64" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F64" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B65" s="42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E65" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F65" s="46"/>
       <c r="G65" s="42" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C66" s="44" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D66" s="44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E66" s="44" t="s">
         <v>109</v>
       </c>
       <c r="F66" s="43"/>
       <c r="G66" s="42" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -15311,7 +15308,7 @@
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
       <c r="B1" s="257" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C1" s="257"/>
       <c r="D1" s="257"/>
@@ -15338,172 +15335,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H2" s="256" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="W2" s="256" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="X2" s="102" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AB2" s="256" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AL2" s="256" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AZ2" s="256" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BJ2" s="256" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15514,78 +15511,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H3" s="256"/>
       <c r="I3" s="101" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="W3" s="256"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AB3" s="256"/>
       <c r="AC3" s="98" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15594,273 +15591,273 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AL3" s="256"/>
       <c r="AM3" s="98" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AZ3" s="256"/>
       <c r="BA3" s="97" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="BJ3" s="256"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H4" s="256"/>
       <c r="I4" s="101" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="W4" s="256"/>
       <c r="X4" s="99" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AB4" s="256"/>
       <c r="AC4" s="98" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AL4" s="256"/>
       <c r="AM4" s="98" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AZ4" s="256"/>
       <c r="BA4" s="97" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="BJ4" s="256"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
@@ -15876,25 +15873,25 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q5" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="Q5" s="74" t="s">
-        <v>225</v>
-      </c>
       <c r="R5" s="74" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="S5" s="74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="T5" s="74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="U5" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15917,10 +15914,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15928,10 +15925,10 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
@@ -15944,25 +15941,25 @@
       <c r="AQ5" s="92"/>
       <c r="AR5" s="92"/>
       <c r="AS5" s="74" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AT5" s="74" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AU5" s="74" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AV5" s="74" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AW5" s="74" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AX5" s="74" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AY5" s="74" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -15984,25 +15981,25 @@
     </row>
     <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -16010,49 +16007,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16061,47 +16058,47 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="74" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AN6" s="74" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AO6" s="74" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AP6" s="74" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AQ6" s="74" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AR6" s="74" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AS6" s="92"/>
       <c r="AT6" s="92"/>
@@ -16109,10 +16106,10 @@
       <c r="AV6" s="92"/>
       <c r="AW6" s="92"/>
       <c r="AX6" s="74" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AY6" s="74" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16134,22 +16131,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16184,22 +16181,22 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
@@ -16218,7 +16215,7 @@
       <c r="AW7" s="75"/>
       <c r="AX7" s="75"/>
       <c r="AY7" s="74" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16240,25 +16237,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16278,23 +16275,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16346,25 +16343,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16384,23 +16381,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16408,22 +16405,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16442,7 +16439,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16464,25 +16461,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16502,23 +16499,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16526,22 +16523,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16560,7 +16557,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16582,25 +16579,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16620,23 +16617,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16644,22 +16641,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16678,7 +16675,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16700,25 +16697,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16738,23 +16735,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16762,22 +16759,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16796,7 +16793,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16816,27 +16813,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="74" t="s">
         <v>231</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="C13" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="77" t="s">
-        <v>236</v>
-      </c>
-      <c r="F13" s="77" t="s">
-        <v>235</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>234</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16856,23 +16853,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16924,25 +16921,25 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B14" s="78" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="77" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="F14" s="77" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>232</v>
-      </c>
       <c r="G14" s="74" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
@@ -16952,43 +16949,43 @@
         <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K14" s="74" t="s">
+        <v>211</v>
+      </c>
+      <c r="L14" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="M14" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="N14" s="74" t="s">
+        <v>215</v>
+      </c>
+      <c r="O14" s="74" t="s">
         <v>214</v>
       </c>
-      <c r="L14" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="M14" s="74" t="s">
+      <c r="P14" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="N14" s="74" t="s">
-        <v>218</v>
-      </c>
-      <c r="O14" s="74" t="s">
-        <v>217</v>
-      </c>
-      <c r="P14" s="74" t="s">
+      <c r="Q14" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="Q14" s="74" t="s">
-        <v>225</v>
-      </c>
       <c r="R14" s="74" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S14" s="74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="T14" s="74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="U14" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V14" s="74" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -17003,72 +17000,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD14" s="74" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AE14" s="74" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AF14" s="74" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG14" s="74" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AH14" s="74" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AI14" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AN14" s="74" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AO14" s="74" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AP14" s="74" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AQ14" s="74" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AR14" s="74" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AS14" s="74" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AT14" s="74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AU14" s="74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AV14" s="74" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AW14" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -17090,25 +17087,25 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
@@ -17118,43 +17115,43 @@
         <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K15" s="74" t="s">
+        <v>211</v>
+      </c>
+      <c r="L15" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="M15" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="N15" s="74" t="s">
+        <v>215</v>
+      </c>
+      <c r="O15" s="74" t="s">
         <v>214</v>
       </c>
-      <c r="L15" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="M15" s="74" t="s">
+      <c r="P15" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="N15" s="74" t="s">
-        <v>218</v>
-      </c>
-      <c r="O15" s="74" t="s">
-        <v>217</v>
-      </c>
-      <c r="P15" s="74" t="s">
+      <c r="Q15" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="Q15" s="74" t="s">
-        <v>225</v>
-      </c>
       <c r="R15" s="74" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S15" s="74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="T15" s="74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="U15" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V15" s="74" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17169,72 +17166,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD15" s="74" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AE15" s="74" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AF15" s="74" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG15" s="74" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AH15" s="74" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AI15" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AN15" s="74" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AO15" s="74" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AP15" s="74" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AQ15" s="74" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AR15" s="74" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AS15" s="74" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AT15" s="74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AU15" s="74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AV15" s="74" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AW15" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17261,7 +17258,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17529,7 +17526,7 @@
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="259" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C1" s="259"/>
       <c r="D1" s="259"/>
@@ -17547,172 +17544,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17723,78 +17720,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17803,255 +17800,255 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -18060,10 +18057,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18244,7 +18241,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18253,10 +18250,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18456,7 +18453,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18465,10 +18462,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18574,7 +18571,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18583,10 +18580,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18683,7 +18680,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18692,10 +18689,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18862,7 +18859,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18871,10 +18868,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18998,7 +18995,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -19007,10 +19004,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19134,7 +19131,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -19143,10 +19140,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19276,7 +19273,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19285,10 +19282,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19385,7 +19382,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19394,10 +19391,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19607,7 +19604,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19616,10 +19613,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19834,7 +19831,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -20137,7 +20134,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7161F2AA-EFD1-F948-B7A2-01F41596DC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31930DC9-534D-2849-8A1A-BC0A9312649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="521">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -2771,6 +2771,9 @@
   </si>
   <si>
     <t>CONT C JP Greffe</t>
+  </si>
+  <si>
+    <t>CONT A JP Autour du magistrat</t>
   </si>
 </sst>
 </file>
@@ -13924,7 +13927,7 @@
   <sheetPr codeName="Feuil14">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" style="41" bestFit="1" customWidth="1"/>
@@ -15225,49 +15228,69 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="47" t="s">
+      <c r="A65" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="48" t="s">
+        <v>520</v>
+      </c>
+      <c r="D65" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="C65" s="42" t="s">
+      <c r="C66" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="42" t="s">
+      <c r="D66" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="E65" s="42" t="s">
+      <c r="E66" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="F65" s="46"/>
-      <c r="G65" s="42" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="B66" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D66" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F66" s="43"/>
+      <c r="F66" s="46"/>
       <c r="G66" s="42" t="s">
         <v>133</v>
       </c>
     </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="43"/>
+      <c r="G67" s="42" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F66" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:F67" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="74" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -16813,7 +16836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
         <v>228</v>
       </c>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C175DC4F-D524-694E-A1E8-046EB5A40464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFF230F-D554-BF4B-801A-5BCCA5A7E477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETPT A-JUST'!$A$2:$DN$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ETPT Format DDG'!$A$2:$DT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Table_Fonctions!$A$1:$F$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="523">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -2777,6 +2777,9 @@
   </si>
   <si>
     <t>JA VIF</t>
+  </si>
+  <si>
+    <t>CONT A JP Autour du magistrat</t>
   </si>
 </sst>
 </file>
@@ -4592,6 +4595,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4678,12 +4687,6 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5166,9 +5169,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5206,7 +5209,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5312,7 +5315,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5454,7 +5457,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5483,11 +5486,11 @@
       <c r="B1" s="197" t="s">
         <v>492</v>
       </c>
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="235" t="s">
         <v>493</v>
       </c>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
       <c r="F1" s="198"/>
       <c r="H1" s="28" t="s">
         <v>0</v>
@@ -5496,11 +5499,11 @@
     <row r="2" spans="1:8" s="202" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="236" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
       <c r="F2" s="201"/>
       <c r="H2" s="28" t="s">
         <v>0</v>
@@ -5524,10 +5527,10 @@
       <c r="D4" s="207" t="s">
         <v>497</v>
       </c>
-      <c r="E4" s="240" t="s">
+      <c r="E4" s="242" t="s">
         <v>498</v>
       </c>
-      <c r="F4" s="241"/>
+      <c r="F4" s="243"/>
       <c r="G4" s="216"/>
       <c r="H4" s="28" t="s">
         <v>0</v>
@@ -5544,10 +5547,10 @@
       <c r="D5" s="213" t="s">
         <v>501</v>
       </c>
-      <c r="E5" s="242" t="s">
+      <c r="E5" s="244" t="s">
         <v>514</v>
       </c>
-      <c r="F5" s="243"/>
+      <c r="F5" s="245"/>
       <c r="G5" s="215"/>
       <c r="H5" s="28" t="s">
         <v>0</v>
@@ -5564,10 +5567,10 @@
       <c r="D6" s="214" t="s">
         <v>504</v>
       </c>
-      <c r="E6" s="244" t="s">
+      <c r="E6" s="246" t="s">
         <v>515</v>
       </c>
-      <c r="F6" s="245"/>
+      <c r="F6" s="247"/>
       <c r="G6" s="215"/>
       <c r="H6" s="28" t="s">
         <v>0</v>
@@ -5584,10 +5587,10 @@
       <c r="D7" s="214" t="s">
         <v>507</v>
       </c>
-      <c r="E7" s="244" t="s">
+      <c r="E7" s="246" t="s">
         <v>514</v>
       </c>
-      <c r="F7" s="245"/>
+      <c r="F7" s="247"/>
       <c r="G7" s="215"/>
       <c r="H7" s="28" t="s">
         <v>0</v>
@@ -5598,16 +5601,16 @@
       <c r="B8" s="223" t="s">
         <v>508</v>
       </c>
-      <c r="C8" s="235" t="s">
+      <c r="C8" s="237" t="s">
         <v>509</v>
       </c>
-      <c r="D8" s="235" t="s">
+      <c r="D8" s="237" t="s">
         <v>510</v>
       </c>
-      <c r="E8" s="246" t="s">
+      <c r="E8" s="248" t="s">
         <v>516</v>
       </c>
-      <c r="F8" s="247"/>
+      <c r="F8" s="249"/>
       <c r="G8" s="215"/>
       <c r="H8" s="28" t="s">
         <v>0</v>
@@ -5618,10 +5621,10 @@
       <c r="B9" s="224" t="s">
         <v>511</v>
       </c>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="249"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="251"/>
       <c r="G9" s="215"/>
       <c r="H9" s="28" t="s">
         <v>0</v>
@@ -5632,10 +5635,10 @@
       <c r="B10" s="225" t="s">
         <v>512</v>
       </c>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="251"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="253"/>
       <c r="G10" s="215"/>
       <c r="H10" s="28" t="s">
         <v>0</v>
@@ -5655,11 +5658,11 @@
     <row r="12" spans="1:8" s="28" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
-      <c r="C12" s="239" t="s">
+      <c r="C12" s="241" t="s">
         <v>513</v>
       </c>
-      <c r="D12" s="239"/>
-      <c r="E12" s="239"/>
+      <c r="D12" s="241"/>
+      <c r="E12" s="241"/>
       <c r="F12" s="218"/>
       <c r="H12" s="28" t="s">
         <v>0</v>
@@ -5673,14 +5676,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="237"/>
-      <c r="C14" s="237"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="237"/>
-      <c r="F14" s="238"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="239"/>
+      <c r="F14" s="240"/>
       <c r="H14" s="28" t="s">
         <v>0</v>
       </c>
@@ -5725,16 +5728,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="262" t="s">
         <v>481</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
       <c r="I1" s="112"/>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -5773,7 +5776,7 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -5806,13 +5809,13 @@
       <c r="R2" s="155" t="s">
         <v>434</v>
       </c>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="258" t="s">
+      <c r="U2" s="260" t="s">
         <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -5842,7 +5845,7 @@
       <c r="AD2" s="155" t="s">
         <v>431</v>
       </c>
-      <c r="AE2" s="258" t="s">
+      <c r="AE2" s="260" t="s">
         <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -5854,7 +5857,7 @@
       <c r="AH2" s="155" t="s">
         <v>479</v>
       </c>
-      <c r="AI2" s="258" t="s">
+      <c r="AI2" s="260" t="s">
         <v>478</v>
       </c>
     </row>
@@ -5868,7 +5871,7 @@
       <c r="G3" s="155" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
         <v>477</v>
       </c>
@@ -5899,11 +5902,11 @@
       <c r="R3" s="155" t="s">
         <v>412</v>
       </c>
-      <c r="S3" s="258"/>
+      <c r="S3" s="260"/>
       <c r="T3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="U3" s="258"/>
+      <c r="U3" s="260"/>
       <c r="V3" s="155" t="s">
         <v>468</v>
       </c>
@@ -5931,7 +5934,7 @@
       <c r="AD3" s="155" t="s">
         <v>460</v>
       </c>
-      <c r="AE3" s="258"/>
+      <c r="AE3" s="260"/>
       <c r="AF3" s="155" t="s">
         <v>459</v>
       </c>
@@ -5941,7 +5944,7 @@
       <c r="AH3" s="155" t="s">
         <v>389</v>
       </c>
-      <c r="AI3" s="258"/>
+      <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -5963,7 +5966,7 @@
       <c r="G4" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
         <v>458</v>
       </c>
@@ -5994,11 +5997,11 @@
       <c r="R4" s="155" t="s">
         <v>361</v>
       </c>
-      <c r="S4" s="258"/>
+      <c r="S4" s="260"/>
       <c r="T4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="U4" s="258"/>
+      <c r="U4" s="260"/>
       <c r="V4" s="155" t="s">
         <v>449</v>
       </c>
@@ -6026,7 +6029,7 @@
       <c r="AD4" s="155" t="s">
         <v>441</v>
       </c>
-      <c r="AE4" s="258"/>
+      <c r="AE4" s="260"/>
       <c r="AF4" s="155" t="s">
         <v>440</v>
       </c>
@@ -6036,7 +6039,7 @@
       <c r="AH4" s="155" t="s">
         <v>336</v>
       </c>
-      <c r="AI4" s="258"/>
+      <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -7140,13 +7143,13 @@
       <c r="G2" s="155" t="s">
         <v>434</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="258" t="s">
+      <c r="J2" s="260" t="s">
         <v>432</v>
       </c>
     </row>
@@ -7160,11 +7163,11 @@
       <c r="G3" s="155" t="s">
         <v>412</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="J3" s="258"/>
+      <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -7186,11 +7189,11 @@
       <c r="G4" s="155" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="J4" s="258"/>
+      <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -7589,7 +7592,7 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -7634,7 +7637,7 @@
       <c r="V2" s="154" t="s">
         <v>434</v>
       </c>
-      <c r="W2" s="258" t="s">
+      <c r="W2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -7649,7 +7652,7 @@
       <c r="AA2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="AB2" s="258" t="s">
+      <c r="AB2" s="260" t="s">
         <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -7679,7 +7682,7 @@
       <c r="AK2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AL2" s="258" t="s">
+      <c r="AL2" s="260" t="s">
         <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -7721,7 +7724,7 @@
       <c r="AY2" s="152" t="s">
         <v>429</v>
       </c>
-      <c r="AZ2" s="258" t="s">
+      <c r="AZ2" s="260" t="s">
         <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -7751,7 +7754,7 @@
       <c r="BI2" s="151" t="s">
         <v>427</v>
       </c>
-      <c r="BJ2" s="258" t="s">
+      <c r="BJ2" s="260" t="s">
         <v>426</v>
       </c>
       <c r="BK2"/>
@@ -7766,7 +7769,7 @@
       <c r="G3" s="155" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
         <v>424</v>
       </c>
@@ -7807,7 +7810,7 @@
       <c r="V3" s="154" t="s">
         <v>412</v>
       </c>
-      <c r="W3" s="258"/>
+      <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>411</v>
@@ -7818,7 +7821,7 @@
       <c r="AA3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="AB3" s="258"/>
+      <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
         <v>408</v>
       </c>
@@ -7846,7 +7849,7 @@
       <c r="AK3" s="152" t="s">
         <v>402</v>
       </c>
-      <c r="AL3" s="258"/>
+      <c r="AL3" s="260"/>
       <c r="AM3" s="152" t="s">
         <v>401</v>
       </c>
@@ -7886,7 +7889,7 @@
       <c r="AY3" s="152" t="s">
         <v>389</v>
       </c>
-      <c r="AZ3" s="258"/>
+      <c r="AZ3" s="260"/>
       <c r="BA3" s="151" t="s">
         <v>388</v>
       </c>
@@ -7914,7 +7917,7 @@
       <c r="BI3" s="151" t="s">
         <v>380</v>
       </c>
-      <c r="BJ3" s="258"/>
+      <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
@@ -7936,7 +7939,7 @@
       <c r="G4" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="154" t="s">
         <v>374</v>
       </c>
@@ -7979,7 +7982,7 @@
       <c r="V4" s="154" t="s">
         <v>361</v>
       </c>
-      <c r="W4" s="258"/>
+      <c r="W4" s="260"/>
       <c r="X4" s="153" t="s">
         <v>360</v>
       </c>
@@ -7992,7 +7995,7 @@
       <c r="AA4" s="153" t="s">
         <v>357</v>
       </c>
-      <c r="AB4" s="258"/>
+      <c r="AB4" s="260"/>
       <c r="AC4" s="152" t="s">
         <v>356</v>
       </c>
@@ -8020,7 +8023,7 @@
       <c r="AK4" s="152" t="s">
         <v>349</v>
       </c>
-      <c r="AL4" s="258"/>
+      <c r="AL4" s="260"/>
       <c r="AM4" s="152" t="s">
         <v>348</v>
       </c>
@@ -8060,7 +8063,7 @@
       <c r="AY4" s="152" t="s">
         <v>336</v>
       </c>
-      <c r="AZ4" s="258"/>
+      <c r="AZ4" s="260"/>
       <c r="BA4" s="151" t="s">
         <v>335</v>
       </c>
@@ -8088,7 +8091,7 @@
       <c r="BI4" s="151" t="s">
         <v>327</v>
       </c>
-      <c r="BJ4" s="258"/>
+      <c r="BJ4" s="260"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -10804,7 +10807,7 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
@@ -10837,13 +10840,13 @@
       <c r="R2" s="155" t="s">
         <v>434</v>
       </c>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="258" t="s">
+      <c r="U2" s="260" t="s">
         <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
@@ -10873,7 +10876,7 @@
       <c r="AD2" s="155" t="s">
         <v>431</v>
       </c>
-      <c r="AE2" s="258" t="s">
+      <c r="AE2" s="260" t="s">
         <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
@@ -10885,7 +10888,7 @@
       <c r="AH2" s="155" t="s">
         <v>479</v>
       </c>
-      <c r="AI2" s="258" t="s">
+      <c r="AI2" s="260" t="s">
         <v>478</v>
       </c>
     </row>
@@ -10899,7 +10902,7 @@
       <c r="G3" s="155" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
         <v>477</v>
       </c>
@@ -10930,11 +10933,11 @@
       <c r="R3" s="155" t="s">
         <v>412</v>
       </c>
-      <c r="S3" s="258"/>
+      <c r="S3" s="260"/>
       <c r="T3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="U3" s="258"/>
+      <c r="U3" s="260"/>
       <c r="V3" s="155" t="s">
         <v>468</v>
       </c>
@@ -10962,7 +10965,7 @@
       <c r="AD3" s="155" t="s">
         <v>460</v>
       </c>
-      <c r="AE3" s="258"/>
+      <c r="AE3" s="260"/>
       <c r="AF3" s="155" t="s">
         <v>459</v>
       </c>
@@ -10972,7 +10975,7 @@
       <c r="AH3" s="155" t="s">
         <v>389</v>
       </c>
-      <c r="AI3" s="258"/>
+      <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
@@ -10994,7 +10997,7 @@
       <c r="G4" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
         <v>458</v>
       </c>
@@ -11025,11 +11028,11 @@
       <c r="R4" s="155" t="s">
         <v>361</v>
       </c>
-      <c r="S4" s="258"/>
+      <c r="S4" s="260"/>
       <c r="T4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="U4" s="258"/>
+      <c r="U4" s="260"/>
       <c r="V4" s="155" t="s">
         <v>449</v>
       </c>
@@ -11057,7 +11060,7 @@
       <c r="AD4" s="155" t="s">
         <v>441</v>
       </c>
-      <c r="AE4" s="258"/>
+      <c r="AE4" s="260"/>
       <c r="AF4" s="155" t="s">
         <v>440</v>
       </c>
@@ -11067,7 +11070,7 @@
       <c r="AH4" s="155" t="s">
         <v>336</v>
       </c>
-      <c r="AI4" s="258"/>
+      <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
@@ -12799,13 +12802,13 @@
       <c r="G2" s="155" t="s">
         <v>434</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="258" t="s">
+      <c r="J2" s="260" t="s">
         <v>432</v>
       </c>
     </row>
@@ -12819,11 +12822,11 @@
       <c r="G3" s="155" t="s">
         <v>412</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="J3" s="258"/>
+      <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
@@ -12845,11 +12848,11 @@
       <c r="G4" s="155" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="J4" s="258"/>
+      <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
@@ -13554,14 +13557,14 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="EA1" s="252" t="s">
+      <c r="EA1" s="254" t="s">
         <v>490</v>
       </c>
-      <c r="EB1" s="252"/>
-      <c r="EC1" s="252"/>
-      <c r="ED1" s="252"/>
-      <c r="EE1" s="252"/>
-      <c r="EF1" s="252"/>
+      <c r="EB1" s="254"/>
+      <c r="EC1" s="254"/>
+      <c r="ED1" s="254"/>
+      <c r="EE1" s="254"/>
+      <c r="EF1" s="254"/>
       <c r="EG1" s="8" t="s">
         <v>0</v>
       </c>
@@ -13686,20 +13689,20 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="253" t="s">
+      <c r="E4" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="254"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="253" t="s">
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="255" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="254"/>
-      <c r="L4" s="254"/>
-      <c r="M4" s="254"/>
-      <c r="N4" s="255"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
+      <c r="M4" s="256"/>
+      <c r="N4" s="257"/>
       <c r="O4" s="30" t="s">
         <v>28</v>
       </c>
@@ -13936,7 +13939,7 @@
   <sheetPr codeName="Feuil14">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" style="41" bestFit="1" customWidth="1"/>
@@ -15176,19 +15179,19 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="261" t="s">
+      <c r="A62" s="233" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="262" t="s">
+      <c r="B62" s="234" t="s">
         <v>520</v>
       </c>
-      <c r="C62" s="262" t="s">
+      <c r="C62" s="234" t="s">
         <v>521</v>
       </c>
-      <c r="D62" s="262" t="s">
+      <c r="D62" s="234" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="262" t="s">
+      <c r="E62" s="234" t="s">
         <v>109</v>
       </c>
       <c r="F62" s="48" t="s">
@@ -15237,49 +15240,69 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="47" t="s">
+      <c r="A65" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="D65" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="42" t="s">
+      <c r="C66" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="42" t="s">
+      <c r="D66" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="E65" s="42" t="s">
+      <c r="E66" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="F65" s="46"/>
-      <c r="G65" s="42" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B66" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="C66" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E66" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F66" s="43"/>
+      <c r="F66" s="46"/>
       <c r="G66" s="42" t="s">
         <v>136</v>
       </c>
     </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E67" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="43"/>
+      <c r="G67" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F66" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:F67" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="74" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -15319,16 +15342,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
-      <c r="B1" s="257" t="s">
+      <c r="B1" s="259" t="s">
         <v>437</v>
       </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
-      <c r="G1" s="257"/>
-      <c r="H1" s="257"/>
-      <c r="I1" s="257"/>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
       <c r="AC1" s="106"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
@@ -15349,7 +15372,7 @@
       <c r="G2" s="102" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="256" t="s">
+      <c r="H2" s="258" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="101" t="s">
@@ -15394,7 +15417,7 @@
       <c r="V2" s="101" t="s">
         <v>434</v>
       </c>
-      <c r="W2" s="256" t="s">
+      <c r="W2" s="258" t="s">
         <v>433</v>
       </c>
       <c r="X2" s="102" t="s">
@@ -15409,7 +15432,7 @@
       <c r="AA2" s="102" t="s">
         <v>150</v>
       </c>
-      <c r="AB2" s="256" t="s">
+      <c r="AB2" s="258" t="s">
         <v>432</v>
       </c>
       <c r="AC2" s="98" t="s">
@@ -15439,7 +15462,7 @@
       <c r="AK2" s="98" t="s">
         <v>431</v>
       </c>
-      <c r="AL2" s="256" t="s">
+      <c r="AL2" s="258" t="s">
         <v>430</v>
       </c>
       <c r="AM2" s="98" t="s">
@@ -15481,7 +15504,7 @@
       <c r="AY2" s="98" t="s">
         <v>429</v>
       </c>
-      <c r="AZ2" s="256" t="s">
+      <c r="AZ2" s="258" t="s">
         <v>428</v>
       </c>
       <c r="BA2" s="97" t="s">
@@ -15511,7 +15534,7 @@
       <c r="BI2" s="97" t="s">
         <v>427</v>
       </c>
-      <c r="BJ2" s="256" t="s">
+      <c r="BJ2" s="258" t="s">
         <v>426</v>
       </c>
     </row>
@@ -15525,7 +15548,7 @@
       <c r="G3" s="102" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="256"/>
+      <c r="H3" s="258"/>
       <c r="I3" s="101" t="s">
         <v>424</v>
       </c>
@@ -15566,7 +15589,7 @@
       <c r="V3" s="101" t="s">
         <v>412</v>
       </c>
-      <c r="W3" s="256"/>
+      <c r="W3" s="258"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
         <v>411</v>
@@ -15577,7 +15600,7 @@
       <c r="AA3" s="102" t="s">
         <v>409</v>
       </c>
-      <c r="AB3" s="256"/>
+      <c r="AB3" s="258"/>
       <c r="AC3" s="98" t="s">
         <v>408</v>
       </c>
@@ -15605,7 +15628,7 @@
       <c r="AK3" s="98" t="s">
         <v>402</v>
       </c>
-      <c r="AL3" s="256"/>
+      <c r="AL3" s="258"/>
       <c r="AM3" s="98" t="s">
         <v>401</v>
       </c>
@@ -15645,7 +15668,7 @@
       <c r="AY3" s="98" t="s">
         <v>389</v>
       </c>
-      <c r="AZ3" s="256"/>
+      <c r="AZ3" s="258"/>
       <c r="BA3" s="97" t="s">
         <v>388</v>
       </c>
@@ -15673,7 +15696,7 @@
       <c r="BI3" s="97" t="s">
         <v>380</v>
       </c>
-      <c r="BJ3" s="256"/>
+      <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
@@ -15695,7 +15718,7 @@
       <c r="G4" s="102" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="256"/>
+      <c r="H4" s="258"/>
       <c r="I4" s="101" t="s">
         <v>374</v>
       </c>
@@ -15738,7 +15761,7 @@
       <c r="V4" s="100" t="s">
         <v>361</v>
       </c>
-      <c r="W4" s="256"/>
+      <c r="W4" s="258"/>
       <c r="X4" s="99" t="s">
         <v>360</v>
       </c>
@@ -15751,7 +15774,7 @@
       <c r="AA4" s="99" t="s">
         <v>357</v>
       </c>
-      <c r="AB4" s="256"/>
+      <c r="AB4" s="258"/>
       <c r="AC4" s="98" t="s">
         <v>356</v>
       </c>
@@ -15779,7 +15802,7 @@
       <c r="AK4" s="98" t="s">
         <v>349</v>
       </c>
-      <c r="AL4" s="256"/>
+      <c r="AL4" s="258"/>
       <c r="AM4" s="98" t="s">
         <v>348</v>
       </c>
@@ -15819,7 +15842,7 @@
       <c r="AY4" s="98" t="s">
         <v>336</v>
       </c>
-      <c r="AZ4" s="256"/>
+      <c r="AZ4" s="258"/>
       <c r="BA4" s="97" t="s">
         <v>335</v>
       </c>
@@ -15847,7 +15870,7 @@
       <c r="BI4" s="97" t="s">
         <v>327</v>
       </c>
-      <c r="BJ4" s="256"/>
+      <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
@@ -16825,7 +16848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
         <v>231</v>
       </c>
@@ -17537,16 +17560,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="259" t="s">
+      <c r="B1" s="261" t="s">
         <v>437</v>
       </c>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
     </row>
     <row r="2" spans="1:62" s="112" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="158"/>
@@ -17558,7 +17581,7 @@
       <c r="G2" s="155" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="260" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
@@ -17603,7 +17626,7 @@
       <c r="V2" s="154" t="s">
         <v>434</v>
       </c>
-      <c r="W2" s="258" t="s">
+      <c r="W2" s="260" t="s">
         <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
@@ -17618,7 +17641,7 @@
       <c r="AA2" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="AB2" s="258" t="s">
+      <c r="AB2" s="260" t="s">
         <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
@@ -17648,7 +17671,7 @@
       <c r="AK2" s="152" t="s">
         <v>431</v>
       </c>
-      <c r="AL2" s="258" t="s">
+      <c r="AL2" s="260" t="s">
         <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
@@ -17690,7 +17713,7 @@
       <c r="AY2" s="152" t="s">
         <v>429</v>
       </c>
-      <c r="AZ2" s="258" t="s">
+      <c r="AZ2" s="260" t="s">
         <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
@@ -17720,7 +17743,7 @@
       <c r="BI2" s="151" t="s">
         <v>427</v>
       </c>
-      <c r="BJ2" s="258" t="s">
+      <c r="BJ2" s="260" t="s">
         <v>426</v>
       </c>
     </row>
@@ -17734,7 +17757,7 @@
       <c r="G3" s="155" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="258"/>
+      <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
         <v>424</v>
       </c>
@@ -17775,7 +17798,7 @@
       <c r="V3" s="154" t="s">
         <v>412</v>
       </c>
-      <c r="W3" s="258"/>
+      <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
         <v>411</v>
@@ -17786,7 +17809,7 @@
       <c r="AA3" s="155" t="s">
         <v>409</v>
       </c>
-      <c r="AB3" s="258"/>
+      <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
         <v>408</v>
       </c>
@@ -17814,7 +17837,7 @@
       <c r="AK3" s="152" t="s">
         <v>402</v>
       </c>
-      <c r="AL3" s="258"/>
+      <c r="AL3" s="260"/>
       <c r="AM3" s="152" t="s">
         <v>401</v>
       </c>
@@ -17854,7 +17877,7 @@
       <c r="AY3" s="152" t="s">
         <v>389</v>
       </c>
-      <c r="AZ3" s="258"/>
+      <c r="AZ3" s="260"/>
       <c r="BA3" s="151" t="s">
         <v>388</v>
       </c>
@@ -17882,7 +17905,7 @@
       <c r="BI3" s="151" t="s">
         <v>380</v>
       </c>
-      <c r="BJ3" s="258"/>
+      <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
@@ -17904,7 +17927,7 @@
       <c r="G4" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="258"/>
+      <c r="H4" s="260"/>
       <c r="I4" s="154" t="s">
         <v>374</v>
       </c>
@@ -17947,7 +17970,7 @@
       <c r="V4" s="154" t="s">
         <v>361</v>
       </c>
-      <c r="W4" s="258"/>
+      <c r="W4" s="260"/>
       <c r="X4" s="153" t="s">
         <v>360</v>
       </c>
@@ -17960,7 +17983,7 @@
       <c r="AA4" s="153" t="s">
         <v>357</v>
       </c>
-      <c r="AB4" s="258"/>
+      <c r="AB4" s="260"/>
       <c r="AC4" s="152" t="s">
         <v>356</v>
       </c>
@@ -17988,7 +18011,7 @@
       <c r="AK4" s="152" t="s">
         <v>349</v>
       </c>
-      <c r="AL4" s="258"/>
+      <c r="AL4" s="260"/>
       <c r="AM4" s="152" t="s">
         <v>348</v>
       </c>
@@ -18028,7 +18051,7 @@
       <c r="AY4" s="152" t="s">
         <v>336</v>
       </c>
-      <c r="AZ4" s="258"/>
+      <c r="AZ4" s="260"/>
       <c r="BA4" s="151" t="s">
         <v>335</v>
       </c>
@@ -18056,7 +18079,7 @@
       <c r="BI4" s="151" t="s">
         <v>327</v>
       </c>
-      <c r="BJ4" s="258"/>
+      <c r="BJ4" s="260"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31930DC9-534D-2849-8A1A-BC0A9312649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCBBBAA-C534-9443-8076-9D370AC76906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="2940" yWindow="760" windowWidth="25300" windowHeight="13260" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ACCUEIL" sheetId="33" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="510">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -1262,147 +1262,6 @@
   </si>
   <si>
     <t>166-04-NC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE NS :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Temps ventilés sur la période (affaires pénales) - somme colonnes précédentes S et NS (sauf activités non spécialisées des juges spécialisées)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE S :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Temps ventilés sur la période (affaires pénales)  - somme colonnes ligne action pénale du SIEGE S 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TJ et TPR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.6 Tribunal de police + 7.7 OP contraventionnelles
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.122 Collégiales autres sections spécialisées
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.12 Collégiales JIRS crim-org
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.121 Collégiales JIRS eco-fi
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.52 cour criminelle
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.5 + 7.51 Cour d'assises JIRS et hors JIRS
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1825,121 +1684,6 @@
   </si>
   <si>
     <t>166-02-NC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE NS :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Temps ventilés sur la période (contentieux civils et sociaux) - somme colonnes précédentes S et NS (sauf activités non spécialisées des juges spécialisées)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> :
-Temps ventilés sur la période (contentieux civils et sociaux) - somme colonnes ligne action civile du SIEGE S </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2. TOTAL CONTENTIEUX JAF
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. TOTAL CONTENTIEUX SOCIAL - 1.1 Contentieux du travail
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.43 Injonctions de payer + 3.44 Saisies des rémunérations
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">4.0 Contentieux général &lt; 10000 euros
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.1 Contentieux du travail
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Pour Magistrats SIEGE NS seulement)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2774,6 +2518,86 @@
   </si>
   <si>
     <t>CONT A JP Autour du magistrat</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> :
+4. TOTAL CIVIL NON SPÉCIALISÉ - 4.0 Contentieux général &lt; 10000 euros</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE NS :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+4. TOTAL CIVIL NON SPÉCIALISÉ - 4.0 Contentieux général &lt; 10000 euros</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE S :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+7. TOTAL SIÈGE PÉNAL - 7.12. COLLÉGIALES JIRS CRIM-ORG - 7.121. COLLÉGIALES JIRS ECO-FI - 7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES - 7.5. COUR D'ASSISES HORS JIRS - 7.51. COUR D'ASSISES JIRS - 7.52. COUR CRIMINELLE - 7.6. TRIBUNAL DE POLICE - 7.7. OP CONTRAVENTIONNELLES</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE NS :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+7. TOTAL SIÈGE PÉNAL - 7.12. COLLÉGIALES JIRS CRIM-ORG - 7.121. COLLÉGIALES JIRS ECO-FI - 7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES - 7.5. COUR D'ASSISES HORS JIRS - 7.51. COUR D'ASSISES JIRS - 7.52. COUR CRIMINELLE - 7.6. TRIBUNAL DE POLICE - 7.7. OP CONTRAVENTIONNELLES</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3840,7 +3664,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4675,6 +4499,15 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5472,10 +5305,10 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="C1" s="233" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="D1" s="233"/>
       <c r="E1" s="233"/>
@@ -5488,7 +5321,7 @@
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
       <c r="C2" s="234" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="D2" s="234"/>
       <c r="E2" s="234"/>
@@ -5507,16 +5340,16 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C4" s="207" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="D4" s="207" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="E4" s="240" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="F4" s="241"/>
       <c r="G4" s="216"/>
@@ -5527,16 +5360,16 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
+        <v>481</v>
+      </c>
+      <c r="C5" s="213" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" s="213" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" s="242" t="s">
         <v>496</v>
-      </c>
-      <c r="C5" s="213" t="s">
-        <v>497</v>
-      </c>
-      <c r="D5" s="213" t="s">
-        <v>498</v>
-      </c>
-      <c r="E5" s="242" t="s">
-        <v>511</v>
       </c>
       <c r="F5" s="243"/>
       <c r="G5" s="215"/>
@@ -5547,16 +5380,16 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C6" s="214" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="D6" s="214" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="E6" s="244" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="F6" s="245"/>
       <c r="G6" s="215"/>
@@ -5567,16 +5400,16 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C7" s="214" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="D7" s="214" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="E7" s="244" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="F7" s="245"/>
       <c r="G7" s="215"/>
@@ -5587,16 +5420,16 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="C8" s="235" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="D8" s="235" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="E8" s="246" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="F8" s="247"/>
       <c r="G8" s="215"/>
@@ -5607,7 +5440,7 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="C9" s="235"/>
       <c r="D9" s="235"/>
@@ -5621,7 +5454,7 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="236"/>
@@ -5647,7 +5480,7 @@
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
       <c r="C12" s="239" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
@@ -5717,7 +5550,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="260" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -5762,91 +5595,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>147</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5857,181 +5690,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6040,10 +5873,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6147,7 +5980,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6156,10 +5989,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6208,7 +6041,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6269,7 +6102,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6342,7 +6175,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6424,7 +6257,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6497,7 +6330,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6570,7 +6403,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6646,7 +6479,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6716,7 +6549,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6829,7 +6662,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -7077,7 +6910,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -7112,7 +6945,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7129,16 +6962,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>147</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7149,43 +6982,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7194,10 +7027,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7218,7 +7051,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7245,7 +7078,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7272,7 +7105,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7299,7 +7132,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7326,7 +7159,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7353,7 +7186,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7380,7 +7213,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7410,7 +7243,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7504,12 +7337,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7578,55 +7411,55 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="X2" s="155" t="s">
         <v>147</v>
@@ -7641,109 +7474,109 @@
         <v>147</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7755,78 +7588,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7835,249 +7668,249 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="BJ4" s="258"/>
       <c r="BK4"/>
@@ -8090,10 +7923,10 @@
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8305,10 +8138,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -10674,7 +10507,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10719,12 +10552,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10793,91 +10626,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="S2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="T2" s="155" t="s">
         <v>147</v>
       </c>
       <c r="U2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AE2" s="258" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AI2" s="258" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10888,190 +10721,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="S3" s="258"/>
       <c r="T3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="U3" s="258"/>
       <c r="V3" s="155" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="AE3" s="258"/>
       <c r="AF3" s="155" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AI3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="S4" s="258"/>
       <c r="T4" s="155" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="U4" s="258"/>
       <c r="V4" s="155" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="AE4" s="258"/>
       <c r="AF4" s="155" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AI4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11192,7 +11025,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11201,10 +11034,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11325,7 +11158,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11458,7 +11291,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11591,7 +11424,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11724,7 +11557,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11857,7 +11690,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11990,7 +11823,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -12123,7 +11956,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12256,7 +12089,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12389,7 +12222,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12651,7 +12484,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12673,7 +12506,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12714,12 +12547,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12788,16 +12621,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="I2" s="155" t="s">
         <v>147</v>
       </c>
       <c r="J2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12808,52 +12641,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="J3" s="258"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="155" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="J4" s="258"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12874,7 +12707,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12907,7 +12740,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12940,7 +12773,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12973,7 +12806,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -13006,7 +12839,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13039,7 +12872,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13072,7 +12905,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13105,7 +12938,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13164,7 +12997,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13212,7 +13045,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13535,7 +13368,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13546,7 +13379,7 @@
         <v>6</v>
       </c>
       <c r="EA1" s="252" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="EB1" s="252"/>
       <c r="EC1" s="252"/>
@@ -13633,7 +13466,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13882,7 +13715,7 @@
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -15008,7 +14841,7 @@
         <v>139</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="D54" s="48" t="s">
         <v>134</v>
@@ -15028,7 +14861,7 @@
         <v>136</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="D55" s="54" t="s">
         <v>134</v>
@@ -15194,7 +15027,7 @@
         <v>140</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="D63" s="48" t="s">
         <v>134</v>
@@ -15215,7 +15048,7 @@
         <v>140</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="D64" s="48" t="s">
         <v>134</v>
@@ -15235,7 +15068,7 @@
         <v>140</v>
       </c>
       <c r="C65" s="48" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="D65" s="48" t="s">
         <v>134</v>
@@ -15331,7 +15164,7 @@
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
       <c r="B1" s="257" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C1" s="257"/>
       <c r="D1" s="257"/>
@@ -15358,55 +15191,55 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="H2" s="256" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="W2" s="256" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="X2" s="102" t="s">
         <v>147</v>
@@ -15421,109 +15254,109 @@
         <v>147</v>
       </c>
       <c r="AB2" s="256" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AL2" s="256" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AZ2" s="256" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BJ2" s="256" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15534,78 +15367,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H3" s="256"/>
       <c r="I3" s="101" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="W3" s="256"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="AB3" s="256"/>
       <c r="AC3" s="98" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15614,253 +15447,253 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AL3" s="256"/>
       <c r="AM3" s="98" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AZ3" s="256"/>
       <c r="BA3" s="97" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="BJ3" s="256"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H4" s="256"/>
       <c r="I4" s="101" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="W4" s="256"/>
       <c r="X4" s="99" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="AB4" s="256"/>
       <c r="AC4" s="98" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AL4" s="256"/>
       <c r="AM4" s="98" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AZ4" s="256"/>
       <c r="BA4" s="97" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="BJ4" s="256"/>
     </row>
-    <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:62" s="64" customFormat="1" ht="120" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
         <v>228</v>
       </c>
@@ -15874,10 +15707,10 @@
         <v>131</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="74" t="s">
         <v>198</v>
@@ -15902,7 +15735,7 @@
         <v>222</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="S5" s="74" t="s">
         <v>203</v>
@@ -15914,7 +15747,7 @@
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15937,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15948,41 +15781,41 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="92"/>
-      <c r="AN5" s="92"/>
-      <c r="AO5" s="92"/>
-      <c r="AP5" s="92"/>
-      <c r="AQ5" s="92"/>
-      <c r="AR5" s="92"/>
-      <c r="AS5" s="74" t="s">
-        <v>315</v>
-      </c>
-      <c r="AT5" s="74" t="s">
-        <v>314</v>
-      </c>
-      <c r="AU5" s="74" t="s">
-        <v>313</v>
-      </c>
-      <c r="AV5" s="74" t="s">
-        <v>312</v>
-      </c>
-      <c r="AW5" s="74" t="s">
-        <v>311</v>
-      </c>
-      <c r="AX5" s="74" t="s">
-        <v>310</v>
-      </c>
-      <c r="AY5" s="74" t="s">
-        <v>309</v>
+      <c r="AM5" s="261"/>
+      <c r="AN5" s="261"/>
+      <c r="AO5" s="261"/>
+      <c r="AP5" s="261"/>
+      <c r="AQ5" s="261"/>
+      <c r="AR5" s="261"/>
+      <c r="AS5" s="262" t="s">
+        <v>205</v>
+      </c>
+      <c r="AT5" s="262" t="s">
+        <v>204</v>
+      </c>
+      <c r="AU5" s="262" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV5" s="262" t="s">
+        <v>202</v>
+      </c>
+      <c r="AW5" s="262" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX5" s="262" t="s">
+        <v>506</v>
+      </c>
+      <c r="AY5" s="262" t="s">
+        <v>507</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -16002,7 +15835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:62" s="64" customFormat="1" ht="339" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
         <v>228</v>
       </c>
@@ -16016,13 +15849,13 @@
         <v>131</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -16030,49 +15863,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16081,58 +15914,58 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="AN6" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="AO6" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="AP6" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="AQ6" s="74" t="s">
-        <v>285</v>
-      </c>
-      <c r="AR6" s="74" t="s">
-        <v>284</v>
-      </c>
-      <c r="AS6" s="92"/>
-      <c r="AT6" s="92"/>
-      <c r="AU6" s="92"/>
-      <c r="AV6" s="92"/>
-      <c r="AW6" s="92"/>
-      <c r="AX6" s="74" t="s">
-        <v>283</v>
-      </c>
-      <c r="AY6" s="74" t="s">
-        <v>282</v>
+      <c r="AM6" s="262" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN6" s="262" t="s">
+        <v>210</v>
+      </c>
+      <c r="AO6" s="262" t="s">
+        <v>209</v>
+      </c>
+      <c r="AP6" s="262" t="s">
+        <v>208</v>
+      </c>
+      <c r="AQ6" s="262" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR6" s="262" t="s">
+        <v>206</v>
+      </c>
+      <c r="AS6" s="261"/>
+      <c r="AT6" s="261"/>
+      <c r="AU6" s="261"/>
+      <c r="AV6" s="261"/>
+      <c r="AW6" s="261"/>
+      <c r="AX6" s="262" t="s">
+        <v>508</v>
+      </c>
+      <c r="AY6" s="262" t="s">
+        <v>509</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16225,19 +16058,19 @@
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="75"/>
-      <c r="AR7" s="75"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="75"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="75"/>
-      <c r="AW7" s="75"/>
-      <c r="AX7" s="75"/>
-      <c r="AY7" s="74" t="s">
+      <c r="AM7" s="263"/>
+      <c r="AN7" s="263"/>
+      <c r="AO7" s="263"/>
+      <c r="AP7" s="263"/>
+      <c r="AQ7" s="263"/>
+      <c r="AR7" s="263"/>
+      <c r="AS7" s="263"/>
+      <c r="AT7" s="263"/>
+      <c r="AU7" s="263"/>
+      <c r="AV7" s="263"/>
+      <c r="AW7" s="263"/>
+      <c r="AX7" s="263"/>
+      <c r="AY7" s="262" t="s">
         <v>274</v>
       </c>
       <c r="AZ7" s="65">
@@ -17549,7 +17382,7 @@
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="259" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C1" s="259"/>
       <c r="D1" s="259"/>
@@ -17567,55 +17400,55 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="X2" s="155" t="s">
         <v>147</v>
@@ -17630,109 +17463,109 @@
         <v>147</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17743,78 +17576,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="154" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="152" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17823,249 +17656,249 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="152" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="151" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="154" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="153" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="152" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="152" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="151" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="BJ4" s="258"/>
     </row>
@@ -18080,10 +17913,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18202,46 +18035,35 @@
       <c r="AQ5" s="143"/>
       <c r="AR5" s="143"/>
       <c r="AS5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AT5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AU5" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AV5" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AW5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AX5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3. TOTAL CONTENTIEUX DE LA PROTECTION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4. TOTAL CIVIL NON SPÉCIALISÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AY5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-(SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3. TOTAL CONTENTIEUX DE LA PROTECTION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS"))-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUM(AS5:AW5)</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4. TOTAL CIVIL NON SPÉCIALISÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AZ5" s="117" t="e">
@@ -18273,10 +18095,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18404,28 +18226,30 @@
       </c>
       <c r="AM6" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AN6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AO6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AP6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AQ6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AR6" s="126" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AS6" s="143"/>
@@ -18441,7 +18265,7 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AY6" s="142" t="e">
@@ -18452,8 +18276,7 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUM(AM6:AW6)</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AZ6" s="117" t="e">
@@ -20157,7 +19980,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCBBBAA-C534-9443-8076-9D370AC76906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFF230F-D554-BF4B-801A-5BCCA5A7E477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="760" windowWidth="25300" windowHeight="13260" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ACCUEIL" sheetId="33" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="523">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -410,7 +410,16 @@
     <t>VACATAIRES</t>
   </si>
   <si>
+    <t>CONT A JP</t>
+  </si>
+  <si>
     <t>CONT A JP Greffe</t>
+  </si>
+  <si>
+    <t>CONT B JP</t>
+  </si>
+  <si>
+    <t>CONT C JP</t>
   </si>
   <si>
     <t>AS</t>
@@ -1262,6 +1271,147 @@
   </si>
   <si>
     <t>166-04-NC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE NS :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Temps ventilés sur la période (affaires pénales) - somme colonnes précédentes S et NS (sauf activités non spécialisées des juges spécialisées)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE S :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Temps ventilés sur la période (affaires pénales)  - somme colonnes ligne action pénale du SIEGE S 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TJ et TPR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.6 Tribunal de police + 7.7 OP contraventionnelles
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.122 Collégiales autres sections spécialisées
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.12 Collégiales JIRS crim-org
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.121 Collégiales JIRS eco-fi
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.52 cour criminelle
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7.5 + 7.51 Cour d'assises JIRS et hors JIRS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1684,6 +1834,121 @@
   </si>
   <si>
     <t>166-02-NC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE NS :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Temps ventilés sur la période (contentieux civils et sociaux) - somme colonnes précédentes S et NS (sauf activités non spécialisées des juges spécialisées)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pour Magistrats SIEGE S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> :
+Temps ventilés sur la période (contentieux civils et sociaux) - somme colonnes ligne action civile du SIEGE S </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. TOTAL CONTENTIEUX JAF
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. TOTAL CONTENTIEUX SOCIAL - 1.1 Contentieux du travail
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.43 Injonctions de payer + 3.44 Saisies des rémunérations
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4.0 Contentieux général &lt; 10000 euros
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.1 Contentieux du travail
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pour Magistrats SIEGE NS seulement)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2508,96 +2773,13 @@
     <t>JA JP</t>
   </si>
   <si>
+    <t>JURISTE ASSISTANT Vif</t>
+  </si>
+  <si>
     <t>JA VIF</t>
   </si>
   <si>
-    <t>CONT B JP Greffe</t>
-  </si>
-  <si>
-    <t>CONT C JP Greffe</t>
-  </si>
-  <si>
     <t>CONT A JP Autour du magistrat</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> :
-4. TOTAL CIVIL NON SPÉCIALISÉ - 4.0 Contentieux général &lt; 10000 euros</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE NS :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-4. TOTAL CIVIL NON SPÉCIALISÉ - 4.0 Contentieux général &lt; 10000 euros</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE S :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-7. TOTAL SIÈGE PÉNAL - 7.12. COLLÉGIALES JIRS CRIM-ORG - 7.121. COLLÉGIALES JIRS ECO-FI - 7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES - 7.5. COUR D'ASSISES HORS JIRS - 7.51. COUR D'ASSISES JIRS - 7.52. COUR CRIMINELLE - 7.6. TRIBUNAL DE POLICE - 7.7. OP CONTRAVENTIONNELLES</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pour Magistrats SIEGE NS :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-7. TOTAL SIÈGE PÉNAL - 7.12. COLLÉGIALES JIRS CRIM-ORG - 7.121. COLLÉGIALES JIRS ECO-FI - 7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES - 7.5. COUR D'ASSISES HORS JIRS - 7.51. COUR D'ASSISES JIRS - 7.52. COUR CRIMINELLE - 7.6. TRIBUNAL DE POLICE - 7.7. OP CONTRAVENTIONNELLES</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -3664,7 +3846,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4413,6 +4595,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4499,15 +4687,6 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5305,13 +5484,13 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
-        <v>474</v>
-      </c>
-      <c r="C1" s="233" t="s">
-        <v>475</v>
-      </c>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
+        <v>492</v>
+      </c>
+      <c r="C1" s="235" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
       <c r="F1" s="198"/>
       <c r="H1" s="28" t="s">
         <v>0</v>
@@ -5320,11 +5499,11 @@
     <row r="2" spans="1:8" s="202" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
-      <c r="C2" s="234" t="s">
-        <v>476</v>
-      </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
+      <c r="C2" s="236" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
       <c r="F2" s="201"/>
       <c r="H2" s="28" t="s">
         <v>0</v>
@@ -5340,18 +5519,18 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C4" s="207" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D4" s="207" t="s">
-        <v>479</v>
-      </c>
-      <c r="E4" s="240" t="s">
-        <v>480</v>
-      </c>
-      <c r="F4" s="241"/>
+        <v>497</v>
+      </c>
+      <c r="E4" s="242" t="s">
+        <v>498</v>
+      </c>
+      <c r="F4" s="243"/>
       <c r="G4" s="216"/>
       <c r="H4" s="28" t="s">
         <v>0</v>
@@ -5360,18 +5539,18 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="C5" s="213" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D5" s="213" t="s">
-        <v>483</v>
-      </c>
-      <c r="E5" s="242" t="s">
-        <v>496</v>
-      </c>
-      <c r="F5" s="243"/>
+        <v>501</v>
+      </c>
+      <c r="E5" s="244" t="s">
+        <v>514</v>
+      </c>
+      <c r="F5" s="245"/>
       <c r="G5" s="215"/>
       <c r="H5" s="28" t="s">
         <v>0</v>
@@ -5380,18 +5559,18 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="C6" s="214" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="D6" s="214" t="s">
-        <v>486</v>
-      </c>
-      <c r="E6" s="244" t="s">
-        <v>497</v>
-      </c>
-      <c r="F6" s="245"/>
+        <v>504</v>
+      </c>
+      <c r="E6" s="246" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" s="247"/>
       <c r="G6" s="215"/>
       <c r="H6" s="28" t="s">
         <v>0</v>
@@ -5400,18 +5579,18 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="C7" s="214" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D7" s="214" t="s">
-        <v>489</v>
-      </c>
-      <c r="E7" s="244" t="s">
-        <v>496</v>
-      </c>
-      <c r="F7" s="245"/>
+        <v>507</v>
+      </c>
+      <c r="E7" s="246" t="s">
+        <v>514</v>
+      </c>
+      <c r="F7" s="247"/>
       <c r="G7" s="215"/>
       <c r="H7" s="28" t="s">
         <v>0</v>
@@ -5420,18 +5599,18 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
-        <v>490</v>
-      </c>
-      <c r="C8" s="235" t="s">
-        <v>491</v>
-      </c>
-      <c r="D8" s="235" t="s">
-        <v>492</v>
-      </c>
-      <c r="E8" s="246" t="s">
-        <v>498</v>
-      </c>
-      <c r="F8" s="247"/>
+        <v>508</v>
+      </c>
+      <c r="C8" s="237" t="s">
+        <v>509</v>
+      </c>
+      <c r="D8" s="237" t="s">
+        <v>510</v>
+      </c>
+      <c r="E8" s="248" t="s">
+        <v>516</v>
+      </c>
+      <c r="F8" s="249"/>
       <c r="G8" s="215"/>
       <c r="H8" s="28" t="s">
         <v>0</v>
@@ -5440,12 +5619,12 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>493</v>
-      </c>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="249"/>
+        <v>511</v>
+      </c>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="251"/>
       <c r="G9" s="215"/>
       <c r="H9" s="28" t="s">
         <v>0</v>
@@ -5454,12 +5633,12 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>494</v>
-      </c>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="251"/>
+        <v>512</v>
+      </c>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="253"/>
       <c r="G10" s="215"/>
       <c r="H10" s="28" t="s">
         <v>0</v>
@@ -5479,11 +5658,11 @@
     <row r="12" spans="1:8" s="28" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
-      <c r="C12" s="239" t="s">
-        <v>495</v>
-      </c>
-      <c r="D12" s="239"/>
-      <c r="E12" s="239"/>
+      <c r="C12" s="241" t="s">
+        <v>513</v>
+      </c>
+      <c r="D12" s="241"/>
+      <c r="E12" s="241"/>
       <c r="F12" s="218"/>
       <c r="H12" s="28" t="s">
         <v>0</v>
@@ -5497,14 +5676,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="237"/>
-      <c r="C14" s="237"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="237"/>
-      <c r="F14" s="238"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="239"/>
+      <c r="F14" s="240"/>
       <c r="H14" s="28" t="s">
         <v>0</v>
       </c>
@@ -5549,16 +5728,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="260" t="s">
-        <v>463</v>
-      </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
+      <c r="A1" s="262" t="s">
+        <v>481</v>
+      </c>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
       <c r="I1" s="112"/>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -5595,91 +5774,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>417</v>
+        <v>436</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>416</v>
-      </c>
-      <c r="S2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="S2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="U2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="U2" s="260" t="s">
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>413</v>
-      </c>
-      <c r="AE2" s="258" t="s">
-        <v>462</v>
+        <v>431</v>
+      </c>
+      <c r="AE2" s="260" t="s">
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>461</v>
-      </c>
-      <c r="AI2" s="258" t="s">
-        <v>460</v>
+        <v>479</v>
+      </c>
+      <c r="AI2" s="260" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5690,181 +5869,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>425</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
+        <v>477</v>
+      </c>
+      <c r="J3" s="155" t="s">
+        <v>476</v>
+      </c>
+      <c r="K3" s="155" t="s">
+        <v>475</v>
+      </c>
+      <c r="L3" s="155" t="s">
+        <v>474</v>
+      </c>
+      <c r="M3" s="155" t="s">
+        <v>473</v>
+      </c>
+      <c r="N3" s="155" t="s">
+        <v>472</v>
+      </c>
+      <c r="O3" s="191" t="s">
+        <v>471</v>
+      </c>
+      <c r="P3" s="191" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q3" s="155" t="s">
+        <v>469</v>
+      </c>
+      <c r="R3" s="155" t="s">
+        <v>412</v>
+      </c>
+      <c r="S3" s="260"/>
+      <c r="T3" s="155" t="s">
+        <v>409</v>
+      </c>
+      <c r="U3" s="260"/>
+      <c r="V3" s="155" t="s">
+        <v>468</v>
+      </c>
+      <c r="W3" s="155" t="s">
+        <v>467</v>
+      </c>
+      <c r="X3" s="155" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y3" s="155" t="s">
+        <v>465</v>
+      </c>
+      <c r="Z3" s="155" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA3" s="155" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB3" s="191" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC3" s="191" t="s">
+        <v>461</v>
+      </c>
+      <c r="AD3" s="155" t="s">
+        <v>460</v>
+      </c>
+      <c r="AE3" s="260"/>
+      <c r="AF3" s="155" t="s">
         <v>459</v>
       </c>
-      <c r="J3" s="155" t="s">
-        <v>458</v>
-      </c>
-      <c r="K3" s="155" t="s">
-        <v>457</v>
-      </c>
-      <c r="L3" s="155" t="s">
-        <v>456</v>
-      </c>
-      <c r="M3" s="155" t="s">
-        <v>455</v>
-      </c>
-      <c r="N3" s="155" t="s">
-        <v>454</v>
-      </c>
-      <c r="O3" s="191" t="s">
-        <v>453</v>
-      </c>
-      <c r="P3" s="191" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q3" s="155" t="s">
-        <v>451</v>
-      </c>
-      <c r="R3" s="155" t="s">
-        <v>394</v>
-      </c>
-      <c r="S3" s="258"/>
-      <c r="T3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="U3" s="258"/>
-      <c r="V3" s="155" t="s">
-        <v>450</v>
-      </c>
-      <c r="W3" s="155" t="s">
-        <v>449</v>
-      </c>
-      <c r="X3" s="155" t="s">
-        <v>448</v>
-      </c>
-      <c r="Y3" s="155" t="s">
-        <v>447</v>
-      </c>
-      <c r="Z3" s="155" t="s">
-        <v>446</v>
-      </c>
-      <c r="AA3" s="155" t="s">
-        <v>445</v>
-      </c>
-      <c r="AB3" s="191" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC3" s="191" t="s">
-        <v>443</v>
-      </c>
-      <c r="AD3" s="155" t="s">
-        <v>442</v>
-      </c>
-      <c r="AE3" s="258"/>
-      <c r="AF3" s="155" t="s">
-        <v>441</v>
-      </c>
       <c r="AG3" s="155" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI3" s="258"/>
+        <v>389</v>
+      </c>
+      <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="260"/>
+      <c r="I4" s="155" t="s">
+        <v>458</v>
+      </c>
+      <c r="J4" s="155" t="s">
+        <v>457</v>
+      </c>
+      <c r="K4" s="155" t="s">
+        <v>456</v>
+      </c>
+      <c r="L4" s="155" t="s">
+        <v>455</v>
+      </c>
+      <c r="M4" s="155" t="s">
+        <v>454</v>
+      </c>
+      <c r="N4" s="155" t="s">
+        <v>453</v>
+      </c>
+      <c r="O4" s="191" t="s">
+        <v>452</v>
+      </c>
+      <c r="P4" s="191" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q4" s="155" t="s">
+        <v>450</v>
+      </c>
+      <c r="R4" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="S4" s="260"/>
+      <c r="T4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="258"/>
-      <c r="I4" s="155" t="s">
+      <c r="U4" s="260"/>
+      <c r="V4" s="155" t="s">
+        <v>449</v>
+      </c>
+      <c r="W4" s="155" t="s">
+        <v>448</v>
+      </c>
+      <c r="X4" s="155" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y4" s="155" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z4" s="155" t="s">
+        <v>445</v>
+      </c>
+      <c r="AA4" s="155" t="s">
+        <v>444</v>
+      </c>
+      <c r="AB4" s="191" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC4" s="191" t="s">
+        <v>442</v>
+      </c>
+      <c r="AD4" s="155" t="s">
+        <v>441</v>
+      </c>
+      <c r="AE4" s="260"/>
+      <c r="AF4" s="155" t="s">
         <v>440</v>
       </c>
-      <c r="J4" s="155" t="s">
-        <v>439</v>
-      </c>
-      <c r="K4" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="L4" s="155" t="s">
-        <v>437</v>
-      </c>
-      <c r="M4" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="N4" s="155" t="s">
-        <v>435</v>
-      </c>
-      <c r="O4" s="191" t="s">
-        <v>434</v>
-      </c>
-      <c r="P4" s="191" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q4" s="155" t="s">
-        <v>432</v>
-      </c>
-      <c r="R4" s="155" t="s">
-        <v>343</v>
-      </c>
-      <c r="S4" s="258"/>
-      <c r="T4" s="155" t="s">
-        <v>339</v>
-      </c>
-      <c r="U4" s="258"/>
-      <c r="V4" s="155" t="s">
-        <v>431</v>
-      </c>
-      <c r="W4" s="155" t="s">
-        <v>430</v>
-      </c>
-      <c r="X4" s="155" t="s">
-        <v>429</v>
-      </c>
-      <c r="Y4" s="155" t="s">
-        <v>428</v>
-      </c>
-      <c r="Z4" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA4" s="155" t="s">
-        <v>426</v>
-      </c>
-      <c r="AB4" s="191" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC4" s="191" t="s">
-        <v>424</v>
-      </c>
-      <c r="AD4" s="155" t="s">
-        <v>423</v>
-      </c>
-      <c r="AE4" s="258"/>
-      <c r="AF4" s="155" t="s">
-        <v>422</v>
-      </c>
       <c r="AG4" s="155" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI4" s="258"/>
+        <v>336</v>
+      </c>
+      <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -5873,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -5980,7 +6159,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -5989,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6041,7 +6220,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6050,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6102,7 +6281,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6111,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6175,7 +6354,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6184,10 +6363,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6257,7 +6436,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6266,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6330,7 +6509,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6339,10 +6518,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6403,7 +6582,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6412,10 +6591,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6479,7 +6658,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6488,10 +6667,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6549,7 +6728,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6558,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6662,7 +6841,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6671,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6780,7 +6959,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -6910,7 +7089,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -6945,7 +7124,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -6962,16 +7141,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>416</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="J2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="J2" s="260" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6982,43 +7161,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>394</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>412</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="J3" s="258"/>
+        <v>409</v>
+      </c>
+      <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>343</v>
-      </c>
-      <c r="H4" s="258"/>
+        <v>361</v>
+      </c>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>339</v>
-      </c>
-      <c r="J4" s="258"/>
+        <v>357</v>
+      </c>
+      <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7027,10 +7206,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7051,7 +7230,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7060,10 +7239,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7078,7 +7257,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7087,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7105,7 +7284,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7114,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7132,7 +7311,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7141,10 +7320,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7159,7 +7338,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7168,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7186,7 +7365,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7195,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7213,7 +7392,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7222,10 +7401,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7243,7 +7422,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7252,10 +7431,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7278,7 +7457,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7337,12 +7516,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7411,172 +7590,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>417</v>
+        <v>436</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>416</v>
-      </c>
-      <c r="W2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="W2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="AB2" s="260" t="s">
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>413</v>
-      </c>
-      <c r="AL2" s="258" t="s">
-        <v>412</v>
+        <v>431</v>
+      </c>
+      <c r="AL2" s="260" t="s">
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>411</v>
-      </c>
-      <c r="AZ2" s="258" t="s">
-        <v>410</v>
+        <v>429</v>
+      </c>
+      <c r="AZ2" s="260" t="s">
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>409</v>
-      </c>
-      <c r="BJ2" s="258" t="s">
-        <v>408</v>
+        <v>427</v>
+      </c>
+      <c r="BJ2" s="260" t="s">
+        <v>426</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7588,78 +7767,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>425</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="W3" s="258"/>
+        <v>412</v>
+      </c>
+      <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB3" s="258"/>
+        <v>409</v>
+      </c>
+      <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7668,265 +7847,265 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
+        <v>402</v>
+      </c>
+      <c r="AL3" s="260"/>
+      <c r="AM3" s="152" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN3" s="152" t="s">
+        <v>400</v>
+      </c>
+      <c r="AO3" s="152" t="s">
+        <v>399</v>
+      </c>
+      <c r="AP3" s="152" t="s">
+        <v>398</v>
+      </c>
+      <c r="AQ3" s="152" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR3" s="152" t="s">
+        <v>396</v>
+      </c>
+      <c r="AS3" s="152" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT3" s="152" t="s">
+        <v>394</v>
+      </c>
+      <c r="AU3" s="152" t="s">
+        <v>393</v>
+      </c>
+      <c r="AV3" s="152" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW3" s="152" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX3" s="152" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY3" s="152" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ3" s="260"/>
+      <c r="BA3" s="151" t="s">
+        <v>388</v>
+      </c>
+      <c r="BB3" s="151" t="s">
+        <v>387</v>
+      </c>
+      <c r="BC3" s="151" t="s">
+        <v>386</v>
+      </c>
+      <c r="BD3" s="151" t="s">
+        <v>385</v>
+      </c>
+      <c r="BE3" s="151" t="s">
         <v>384</v>
       </c>
-      <c r="AL3" s="258"/>
-      <c r="AM3" s="152" t="s">
+      <c r="BF3" s="151" t="s">
         <v>383</v>
       </c>
-      <c r="AN3" s="152" t="s">
+      <c r="BG3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="AO3" s="152" t="s">
+      <c r="BH3" s="151" t="s">
         <v>381</v>
       </c>
-      <c r="AP3" s="152" t="s">
+      <c r="BI3" s="151" t="s">
         <v>380</v>
       </c>
-      <c r="AQ3" s="152" t="s">
-        <v>379</v>
-      </c>
-      <c r="AR3" s="152" t="s">
-        <v>378</v>
-      </c>
-      <c r="AS3" s="152" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT3" s="152" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU3" s="152" t="s">
-        <v>375</v>
-      </c>
-      <c r="AV3" s="152" t="s">
-        <v>374</v>
-      </c>
-      <c r="AW3" s="152" t="s">
-        <v>373</v>
-      </c>
-      <c r="AX3" s="152" t="s">
-        <v>372</v>
-      </c>
-      <c r="AY3" s="152" t="s">
-        <v>371</v>
-      </c>
-      <c r="AZ3" s="258"/>
-      <c r="BA3" s="151" t="s">
-        <v>370</v>
-      </c>
-      <c r="BB3" s="151" t="s">
-        <v>369</v>
-      </c>
-      <c r="BC3" s="151" t="s">
-        <v>368</v>
-      </c>
-      <c r="BD3" s="151" t="s">
-        <v>367</v>
-      </c>
-      <c r="BE3" s="151" t="s">
-        <v>366</v>
-      </c>
-      <c r="BF3" s="151" t="s">
-        <v>365</v>
-      </c>
-      <c r="BG3" s="151" t="s">
-        <v>364</v>
-      </c>
-      <c r="BH3" s="151" t="s">
-        <v>363</v>
-      </c>
-      <c r="BI3" s="151" t="s">
-        <v>362</v>
-      </c>
-      <c r="BJ3" s="258"/>
+      <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
+        <v>377</v>
+      </c>
+      <c r="F4" s="156" t="s">
+        <v>376</v>
+      </c>
+      <c r="G4" s="155" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="260"/>
+      <c r="I4" s="154" t="s">
+        <v>374</v>
+      </c>
+      <c r="J4" s="154" t="s">
+        <v>373</v>
+      </c>
+      <c r="K4" s="154" t="s">
+        <v>372</v>
+      </c>
+      <c r="L4" s="154" t="s">
+        <v>371</v>
+      </c>
+      <c r="M4" s="154" t="s">
+        <v>370</v>
+      </c>
+      <c r="N4" s="154" t="s">
+        <v>369</v>
+      </c>
+      <c r="O4" s="154" t="s">
+        <v>368</v>
+      </c>
+      <c r="P4" s="154" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q4" s="154" t="s">
+        <v>366</v>
+      </c>
+      <c r="R4" s="154" t="s">
+        <v>365</v>
+      </c>
+      <c r="S4" s="154" t="s">
+        <v>364</v>
+      </c>
+      <c r="T4" s="154" t="s">
+        <v>363</v>
+      </c>
+      <c r="U4" s="154" t="s">
+        <v>362</v>
+      </c>
+      <c r="V4" s="154" t="s">
+        <v>361</v>
+      </c>
+      <c r="W4" s="260"/>
+      <c r="X4" s="153" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="156" t="s">
+      <c r="Z4" s="153" t="s">
         <v>358</v>
       </c>
-      <c r="G4" s="155" t="s">
+      <c r="AA4" s="153" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="258"/>
-      <c r="I4" s="154" t="s">
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="152" t="s">
         <v>356</v>
       </c>
-      <c r="J4" s="154" t="s">
+      <c r="AD4" s="152" t="s">
         <v>355</v>
       </c>
-      <c r="K4" s="154" t="s">
+      <c r="AE4" s="152" t="s">
         <v>354</v>
       </c>
-      <c r="L4" s="154" t="s">
+      <c r="AF4" s="152" t="s">
         <v>353</v>
       </c>
-      <c r="M4" s="154" t="s">
+      <c r="AG4" s="152" t="s">
         <v>352</v>
       </c>
-      <c r="N4" s="154" t="s">
+      <c r="AH4" s="152" t="s">
         <v>351</v>
-      </c>
-      <c r="O4" s="154" t="s">
-        <v>350</v>
-      </c>
-      <c r="P4" s="154" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q4" s="154" t="s">
-        <v>348</v>
-      </c>
-      <c r="R4" s="154" t="s">
-        <v>347</v>
-      </c>
-      <c r="S4" s="154" t="s">
-        <v>346</v>
-      </c>
-      <c r="T4" s="154" t="s">
-        <v>345</v>
-      </c>
-      <c r="U4" s="154" t="s">
-        <v>344</v>
-      </c>
-      <c r="V4" s="154" t="s">
-        <v>343</v>
-      </c>
-      <c r="W4" s="258"/>
-      <c r="X4" s="153" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y4" s="153" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z4" s="153" t="s">
-        <v>340</v>
-      </c>
-      <c r="AA4" s="153" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB4" s="258"/>
-      <c r="AC4" s="152" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD4" s="152" t="s">
-        <v>337</v>
-      </c>
-      <c r="AE4" s="152" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF4" s="152" t="s">
-        <v>335</v>
-      </c>
-      <c r="AG4" s="152" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH4" s="152" t="s">
-        <v>333</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK4" s="152" t="s">
+        <v>349</v>
+      </c>
+      <c r="AL4" s="260"/>
+      <c r="AM4" s="152" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN4" s="152" t="s">
+        <v>347</v>
+      </c>
+      <c r="AO4" s="152" t="s">
+        <v>346</v>
+      </c>
+      <c r="AP4" s="152" t="s">
+        <v>345</v>
+      </c>
+      <c r="AQ4" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="AR4" s="152" t="s">
+        <v>343</v>
+      </c>
+      <c r="AS4" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="AT4" s="152" t="s">
+        <v>341</v>
+      </c>
+      <c r="AU4" s="152" t="s">
+        <v>340</v>
+      </c>
+      <c r="AV4" s="152" t="s">
+        <v>339</v>
+      </c>
+      <c r="AW4" s="152" t="s">
+        <v>338</v>
+      </c>
+      <c r="AX4" s="152" t="s">
+        <v>337</v>
+      </c>
+      <c r="AY4" s="152" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ4" s="260"/>
+      <c r="BA4" s="151" t="s">
+        <v>335</v>
+      </c>
+      <c r="BB4" s="151" t="s">
+        <v>334</v>
+      </c>
+      <c r="BC4" s="151" t="s">
+        <v>333</v>
+      </c>
+      <c r="BD4" s="151" t="s">
         <v>332</v>
       </c>
-      <c r="AK4" s="152" t="s">
+      <c r="BE4" s="151" t="s">
         <v>331</v>
       </c>
-      <c r="AL4" s="258"/>
-      <c r="AM4" s="152" t="s">
+      <c r="BF4" s="151" t="s">
         <v>330</v>
       </c>
-      <c r="AN4" s="152" t="s">
+      <c r="BG4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="AO4" s="152" t="s">
+      <c r="BH4" s="151" t="s">
         <v>328</v>
       </c>
-      <c r="AP4" s="152" t="s">
+      <c r="BI4" s="151" t="s">
         <v>327</v>
       </c>
-      <c r="AQ4" s="152" t="s">
-        <v>326</v>
-      </c>
-      <c r="AR4" s="152" t="s">
-        <v>325</v>
-      </c>
-      <c r="AS4" s="152" t="s">
-        <v>324</v>
-      </c>
-      <c r="AT4" s="152" t="s">
-        <v>323</v>
-      </c>
-      <c r="AU4" s="152" t="s">
-        <v>322</v>
-      </c>
-      <c r="AV4" s="152" t="s">
-        <v>321</v>
-      </c>
-      <c r="AW4" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="AX4" s="152" t="s">
-        <v>319</v>
-      </c>
-      <c r="AY4" s="152" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ4" s="258"/>
-      <c r="BA4" s="151" t="s">
-        <v>317</v>
-      </c>
-      <c r="BB4" s="151" t="s">
-        <v>316</v>
-      </c>
-      <c r="BC4" s="151" t="s">
-        <v>315</v>
-      </c>
-      <c r="BD4" s="151" t="s">
-        <v>314</v>
-      </c>
-      <c r="BE4" s="151" t="s">
-        <v>313</v>
-      </c>
-      <c r="BF4" s="151" t="s">
-        <v>312</v>
-      </c>
-      <c r="BG4" s="151" t="s">
-        <v>311</v>
-      </c>
-      <c r="BH4" s="151" t="s">
-        <v>310</v>
-      </c>
-      <c r="BI4" s="151" t="s">
-        <v>309</v>
-      </c>
-      <c r="BJ4" s="258"/>
+      <c r="BJ4" s="260"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8129,7 +8308,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8138,10 +8317,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8343,7 +8522,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8352,10 +8531,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8557,7 +8736,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8566,10 +8745,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8771,7 +8950,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8780,10 +8959,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -8985,7 +9164,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -8994,10 +9173,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9199,7 +9378,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9208,10 +9387,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9413,7 +9592,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9422,10 +9601,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9627,7 +9806,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9636,10 +9815,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -9841,7 +10020,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -9850,10 +10029,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10055,7 +10234,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10064,10 +10243,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10274,7 +10453,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10507,7 +10686,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10552,12 +10731,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10626,91 +10805,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>417</v>
+        <v>436</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>435</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>416</v>
-      </c>
-      <c r="S2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="S2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="U2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="U2" s="260" t="s">
+        <v>432</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>413</v>
-      </c>
-      <c r="AE2" s="258" t="s">
-        <v>462</v>
+        <v>431</v>
+      </c>
+      <c r="AE2" s="260" t="s">
+        <v>480</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>461</v>
-      </c>
-      <c r="AI2" s="258" t="s">
-        <v>460</v>
+        <v>479</v>
+      </c>
+      <c r="AI2" s="260" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10721,190 +10900,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>425</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
+        <v>477</v>
+      </c>
+      <c r="J3" s="155" t="s">
+        <v>476</v>
+      </c>
+      <c r="K3" s="155" t="s">
+        <v>475</v>
+      </c>
+      <c r="L3" s="155" t="s">
+        <v>474</v>
+      </c>
+      <c r="M3" s="155" t="s">
+        <v>473</v>
+      </c>
+      <c r="N3" s="155" t="s">
+        <v>472</v>
+      </c>
+      <c r="O3" s="155" t="s">
+        <v>471</v>
+      </c>
+      <c r="P3" s="155" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q3" s="155" t="s">
+        <v>469</v>
+      </c>
+      <c r="R3" s="155" t="s">
+        <v>412</v>
+      </c>
+      <c r="S3" s="260"/>
+      <c r="T3" s="155" t="s">
+        <v>409</v>
+      </c>
+      <c r="U3" s="260"/>
+      <c r="V3" s="155" t="s">
+        <v>468</v>
+      </c>
+      <c r="W3" s="155" t="s">
+        <v>467</v>
+      </c>
+      <c r="X3" s="155" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y3" s="155" t="s">
+        <v>465</v>
+      </c>
+      <c r="Z3" s="155" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA3" s="155" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB3" s="155" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC3" s="155" t="s">
+        <v>461</v>
+      </c>
+      <c r="AD3" s="155" t="s">
+        <v>460</v>
+      </c>
+      <c r="AE3" s="260"/>
+      <c r="AF3" s="155" t="s">
         <v>459</v>
       </c>
-      <c r="J3" s="155" t="s">
-        <v>458</v>
-      </c>
-      <c r="K3" s="155" t="s">
-        <v>457</v>
-      </c>
-      <c r="L3" s="155" t="s">
-        <v>456</v>
-      </c>
-      <c r="M3" s="155" t="s">
-        <v>455</v>
-      </c>
-      <c r="N3" s="155" t="s">
-        <v>454</v>
-      </c>
-      <c r="O3" s="155" t="s">
-        <v>453</v>
-      </c>
-      <c r="P3" s="155" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q3" s="155" t="s">
-        <v>451</v>
-      </c>
-      <c r="R3" s="155" t="s">
-        <v>394</v>
-      </c>
-      <c r="S3" s="258"/>
-      <c r="T3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="U3" s="258"/>
-      <c r="V3" s="155" t="s">
-        <v>450</v>
-      </c>
-      <c r="W3" s="155" t="s">
-        <v>449</v>
-      </c>
-      <c r="X3" s="155" t="s">
-        <v>448</v>
-      </c>
-      <c r="Y3" s="155" t="s">
-        <v>447</v>
-      </c>
-      <c r="Z3" s="155" t="s">
-        <v>446</v>
-      </c>
-      <c r="AA3" s="155" t="s">
-        <v>445</v>
-      </c>
-      <c r="AB3" s="155" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC3" s="155" t="s">
-        <v>443</v>
-      </c>
-      <c r="AD3" s="155" t="s">
-        <v>442</v>
-      </c>
-      <c r="AE3" s="258"/>
-      <c r="AF3" s="155" t="s">
-        <v>441</v>
-      </c>
       <c r="AG3" s="155" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI3" s="258"/>
+        <v>389</v>
+      </c>
+      <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="260"/>
+      <c r="I4" s="155" t="s">
+        <v>458</v>
+      </c>
+      <c r="J4" s="155" t="s">
+        <v>457</v>
+      </c>
+      <c r="K4" s="155" t="s">
+        <v>456</v>
+      </c>
+      <c r="L4" s="155" t="s">
+        <v>455</v>
+      </c>
+      <c r="M4" s="155" t="s">
+        <v>454</v>
+      </c>
+      <c r="N4" s="155" t="s">
+        <v>453</v>
+      </c>
+      <c r="O4" s="155" t="s">
+        <v>452</v>
+      </c>
+      <c r="P4" s="155" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q4" s="155" t="s">
+        <v>450</v>
+      </c>
+      <c r="R4" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="S4" s="260"/>
+      <c r="T4" s="155" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="258"/>
-      <c r="I4" s="155" t="s">
+      <c r="U4" s="260"/>
+      <c r="V4" s="155" t="s">
+        <v>449</v>
+      </c>
+      <c r="W4" s="155" t="s">
+        <v>448</v>
+      </c>
+      <c r="X4" s="155" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y4" s="155" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z4" s="155" t="s">
+        <v>445</v>
+      </c>
+      <c r="AA4" s="155" t="s">
+        <v>444</v>
+      </c>
+      <c r="AB4" s="155" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC4" s="155" t="s">
+        <v>442</v>
+      </c>
+      <c r="AD4" s="155" t="s">
+        <v>441</v>
+      </c>
+      <c r="AE4" s="260"/>
+      <c r="AF4" s="155" t="s">
         <v>440</v>
       </c>
-      <c r="J4" s="155" t="s">
-        <v>439</v>
-      </c>
-      <c r="K4" s="155" t="s">
-        <v>438</v>
-      </c>
-      <c r="L4" s="155" t="s">
-        <v>437</v>
-      </c>
-      <c r="M4" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="N4" s="155" t="s">
-        <v>435</v>
-      </c>
-      <c r="O4" s="155" t="s">
-        <v>434</v>
-      </c>
-      <c r="P4" s="155" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q4" s="155" t="s">
-        <v>432</v>
-      </c>
-      <c r="R4" s="155" t="s">
-        <v>343</v>
-      </c>
-      <c r="S4" s="258"/>
-      <c r="T4" s="155" t="s">
-        <v>339</v>
-      </c>
-      <c r="U4" s="258"/>
-      <c r="V4" s="155" t="s">
-        <v>431</v>
-      </c>
-      <c r="W4" s="155" t="s">
-        <v>430</v>
-      </c>
-      <c r="X4" s="155" t="s">
-        <v>429</v>
-      </c>
-      <c r="Y4" s="155" t="s">
-        <v>428</v>
-      </c>
-      <c r="Z4" s="155" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA4" s="155" t="s">
-        <v>426</v>
-      </c>
-      <c r="AB4" s="155" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC4" s="155" t="s">
-        <v>424</v>
-      </c>
-      <c r="AD4" s="155" t="s">
-        <v>423</v>
-      </c>
-      <c r="AE4" s="258"/>
-      <c r="AF4" s="155" t="s">
-        <v>422</v>
-      </c>
       <c r="AG4" s="155" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI4" s="258"/>
+        <v>336</v>
+      </c>
+      <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11025,7 +11204,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11034,10 +11213,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11158,7 +11337,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11167,10 +11346,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11291,7 +11470,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11300,10 +11479,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11424,7 +11603,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11433,10 +11612,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11557,7 +11736,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11566,10 +11745,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11690,7 +11869,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11699,10 +11878,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -11823,7 +12002,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -11832,10 +12011,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -11956,7 +12135,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -11965,10 +12144,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12089,7 +12268,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12098,10 +12277,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12222,7 +12401,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12231,10 +12410,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12360,7 +12539,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12484,7 +12663,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12506,7 +12685,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12547,12 +12726,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12621,16 +12800,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>416</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="J2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="J2" s="260" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12641,52 +12820,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>394</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>412</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="J3" s="258"/>
+        <v>409</v>
+      </c>
+      <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>343</v>
-      </c>
-      <c r="H4" s="258"/>
+        <v>361</v>
+      </c>
+      <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>339</v>
-      </c>
-      <c r="J4" s="258"/>
+        <v>357</v>
+      </c>
+      <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12707,7 +12886,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12716,10 +12895,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12740,7 +12919,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12749,10 +12928,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12773,7 +12952,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12782,10 +12961,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12806,7 +12985,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12815,10 +12994,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -12839,7 +13018,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -12848,10 +13027,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -12872,7 +13051,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -12881,10 +13060,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -12905,7 +13084,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -12914,10 +13093,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -12938,7 +13117,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -12947,10 +13126,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -12976,7 +13155,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -12997,7 +13176,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13045,7 +13224,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13368,7 +13547,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13378,14 +13557,14 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="EA1" s="252" t="s">
-        <v>472</v>
-      </c>
-      <c r="EB1" s="252"/>
-      <c r="EC1" s="252"/>
-      <c r="ED1" s="252"/>
-      <c r="EE1" s="252"/>
-      <c r="EF1" s="252"/>
+      <c r="EA1" s="254" t="s">
+        <v>490</v>
+      </c>
+      <c r="EB1" s="254"/>
+      <c r="EC1" s="254"/>
+      <c r="ED1" s="254"/>
+      <c r="EE1" s="254"/>
+      <c r="EF1" s="254"/>
       <c r="EG1" s="8" t="s">
         <v>0</v>
       </c>
@@ -13466,7 +13645,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13510,20 +13689,20 @@
     </row>
     <row r="4" spans="1:16" ht="40" x14ac:dyDescent="0.2">
       <c r="C4" s="9"/>
-      <c r="E4" s="253" t="s">
+      <c r="E4" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="254"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="253" t="s">
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="255" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="254"/>
-      <c r="L4" s="254"/>
-      <c r="M4" s="254"/>
-      <c r="N4" s="255"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
+      <c r="M4" s="256"/>
+      <c r="N4" s="257"/>
       <c r="O4" s="30" t="s">
         <v>28</v>
       </c>
@@ -13707,15 +13886,15 @@
       </c>
       <c r="B1"/>
       <c r="D1" s="40" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E1"/>
       <c r="G1" s="40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13775,19 +13954,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F1" s="59" t="s">
         <v>34</v>
@@ -13795,16 +13974,16 @@
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>46</v>
@@ -13815,16 +13994,16 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>46</v>
@@ -13835,16 +14014,16 @@
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>46</v>
@@ -13855,16 +14034,16 @@
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>46</v>
@@ -13875,16 +14054,16 @@
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>46</v>
@@ -13895,16 +14074,16 @@
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>46</v>
@@ -13915,16 +14094,16 @@
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>46</v>
@@ -13935,16 +14114,16 @@
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>46</v>
@@ -13955,16 +14134,16 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>46</v>
@@ -13975,16 +14154,16 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>46</v>
@@ -13995,16 +14174,16 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>46</v>
@@ -14015,16 +14194,16 @@
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>46</v>
@@ -14035,16 +14214,16 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>46</v>
@@ -14055,16 +14234,16 @@
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>46</v>
@@ -14075,16 +14254,16 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>46</v>
@@ -14095,16 +14274,16 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>46</v>
@@ -14115,16 +14294,16 @@
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>46</v>
@@ -14135,16 +14314,16 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>46</v>
@@ -14155,16 +14334,16 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>46</v>
@@ -14175,16 +14354,16 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>46</v>
@@ -14195,16 +14374,16 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>69</v>
@@ -14215,16 +14394,16 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C23" s="57" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>69</v>
@@ -14235,16 +14414,16 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C24" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>73</v>
@@ -14255,16 +14434,16 @@
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C25" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>73</v>
@@ -14275,16 +14454,16 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>77</v>
@@ -14295,16 +14474,16 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>77</v>
@@ -14315,16 +14494,16 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E28" s="41" t="s">
         <v>77</v>
@@ -14335,16 +14514,16 @@
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C29" s="54" t="s">
         <v>81</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>77</v>
@@ -14355,7 +14534,7 @@
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
@@ -14364,7 +14543,7 @@
         <v>83</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>84</v>
@@ -14375,16 +14554,16 @@
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>84</v>
@@ -14395,16 +14574,16 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>84</v>
@@ -14415,7 +14594,7 @@
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>88</v>
@@ -14424,7 +14603,7 @@
         <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>84</v>
@@ -14435,7 +14614,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>89</v>
@@ -14444,7 +14623,7 @@
         <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>84</v>
@@ -14455,7 +14634,7 @@
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>90</v>
@@ -14464,7 +14643,7 @@
         <v>90</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>84</v>
@@ -14475,7 +14654,7 @@
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>92</v>
@@ -14484,7 +14663,7 @@
         <v>92</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>93</v>
@@ -14495,16 +14674,16 @@
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>93</v>
@@ -14515,7 +14694,7 @@
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>96</v>
@@ -14524,7 +14703,7 @@
         <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>93</v>
@@ -14535,7 +14714,7 @@
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>97</v>
@@ -14544,7 +14723,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>93</v>
@@ -14555,7 +14734,7 @@
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>98</v>
@@ -14564,7 +14743,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>93</v>
@@ -14575,7 +14754,7 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>100</v>
@@ -14584,7 +14763,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E41" s="48" t="s">
         <v>101</v>
@@ -14595,16 +14774,16 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C42" s="48" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E42" s="48" t="s">
         <v>101</v>
@@ -14615,7 +14794,7 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>104</v>
@@ -14624,7 +14803,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E43" s="48" t="s">
         <v>101</v>
@@ -14635,7 +14814,7 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>105</v>
@@ -14644,7 +14823,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E44" s="48" t="s">
         <v>101</v>
@@ -14655,7 +14834,7 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>106</v>
@@ -14664,7 +14843,7 @@
         <v>106</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>101</v>
@@ -14675,16 +14854,16 @@
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C46" s="48" t="s">
         <v>108</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E46" s="48" t="s">
         <v>109</v>
@@ -14695,16 +14874,16 @@
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C47" s="48" t="s">
         <v>111</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E47" s="48" t="s">
         <v>109</v>
@@ -14715,16 +14894,16 @@
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C48" s="48" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E48" s="48" t="s">
         <v>109</v>
@@ -14735,16 +14914,16 @@
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C49" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E49" s="48" t="s">
         <v>109</v>
@@ -14755,16 +14934,16 @@
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E50" s="48" t="s">
         <v>109</v>
@@ -14775,16 +14954,16 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>109</v>
@@ -14795,16 +14974,16 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>116</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>109</v>
@@ -14815,36 +14994,36 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>118</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>503</v>
+        <v>120</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>109</v>
@@ -14855,16 +15034,16 @@
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>504</v>
+        <v>121</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E55" s="53" t="s">
         <v>109</v>
@@ -14875,251 +15054,251 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="51" t="s">
         <v>137</v>
-      </c>
-      <c r="B56" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="C56" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" s="51" t="s">
-        <v>134</v>
       </c>
       <c r="E56" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="41" t="s">
         <v>137</v>
-      </c>
-      <c r="B57" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="C57" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>134</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>109</v>
       </c>
       <c r="F57" s="41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" s="42" t="s">
         <v>137</v>
-      </c>
-      <c r="B58" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D58" s="42" t="s">
-        <v>134</v>
       </c>
       <c r="E58" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B59" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C59" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F59" s="48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B60" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F60" s="48" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B61" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="C61" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F61" s="48" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="233" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="234" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" s="234" t="s">
+        <v>521</v>
+      </c>
+      <c r="D62" s="234" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="G62" s="42" t="s">
-        <v>141</v>
-      </c>
+      <c r="F62" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="42"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B63" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="48" t="s">
-        <v>502</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="F63" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="G63" s="42"/>
+      <c r="G63" s="42" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="D64" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B64" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="D64" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E64" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F64" s="48" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="D65" s="48" t="s">
         <v>137</v>
-      </c>
-      <c r="B65" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="48" t="s">
-        <v>505</v>
-      </c>
-      <c r="D65" s="48" t="s">
-        <v>134</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>109</v>
       </c>
       <c r="F65" s="48" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="42" t="s">
         <v>137</v>
-      </c>
-      <c r="B66" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C66" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="42" t="s">
-        <v>134</v>
       </c>
       <c r="E66" s="42" t="s">
         <v>109</v>
       </c>
       <c r="F66" s="46"/>
       <c r="G66" s="42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="44" t="s">
         <v>137</v>
-      </c>
-      <c r="B67" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D67" s="44" t="s">
-        <v>134</v>
       </c>
       <c r="E67" s="44" t="s">
         <v>109</v>
       </c>
       <c r="F67" s="43"/>
       <c r="G67" s="42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -15163,16 +15342,16 @@
   <sheetData>
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
-      <c r="B1" s="257" t="s">
-        <v>419</v>
-      </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
-      <c r="G1" s="257"/>
-      <c r="H1" s="257"/>
-      <c r="I1" s="257"/>
+      <c r="B1" s="259" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
       <c r="AC1" s="106"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
@@ -15191,172 +15370,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="256" t="s">
-        <v>417</v>
+        <v>436</v>
+      </c>
+      <c r="H2" s="258" t="s">
+        <v>435</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>416</v>
-      </c>
-      <c r="W2" s="256" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="W2" s="258" t="s">
+        <v>433</v>
       </c>
       <c r="X2" s="102" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB2" s="256" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="AB2" s="258" t="s">
+        <v>432</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>413</v>
-      </c>
-      <c r="AL2" s="256" t="s">
-        <v>412</v>
+        <v>431</v>
+      </c>
+      <c r="AL2" s="258" t="s">
+        <v>430</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>411</v>
-      </c>
-      <c r="AZ2" s="256" t="s">
-        <v>410</v>
+        <v>429</v>
+      </c>
+      <c r="AZ2" s="258" t="s">
+        <v>428</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>409</v>
-      </c>
-      <c r="BJ2" s="256" t="s">
-        <v>408</v>
+        <v>427</v>
+      </c>
+      <c r="BJ2" s="258" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15367,78 +15546,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" s="256"/>
+        <v>425</v>
+      </c>
+      <c r="H3" s="258"/>
       <c r="I3" s="101" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>394</v>
-      </c>
-      <c r="W3" s="256"/>
+        <v>412</v>
+      </c>
+      <c r="W3" s="258"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB3" s="256"/>
+        <v>409</v>
+      </c>
+      <c r="AB3" s="258"/>
       <c r="AC3" s="98" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15447,273 +15626,273 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
+        <v>402</v>
+      </c>
+      <c r="AL3" s="258"/>
+      <c r="AM3" s="98" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN3" s="98" t="s">
+        <v>400</v>
+      </c>
+      <c r="AO3" s="98" t="s">
+        <v>399</v>
+      </c>
+      <c r="AP3" s="98" t="s">
+        <v>398</v>
+      </c>
+      <c r="AQ3" s="98" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR3" s="98" t="s">
+        <v>396</v>
+      </c>
+      <c r="AS3" s="98" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT3" s="98" t="s">
+        <v>394</v>
+      </c>
+      <c r="AU3" s="98" t="s">
+        <v>393</v>
+      </c>
+      <c r="AV3" s="98" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW3" s="98" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX3" s="98" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY3" s="98" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ3" s="258"/>
+      <c r="BA3" s="97" t="s">
+        <v>388</v>
+      </c>
+      <c r="BB3" s="97" t="s">
+        <v>387</v>
+      </c>
+      <c r="BC3" s="97" t="s">
+        <v>386</v>
+      </c>
+      <c r="BD3" s="97" t="s">
+        <v>385</v>
+      </c>
+      <c r="BE3" s="97" t="s">
         <v>384</v>
       </c>
-      <c r="AL3" s="256"/>
-      <c r="AM3" s="98" t="s">
+      <c r="BF3" s="97" t="s">
         <v>383</v>
       </c>
-      <c r="AN3" s="98" t="s">
+      <c r="BG3" s="97" t="s">
         <v>382</v>
       </c>
-      <c r="AO3" s="98" t="s">
+      <c r="BH3" s="97" t="s">
         <v>381</v>
       </c>
-      <c r="AP3" s="98" t="s">
+      <c r="BI3" s="97" t="s">
         <v>380</v>
       </c>
-      <c r="AQ3" s="98" t="s">
-        <v>379</v>
-      </c>
-      <c r="AR3" s="98" t="s">
-        <v>378</v>
-      </c>
-      <c r="AS3" s="98" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT3" s="98" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU3" s="98" t="s">
-        <v>375</v>
-      </c>
-      <c r="AV3" s="98" t="s">
-        <v>374</v>
-      </c>
-      <c r="AW3" s="98" t="s">
-        <v>373</v>
-      </c>
-      <c r="AX3" s="98" t="s">
-        <v>372</v>
-      </c>
-      <c r="AY3" s="98" t="s">
-        <v>371</v>
-      </c>
-      <c r="AZ3" s="256"/>
-      <c r="BA3" s="97" t="s">
-        <v>370</v>
-      </c>
-      <c r="BB3" s="97" t="s">
-        <v>369</v>
-      </c>
-      <c r="BC3" s="97" t="s">
-        <v>368</v>
-      </c>
-      <c r="BD3" s="97" t="s">
-        <v>367</v>
-      </c>
-      <c r="BE3" s="97" t="s">
-        <v>366</v>
-      </c>
-      <c r="BF3" s="97" t="s">
-        <v>365</v>
-      </c>
-      <c r="BG3" s="97" t="s">
-        <v>364</v>
-      </c>
-      <c r="BH3" s="97" t="s">
-        <v>363</v>
-      </c>
-      <c r="BI3" s="97" t="s">
-        <v>362</v>
-      </c>
-      <c r="BJ3" s="256"/>
+      <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
+        <v>377</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>376</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="258"/>
+      <c r="I4" s="101" t="s">
+        <v>374</v>
+      </c>
+      <c r="J4" s="100" t="s">
+        <v>373</v>
+      </c>
+      <c r="K4" s="101" t="s">
+        <v>372</v>
+      </c>
+      <c r="L4" s="101" t="s">
+        <v>371</v>
+      </c>
+      <c r="M4" s="101" t="s">
+        <v>370</v>
+      </c>
+      <c r="N4" s="101" t="s">
+        <v>369</v>
+      </c>
+      <c r="O4" s="101" t="s">
+        <v>368</v>
+      </c>
+      <c r="P4" s="101" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q4" s="101" t="s">
+        <v>366</v>
+      </c>
+      <c r="R4" s="100" t="s">
+        <v>365</v>
+      </c>
+      <c r="S4" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="T4" s="101" t="s">
+        <v>363</v>
+      </c>
+      <c r="U4" s="101" t="s">
+        <v>362</v>
+      </c>
+      <c r="V4" s="100" t="s">
+        <v>361</v>
+      </c>
+      <c r="W4" s="258"/>
+      <c r="X4" s="99" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y4" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="Z4" s="99" t="s">
         <v>358</v>
       </c>
-      <c r="G4" s="102" t="s">
+      <c r="AA4" s="99" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="256"/>
-      <c r="I4" s="101" t="s">
+      <c r="AB4" s="258"/>
+      <c r="AC4" s="98" t="s">
         <v>356</v>
       </c>
-      <c r="J4" s="100" t="s">
+      <c r="AD4" s="98" t="s">
         <v>355</v>
       </c>
-      <c r="K4" s="101" t="s">
+      <c r="AE4" s="98" t="s">
         <v>354</v>
       </c>
-      <c r="L4" s="101" t="s">
+      <c r="AF4" s="98" t="s">
         <v>353</v>
       </c>
-      <c r="M4" s="101" t="s">
+      <c r="AG4" s="98" t="s">
         <v>352</v>
       </c>
-      <c r="N4" s="101" t="s">
+      <c r="AH4" s="98" t="s">
         <v>351</v>
-      </c>
-      <c r="O4" s="101" t="s">
-        <v>350</v>
-      </c>
-      <c r="P4" s="101" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q4" s="101" t="s">
-        <v>348</v>
-      </c>
-      <c r="R4" s="100" t="s">
-        <v>347</v>
-      </c>
-      <c r="S4" s="101" t="s">
-        <v>346</v>
-      </c>
-      <c r="T4" s="101" t="s">
-        <v>345</v>
-      </c>
-      <c r="U4" s="101" t="s">
-        <v>344</v>
-      </c>
-      <c r="V4" s="100" t="s">
-        <v>343</v>
-      </c>
-      <c r="W4" s="256"/>
-      <c r="X4" s="99" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y4" s="99" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z4" s="99" t="s">
-        <v>340</v>
-      </c>
-      <c r="AA4" s="99" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB4" s="256"/>
-      <c r="AC4" s="98" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD4" s="98" t="s">
-        <v>337</v>
-      </c>
-      <c r="AE4" s="98" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF4" s="98" t="s">
-        <v>335</v>
-      </c>
-      <c r="AG4" s="98" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH4" s="98" t="s">
-        <v>333</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK4" s="98" t="s">
+        <v>349</v>
+      </c>
+      <c r="AL4" s="258"/>
+      <c r="AM4" s="98" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN4" s="98" t="s">
+        <v>347</v>
+      </c>
+      <c r="AO4" s="98" t="s">
+        <v>346</v>
+      </c>
+      <c r="AP4" s="98" t="s">
+        <v>345</v>
+      </c>
+      <c r="AQ4" s="98" t="s">
+        <v>344</v>
+      </c>
+      <c r="AR4" s="98" t="s">
+        <v>343</v>
+      </c>
+      <c r="AS4" s="98" t="s">
+        <v>342</v>
+      </c>
+      <c r="AT4" s="98" t="s">
+        <v>341</v>
+      </c>
+      <c r="AU4" s="98" t="s">
+        <v>340</v>
+      </c>
+      <c r="AV4" s="98" t="s">
+        <v>339</v>
+      </c>
+      <c r="AW4" s="98" t="s">
+        <v>338</v>
+      </c>
+      <c r="AX4" s="98" t="s">
+        <v>337</v>
+      </c>
+      <c r="AY4" s="98" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ4" s="258"/>
+      <c r="BA4" s="97" t="s">
+        <v>335</v>
+      </c>
+      <c r="BB4" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="BC4" s="97" t="s">
+        <v>333</v>
+      </c>
+      <c r="BD4" s="97" t="s">
         <v>332</v>
       </c>
-      <c r="AK4" s="98" t="s">
+      <c r="BE4" s="97" t="s">
         <v>331</v>
       </c>
-      <c r="AL4" s="256"/>
-      <c r="AM4" s="98" t="s">
+      <c r="BF4" s="97" t="s">
         <v>330</v>
       </c>
-      <c r="AN4" s="98" t="s">
+      <c r="BG4" s="97" t="s">
         <v>329</v>
       </c>
-      <c r="AO4" s="98" t="s">
+      <c r="BH4" s="97" t="s">
         <v>328</v>
       </c>
-      <c r="AP4" s="98" t="s">
+      <c r="BI4" s="97" t="s">
         <v>327</v>
       </c>
-      <c r="AQ4" s="98" t="s">
+      <c r="BJ4" s="258"/>
+    </row>
+    <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
+      <c r="A5" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="77" t="s">
         <v>326</v>
       </c>
-      <c r="AR4" s="98" t="s">
+      <c r="F5" s="77" t="s">
         <v>325</v>
       </c>
-      <c r="AS4" s="98" t="s">
-        <v>324</v>
-      </c>
-      <c r="AT4" s="98" t="s">
-        <v>323</v>
-      </c>
-      <c r="AU4" s="98" t="s">
-        <v>322</v>
-      </c>
-      <c r="AV4" s="98" t="s">
-        <v>321</v>
-      </c>
-      <c r="AW4" s="98" t="s">
-        <v>320</v>
-      </c>
-      <c r="AX4" s="98" t="s">
-        <v>319</v>
-      </c>
-      <c r="AY4" s="98" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ4" s="256"/>
-      <c r="BA4" s="97" t="s">
-        <v>317</v>
-      </c>
-      <c r="BB4" s="97" t="s">
-        <v>316</v>
-      </c>
-      <c r="BC4" s="97" t="s">
-        <v>315</v>
-      </c>
-      <c r="BD4" s="97" t="s">
-        <v>314</v>
-      </c>
-      <c r="BE4" s="97" t="s">
-        <v>313</v>
-      </c>
-      <c r="BF4" s="97" t="s">
-        <v>312</v>
-      </c>
-      <c r="BG4" s="97" t="s">
-        <v>311</v>
-      </c>
-      <c r="BH4" s="97" t="s">
-        <v>310</v>
-      </c>
-      <c r="BI4" s="97" t="s">
-        <v>309</v>
-      </c>
-      <c r="BJ4" s="256"/>
-    </row>
-    <row r="5" spans="1:62" s="64" customFormat="1" ht="120" x14ac:dyDescent="0.15">
-      <c r="A5" s="72" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>227</v>
-      </c>
-      <c r="C5" s="78" t="s">
-        <v>226</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="77" t="s">
-        <v>308</v>
-      </c>
-      <c r="F5" s="77" t="s">
-        <v>307</v>
-      </c>
       <c r="G5" s="74" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
@@ -15729,25 +15908,25 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q5" s="74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="S5" s="74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="T5" s="74" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="U5" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15770,10 +15949,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15781,41 +15960,41 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="261"/>
-      <c r="AN5" s="261"/>
-      <c r="AO5" s="261"/>
-      <c r="AP5" s="261"/>
-      <c r="AQ5" s="261"/>
-      <c r="AR5" s="261"/>
-      <c r="AS5" s="262" t="s">
-        <v>205</v>
-      </c>
-      <c r="AT5" s="262" t="s">
-        <v>204</v>
-      </c>
-      <c r="AU5" s="262" t="s">
-        <v>203</v>
-      </c>
-      <c r="AV5" s="262" t="s">
-        <v>202</v>
-      </c>
-      <c r="AW5" s="262" t="s">
-        <v>39</v>
-      </c>
-      <c r="AX5" s="262" t="s">
-        <v>506</v>
-      </c>
-      <c r="AY5" s="262" t="s">
-        <v>507</v>
+      <c r="AM5" s="92"/>
+      <c r="AN5" s="92"/>
+      <c r="AO5" s="92"/>
+      <c r="AP5" s="92"/>
+      <c r="AQ5" s="92"/>
+      <c r="AR5" s="92"/>
+      <c r="AS5" s="74" t="s">
+        <v>318</v>
+      </c>
+      <c r="AT5" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="AU5" s="74" t="s">
+        <v>316</v>
+      </c>
+      <c r="AV5" s="74" t="s">
+        <v>315</v>
+      </c>
+      <c r="AW5" s="74" t="s">
+        <v>314</v>
+      </c>
+      <c r="AX5" s="74" t="s">
+        <v>313</v>
+      </c>
+      <c r="AY5" s="74" t="s">
+        <v>312</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -15835,27 +16014,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:62" s="64" customFormat="1" ht="339" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -15863,49 +16042,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -15914,58 +16093,58 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="262" t="s">
-        <v>211</v>
-      </c>
-      <c r="AN6" s="262" t="s">
-        <v>210</v>
-      </c>
-      <c r="AO6" s="262" t="s">
-        <v>209</v>
-      </c>
-      <c r="AP6" s="262" t="s">
-        <v>208</v>
-      </c>
-      <c r="AQ6" s="262" t="s">
-        <v>207</v>
-      </c>
-      <c r="AR6" s="262" t="s">
-        <v>206</v>
-      </c>
-      <c r="AS6" s="261"/>
-      <c r="AT6" s="261"/>
-      <c r="AU6" s="261"/>
-      <c r="AV6" s="261"/>
-      <c r="AW6" s="261"/>
-      <c r="AX6" s="262" t="s">
-        <v>508</v>
-      </c>
-      <c r="AY6" s="262" t="s">
-        <v>509</v>
+      <c r="AM6" s="74" t="s">
+        <v>292</v>
+      </c>
+      <c r="AN6" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO6" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="AP6" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="AQ6" s="74" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR6" s="74" t="s">
+        <v>287</v>
+      </c>
+      <c r="AS6" s="92"/>
+      <c r="AT6" s="92"/>
+      <c r="AU6" s="92"/>
+      <c r="AV6" s="92"/>
+      <c r="AW6" s="92"/>
+      <c r="AX6" s="74" t="s">
+        <v>286</v>
+      </c>
+      <c r="AY6" s="74" t="s">
+        <v>285</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -15987,22 +16166,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16037,41 +16216,41 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="263"/>
-      <c r="AN7" s="263"/>
-      <c r="AO7" s="263"/>
-      <c r="AP7" s="263"/>
-      <c r="AQ7" s="263"/>
-      <c r="AR7" s="263"/>
-      <c r="AS7" s="263"/>
-      <c r="AT7" s="263"/>
-      <c r="AU7" s="263"/>
-      <c r="AV7" s="263"/>
-      <c r="AW7" s="263"/>
-      <c r="AX7" s="263"/>
-      <c r="AY7" s="262" t="s">
-        <v>274</v>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="75"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="74" t="s">
+        <v>277</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16093,25 +16272,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16131,23 +16310,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16199,25 +16378,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E9" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="77" t="s">
+        <v>272</v>
+      </c>
+      <c r="G9" s="74" t="s">
         <v>270</v>
-      </c>
-      <c r="F9" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>267</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16237,23 +16416,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16261,22 +16440,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16295,7 +16474,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16317,25 +16496,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16355,23 +16534,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16379,22 +16558,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16413,7 +16592,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16435,25 +16614,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16473,23 +16652,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16497,22 +16676,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16531,7 +16710,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16553,25 +16732,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16591,23 +16770,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16615,22 +16794,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16649,7 +16828,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16669,27 +16848,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16709,23 +16888,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16777,25 +16956,25 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G14" s="74" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
@@ -16805,43 +16984,43 @@
         <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K14" s="74" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L14" s="74" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N14" s="74" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O14" s="74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P14" s="74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q14" s="74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="R14" s="74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="S14" s="74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="T14" s="74" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="U14" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V14" s="74" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -16856,72 +17035,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD14" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE14" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF14" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="AD14" s="74" t="s">
+      <c r="AG14" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="AE14" s="74" t="s">
+      <c r="AH14" s="74" t="s">
         <v>217</v>
-      </c>
-      <c r="AF14" s="74" t="s">
-        <v>216</v>
-      </c>
-      <c r="AG14" s="74" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH14" s="74" t="s">
-        <v>214</v>
       </c>
       <c r="AI14" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="AN14" s="74" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO14" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP14" s="74" t="s">
         <v>211</v>
       </c>
-      <c r="AN14" s="74" t="s">
+      <c r="AQ14" s="74" t="s">
         <v>210</v>
       </c>
-      <c r="AO14" s="74" t="s">
+      <c r="AR14" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="AP14" s="74" t="s">
+      <c r="AS14" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="AQ14" s="74" t="s">
+      <c r="AT14" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="AR14" s="74" t="s">
+      <c r="AU14" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="AS14" s="74" t="s">
+      <c r="AV14" s="74" t="s">
         <v>205</v>
-      </c>
-      <c r="AT14" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="AU14" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="AV14" s="74" t="s">
-        <v>202</v>
       </c>
       <c r="AW14" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -16943,25 +17122,25 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="77" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="F15" s="77" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="78" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="77" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" s="77" t="s">
-        <v>224</v>
-      </c>
       <c r="G15" s="74" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
@@ -16971,43 +17150,43 @@
         <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K15" s="74" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L15" s="74" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M15" s="74" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N15" s="74" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O15" s="74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P15" s="74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q15" s="74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="R15" s="74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="S15" s="74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="T15" s="74" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="U15" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V15" s="74" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17022,72 +17201,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD15" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE15" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF15" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="AD15" s="74" t="s">
+      <c r="AG15" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="AE15" s="74" t="s">
+      <c r="AH15" s="74" t="s">
         <v>217</v>
-      </c>
-      <c r="AF15" s="74" t="s">
-        <v>216</v>
-      </c>
-      <c r="AG15" s="74" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH15" s="74" t="s">
-        <v>214</v>
       </c>
       <c r="AI15" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="AN15" s="74" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO15" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP15" s="74" t="s">
         <v>211</v>
       </c>
-      <c r="AN15" s="74" t="s">
+      <c r="AQ15" s="74" t="s">
         <v>210</v>
       </c>
-      <c r="AO15" s="74" t="s">
+      <c r="AR15" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="AP15" s="74" t="s">
+      <c r="AS15" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="AQ15" s="74" t="s">
+      <c r="AT15" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="AR15" s="74" t="s">
+      <c r="AU15" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="AS15" s="74" t="s">
+      <c r="AV15" s="74" t="s">
         <v>205</v>
-      </c>
-      <c r="AT15" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="AU15" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="AV15" s="74" t="s">
-        <v>202</v>
       </c>
       <c r="AW15" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17114,7 +17293,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17381,16 +17560,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="259" t="s">
-        <v>419</v>
-      </c>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
+      <c r="B1" s="261" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
     </row>
     <row r="2" spans="1:62" s="112" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="158"/>
@@ -17400,172 +17579,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="258" t="s">
-        <v>417</v>
+        <v>436</v>
+      </c>
+      <c r="H2" s="260" t="s">
+        <v>435</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>416</v>
-      </c>
-      <c r="W2" s="258" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="W2" s="260" t="s">
+        <v>433</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB2" s="258" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="AB2" s="260" t="s">
+        <v>432</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>413</v>
-      </c>
-      <c r="AL2" s="258" t="s">
-        <v>412</v>
+        <v>431</v>
+      </c>
+      <c r="AL2" s="260" t="s">
+        <v>430</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>411</v>
-      </c>
-      <c r="AZ2" s="258" t="s">
-        <v>410</v>
+        <v>429</v>
+      </c>
+      <c r="AZ2" s="260" t="s">
+        <v>428</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>409</v>
-      </c>
-      <c r="BJ2" s="258" t="s">
-        <v>408</v>
+        <v>427</v>
+      </c>
+      <c r="BJ2" s="260" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17576,78 +17755,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" s="258"/>
+        <v>425</v>
+      </c>
+      <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="W3" s="258"/>
+        <v>412</v>
+      </c>
+      <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB3" s="258"/>
+        <v>409</v>
+      </c>
+      <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17656,255 +17835,255 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
+        <v>402</v>
+      </c>
+      <c r="AL3" s="260"/>
+      <c r="AM3" s="152" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN3" s="152" t="s">
+        <v>400</v>
+      </c>
+      <c r="AO3" s="152" t="s">
+        <v>399</v>
+      </c>
+      <c r="AP3" s="152" t="s">
+        <v>398</v>
+      </c>
+      <c r="AQ3" s="152" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR3" s="152" t="s">
+        <v>396</v>
+      </c>
+      <c r="AS3" s="152" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT3" s="152" t="s">
+        <v>394</v>
+      </c>
+      <c r="AU3" s="152" t="s">
+        <v>393</v>
+      </c>
+      <c r="AV3" s="152" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW3" s="152" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX3" s="152" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY3" s="152" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ3" s="260"/>
+      <c r="BA3" s="151" t="s">
+        <v>388</v>
+      </c>
+      <c r="BB3" s="151" t="s">
+        <v>387</v>
+      </c>
+      <c r="BC3" s="151" t="s">
+        <v>386</v>
+      </c>
+      <c r="BD3" s="151" t="s">
+        <v>385</v>
+      </c>
+      <c r="BE3" s="151" t="s">
         <v>384</v>
       </c>
-      <c r="AL3" s="258"/>
-      <c r="AM3" s="152" t="s">
+      <c r="BF3" s="151" t="s">
         <v>383</v>
       </c>
-      <c r="AN3" s="152" t="s">
+      <c r="BG3" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="AO3" s="152" t="s">
+      <c r="BH3" s="151" t="s">
         <v>381</v>
       </c>
-      <c r="AP3" s="152" t="s">
+      <c r="BI3" s="151" t="s">
         <v>380</v>
       </c>
-      <c r="AQ3" s="152" t="s">
-        <v>379</v>
-      </c>
-      <c r="AR3" s="152" t="s">
-        <v>378</v>
-      </c>
-      <c r="AS3" s="152" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT3" s="152" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU3" s="152" t="s">
-        <v>375</v>
-      </c>
-      <c r="AV3" s="152" t="s">
-        <v>374</v>
-      </c>
-      <c r="AW3" s="152" t="s">
-        <v>373</v>
-      </c>
-      <c r="AX3" s="152" t="s">
-        <v>372</v>
-      </c>
-      <c r="AY3" s="152" t="s">
-        <v>371</v>
-      </c>
-      <c r="AZ3" s="258"/>
-      <c r="BA3" s="151" t="s">
-        <v>370</v>
-      </c>
-      <c r="BB3" s="151" t="s">
-        <v>369</v>
-      </c>
-      <c r="BC3" s="151" t="s">
-        <v>368</v>
-      </c>
-      <c r="BD3" s="151" t="s">
-        <v>367</v>
-      </c>
-      <c r="BE3" s="151" t="s">
-        <v>366</v>
-      </c>
-      <c r="BF3" s="151" t="s">
-        <v>365</v>
-      </c>
-      <c r="BG3" s="151" t="s">
-        <v>364</v>
-      </c>
-      <c r="BH3" s="151" t="s">
-        <v>363</v>
-      </c>
-      <c r="BI3" s="151" t="s">
-        <v>362</v>
-      </c>
-      <c r="BJ3" s="258"/>
+      <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
+        <v>377</v>
+      </c>
+      <c r="F4" s="156" t="s">
+        <v>376</v>
+      </c>
+      <c r="G4" s="155" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="260"/>
+      <c r="I4" s="154" t="s">
+        <v>374</v>
+      </c>
+      <c r="J4" s="154" t="s">
+        <v>373</v>
+      </c>
+      <c r="K4" s="154" t="s">
+        <v>372</v>
+      </c>
+      <c r="L4" s="154" t="s">
+        <v>371</v>
+      </c>
+      <c r="M4" s="154" t="s">
+        <v>370</v>
+      </c>
+      <c r="N4" s="154" t="s">
+        <v>369</v>
+      </c>
+      <c r="O4" s="154" t="s">
+        <v>368</v>
+      </c>
+      <c r="P4" s="154" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q4" s="154" t="s">
+        <v>366</v>
+      </c>
+      <c r="R4" s="154" t="s">
+        <v>365</v>
+      </c>
+      <c r="S4" s="154" t="s">
+        <v>364</v>
+      </c>
+      <c r="T4" s="154" t="s">
+        <v>363</v>
+      </c>
+      <c r="U4" s="154" t="s">
+        <v>362</v>
+      </c>
+      <c r="V4" s="154" t="s">
+        <v>361</v>
+      </c>
+      <c r="W4" s="260"/>
+      <c r="X4" s="153" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y4" s="153" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="156" t="s">
+      <c r="Z4" s="153" t="s">
         <v>358</v>
       </c>
-      <c r="G4" s="155" t="s">
+      <c r="AA4" s="153" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="258"/>
-      <c r="I4" s="154" t="s">
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="152" t="s">
         <v>356</v>
       </c>
-      <c r="J4" s="154" t="s">
+      <c r="AD4" s="152" t="s">
         <v>355</v>
       </c>
-      <c r="K4" s="154" t="s">
+      <c r="AE4" s="152" t="s">
         <v>354</v>
       </c>
-      <c r="L4" s="154" t="s">
+      <c r="AF4" s="152" t="s">
         <v>353</v>
       </c>
-      <c r="M4" s="154" t="s">
+      <c r="AG4" s="152" t="s">
         <v>352</v>
       </c>
-      <c r="N4" s="154" t="s">
+      <c r="AH4" s="152" t="s">
         <v>351</v>
-      </c>
-      <c r="O4" s="154" t="s">
-        <v>350</v>
-      </c>
-      <c r="P4" s="154" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q4" s="154" t="s">
-        <v>348</v>
-      </c>
-      <c r="R4" s="154" t="s">
-        <v>347</v>
-      </c>
-      <c r="S4" s="154" t="s">
-        <v>346</v>
-      </c>
-      <c r="T4" s="154" t="s">
-        <v>345</v>
-      </c>
-      <c r="U4" s="154" t="s">
-        <v>344</v>
-      </c>
-      <c r="V4" s="154" t="s">
-        <v>343</v>
-      </c>
-      <c r="W4" s="258"/>
-      <c r="X4" s="153" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y4" s="153" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z4" s="153" t="s">
-        <v>340</v>
-      </c>
-      <c r="AA4" s="153" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB4" s="258"/>
-      <c r="AC4" s="152" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD4" s="152" t="s">
-        <v>337</v>
-      </c>
-      <c r="AE4" s="152" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF4" s="152" t="s">
-        <v>335</v>
-      </c>
-      <c r="AG4" s="152" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH4" s="152" t="s">
-        <v>333</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK4" s="152" t="s">
+        <v>349</v>
+      </c>
+      <c r="AL4" s="260"/>
+      <c r="AM4" s="152" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN4" s="152" t="s">
+        <v>347</v>
+      </c>
+      <c r="AO4" s="152" t="s">
+        <v>346</v>
+      </c>
+      <c r="AP4" s="152" t="s">
+        <v>345</v>
+      </c>
+      <c r="AQ4" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="AR4" s="152" t="s">
+        <v>343</v>
+      </c>
+      <c r="AS4" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="AT4" s="152" t="s">
+        <v>341</v>
+      </c>
+      <c r="AU4" s="152" t="s">
+        <v>340</v>
+      </c>
+      <c r="AV4" s="152" t="s">
+        <v>339</v>
+      </c>
+      <c r="AW4" s="152" t="s">
+        <v>338</v>
+      </c>
+      <c r="AX4" s="152" t="s">
+        <v>337</v>
+      </c>
+      <c r="AY4" s="152" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ4" s="260"/>
+      <c r="BA4" s="151" t="s">
+        <v>335</v>
+      </c>
+      <c r="BB4" s="151" t="s">
+        <v>334</v>
+      </c>
+      <c r="BC4" s="151" t="s">
+        <v>333</v>
+      </c>
+      <c r="BD4" s="151" t="s">
         <v>332</v>
       </c>
-      <c r="AK4" s="152" t="s">
+      <c r="BE4" s="151" t="s">
         <v>331</v>
       </c>
-      <c r="AL4" s="258"/>
-      <c r="AM4" s="152" t="s">
+      <c r="BF4" s="151" t="s">
         <v>330</v>
       </c>
-      <c r="AN4" s="152" t="s">
+      <c r="BG4" s="151" t="s">
         <v>329</v>
       </c>
-      <c r="AO4" s="152" t="s">
+      <c r="BH4" s="151" t="s">
         <v>328</v>
       </c>
-      <c r="AP4" s="152" t="s">
+      <c r="BI4" s="151" t="s">
         <v>327</v>
       </c>
-      <c r="AQ4" s="152" t="s">
-        <v>326</v>
-      </c>
-      <c r="AR4" s="152" t="s">
-        <v>325</v>
-      </c>
-      <c r="AS4" s="152" t="s">
-        <v>324</v>
-      </c>
-      <c r="AT4" s="152" t="s">
-        <v>323</v>
-      </c>
-      <c r="AU4" s="152" t="s">
-        <v>322</v>
-      </c>
-      <c r="AV4" s="152" t="s">
-        <v>321</v>
-      </c>
-      <c r="AW4" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="AX4" s="152" t="s">
-        <v>319</v>
-      </c>
-      <c r="AY4" s="152" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ4" s="258"/>
-      <c r="BA4" s="151" t="s">
-        <v>317</v>
-      </c>
-      <c r="BB4" s="151" t="s">
-        <v>316</v>
-      </c>
-      <c r="BC4" s="151" t="s">
-        <v>315</v>
-      </c>
-      <c r="BD4" s="151" t="s">
-        <v>314</v>
-      </c>
-      <c r="BE4" s="151" t="s">
-        <v>313</v>
-      </c>
-      <c r="BF4" s="151" t="s">
-        <v>312</v>
-      </c>
-      <c r="BG4" s="151" t="s">
-        <v>311</v>
-      </c>
-      <c r="BH4" s="151" t="s">
-        <v>310</v>
-      </c>
-      <c r="BI4" s="151" t="s">
-        <v>309</v>
-      </c>
-      <c r="BJ4" s="258"/>
+      <c r="BJ4" s="260"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -17913,10 +18092,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18035,35 +18214,46 @@
       <c r="AQ5" s="143"/>
       <c r="AR5" s="143"/>
       <c r="AS5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AT5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AU5" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AV5" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AW5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AX5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4. TOTAL CIVIL NON SPÉCIALISÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3. TOTAL CONTENTIEUX DE LA PROTECTION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AY5" s="126" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4. TOTAL CIVIL NON SPÉCIALISÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("4.0. CONTENTIEUX GÉNÉRAL &lt;10.000€",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+(SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3. TOTAL CONTENTIEUX DE LA PROTECTION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.43. INJONCTIONS DE PAYER",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS"))-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUM(AS5:AW5)</f>
         <v>#N/A</v>
       </c>
       <c r="AZ5" s="117" t="e">
@@ -18086,7 +18276,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18095,10 +18285,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18226,30 +18416,28 @@
       </c>
       <c r="AM6" s="124" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AN6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AO6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AP6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AQ6" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AR6" s="126" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AS6" s="143"/>
@@ -18265,7 +18453,7 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AY6" s="142" t="e">
@@ -18276,7 +18464,8 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")-
+SUM(AM6:AW6)</f>
         <v>#N/A</v>
       </c>
       <c r="AZ6" s="117" t="e">
@@ -18299,7 +18488,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18308,10 +18497,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18417,7 +18606,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18426,10 +18615,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18526,7 +18715,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18535,10 +18724,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18705,7 +18894,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18714,10 +18903,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18841,7 +19030,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -18850,10 +19039,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18977,7 +19166,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -18986,10 +19175,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19119,7 +19308,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19128,10 +19317,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19228,7 +19417,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19237,10 +19426,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19450,7 +19639,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19459,10 +19648,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19677,7 +19866,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -19980,7 +20169,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFF230F-D554-BF4B-801A-5BCCA5A7E477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234BC58B-24CA-154E-AFA4-B474FE535B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22940" windowHeight="13240" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22940" windowHeight="13240" activeTab="6" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ACCUEIL" sheetId="33" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Agrégats DDG" sheetId="10" r:id="rId4"/>
     <sheet name="codage tribunal" sheetId="12" state="hidden" r:id="rId5"/>
     <sheet name="Juridictions" sheetId="17" state="hidden" r:id="rId6"/>
-    <sheet name="Table_Fonctions" sheetId="19" state="hidden" r:id="rId7"/>
+    <sheet name="Table_Fonctions" sheetId="19" r:id="rId7"/>
     <sheet name="ETPT_TJ_corresp-AJUST2" sheetId="24" state="hidden" r:id="rId8"/>
     <sheet name="ETPT_TJ" sheetId="25" state="hidden" r:id="rId9"/>
     <sheet name="ETPT_TPRX" sheetId="26" state="hidden" r:id="rId10"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="522">
   <si>
     <t>#! END_ROW</t>
   </si>
@@ -492,9 +492,6 @@
   </si>
   <si>
     <t>ELEVE AVOCAT</t>
-  </si>
-  <si>
-    <t>Manque affectation (siège Autres/parquet/pôle social) ?</t>
   </si>
   <si>
     <t>JURISTE ASSISTANT Parquet</t>
@@ -5484,10 +5481,10 @@
     <row r="1" spans="1:8" s="28" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="196"/>
       <c r="B1" s="197" t="s">
+        <v>491</v>
+      </c>
+      <c r="C1" s="235" t="s">
         <v>492</v>
-      </c>
-      <c r="C1" s="235" t="s">
-        <v>493</v>
       </c>
       <c r="D1" s="235"/>
       <c r="E1" s="235"/>
@@ -5500,7 +5497,7 @@
       <c r="A2" s="199"/>
       <c r="B2" s="200"/>
       <c r="C2" s="236" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D2" s="236"/>
       <c r="E2" s="236"/>
@@ -5519,16 +5516,16 @@
     <row r="4" spans="1:8" s="208" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="205"/>
       <c r="B4" s="206" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="207" t="s">
         <v>495</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="D4" s="207" t="s">
         <v>496</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="E4" s="242" t="s">
         <v>497</v>
-      </c>
-      <c r="E4" s="242" t="s">
-        <v>498</v>
       </c>
       <c r="F4" s="243"/>
       <c r="G4" s="216"/>
@@ -5539,16 +5536,16 @@
     <row r="5" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="203"/>
       <c r="B5" s="220" t="s">
+        <v>498</v>
+      </c>
+      <c r="C5" s="213" t="s">
         <v>499</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="D5" s="213" t="s">
         <v>500</v>
       </c>
-      <c r="D5" s="213" t="s">
-        <v>501</v>
-      </c>
       <c r="E5" s="244" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F5" s="245"/>
       <c r="G5" s="215"/>
@@ -5559,16 +5556,16 @@
     <row r="6" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="203"/>
       <c r="B6" s="221" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="214" t="s">
         <v>502</v>
       </c>
-      <c r="C6" s="214" t="s">
+      <c r="D6" s="214" t="s">
         <v>503</v>
       </c>
-      <c r="D6" s="214" t="s">
-        <v>504</v>
-      </c>
       <c r="E6" s="246" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F6" s="247"/>
       <c r="G6" s="215"/>
@@ -5579,16 +5576,16 @@
     <row r="7" spans="1:8" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="203"/>
       <c r="B7" s="222" t="s">
+        <v>504</v>
+      </c>
+      <c r="C7" s="214" t="s">
         <v>505</v>
       </c>
-      <c r="C7" s="214" t="s">
+      <c r="D7" s="214" t="s">
         <v>506</v>
       </c>
-      <c r="D7" s="214" t="s">
-        <v>507</v>
-      </c>
       <c r="E7" s="246" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F7" s="247"/>
       <c r="G7" s="215"/>
@@ -5599,16 +5596,16 @@
     <row r="8" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="203"/>
       <c r="B8" s="223" t="s">
+        <v>507</v>
+      </c>
+      <c r="C8" s="237" t="s">
         <v>508</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="D8" s="237" t="s">
         <v>509</v>
       </c>
-      <c r="D8" s="237" t="s">
-        <v>510</v>
-      </c>
       <c r="E8" s="248" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F8" s="249"/>
       <c r="G8" s="215"/>
@@ -5619,7 +5616,7 @@
     <row r="9" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="203"/>
       <c r="B9" s="224" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C9" s="237"/>
       <c r="D9" s="237"/>
@@ -5633,7 +5630,7 @@
     <row r="10" spans="1:8" s="28" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="203"/>
       <c r="B10" s="225" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C10" s="238"/>
       <c r="D10" s="238"/>
@@ -5659,7 +5656,7 @@
       <c r="A12" s="203"/>
       <c r="B12" s="217"/>
       <c r="C12" s="241" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D12" s="241"/>
       <c r="E12" s="241"/>
@@ -5729,7 +5726,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="262" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B1" s="262"/>
       <c r="C1" s="262"/>
@@ -5774,91 +5771,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O2" s="191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AB2" s="191" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC2" s="191" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE2" s="260" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AI2" s="260" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" x14ac:dyDescent="0.2">
@@ -5869,181 +5866,181 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="S3" s="260"/>
       <c r="T3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="U3" s="260"/>
       <c r="V3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AB3" s="191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AC3" s="191" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AE3" s="260"/>
       <c r="AF3" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="S4" s="260"/>
       <c r="T4" s="155" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U4" s="260"/>
       <c r="V4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AB4" s="191" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AC4" s="191" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AE4" s="260"/>
       <c r="AF4" s="155" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
@@ -6052,10 +6049,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6159,7 +6156,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="182" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
@@ -6168,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6" s="183" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" s="140"/>
       <c r="H6" s="184">
@@ -6220,7 +6217,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -6229,10 +6226,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="162">
@@ -6281,7 +6278,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -6290,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6354,7 +6351,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -6363,10 +6360,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -6436,7 +6433,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -6445,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6509,7 +6506,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -6518,10 +6515,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6582,7 +6579,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -6591,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -6658,7 +6655,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -6667,10 +6664,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -6728,7 +6725,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -6737,10 +6734,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -6841,7 +6838,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -6850,10 +6847,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -6959,7 +6956,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" s="117" t="e">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -7089,7 +7086,7 @@
     </row>
     <row r="19" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -7124,7 +7121,7 @@
       <c r="A1" s="112"/>
       <c r="C1" s="180"/>
       <c r="D1" s="180" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
@@ -7141,16 +7138,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7161,43 +7158,43 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -7206,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
@@ -7230,7 +7227,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -7239,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G6" s="173"/>
       <c r="H6" s="164">
@@ -7257,7 +7254,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -7266,10 +7263,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G7" s="173"/>
       <c r="H7" s="164">
@@ -7284,7 +7281,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -7293,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G8" s="173"/>
       <c r="H8" s="164">
@@ -7311,7 +7308,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7320,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G9" s="173"/>
       <c r="H9" s="164">
@@ -7338,7 +7335,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -7347,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="173"/>
       <c r="H10" s="164">
@@ -7365,7 +7362,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -7374,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G11" s="173"/>
       <c r="H11" s="164">
@@ -7392,7 +7389,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -7401,10 +7398,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -7422,7 +7419,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -7431,10 +7428,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G13" s="169" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -7457,7 +7454,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G14" s="164" t="e">
         <f>SUM(G5:G13)</f>
@@ -7516,12 +7513,12 @@
   <sheetData>
     <row r="1" spans="1:63" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -7590,172 +7587,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="W2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AL2" s="260" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AZ2" s="260" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BJ2" s="260" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="BK2"/>
     </row>
@@ -7767,78 +7764,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -7847,265 +7844,265 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AL3" s="260"/>
       <c r="AM3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AZ3" s="260"/>
       <c r="BA3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:63" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="W4" s="260"/>
       <c r="X4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB4" s="260"/>
       <c r="AC4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AL4" s="260"/>
       <c r="AM4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AZ4" s="260"/>
       <c r="BA4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BJ4" s="260"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="112" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
       <c r="D5" s="211"/>
       <c r="E5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G5),"",IF(ETPT_TJ!G5=0,"",ETPT_TJ!G5)))</f>
@@ -8308,7 +8305,7 @@
     </row>
     <row r="6" spans="1:63" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -8317,10 +8314,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G6),"",IF(ETPT_TJ!G6=0,"",ETPT_TJ!G6)))</f>
@@ -8522,7 +8519,7 @@
     </row>
     <row r="7" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -8531,10 +8528,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G7),"",IF(ETPT_TJ!G7=0,"",ETPT_TJ!G7)))</f>
@@ -8736,7 +8733,7 @@
     </row>
     <row r="8" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -8745,10 +8742,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G8),"",IF(ETPT_TJ!G8=0,"",ETPT_TJ!G8)))</f>
@@ -8950,7 +8947,7 @@
     </row>
     <row r="9" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -8959,10 +8956,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G9),"",IF(ETPT_TJ!G9=0,"",ETPT_TJ!G9)))</f>
@@ -9164,7 +9161,7 @@
     </row>
     <row r="10" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -9173,10 +9170,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G10),"",IF(ETPT_TJ!G10=0,"",ETPT_TJ!G10)))</f>
@@ -9378,7 +9375,7 @@
     </row>
     <row r="11" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -9387,10 +9384,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G11),"",IF(ETPT_TJ!G11=0,"",ETPT_TJ!G11)))</f>
@@ -9592,7 +9589,7 @@
     </row>
     <row r="12" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -9601,10 +9598,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G12),"",IF(ETPT_TJ!G12=0,"",ETPT_TJ!G12)))</f>
@@ -9806,7 +9803,7 @@
     </row>
     <row r="13" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -9815,10 +9812,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G13),"",IF(ETPT_TJ!G13=0,"",ETPT_TJ!G13)))</f>
@@ -10020,7 +10017,7 @@
     </row>
     <row r="14" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -10029,10 +10026,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G14),"",IF(ETPT_TJ!G14=0,"",ETPT_TJ!G14)))</f>
@@ -10234,7 +10231,7 @@
     </row>
     <row r="15" spans="1:63" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -10243,10 +10240,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="127" t="str">
         <f>IF(ISBLANK(ETPT_TJ_DDG!$D$5),"",IF(ISERROR(ETPT_TJ!G15),"",IF(ETPT_TJ!G15=0,"",ETPT_TJ!G15)))</f>
@@ -10453,7 +10450,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" s="118">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -10686,7 +10683,7 @@
     </row>
     <row r="18" spans="4:52" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="229" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -10731,12 +10728,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -10805,91 +10802,91 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="V2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AB2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AD2" s="155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE2" s="260" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AF2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AH2" s="155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AI2" s="260" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -10900,190 +10897,190 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J3" s="155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K3" s="155" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L3" s="155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M3" s="155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N3" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O3" s="155" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P3" s="155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q3" s="155" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="S3" s="260"/>
       <c r="T3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="U3" s="260"/>
       <c r="V3" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="W3" s="155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="X3" s="155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y3" s="155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AB3" s="155" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AC3" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AD3" s="155" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AE3" s="260"/>
       <c r="AF3" s="155" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG3" s="155" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="155" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AI3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="158"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J4" s="155" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K4" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M4" s="155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N4" s="155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O4" s="155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P4" s="155" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q4" s="155" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R4" s="155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="S4" s="260"/>
       <c r="T4" s="155" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U4" s="260"/>
       <c r="V4" s="155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="W4" s="155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="X4" s="155" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y4" s="155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z4" s="155" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AA4" s="155" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AB4" s="155" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AC4" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AD4" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AE4" s="260"/>
       <c r="AF4" s="155" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG4" s="155" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AH4" s="155" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AI4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B5" s="133"/>
       <c r="C5" s="133"/>
       <c r="D5" s="192"/>
       <c r="E5" s="133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G5),"",IF(ETPT_TPRX!G5=0,"",ETPT_TPRX!G5)))</f>
@@ -11204,7 +11201,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B6" s="133"/>
       <c r="C6" s="133"/>
@@ -11213,10 +11210,10 @@
         <v/>
       </c>
       <c r="E6" s="133" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6" s="133" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G6),"",IF(ETPT_TPRX!G6=0,"",ETPT_TPRX!G6)))</f>
@@ -11337,7 +11334,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B7" s="133"/>
       <c r="C7" s="133"/>
@@ -11346,10 +11343,10 @@
         <v/>
       </c>
       <c r="E7" s="133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G7),"",IF(ETPT_TPRX!G7=0,"",ETPT_TPRX!G7)))</f>
@@ -11470,7 +11467,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="133"/>
@@ -11479,10 +11476,10 @@
         <v/>
       </c>
       <c r="E8" s="133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G8),"",IF(ETPT_TPRX!G8=0,"",ETPT_TPRX!G8)))</f>
@@ -11603,7 +11600,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -11612,10 +11609,10 @@
         <v/>
       </c>
       <c r="E9" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G9" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G9),"",IF(ETPT_TPRX!G9=0,"",ETPT_TPRX!G9)))</f>
@@ -11736,7 +11733,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B10" s="133"/>
       <c r="C10" s="133"/>
@@ -11745,10 +11742,10 @@
         <v/>
       </c>
       <c r="E10" s="133" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G10" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G10),"",IF(ETPT_TPRX!G10=0,"",ETPT_TPRX!G10)))</f>
@@ -11869,7 +11866,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -11878,10 +11875,10 @@
         <v/>
       </c>
       <c r="E11" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G11),"",IF(ETPT_TPRX!G11=0,"",ETPT_TPRX!G11)))</f>
@@ -12002,7 +11999,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
@@ -12011,10 +12008,10 @@
         <v/>
       </c>
       <c r="E12" s="133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G12),"",IF(ETPT_TPRX!G12=0,"",ETPT_TPRX!G12)))</f>
@@ -12135,7 +12132,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -12144,10 +12141,10 @@
         <v/>
       </c>
       <c r="E13" s="133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G13),"",IF(ETPT_TPRX!G13=0,"",ETPT_TPRX!G13)))</f>
@@ -12268,7 +12265,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A14" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B14" s="133"/>
       <c r="C14" s="133"/>
@@ -12277,10 +12274,10 @@
         <v/>
       </c>
       <c r="E14" s="133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="133" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G14),"",IF(ETPT_TPRX!G14=0,"",ETPT_TPRX!G14)))</f>
@@ -12401,7 +12398,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A15" s="161" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -12410,10 +12407,10 @@
         <v/>
       </c>
       <c r="E15" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="140" t="str">
         <f>IF(ISBLANK(ETPT_TPRX_DDG!$D$5),"",IF(ISERROR(ETPT_TPRX!G15),"",IF(ETPT_TPRX!G15=0,"",ETPT_TPRX!G15)))</f>
@@ -12539,7 +12536,7 @@
       <c r="D16" s="160"/>
       <c r="E16" s="160"/>
       <c r="F16" s="159" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" s="117">
         <f t="shared" ref="G16:AI16" si="6">SUM(G5:G15)</f>
@@ -12663,7 +12660,7 @@
     </row>
     <row r="18" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D18" s="226" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E18" s="227"/>
       <c r="F18"/>
@@ -12685,7 +12682,7 @@
     </row>
     <row r="20" spans="4:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="229" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E20" s="230"/>
       <c r="F20" s="231"/>
@@ -12726,12 +12723,12 @@
   <sheetData>
     <row r="1" spans="1:62" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="6"/>
@@ -12800,16 +12797,16 @@
       <c r="E2" s="178"/>
       <c r="F2" s="178"/>
       <c r="G2" s="155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="36" x14ac:dyDescent="0.2">
@@ -12820,52 +12817,52 @@
       <c r="E3" s="178"/>
       <c r="F3" s="178"/>
       <c r="G3" s="155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J3" s="260"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="177"/>
       <c r="B4" s="176" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="176" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="176" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="155" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J4" s="260"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
       <c r="D5" s="193"/>
       <c r="E5" s="170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="170" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G5),"",IF(ETPT_CPH!G5=0,"",ETPT_CPH!G5)))</f>
@@ -12886,7 +12883,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B6" s="170"/>
       <c r="C6" s="170"/>
@@ -12895,10 +12892,10 @@
         <v/>
       </c>
       <c r="E6" s="170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F6" s="170" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G6),"",IF(ETPT_CPH!G6=0,"",ETPT_CPH!G6)))</f>
@@ -12919,7 +12916,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A7" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="170"/>
       <c r="C7" s="170"/>
@@ -12928,10 +12925,10 @@
         <v/>
       </c>
       <c r="E7" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G7),"",IF(ETPT_CPH!G7=0,"",ETPT_CPH!G7)))</f>
@@ -12952,7 +12949,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A8" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B8" s="170"/>
       <c r="C8" s="170"/>
@@ -12961,10 +12958,10 @@
         <v/>
       </c>
       <c r="E8" s="170" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F8" s="170" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G8" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G8),"",IF(ETPT_CPH!G8=0,"",ETPT_CPH!G8)))</f>
@@ -12985,7 +12982,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A9" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -12994,10 +12991,10 @@
         <v/>
       </c>
       <c r="E9" s="170" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F9" s="170" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G9" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G9),"",IF(ETPT_CPH!G9=0,"",ETPT_CPH!G9)))</f>
@@ -13018,7 +13015,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A10" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -13027,10 +13024,10 @@
         <v/>
       </c>
       <c r="E10" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F10" s="170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G10),"",IF(ETPT_CPH!G10=0,"",ETPT_CPH!G10)))</f>
@@ -13051,7 +13048,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B11" s="170"/>
       <c r="C11" s="170"/>
@@ -13060,10 +13057,10 @@
         <v/>
       </c>
       <c r="E11" s="170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F11" s="170" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G11),"",IF(ETPT_CPH!G11=0,"",ETPT_CPH!G11)))</f>
@@ -13084,7 +13081,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A12" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B12" s="170"/>
       <c r="C12" s="170"/>
@@ -13093,10 +13090,10 @@
         <v/>
       </c>
       <c r="E12" s="170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F12" s="170" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G12),"",IF(ETPT_CPH!G12=0,"",ETPT_CPH!G12)))</f>
@@ -13117,7 +13114,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A13" s="171" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B13" s="170"/>
       <c r="C13" s="170"/>
@@ -13126,10 +13123,10 @@
         <v/>
       </c>
       <c r="E13" s="170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13" s="170" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IF(ISBLANK(ETPT_CPH_DDG!$D$5),"",IF(ISERROR(ETPT_CPH!G13),"",IF(ETPT_CPH!G13=0,"",ETPT_CPH!G13)))</f>
@@ -13155,7 +13152,7 @@
       <c r="D14" s="167"/>
       <c r="E14" s="166"/>
       <c r="F14" s="165" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G14" s="164">
         <f>SUM(G5:G13)</f>
@@ -13176,7 +13173,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D16" s="226" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E16" s="227"/>
       <c r="F16" s="23"/>
@@ -13224,7 +13221,7 @@
   <sheetData>
     <row r="1" spans="1:118" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13547,7 +13544,7 @@
   <sheetData>
     <row r="1" spans="1:137" s="4" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -13558,7 +13555,7 @@
         <v>6</v>
       </c>
       <c r="EA1" s="254" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="EB1" s="254"/>
       <c r="EC1" s="254"/>
@@ -13645,7 +13642,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
       <c r="C1" s="210" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -13894,7 +13891,7 @@
       </c>
       <c r="H1"/>
       <c r="I1" s="195" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -13954,19 +13951,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F1" s="59" t="s">
         <v>34</v>
@@ -13974,16 +13971,16 @@
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>46</v>
@@ -13994,16 +13991,16 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>46</v>
@@ -14014,16 +14011,16 @@
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>46</v>
@@ -14034,16 +14031,16 @@
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>46</v>
@@ -14054,16 +14051,16 @@
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>46</v>
@@ -14074,16 +14071,16 @@
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>46</v>
@@ -14094,16 +14091,16 @@
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>46</v>
@@ -14114,16 +14111,16 @@
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>46</v>
@@ -14134,16 +14131,16 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>46</v>
@@ -14154,16 +14151,16 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>46</v>
@@ -14174,16 +14171,16 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>46</v>
@@ -14194,16 +14191,16 @@
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>46</v>
@@ -14214,16 +14211,16 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>46</v>
@@ -14234,16 +14231,16 @@
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>46</v>
@@ -14254,16 +14251,16 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>46</v>
@@ -14274,16 +14271,16 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>46</v>
@@ -14294,16 +14291,16 @@
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>46</v>
@@ -14314,16 +14311,16 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>46</v>
@@ -14334,16 +14331,16 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>46</v>
@@ -14354,16 +14351,16 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>46</v>
@@ -14374,16 +14371,16 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>69</v>
@@ -14394,16 +14391,16 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="57" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>69</v>
@@ -14414,16 +14411,16 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>73</v>
@@ -14434,16 +14431,16 @@
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>73</v>
@@ -14454,10 +14451,10 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>76</v>
@@ -14474,10 +14471,10 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>79</v>
@@ -14494,10 +14491,10 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>169</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>170</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>80</v>
@@ -14514,10 +14511,10 @@
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C29" s="54" t="s">
         <v>81</v>
@@ -14534,7 +14531,7 @@
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
@@ -14543,7 +14540,7 @@
         <v>83</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>84</v>
@@ -14554,16 +14551,16 @@
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>84</v>
@@ -14574,16 +14571,16 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>84</v>
@@ -14594,7 +14591,7 @@
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>88</v>
@@ -14603,7 +14600,7 @@
         <v>88</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>84</v>
@@ -14614,7 +14611,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>89</v>
@@ -14623,7 +14620,7 @@
         <v>89</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>84</v>
@@ -14634,7 +14631,7 @@
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>90</v>
@@ -14643,7 +14640,7 @@
         <v>90</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>84</v>
@@ -14654,7 +14651,7 @@
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>92</v>
@@ -14663,7 +14660,7 @@
         <v>92</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>93</v>
@@ -14674,16 +14671,16 @@
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>93</v>
@@ -14694,7 +14691,7 @@
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>96</v>
@@ -14703,7 +14700,7 @@
         <v>96</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>93</v>
@@ -14714,7 +14711,7 @@
     </row>
     <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>97</v>
@@ -14723,7 +14720,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>93</v>
@@ -14734,7 +14731,7 @@
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>98</v>
@@ -14743,7 +14740,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>93</v>
@@ -14754,7 +14751,7 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>100</v>
@@ -14763,7 +14760,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" s="48" t="s">
         <v>101</v>
@@ -14774,16 +14771,16 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C42" s="48" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E42" s="48" t="s">
         <v>101</v>
@@ -14794,7 +14791,7 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>104</v>
@@ -14803,7 +14800,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E43" s="48" t="s">
         <v>101</v>
@@ -14814,7 +14811,7 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>105</v>
@@ -14823,7 +14820,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="48" t="s">
         <v>101</v>
@@ -14834,7 +14831,7 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>106</v>
@@ -14843,7 +14840,7 @@
         <v>106</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>101</v>
@@ -14854,10 +14851,10 @@
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C46" s="48" t="s">
         <v>108</v>
@@ -14874,10 +14871,10 @@
     </row>
     <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C47" s="48" t="s">
         <v>111</v>
@@ -14894,10 +14891,10 @@
     </row>
     <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C48" s="48" t="s">
         <v>112</v>
@@ -14914,10 +14911,10 @@
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C49" s="48" t="s">
         <v>113</v>
@@ -14934,10 +14931,10 @@
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>114</v>
@@ -14954,10 +14951,10 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" s="48" t="s">
         <v>115</v>
@@ -14969,15 +14966,15 @@
         <v>109</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="41" t="s">
         <v>154</v>
-      </c>
-      <c r="B52" s="41" t="s">
-        <v>155</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>116</v>
@@ -14994,7 +14991,7 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B53" s="41" t="s">
         <v>143</v>
@@ -15014,7 +15011,7 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B54" s="41" t="s">
         <v>142</v>
@@ -15034,7 +15031,7 @@
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B55" s="54" t="s">
         <v>139</v>
@@ -15057,7 +15054,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>122</v>
@@ -15077,7 +15074,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>123</v>
@@ -15097,7 +15094,7 @@
         <v>140</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D58" s="42" t="s">
         <v>137</v>
@@ -15106,7 +15103,7 @@
         <v>109</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15114,7 +15111,7 @@
         <v>140</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>125</v>
@@ -15128,16 +15125,14 @@
       <c r="F59" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="G59" s="42" t="s">
-        <v>146</v>
-      </c>
+      <c r="G59" s="42"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>127</v>
@@ -15151,16 +15146,14 @@
       <c r="F60" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="G60" s="42" t="s">
-        <v>146</v>
-      </c>
+      <c r="G60" s="42"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49" t="s">
         <v>140</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C61" s="48" t="s">
         <v>129</v>
@@ -15174,19 +15167,17 @@
       <c r="F61" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="G61" s="42" t="s">
-        <v>146</v>
-      </c>
+      <c r="G61" s="42"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="233" t="s">
         <v>140</v>
       </c>
       <c r="B62" s="234" t="s">
+        <v>519</v>
+      </c>
+      <c r="C62" s="234" t="s">
         <v>520</v>
-      </c>
-      <c r="C62" s="234" t="s">
-        <v>521</v>
       </c>
       <c r="D62" s="234" t="s">
         <v>137</v>
@@ -15227,7 +15218,7 @@
         <v>143</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D64" s="48" t="s">
         <v>137</v>
@@ -15247,7 +15238,7 @@
         <v>143</v>
       </c>
       <c r="C65" s="48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D65" s="48" t="s">
         <v>137</v>
@@ -15343,7 +15334,7 @@
     <row r="1" spans="1:62" s="64" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A1" s="107"/>
       <c r="B1" s="259" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C1" s="259"/>
       <c r="D1" s="259"/>
@@ -15370,172 +15361,172 @@
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="102" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2" s="258" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V2" s="101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="W2" s="258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="X2" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y2" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z2" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA2" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB2" s="258" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AD2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AF2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AH2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AI2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AK2" s="98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AL2" s="258" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AO2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AP2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AQ2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AR2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AT2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AU2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AW2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AX2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AY2" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AZ2" s="258" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BA2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BB2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BC2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BE2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BG2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BH2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BI2" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BJ2" s="258" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
@@ -15546,78 +15537,78 @@
       <c r="E3" s="105"/>
       <c r="F3" s="105"/>
       <c r="G3" s="102" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="258"/>
       <c r="I3" s="101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L3" s="101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M3" s="101" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N3" s="101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O3" s="101" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P3" s="101" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q3" s="101" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="T3" s="101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U3" s="101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V3" s="101" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="W3" s="258"/>
       <c r="X3" s="96"/>
       <c r="Y3" s="102" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Z3" s="102" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA3" s="102" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AB3" s="258"/>
       <c r="AC3" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AD3" s="98" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AE3" s="98" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AF3" s="98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG3" s="98" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AH3" s="98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AI3" s="98" t="s">
         <v>67</v>
@@ -15626,273 +15617,273 @@
         <v>65</v>
       </c>
       <c r="AK3" s="98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AL3" s="258"/>
       <c r="AM3" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN3" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AO3" s="98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AP3" s="98" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AQ3" s="98" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AR3" s="98" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AT3" s="98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AU3" s="98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AV3" s="98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AW3" s="98" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AX3" s="98" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AY3" s="98" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AZ3" s="258"/>
       <c r="BA3" s="97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BB3" s="97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BC3" s="97" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BD3" s="97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BE3" s="97" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BF3" s="97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BG3" s="97" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BH3" s="97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BI3" s="97" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BJ3" s="258"/>
     </row>
     <row r="4" spans="1:62" s="64" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="104"/>
       <c r="B4" s="103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="103" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="102" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="258"/>
       <c r="I4" s="101" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K4" s="101" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L4" s="101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M4" s="101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N4" s="101" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O4" s="101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P4" s="101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q4" s="101" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R4" s="100" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S4" s="101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T4" s="101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U4" s="101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V4" s="100" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="W4" s="258"/>
       <c r="X4" s="99" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y4" s="99" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Z4" s="99" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA4" s="99" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB4" s="258"/>
       <c r="AC4" s="98" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD4" s="98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AE4" s="98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG4" s="98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AH4" s="98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AI4" s="98" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="98" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AL4" s="258"/>
       <c r="AM4" s="98" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AN4" s="98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO4" s="98" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AP4" s="98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AQ4" s="98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AR4" s="98" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AS4" s="98" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AT4" s="98" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AU4" s="98" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AV4" s="98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AW4" s="98" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AX4" s="98" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY4" s="98" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AZ4" s="258"/>
       <c r="BA4" s="97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BB4" s="97" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BC4" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BD4" s="97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BE4" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BF4" s="97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BG4" s="97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BH4" s="97" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BI4" s="97" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BJ4" s="258"/>
     </row>
     <row r="5" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A5" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D5" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H5" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G5:G5)</f>
@@ -15908,25 +15899,25 @@
       <c r="N5" s="93"/>
       <c r="O5" s="93"/>
       <c r="P5" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q5" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R5" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="S5" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="T5" s="74" t="s">
         <v>206</v>
-      </c>
-      <c r="T5" s="74" t="s">
-        <v>207</v>
       </c>
       <c r="U5" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V5" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="W5" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G5:V5)</f>
@@ -15949,10 +15940,10 @@
         <v>0</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AD5" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AE5" s="92"/>
       <c r="AF5" s="92"/>
@@ -15960,10 +15951,10 @@
       <c r="AH5" s="92"/>
       <c r="AI5" s="95"/>
       <c r="AJ5" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AK5" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AL5" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G5:AK5)</f>
@@ -15976,25 +15967,25 @@
       <c r="AQ5" s="92"/>
       <c r="AR5" s="92"/>
       <c r="AS5" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AT5" s="74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AU5" s="74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AV5" s="74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AW5" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AX5" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AY5" s="74" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AZ5" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G5:AY5)</f>
@@ -16016,25 +16007,25 @@
     </row>
     <row r="6" spans="1:62" s="64" customFormat="1" ht="144" x14ac:dyDescent="0.15">
       <c r="A6" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D6" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H6" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G6:G6)</f>
@@ -16042,49 +16033,49 @@
       </c>
       <c r="I6" s="94"/>
       <c r="J6" s="74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L6" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N6" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O6" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
       <c r="R6" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S6" s="93"/>
       <c r="T6" s="93"/>
       <c r="U6" s="93"/>
       <c r="V6" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W6" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G6:V6)</f>
         <v>0</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Z6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AA6" s="74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AB6" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G6:AA6)</f>
@@ -16093,47 +16084,47 @@
       <c r="AC6" s="92"/>
       <c r="AD6" s="92"/>
       <c r="AE6" s="74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AF6" s="74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG6" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH6" s="74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AI6" s="74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AJ6" s="74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AK6" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AL6" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G6:AK6)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AN6" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AO6" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AP6" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AQ6" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AR6" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AS6" s="92"/>
       <c r="AT6" s="92"/>
@@ -16141,10 +16132,10 @@
       <c r="AV6" s="92"/>
       <c r="AW6" s="92"/>
       <c r="AX6" s="74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AY6" s="74" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AZ6" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G6:AY6)</f>
@@ -16166,22 +16157,22 @@
     </row>
     <row r="7" spans="1:62" s="64" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A7" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D7" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="67">
@@ -16216,22 +16207,22 @@
       </c>
       <c r="AC7" s="75"/>
       <c r="AD7" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AE7" s="74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AF7" s="75"/>
       <c r="AG7" s="75"/>
       <c r="AH7" s="75"/>
       <c r="AI7" s="74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ7" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AK7" s="74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL7" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G7:AK7)</f>
@@ -16250,7 +16241,7 @@
       <c r="AW7" s="75"/>
       <c r="AX7" s="75"/>
       <c r="AY7" s="74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AZ7" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G7:AY7)</f>
@@ -16272,25 +16263,25 @@
     </row>
     <row r="8" spans="1:62" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D8" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H8" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G8:G8)</f>
@@ -16310,23 +16301,23 @@
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
       <c r="V8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="W8" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G8:V8)</f>
         <v>0</v>
       </c>
       <c r="X8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AA8" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AB8" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G8:AA8)</f>
@@ -16378,25 +16369,25 @@
     </row>
     <row r="9" spans="1:62" s="64" customFormat="1" ht="156" x14ac:dyDescent="0.15">
       <c r="A9" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D9" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H9" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G9:G9)</f>
@@ -16416,23 +16407,23 @@
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
       <c r="V9" s="74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W9" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G9:V9)</f>
         <v>0</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AA9" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AB9" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G9:AA9)</f>
@@ -16440,22 +16431,22 @@
       </c>
       <c r="AC9" s="84"/>
       <c r="AD9" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AE9" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AF9" s="83"/>
       <c r="AG9" s="83"/>
       <c r="AH9" s="83"/>
       <c r="AI9" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ9" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AK9" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL9" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G9:AK9)</f>
@@ -16474,7 +16465,7 @@
       <c r="AW9" s="75"/>
       <c r="AX9" s="75"/>
       <c r="AY9" s="74" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AZ9" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G9:AY9)</f>
@@ -16496,25 +16487,25 @@
     </row>
     <row r="10" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A10" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D10" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H10" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G10:G10)</f>
@@ -16534,23 +16525,23 @@
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="W10" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G10:V10)</f>
         <v>0</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Y10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Z10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AA10" s="74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AB10" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G10:AA10)</f>
@@ -16558,22 +16549,22 @@
       </c>
       <c r="AC10" s="84"/>
       <c r="AD10" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF10" s="83"/>
       <c r="AG10" s="83"/>
       <c r="AH10" s="83"/>
       <c r="AI10" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AJ10" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AK10" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AL10" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G10:AK10)</f>
@@ -16592,7 +16583,7 @@
       <c r="AW10" s="75"/>
       <c r="AX10" s="75"/>
       <c r="AY10" s="74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AZ10" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G10:AY10)</f>
@@ -16614,25 +16605,25 @@
     </row>
     <row r="11" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A11" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D11" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H11" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G11:G11)</f>
@@ -16652,23 +16643,23 @@
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="W11" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G11:V11)</f>
         <v>0</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Y11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Z11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AA11" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AB11" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G11:AA11)</f>
@@ -16676,22 +16667,22 @@
       </c>
       <c r="AC11" s="84"/>
       <c r="AD11" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AE11" s="74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF11" s="84"/>
       <c r="AG11" s="84"/>
       <c r="AH11" s="84"/>
       <c r="AI11" s="74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ11" s="74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AK11" s="74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AL11" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G11:AK11)</f>
@@ -16710,7 +16701,7 @@
       <c r="AW11" s="75"/>
       <c r="AX11" s="75"/>
       <c r="AY11" s="74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AZ11" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G11:AY11)</f>
@@ -16732,25 +16723,25 @@
     </row>
     <row r="12" spans="1:62" s="64" customFormat="1" ht="72" x14ac:dyDescent="0.15">
       <c r="A12" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D12" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H12" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G12:G12)</f>
@@ -16770,23 +16761,23 @@
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W12" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G12:V12)</f>
         <v>0</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Y12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Z12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AA12" s="74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AB12" s="85">
         <f>SUMIF($G$2:AA$2,AA$2,$G12:AA12)</f>
@@ -16794,22 +16785,22 @@
       </c>
       <c r="AC12" s="84"/>
       <c r="AD12" s="74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AE12" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF12" s="83"/>
       <c r="AG12" s="83"/>
       <c r="AH12" s="83"/>
       <c r="AI12" s="74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AJ12" s="74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AK12" s="74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL12" s="82">
         <f>SUMIF($G$2:AK$2,AK$2,$G12:AK12)</f>
@@ -16828,7 +16819,7 @@
       <c r="AW12" s="75"/>
       <c r="AX12" s="75"/>
       <c r="AY12" s="74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AZ12" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G12:AY12)</f>
@@ -16850,25 +16841,25 @@
     </row>
     <row r="13" spans="1:62" s="64" customFormat="1" ht="36" x14ac:dyDescent="0.15">
       <c r="A13" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D13" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H13" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G13:G13)</f>
@@ -16888,23 +16879,23 @@
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W13" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G13:V13)</f>
         <v>0</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Y13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Z13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AA13" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB13" s="65">
         <f>SUMIF($G$2:AA$2,AA$2,$G13:AA13)</f>
@@ -16956,25 +16947,25 @@
     </row>
     <row r="14" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A14" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D14" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H14" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G14:G14)</f>
@@ -16984,43 +16975,43 @@
         <v>41</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L14" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O14" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P14" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q14" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R14" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S14" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="T14" s="74" t="s">
         <v>206</v>
-      </c>
-      <c r="T14" s="74" t="s">
-        <v>207</v>
       </c>
       <c r="U14" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V14" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="W14" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G14:V14)</f>
@@ -17035,72 +17026,72 @@
         <v>0</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AD14" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE14" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AF14" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG14" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AH14" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AI14" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ14" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AK14" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL14" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G14:AK14)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AN14" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AO14" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AP14" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AQ14" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AR14" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AS14" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT14" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU14" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AV14" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AW14" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX14" s="79"/>
       <c r="AY14" s="74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ14" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G14:AY14)</f>
@@ -17122,25 +17113,25 @@
     </row>
     <row r="15" spans="1:62" s="64" customFormat="1" ht="180" x14ac:dyDescent="0.15">
       <c r="A15" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D15" s="77" t="s">
         <v>134</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H15" s="67">
         <f>SUMIF($G$2:G$2,G$2,$G15:G15)</f>
@@ -17150,43 +17141,43 @@
         <v>41</v>
       </c>
       <c r="J15" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L15" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O15" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P15" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q15" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R15" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S15" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="T15" s="74" t="s">
         <v>206</v>
-      </c>
-      <c r="T15" s="74" t="s">
-        <v>207</v>
       </c>
       <c r="U15" s="74" t="s">
         <v>38</v>
       </c>
       <c r="V15" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="W15" s="67">
         <f>SUMIF($G$2:V$2,V$2,$G15:V15)</f>
@@ -17201,72 +17192,72 @@
         <v>0</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AD15" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE15" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AF15" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG15" s="74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AH15" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AI15" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AJ15" s="74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AK15" s="74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL15" s="65">
         <f>SUMIF($G$2:AK$2,AK$2,$G15:AK15)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AN15" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AO15" s="74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AP15" s="74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AQ15" s="74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AR15" s="74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AS15" s="74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT15" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU15" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AV15" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AW15" s="74" t="s">
         <v>39</v>
       </c>
       <c r="AX15" s="75"/>
       <c r="AY15" s="74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ15" s="65">
         <f>SUMIF($G$2:AY$2,AU$2,$G15:AY15)</f>
@@ -17293,7 +17284,7 @@
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="69" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" s="68">
         <f>SUMIF($C$5:$C15,$C15,G$5:G15)</f>
@@ -17561,7 +17552,7 @@
   <sheetData>
     <row r="1" spans="1:62" s="112" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="261" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C1" s="261"/>
       <c r="D1" s="261"/>
@@ -17579,172 +17570,172 @@
       <c r="E2" s="158"/>
       <c r="F2" s="158"/>
       <c r="G2" s="155" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2" s="260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="T2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V2" s="154" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="W2" s="260" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="X2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA2" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB2" s="260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AD2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AF2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AH2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AI2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AK2" s="152" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AL2" s="260" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AO2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AP2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AQ2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AR2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AS2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AT2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AU2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AW2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AX2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AY2" s="152" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AZ2" s="260" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BA2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BB2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BC2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BE2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BG2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BH2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BI2" s="151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BJ2" s="260" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="112" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -17755,78 +17746,78 @@
       <c r="E3" s="158"/>
       <c r="F3" s="158"/>
       <c r="G3" s="155" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="260"/>
       <c r="I3" s="154" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J3" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K3" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L3" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M3" s="154" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N3" s="154" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O3" s="154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P3" s="154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q3" s="154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R3" s="154"/>
       <c r="S3" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="T3" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U3" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V3" s="154" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="W3" s="260"/>
       <c r="X3" s="150"/>
       <c r="Y3" s="155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Z3" s="155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA3" s="155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AB3" s="260"/>
       <c r="AC3" s="152" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AD3" s="152" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AE3" s="152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AF3" s="152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG3" s="152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AH3" s="152" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AI3" s="152" t="s">
         <v>67</v>
@@ -17835,255 +17826,255 @@
         <v>65</v>
       </c>
       <c r="AK3" s="152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AL3" s="260"/>
       <c r="AM3" s="152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN3" s="152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AO3" s="152" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AP3" s="152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AQ3" s="152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AR3" s="152" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AS3" s="152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AT3" s="152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AU3" s="152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AV3" s="152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AW3" s="152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AX3" s="152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AY3" s="152" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AZ3" s="260"/>
       <c r="BA3" s="151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BB3" s="151" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BC3" s="151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BD3" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BE3" s="151" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BF3" s="151" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BG3" s="151" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BH3" s="151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BI3" s="151" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BJ3" s="260"/>
     </row>
     <row r="4" spans="1:62" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="157"/>
       <c r="B4" s="156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="156" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F4" s="156" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G4" s="155" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="260"/>
       <c r="I4" s="154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J4" s="154" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K4" s="154" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L4" s="154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M4" s="154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N4" s="154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O4" s="154" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P4" s="154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q4" s="154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R4" s="154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S4" s="154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T4" s="154" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U4" s="154" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V4" s="154" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="W4" s="260"/>
       <c r="X4" s="153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y4" s="153" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Z4" s="153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA4" s="153" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB4" s="260"/>
       <c r="AC4" s="152" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD4" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AE4" s="152" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AF4" s="152" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG4" s="152" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AH4" s="152" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AI4" s="152" t="s">
         <v>67</v>
       </c>
       <c r="AJ4" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AK4" s="152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AL4" s="260"/>
       <c r="AM4" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AN4" s="152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO4" s="152" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AP4" s="152" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AQ4" s="152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AR4" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AS4" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AT4" s="152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AU4" s="152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AV4" s="152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AW4" s="152" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AX4" s="152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY4" s="152" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AZ4" s="260"/>
       <c r="BA4" s="151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BB4" s="151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BC4" s="151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BD4" s="151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BE4" s="151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BF4" s="151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BG4" s="151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BH4" s="151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BI4" s="151" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BJ4" s="260"/>
     </row>
     <row r="5" spans="1:62" s="112" customFormat="1" ht="11" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -18092,10 +18083,10 @@
         <v/>
       </c>
       <c r="E5" s="132" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="132" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="181">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18276,7 +18267,7 @@
     </row>
     <row r="6" spans="1:62" s="112" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="A6" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -18285,10 +18276,10 @@
         <v/>
       </c>
       <c r="E6" s="132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6" s="132" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" s="137">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (affaires pénales)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18488,7 +18479,7 @@
     </row>
     <row r="7" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -18497,10 +18488,10 @@
         <v/>
       </c>
       <c r="E7" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="132" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="140"/>
       <c r="H7" s="130">
@@ -18606,7 +18597,7 @@
     </row>
     <row r="8" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -18615,10 +18606,10 @@
         <v/>
       </c>
       <c r="E8" s="132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.51. ACCUEIL DU JUSTICIABLE (DONT SAUJ)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -18715,7 +18706,7 @@
     </row>
     <row r="9" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -18724,10 +18715,10 @@
         <v/>
       </c>
       <c r="E9" s="132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="132" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G9" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.1. SOUTIEN (HORS FORMATIONS SUIVIES)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")+
@@ -18894,7 +18885,7 @@
     </row>
     <row r="10" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -18903,10 +18894,10 @@
         <v/>
       </c>
       <c r="E10" s="132" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F10" s="132" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G10" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.3. FORMATIONS DISPENSÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19030,7 +19021,7 @@
     </row>
     <row r="11" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -19039,10 +19030,10 @@
         <v/>
       </c>
       <c r="E11" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" s="132" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.4. ACCÈS AU DROIT ET À LA JUSTICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19166,7 +19157,7 @@
     </row>
     <row r="12" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -19175,10 +19166,10 @@
         <v/>
       </c>
       <c r="E12" s="132" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F12" s="132" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G12" s="137" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12. TOTAL INDISPONIBILITÉ",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")-
@@ -19308,7 +19299,7 @@
     </row>
     <row r="13" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B13" s="132"/>
       <c r="C13" s="132"/>
@@ -19317,10 +19308,10 @@
         <v/>
       </c>
       <c r="E13" s="132" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="132" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="131" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("12.5. MISE À DISPOSITION",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH")</f>
@@ -19417,7 +19408,7 @@
     </row>
     <row r="14" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -19426,10 +19417,10 @@
         <v/>
       </c>
       <c r="E14" s="132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="132" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
@@ -19639,7 +19630,7 @@
     </row>
     <row r="15" spans="1:62" s="112" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B15" s="132"/>
       <c r="C15" s="132"/>
@@ -19648,10 +19639,10 @@
         <v/>
       </c>
       <c r="E15" s="132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="132" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="131">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
@@ -19866,7 +19857,7 @@
       <c r="D16" s="121"/>
       <c r="E16" s="121"/>
       <c r="F16" s="120" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" s="118" t="e">
         <f t="shared" ref="G16:AL16" si="7">SUM(G5:G15)</f>
@@ -20169,7 +20160,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="D19" s="110" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AZ19" s="109"/>
     </row>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234BC58B-24CA-154E-AFA4-B474FE535B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EB9B5-2D8D-1444-8BBA-5B6670528EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22940" windowHeight="13240" activeTab="6" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" activeTab="9" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
   <sheets>
     <sheet name="ACCUEIL" sheetId="33" r:id="rId1"/>
@@ -21,8 +21,8 @@
     <sheet name="Juridictions" sheetId="17" state="hidden" r:id="rId6"/>
     <sheet name="Table_Fonctions" sheetId="19" r:id="rId7"/>
     <sheet name="ETPT_TJ_corresp-AJUST2" sheetId="24" state="hidden" r:id="rId8"/>
-    <sheet name="ETPT_TJ" sheetId="25" state="hidden" r:id="rId9"/>
-    <sheet name="ETPT_TPRX" sheetId="26" state="hidden" r:id="rId10"/>
+    <sheet name="ETPT_TJ" sheetId="25" r:id="rId9"/>
+    <sheet name="ETPT_TPRX" sheetId="26" r:id="rId10"/>
     <sheet name="ETPT_CPH" sheetId="27" state="hidden" r:id="rId11"/>
     <sheet name="ETPT_TJ_DDG" sheetId="28" r:id="rId12"/>
     <sheet name="ETPT_TPRX_DDG" sheetId="29" r:id="rId13"/>
@@ -3160,7 +3160,7 @@
       <name val="Calibri (Corps)"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3326,6 +3326,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B252"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3843,7 +3861,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4683,6 +4701,18 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="29" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="30" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="31" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -6079,15 +6109,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
         <v>#N/A</v>
       </c>
-      <c r="M5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="M5" s="263"/>
+      <c r="N5" s="263"/>
       <c r="O5" s="125"/>
       <c r="P5" s="125"/>
       <c r="Q5" s="134"/>
@@ -6124,15 +6147,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
-      <c r="Z5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="Z5" s="263"/>
+      <c r="AA5" s="263"/>
       <c r="AB5" s="125"/>
       <c r="AC5" s="125"/>
       <c r="AD5" s="125"/>
@@ -6146,7 +6162,7 @@
         <v>#N/A</v>
       </c>
       <c r="AH5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUM(V5:AD5)-AF5-AG5</f>
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilés sur la période (contentieux civils et sociaux)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUM(V5:AD5)-AF5-AG5-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE S")</f>
         <v>#N/A</v>
       </c>
       <c r="AI5" s="162" t="e">
@@ -6764,20 +6780,13 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="M14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="M14" s="263"/>
+      <c r="N14" s="263"/>
       <c r="O14" s="125"/>
       <c r="P14" s="125"/>
       <c r="Q14" s="134"/>
-      <c r="R14" s="129" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")-SUM(I14:Q14)</f>
+      <c r="R14" s="265" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")-SUM(I14:Q14)-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
         <v>#N/A</v>
       </c>
       <c r="S14" s="117" t="e">
@@ -6806,15 +6815,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="Z14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="Z14" s="263"/>
+      <c r="AA14" s="263"/>
       <c r="AB14" s="125"/>
       <c r="AC14" s="125"/>
       <c r="AD14" s="125"/>
@@ -6827,8 +6829,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="AH14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")-SUM(Z14:AG14)</f>
+      <c r="AH14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")-SUM(AE14:AG14)</f>
         <v>#N/A</v>
       </c>
       <c r="AI14" s="162" t="e">
@@ -6877,20 +6879,13 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="M15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="M15" s="263"/>
+      <c r="N15" s="263"/>
       <c r="O15" s="125"/>
       <c r="P15" s="125"/>
       <c r="Q15" s="134"/>
-      <c r="R15" s="129" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")-SUM(I15:Q15)</f>
+      <c r="R15" s="265" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")-SUM(I15:Q15)-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
         <v>#N/A</v>
       </c>
       <c r="S15" s="117" t="e">
@@ -6919,15 +6914,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.2. PROTECTION DES MAJEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="Z15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")-
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2.7. TUTELLES MINEURS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="Z15" s="263"/>
+      <c r="AA15" s="263"/>
       <c r="AB15" s="125"/>
       <c r="AC15" s="125"/>
       <c r="AD15" s="125"/>
@@ -6940,8 +6928,8 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="AH15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")-SUM(Z15:AG15)</f>
+      <c r="AH15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")-SUM(AE15:AG15)</f>
         <v>#N/A</v>
       </c>
       <c r="AI15" s="162" t="e">
@@ -6982,13 +6970,13 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="M16" s="117" t="e">
+      <c r="M16" s="117">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N16" s="117" t="e">
+        <v>0</v>
+      </c>
+      <c r="N16" s="117">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="O16" s="187">
         <f t="shared" si="6"/>
@@ -7034,13 +7022,13 @@
         <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
-      <c r="Z16" s="117" t="e">
+      <c r="Z16" s="117">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA16" s="117" t="e">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="117">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="187">
         <f t="shared" si="6"/>
@@ -18222,8 +18210,8 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
-      <c r="AW5" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
+      <c r="AW5" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat SIEGE NS")</f>
         <v>#N/A</v>
       </c>
       <c r="AX5" s="126" t="e">
@@ -19495,9 +19483,9 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="V14" s="129" t="e">
+      <c r="V14" s="265" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé ADD")-
-SUM(I14:U14)</f>
+SUM(I14:U14)-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé ADD")</f>
         <v>#N/A</v>
       </c>
       <c r="W14" s="117" t="e">
@@ -19523,64 +19511,64 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="AE14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.1. SERVICE GÉNÉRAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.2. JIRS ÉCO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.3. JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AK14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+      <c r="AE14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.1. SERVICE GÉNÉRAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.2. JIRS ÉCO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.3. JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AK14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
       <c r="AL14" s="117" t="e">
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="AM14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AN14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AO14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AP14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AQ14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AR14" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+      <c r="AM14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AN14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AO14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AP14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AQ14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AR14" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
       <c r="AS14" s="124" t="e">
@@ -19601,7 +19589,7 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
-      <c r="AW14" s="124" t="e">
+      <c r="AW14" s="264" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé ADD")</f>
         <v>#N/A</v>
       </c>
@@ -19717,9 +19705,9 @@
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1. TOTAL CONTENTIEUX SOCIAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="V15" s="129" t="e">
+      <c r="V15" s="265" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("Temps ventilé sur la période (y.c. indisponibilité)",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire A-B-CBUR placé SUB")-
-SUM(I15:U15)</f>
+SUM(I15:U15)-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("11.7. FONCTIONNAIRES AFFECTÉS AU CPH",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Fonctionnaire CTECH placé SUB")</f>
         <v>#N/A</v>
       </c>
       <c r="W15" s="117" t="e">
@@ -19745,64 +19733,64 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("3.44. SAISIE DES RÉMUNÉRATIONS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="AE15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.1. SERVICE GÉNÉRAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.2. JIRS ÉCO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.3. JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AK15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+      <c r="AE15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.1. SERVICE GÉNÉRAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.2. JIRS ÉCO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.3. JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("8.4. AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("9. TOTAL JAP",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.1. ACTIVITÉ CIVILE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("6.2. ACTIVITÉ PÉNALE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AK15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("5. TOTAL JLD CIVIL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("10. TOTAL JLD PÉNAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
       <c r="AL15" s="117" t="e">
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="AM15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AN15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AO15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AP15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AQ15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AR15" s="124" t="e">
-        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
-SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+      <c r="AM15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.5. COUR D'ASSISES HORS JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.51. COUR D'ASSISES JIRS",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AN15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.52. COUR CRIMINELLE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AO15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.121. COLLÉGIALES JIRS ECO-FI",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AP15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.12. COLLÉGIALES JIRS CRIM-ORG",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AQ15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.122. COLLÉGIALES AUTRES SECTIONS SPÉCIALISÉES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AR15" s="264" t="e">
+        <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.6. TRIBUNAL DE POLICE",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")+
+SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("7.7. OP CONTRAVENTIONNELLES",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
       <c r="AS15" s="124" t="e">
@@ -19823,7 +19811,7 @@
 SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("1.1. DÉPARTAGE PRUD'HOMAL",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>
-      <c r="AW15" s="124" t="e">
+      <c r="AW15" s="264" t="e">
         <f>SUMIFS( INDEX( 'ETPT Format DDG'!$A:$EF,,MATCH("2. TOTAL CONTENTIEUX JAF",'ETPT Format DDG'!2:2,0)),'ETPT Format DDG'!$C:$C,$D$5,'ETPT Format DDG'!$EA:$EA,"Magistrat placé SUB")</f>
         <v>#N/A</v>
       </c>

--- a/front/src/assets/template4.xlsx
+++ b/front/src/assets/template4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychevallier/Documents/GitHub/a-just/front/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2236A0B-2A89-994D-BFA7-9C2642E3F64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C9A653-5F3B-1848-BAAE-D5C33538B0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" activeTab="3" xr2:uid="{50CB0F02-73D8-432D-BA19-0D33B1FE1838}"/>
   </bookViews>
@@ -2795,13 +2795,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="General;General;\-"/>
     <numFmt numFmtId="168" formatCode="0.###;0.###;\-"/>
     <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
   <fonts count="53" x14ac:knownFonts="1">
     <font>
@@ -4579,6 +4580,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4643,6 +4660,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4663,36 +4689,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="52" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="52" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="52" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="52" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="52" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="52" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4703,67 +4704,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6FC886D6-2077-B34D-B1DF-739B068A66D1}"/>
     <cellStyle name="Normal 3" xfId="4" xr:uid="{6BD57324-3FD5-D341-A299-730D14794802}"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79998168889431442"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79998168889431442"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79998168889431442"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79998168889431442"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -5567,11 +5508,11 @@
       <c r="B1" s="192" t="s">
         <v>492</v>
       </c>
-      <c r="C1" s="230" t="s">
+      <c r="C1" s="236" t="s">
         <v>493</v>
       </c>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
       <c r="F1" s="193"/>
       <c r="H1" s="27" t="s">
         <v>0</v>
@@ -5580,11 +5521,11 @@
     <row r="2" spans="1:8" s="197" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="194"/>
       <c r="B2" s="195"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="237" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
       <c r="F2" s="196"/>
       <c r="H2" s="27" t="s">
         <v>0</v>
@@ -5608,10 +5549,10 @@
       <c r="D4" s="202" t="s">
         <v>497</v>
       </c>
-      <c r="E4" s="237" t="s">
+      <c r="E4" s="243" t="s">
         <v>498</v>
       </c>
-      <c r="F4" s="238"/>
+      <c r="F4" s="244"/>
       <c r="G4" s="211"/>
       <c r="H4" s="27" t="s">
         <v>0</v>
@@ -5628,10 +5569,10 @@
       <c r="D5" s="208" t="s">
         <v>501</v>
       </c>
-      <c r="E5" s="239" t="s">
+      <c r="E5" s="245" t="s">
         <v>514</v>
       </c>
-      <c r="F5" s="240"/>
+      <c r="F5" s="246"/>
       <c r="G5" s="210"/>
       <c r="H5" s="27" t="s">
         <v>0</v>
@@ -5648,10 +5589,10 @@
       <c r="D6" s="209" t="s">
         <v>504</v>
       </c>
-      <c r="E6" s="241" t="s">
+      <c r="E6" s="247" t="s">
         <v>515</v>
       </c>
-      <c r="F6" s="242"/>
+      <c r="F6" s="248"/>
       <c r="G6" s="210"/>
       <c r="H6" s="27" t="s">
         <v>0</v>
@@ -5668,10 +5609,10 @@
       <c r="D7" s="209" t="s">
         <v>507</v>
       </c>
-      <c r="E7" s="241" t="s">
+      <c r="E7" s="247" t="s">
         <v>514</v>
       </c>
-      <c r="F7" s="242"/>
+      <c r="F7" s="248"/>
       <c r="G7" s="210"/>
       <c r="H7" s="27" t="s">
         <v>0</v>
@@ -5682,16 +5623,16 @@
       <c r="B8" s="218" t="s">
         <v>508</v>
       </c>
-      <c r="C8" s="232" t="s">
+      <c r="C8" s="238" t="s">
         <v>509</v>
       </c>
-      <c r="D8" s="232" t="s">
+      <c r="D8" s="238" t="s">
         <v>510</v>
       </c>
-      <c r="E8" s="243" t="s">
+      <c r="E8" s="249" t="s">
         <v>516</v>
       </c>
-      <c r="F8" s="244"/>
+      <c r="F8" s="250"/>
       <c r="G8" s="210"/>
       <c r="H8" s="27" t="s">
         <v>0</v>
@@ -5702,10 +5643,10 @@
       <c r="B9" s="219" t="s">
         <v>511</v>
       </c>
-      <c r="C9" s="232"/>
-      <c r="D9" s="232"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="246"/>
+      <c r="C9" s="238"/>
+      <c r="D9" s="238"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="252"/>
       <c r="G9" s="210"/>
       <c r="H9" s="27" t="s">
         <v>0</v>
@@ -5716,10 +5657,10 @@
       <c r="B10" s="220" t="s">
         <v>512</v>
       </c>
-      <c r="C10" s="233"/>
-      <c r="D10" s="233"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="248"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="254"/>
       <c r="G10" s="210"/>
       <c r="H10" s="27" t="s">
         <v>0</v>
@@ -5739,11 +5680,11 @@
     <row r="12" spans="1:8" s="27" customFormat="1" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="198"/>
       <c r="B12" s="212"/>
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="242" t="s">
         <v>513</v>
       </c>
-      <c r="D12" s="236"/>
-      <c r="E12" s="236"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="242"/>
       <c r="F12" s="213"/>
       <c r="H12" s="27" t="s">
         <v>0</v>
@@ -5757,14 +5698,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="27" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="234" t="s">
+      <c r="A14" s="240" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="235"/>
+      <c r="B14" s="240"/>
+      <c r="C14" s="240"/>
+      <c r="D14" s="240"/>
+      <c r="E14" s="240"/>
+      <c r="F14" s="241"/>
       <c r="H14" s="27" t="s">
         <v>0</v>
       </c>
@@ -5809,16 +5750,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="265" t="s">
         <v>481</v>
       </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
       <c r="I1" s="107"/>
       <c r="J1" s="107"/>
       <c r="K1" s="107"/>
@@ -5857,7 +5798,7 @@
       <c r="G2" s="150" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="254" t="s">
+      <c r="H2" s="263" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="150" t="s">
@@ -5890,13 +5831,13 @@
       <c r="R2" s="150" t="s">
         <v>434</v>
       </c>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="263" t="s">
         <v>433</v>
       </c>
       <c r="T2" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="254" t="s">
+      <c r="U2" s="263" t="s">
         <v>432</v>
       </c>
       <c r="V2" s="150" t="s">
@@ -5926,7 +5867,7 @@
       <c r="AD2" s="150" t="s">
         <v>431</v>
       </c>
-      <c r="AE2" s="254" t="s">
+      <c r="AE2" s="263" t="s">
         <v>480</v>
       </c>
       <c r="AF2" s="150" t="s">
@@ -5938,7 +5879,7 @@
       <c r="AH2" s="150" t="s">
         <v>479</v>
       </c>
-      <c r="AI2" s="254" t="s">
+      <c r="AI2" s="263" t="s">
         <v>478</v>
       </c>
     </row>
@@ -5952,7 +5893,7 @@
       <c r="G3" s="150" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="254"/>
+      <c r="H3" s="263"/>
       <c r="I3" s="150" t="s">
         <v>477</v>
       </c>
@@ -5983,11 +5924,11 @@
       <c r="R3" s="150" t="s">
         <v>412</v>
       </c>
-      <c r="S3" s="254"/>
+      <c r="S3" s="263"/>
       <c r="T3" s="150" t="s">
         <v>409</v>
       </c>
-      <c r="U3" s="254"/>
+      <c r="U3" s="263"/>
       <c r="V3" s="150" t="s">
         <v>468</v>
       </c>
@@ -6015,7 +5956,7 @@
       <c r="AD3" s="150" t="s">
         <v>460</v>
       </c>
-      <c r="AE3" s="254"/>
+      <c r="AE3" s="263"/>
       <c r="AF3" s="150" t="s">
         <v>459</v>
       </c>
@@ -6025,7 +5966,7 @@
       <c r="AH3" s="150" t="s">
         <v>389</v>
       </c>
-      <c r="AI3" s="254"/>
+      <c r="AI3" s="263"/>
     </row>
     <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="153"/>
@@ -6047,7 +5988,7 @@
       <c r="G4" s="150" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="254"/>
+      <c r="H4" s="263"/>
       <c r="I4" s="150" t="s">
         <v>458</v>
       </c>
@@ -6078,11 +6019,11 @@
       <c r="R4" s="150" t="s">
         <v>361</v>
       </c>
-      <c r="S4" s="254"/>
+      <c r="S4" s="263"/>
       <c r="T4" s="150" t="s">
         <v>357</v>
       </c>
-      <c r="U4" s="254"/>
+      <c r="U4" s="263"/>
       <c r="V4" s="150" t="s">
         <v>449</v>
       </c>
@@ -6110,7 +6051,7 @@
       <c r="AD4" s="150" t="s">
         <v>441</v>
       </c>
-      <c r="AE4" s="254"/>
+      <c r="AE4" s="263"/>
       <c r="AF4" s="150" t="s">
         <v>440</v>
       </c>
@@ -6120,7 +6061,7 @@
       <c r="AH4" s="150" t="s">
         <v>336</v>
       </c>
-      <c r="AI4" s="254"/>
+      <c r="AI4" s="263"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="156" t="s">
@@ -7224,13 +7165,13 @@
       <c r="G2" s="150" t="s">
         <v>434</v>
       </c>
-      <c r="H2" s="254" t="s">
+      <c r="H2" s="263" t="s">
         <v>433</v>
       </c>
       <c r="I2" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="254" t="s">
+      <c r="J2" s="263" t="s">
         <v>432</v>
       </c>
     </row>
@@ -7244,11 +7185,11 @@
       <c r="G3" s="150" t="s">
         <v>412</v>
       </c>
-      <c r="H3" s="254"/>
+      <c r="H3" s="263"/>
       <c r="I3" s="150" t="s">
         <v>409</v>
       </c>
-      <c r="J3" s="254"/>
+      <c r="J3" s="263"/>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
@@ -7270,11 +7211,11 @@
       <c r="G4" s="150" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="254"/>
+      <c r="H4" s="263"/>
       <c r="I4" s="150" t="s">
         <v>357</v>
       </c>
-      <c r="J4" s="254"/>
+      <c r="J4" s="263"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="166" t="s">
@@ -7673,7 +7614,7 @@
       <c r="G2" s="150" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="254" t="s">
+      <c r="H2" s="263" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="149" t="s">
@@ -7718,7 +7659,7 @@
       <c r="V2" s="149" t="s">
         <v>434</v>
       </c>
-      <c r="W2" s="254" t="s">
+      <c r="W2" s="263" t="s">
         <v>433</v>
       </c>
       <c r="X2" s="150" t="s">
@@ -7733,7 +7674,7 @@
       <c r="AA2" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="AB2" s="254" t="s">
+      <c r="AB2" s="263" t="s">
         <v>432</v>
       </c>
       <c r="AC2" s="147" t="s">
@@ -7763,7 +7704,7 @@
       <c r="AK2" s="147" t="s">
         <v>431</v>
       </c>
-      <c r="AL2" s="254" t="s">
+      <c r="AL2" s="263" t="s">
         <v>430</v>
       </c>
       <c r="AM2" s="147" t="s">
@@ -7805,7 +7746,7 @@
       <c r="AY2" s="147" t="s">
         <v>429</v>
       </c>
-      <c r="AZ2" s="254" t="s">
+      <c r="AZ2" s="263" t="s">
         <v>428</v>
       </c>
       <c r="BA2" s="146" t="s">
@@ -7835,7 +7776,7 @@
       <c r="BI2" s="146" t="s">
         <v>427</v>
       </c>
-      <c r="BJ2" s="254" t="s">
+      <c r="BJ2" s="263" t="s">
         <v>426</v>
       </c>
       <c r="BK2"/>
@@ -7850,7 +7791,7 @@
       <c r="G3" s="150" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="254"/>
+      <c r="H3" s="263"/>
       <c r="I3" s="149" t="s">
         <v>424</v>
       </c>
@@ -7891,7 +7832,7 @@
       <c r="V3" s="149" t="s">
         <v>412</v>
       </c>
-      <c r="W3" s="254"/>
+      <c r="W3" s="263"/>
       <c r="X3" s="145"/>
       <c r="Y3" s="150" t="s">
         <v>411</v>
@@ -7902,7 +7843,7 @@
       <c r="AA3" s="150" t="s">
         <v>409</v>
       </c>
-      <c r="AB3" s="254"/>
+      <c r="AB3" s="263"/>
       <c r="AC3" s="147" t="s">
         <v>408</v>
       </c>
@@ -7930,7 +7871,7 @@
       <c r="AK3" s="147" t="s">
         <v>402</v>
       </c>
-      <c r="AL3" s="254"/>
+      <c r="AL3" s="263"/>
       <c r="AM3" s="147" t="s">
         <v>401</v>
       </c>
@@ -7970,7 +7911,7 @@
       <c r="AY3" s="147" t="s">
         <v>389</v>
       </c>
-      <c r="AZ3" s="254"/>
+      <c r="AZ3" s="263"/>
       <c r="BA3" s="146" t="s">
         <v>388</v>
       </c>
@@ -7998,7 +7939,7 @@
       <c r="BI3" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="BJ3" s="254"/>
+      <c r="BJ3" s="263"/>
     </row>
     <row r="4" spans="1:63" s="107" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="152"/>
@@ -8020,7 +7961,7 @@
       <c r="G4" s="150" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="254"/>
+      <c r="H4" s="263"/>
       <c r="I4" s="149" t="s">
         <v>374</v>
       </c>
@@ -8063,7 +8004,7 @@
       <c r="V4" s="149" t="s">
         <v>361</v>
       </c>
-      <c r="W4" s="254"/>
+      <c r="W4" s="263"/>
       <c r="X4" s="148" t="s">
         <v>360</v>
       </c>
@@ -8076,7 +8017,7 @@
       <c r="AA4" s="148" t="s">
         <v>357</v>
       </c>
-      <c r="AB4" s="254"/>
+      <c r="AB4" s="263"/>
       <c r="AC4" s="147" t="s">
         <v>356</v>
       </c>
@@ -8104,7 +8045,7 @@
       <c r="AK4" s="147" t="s">
         <v>349</v>
       </c>
-      <c r="AL4" s="254"/>
+      <c r="AL4" s="263"/>
       <c r="AM4" s="147" t="s">
         <v>348</v>
       </c>
@@ -8144,7 +8085,7 @@
       <c r="AY4" s="147" t="s">
         <v>336</v>
       </c>
-      <c r="AZ4" s="254"/>
+      <c r="AZ4" s="263"/>
       <c r="BA4" s="146" t="s">
         <v>335</v>
       </c>
@@ -8172,7 +8113,7 @@
       <c r="BI4" s="146" t="s">
         <v>327</v>
       </c>
-      <c r="BJ4" s="254"/>
+      <c r="BJ4" s="263"/>
       <c r="BK4"/>
     </row>
     <row r="5" spans="1:63" s="107" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -10888,7 +10829,7 @@
       <c r="G2" s="150" t="s">
         <v>436</v>
       </c>
-      <c r="H2" s="254" t="s">
+      <c r="H2" s="263" t="s">
         <v>435</v>
       </c>
       <c r="I2" s="150" t="s">
@@ -10921,13 +10862,13 @@
       <c r="R2" s="150" t="s">
         <v>434</v>
       </c>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="263" t="s">
         <v>433</v>
       </c>
       <c r="T2" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="254" t="s">
+      <c r="U2" s="263" t="s">
         <v>432</v>
       </c>
       <c r="V2" s="150" t="s">
@@ -10957,7 +10898,7 @@
       <c r="AD2" s="150" t="s">
         <v>431</v>
       </c>
-      <c r="AE2" s="254" t="s">
+      <c r="AE2" s="263" t="s">
         <v>480</v>
       </c>
       <c r="AF2" s="150" t="s">
@@ -10969,7 +10910,7 @@
       <c r="AH2" s="150" t="s">
         <v>479</v>
       </c>
-      <c r="AI2" s="254" t="s">
+      <c r="AI2" s="263" t="s">
         <v>478</v>
       </c>
     </row>
@@ -10983,7 +10924,7 @@
       <c r="G3" s="150" t="s">
         <v>425</v>
       </c>
-      <c r="H3" s="254"/>
+      <c r="H3" s="263"/>
       <c r="I3" s="150" t="s">
         <v>477</v>
       </c>
@@ -11014,11 +10955,11 @@
       <c r="R3" s="150" t="s">
         <v>412</v>
       </c>
-      <c r="S3" s="254"/>
+      <c r="S3" s="263"/>
       <c r="T3" s="150" t="s">
         <v>409</v>
       </c>
-      <c r="U3" s="254"/>
+      <c r="U3" s="263"/>
       <c r="V3" s="150" t="s">
         <v>468</v>
       </c>
@@ -11046,7 +10987,7 @@
       <c r="AD3" s="150" t="s">
         <v>460</v>
       </c>
-      <c r="AE3" s="254"/>
+      <c r="AE3" s="263"/>
       <c r="AF3" s="150" t="s">
         <v>459</v>
       </c>
@@ -11056,7 +10997,7 @@
       <c r="AH3" s="150" t="s">
         <v>389</v>
       </c>
-      <c r="AI3" s="254"/>
+      <c r="AI3" s="263"/>
     </row>
     <row r="4" spans="1:62" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" s="153"/>
@@ -11078,7 +11019,7 @@
       <c r="G4" s="150" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="254"/>
+      <c r="H4" s="263"/>
       <c r="I4" s="150" t="s">
         <v>458</v>
       </c>
@@ -11109,11 +11050,11 @@
       <c r="R4" s="150" t="s">
         <v>361</v>
       </c>
-      <c r="S4" s="254"/>
+      <c r="S4" s="263"/>
       <c r="T4" s="150" t="s">
         <v>357</v>
       </c>
-      <c r="U4" s="254"/>
+      <c r="U4" s="263"/>
       <c r="V4" s="150" t="s">
         <v>449</v>
       </c>
@@ -11141,7 +11082,7 @@
       <c r="AD4" s="150" t="s">
         <v>441</v>
       </c>
-      <c r="AE4" s="254"/>
+      <c r="AE4" s="263"/>
       <c r="AF4" s="150" t="s">
         <v>440</v>
       </c>
@@ -11151,7 +11092,7 @@
       <c r="AH4" s="150" t="s">
         <v>336</v>
       </c>
-      <c r="AI4" s="254"/>
+      <c r="AI4" s="263"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="156" t="s">
@@ -12883,13 +12824,13 @@
       <c r="G2" s="150" t="s">
         <v>434</v>
       </c>
-      <c r="H2" s="254" t="s">
+      <c r="H2" s="263" t="s">
         <v>433</v>
       </c>
       <c r="I2" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="254" t="s">
+      <c r="J2" s="263" t="s">
         <v>432</v>
       </c>
     </row>
@@ -12903,11 +12844,11 @@
       <c r="G3" s="150" t="s">
         <v>412</v>
       </c>
-      <c r="H3" s="254"/>
+      <c r="H3" s="263"/>
       <c r="I3" s="150" t="s">
         <v>409</v>
       </c>
-      <c r="J3" s="254"/>
+      <c r="J3" s="263"/>
     </row>
     <row r="4" spans="1:62" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
@@ -12929,11 +12870,11 @@
       <c r="G4" s="150" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="254"/>
+      <c r="H4" s="263"/>
       <c r="I4" s="150" t="s">
         <v>357</v>
       </c>
-      <c r="J4" s="254"/>
+      <c r="J4" s="263"/>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A5" s="166" t="s">
@@ -13638,14 +13579,14 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="EA1" s="249" t="s">
+      <c r="EA1" s="255" t="s">
         <v>490</v>
       </c>
-      <c r="EB1" s="249"/>
-      <c r="EC1" s="249"/>
-      <c r="ED1" s="249"/>
-      <c r="EE1" s="249"/>
-      <c r="EF1" s="249"/>
+      <c r="EB1" s="255"/>
+      <c r="EC1" s="255"/>
+      <c r="ED1" s="255"/>
+      <c r="EE1" s="255"/>
+      <c r="EF1" s="255"/>
       <c r="EG1" s="8" t="s">
         <v>0</v>
       </c>
@@ -13782,30 +13723,30 @@
     </row>
     <row r="4" spans="1:24" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="9"/>
-      <c r="E4" s="264"/>
-      <c r="G4" s="250" t="s">
+      <c r="E4" s="234"/>
+      <c r="G4" s="256" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="M4" s="260"/>
-      <c r="N4" s="250" t="s">
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="M4" s="258"/>
+      <c r="N4" s="256" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="251"/>
-      <c r="P4" s="251"/>
-      <c r="Q4" s="251"/>
-      <c r="R4" s="251"/>
-      <c r="S4" s="261"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="250" t="s">
+      <c r="O4" s="257"/>
+      <c r="P4" s="257"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="256" t="s">
         <v>28</v>
       </c>
-      <c r="V4" s="258"/>
-      <c r="W4" s="267"/>
+      <c r="V4" s="259"/>
+      <c r="W4" s="235"/>
       <c r="X4" t="s">
         <v>0</v>
       </c>
@@ -13818,7 +13759,7 @@
       <c r="G5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="262" t="s">
+      <c r="H5" s="232" t="s">
         <v>525</v>
       </c>
       <c r="I5" s="13" t="s">
@@ -13830,16 +13771,16 @@
       <c r="K5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="259" t="s">
+      <c r="L5" s="231" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="263" t="s">
+      <c r="M5" s="233" t="s">
         <v>525</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="262" t="s">
+      <c r="O5" s="232" t="s">
         <v>525</v>
       </c>
       <c r="P5" s="13" t="s">
@@ -13851,16 +13792,16 @@
       <c r="R5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="259" t="s">
+      <c r="S5" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="T5" s="263" t="s">
+      <c r="T5" s="233" t="s">
         <v>525</v>
       </c>
       <c r="U5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="V5" s="263" t="s">
+      <c r="V5" s="233" t="s">
         <v>525</v>
       </c>
       <c r="W5" t="s">
@@ -13917,7 +13858,7 @@
 'ETPT Format DDG'!$G:$G,"Magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="M6" s="265" t="str">
+      <c r="M6" s="267" t="str">
         <f>IF(OR(LEFT(C6,3)="12.",LEFT(E6,3)="12.",LEFT(E6,5)="CET &gt;", IFERROR(L6/$L$6,"")=0),"", IFERROR(L6/$L$6,""))</f>
         <v/>
       </c>
@@ -13951,7 +13892,7 @@
 'ETPT Format DDG'!$G:$G,"Greffe")</f>
         <v>#N/A</v>
       </c>
-      <c r="T6" s="265" t="str">
+      <c r="T6" s="267" t="str">
         <f>IF(OR(LEFT(C6,3)="12.",LEFT(E6,3)="12.",LEFT(E6,5)="CET &gt;",IFERROR(S6/$S$6,"")=0),"", IFERROR(S6/$S$6,""))</f>
         <v/>
       </c>
@@ -13965,7 +13906,7 @@
 'ETPT Format DDG'!$G:$G,"Autour du magistrat")</f>
         <v>#N/A</v>
       </c>
-      <c r="V6" s="265" t="str">
+      <c r="V6" s="267" t="str">
         <f>IF(OR(LEFT(C6,3)="12.",LEFT(E6,3)="12.",LEFT(E6,5)="CET &gt;",IFERROR(U6/$U$6,"")=0),"", IFERROR(U6/$U$6,""))</f>
         <v/>
       </c>
@@ -13974,589 +13915,589 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I7" s="257"/>
+      <c r="I7" s="230"/>
       <c r="W7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I8" s="257"/>
+      <c r="I8" s="230"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I9" s="257"/>
+      <c r="I9" s="230"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I10" s="257"/>
+      <c r="I10" s="230"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I11" s="257"/>
+      <c r="I11" s="230"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I12" s="257"/>
+      <c r="I12" s="230"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I13" s="257"/>
+      <c r="I13" s="230"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I14" s="257"/>
+      <c r="I14" s="230"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I15" s="257"/>
+      <c r="I15" s="230"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I16" s="257"/>
+      <c r="I16" s="230"/>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I17" s="257"/>
+      <c r="I17" s="230"/>
     </row>
     <row r="18" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I18" s="257"/>
+      <c r="I18" s="230"/>
     </row>
     <row r="19" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I19" s="257"/>
+      <c r="I19" s="230"/>
     </row>
     <row r="20" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I20" s="257"/>
+      <c r="I20" s="230"/>
     </row>
     <row r="21" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I21" s="257"/>
+      <c r="I21" s="230"/>
     </row>
     <row r="22" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I22" s="257"/>
+      <c r="I22" s="230"/>
     </row>
     <row r="23" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I23" s="257"/>
+      <c r="I23" s="230"/>
     </row>
     <row r="24" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I24" s="257"/>
+      <c r="I24" s="230"/>
     </row>
     <row r="25" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I25" s="257"/>
+      <c r="I25" s="230"/>
     </row>
     <row r="26" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I26" s="257"/>
+      <c r="I26" s="230"/>
     </row>
     <row r="27" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I27" s="257"/>
+      <c r="I27" s="230"/>
     </row>
     <row r="28" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I28" s="257"/>
+      <c r="I28" s="230"/>
     </row>
     <row r="29" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I29" s="257"/>
+      <c r="I29" s="230"/>
     </row>
     <row r="30" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I30" s="257"/>
+      <c r="I30" s="230"/>
     </row>
     <row r="31" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I31" s="257"/>
+      <c r="I31" s="230"/>
     </row>
     <row r="32" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I32" s="257"/>
+      <c r="I32" s="230"/>
     </row>
     <row r="33" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I33" s="257"/>
+      <c r="I33" s="230"/>
     </row>
     <row r="34" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I34" s="257"/>
+      <c r="I34" s="230"/>
     </row>
     <row r="35" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I35" s="257"/>
+      <c r="I35" s="230"/>
     </row>
     <row r="36" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I36" s="257"/>
+      <c r="I36" s="230"/>
     </row>
     <row r="37" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I37" s="257"/>
+      <c r="I37" s="230"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I38" s="257"/>
+      <c r="I38" s="230"/>
     </row>
     <row r="39" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I39" s="257"/>
+      <c r="I39" s="230"/>
     </row>
     <row r="40" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I40" s="257"/>
+      <c r="I40" s="230"/>
     </row>
     <row r="41" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I41" s="257"/>
+      <c r="I41" s="230"/>
     </row>
     <row r="42" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I42" s="257"/>
+      <c r="I42" s="230"/>
     </row>
     <row r="43" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I43" s="257"/>
+      <c r="I43" s="230"/>
     </row>
     <row r="44" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I44" s="257"/>
+      <c r="I44" s="230"/>
     </row>
     <row r="45" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I45" s="257"/>
+      <c r="I45" s="230"/>
     </row>
     <row r="46" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I46" s="257"/>
+      <c r="I46" s="230"/>
     </row>
     <row r="47" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I47" s="257"/>
+      <c r="I47" s="230"/>
     </row>
     <row r="48" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I48" s="257"/>
+      <c r="I48" s="230"/>
     </row>
     <row r="49" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I49" s="257"/>
+      <c r="I49" s="230"/>
     </row>
     <row r="50" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I50" s="257"/>
+      <c r="I50" s="230"/>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I51" s="257"/>
+      <c r="I51" s="230"/>
     </row>
     <row r="52" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I52" s="257"/>
+      <c r="I52" s="230"/>
     </row>
     <row r="53" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I53" s="257"/>
+      <c r="I53" s="230"/>
     </row>
     <row r="54" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I54" s="257"/>
+      <c r="I54" s="230"/>
     </row>
     <row r="55" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I55" s="257"/>
+      <c r="I55" s="230"/>
     </row>
     <row r="56" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I56" s="257"/>
+      <c r="I56" s="230"/>
     </row>
     <row r="57" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I57" s="257"/>
+      <c r="I57" s="230"/>
     </row>
     <row r="58" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I58" s="257"/>
+      <c r="I58" s="230"/>
     </row>
     <row r="59" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I59" s="257"/>
+      <c r="I59" s="230"/>
     </row>
     <row r="60" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I60" s="257"/>
+      <c r="I60" s="230"/>
     </row>
     <row r="61" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I61" s="257"/>
+      <c r="I61" s="230"/>
     </row>
     <row r="62" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I62" s="257"/>
+      <c r="I62" s="230"/>
     </row>
     <row r="63" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I63" s="257"/>
+      <c r="I63" s="230"/>
     </row>
     <row r="64" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I64" s="257"/>
+      <c r="I64" s="230"/>
     </row>
     <row r="65" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I65" s="257"/>
+      <c r="I65" s="230"/>
     </row>
     <row r="66" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I66" s="257"/>
+      <c r="I66" s="230"/>
     </row>
     <row r="67" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I67" s="257"/>
+      <c r="I67" s="230"/>
     </row>
     <row r="68" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I68" s="257"/>
+      <c r="I68" s="230"/>
     </row>
     <row r="69" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I69" s="257"/>
+      <c r="I69" s="230"/>
     </row>
     <row r="70" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I70" s="257"/>
+      <c r="I70" s="230"/>
     </row>
     <row r="71" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I71" s="257"/>
+      <c r="I71" s="230"/>
     </row>
     <row r="72" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I72" s="257"/>
+      <c r="I72" s="230"/>
     </row>
     <row r="73" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I73" s="257"/>
+      <c r="I73" s="230"/>
     </row>
     <row r="74" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I74" s="257"/>
+      <c r="I74" s="230"/>
     </row>
     <row r="75" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I75" s="257"/>
+      <c r="I75" s="230"/>
     </row>
     <row r="76" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I76" s="257"/>
+      <c r="I76" s="230"/>
     </row>
     <row r="77" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I77" s="257"/>
+      <c r="I77" s="230"/>
     </row>
     <row r="78" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I78" s="257"/>
+      <c r="I78" s="230"/>
     </row>
     <row r="79" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I79" s="257"/>
+      <c r="I79" s="230"/>
     </row>
     <row r="80" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I80" s="257"/>
+      <c r="I80" s="230"/>
     </row>
     <row r="81" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I81" s="257"/>
+      <c r="I81" s="230"/>
     </row>
     <row r="82" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I82" s="257"/>
+      <c r="I82" s="230"/>
     </row>
     <row r="83" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I83" s="257"/>
+      <c r="I83" s="230"/>
     </row>
     <row r="84" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I84" s="257"/>
+      <c r="I84" s="230"/>
     </row>
     <row r="85" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I85" s="257"/>
+      <c r="I85" s="230"/>
     </row>
     <row r="86" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I86" s="257"/>
+      <c r="I86" s="230"/>
     </row>
     <row r="87" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I87" s="257"/>
+      <c r="I87" s="230"/>
     </row>
     <row r="88" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I88" s="257"/>
+      <c r="I88" s="230"/>
     </row>
     <row r="89" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I89" s="257"/>
+      <c r="I89" s="230"/>
     </row>
     <row r="90" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I90" s="257"/>
+      <c r="I90" s="230"/>
     </row>
     <row r="91" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I91" s="257"/>
+      <c r="I91" s="230"/>
     </row>
     <row r="92" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I92" s="257"/>
+      <c r="I92" s="230"/>
     </row>
     <row r="93" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I93" s="257"/>
+      <c r="I93" s="230"/>
     </row>
     <row r="94" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I94" s="257"/>
+      <c r="I94" s="230"/>
     </row>
     <row r="95" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I95" s="257"/>
+      <c r="I95" s="230"/>
     </row>
     <row r="96" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I96" s="257"/>
+      <c r="I96" s="230"/>
     </row>
     <row r="97" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I97" s="257"/>
+      <c r="I97" s="230"/>
     </row>
     <row r="98" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I98" s="257"/>
+      <c r="I98" s="230"/>
     </row>
     <row r="99" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I99" s="257"/>
+      <c r="I99" s="230"/>
     </row>
     <row r="100" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I100" s="257"/>
+      <c r="I100" s="230"/>
     </row>
     <row r="101" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I101" s="257"/>
+      <c r="I101" s="230"/>
     </row>
     <row r="102" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I102" s="257"/>
+      <c r="I102" s="230"/>
     </row>
     <row r="103" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I103" s="257"/>
+      <c r="I103" s="230"/>
     </row>
     <row r="104" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I104" s="257"/>
+      <c r="I104" s="230"/>
     </row>
     <row r="105" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I105" s="257"/>
+      <c r="I105" s="230"/>
     </row>
     <row r="106" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I106" s="257"/>
+      <c r="I106" s="230"/>
     </row>
     <row r="107" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I107" s="257"/>
+      <c r="I107" s="230"/>
     </row>
     <row r="108" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I108" s="257"/>
+      <c r="I108" s="230"/>
     </row>
     <row r="109" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I109" s="257"/>
+      <c r="I109" s="230"/>
     </row>
     <row r="110" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I110" s="257"/>
+      <c r="I110" s="230"/>
     </row>
     <row r="111" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I111" s="257"/>
+      <c r="I111" s="230"/>
     </row>
     <row r="112" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I112" s="257"/>
+      <c r="I112" s="230"/>
     </row>
     <row r="113" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I113" s="257"/>
+      <c r="I113" s="230"/>
     </row>
     <row r="114" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I114" s="257"/>
+      <c r="I114" s="230"/>
     </row>
     <row r="115" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I115" s="257"/>
+      <c r="I115" s="230"/>
     </row>
     <row r="116" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I116" s="257"/>
+      <c r="I116" s="230"/>
     </row>
     <row r="117" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I117" s="257"/>
+      <c r="I117" s="230"/>
     </row>
     <row r="118" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I118" s="257"/>
+      <c r="I118" s="230"/>
     </row>
     <row r="119" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I119" s="257"/>
+      <c r="I119" s="230"/>
     </row>
     <row r="120" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I120" s="257"/>
+      <c r="I120" s="230"/>
     </row>
     <row r="121" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I121" s="257"/>
+      <c r="I121" s="230"/>
     </row>
     <row r="122" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I122" s="257"/>
+      <c r="I122" s="230"/>
     </row>
     <row r="123" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I123" s="257"/>
+      <c r="I123" s="230"/>
     </row>
     <row r="124" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I124" s="257"/>
+      <c r="I124" s="230"/>
     </row>
     <row r="125" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I125" s="257"/>
+      <c r="I125" s="230"/>
     </row>
     <row r="126" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I126" s="257"/>
+      <c r="I126" s="230"/>
     </row>
     <row r="127" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I127" s="257"/>
+      <c r="I127" s="230"/>
     </row>
     <row r="128" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I128" s="257"/>
+      <c r="I128" s="230"/>
     </row>
     <row r="129" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I129" s="257"/>
+      <c r="I129" s="230"/>
     </row>
     <row r="130" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I130" s="257"/>
+      <c r="I130" s="230"/>
     </row>
     <row r="131" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I131" s="257"/>
+      <c r="I131" s="230"/>
     </row>
     <row r="132" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I132" s="257"/>
+      <c r="I132" s="230"/>
     </row>
     <row r="133" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I133" s="257"/>
+      <c r="I133" s="230"/>
     </row>
     <row r="134" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I134" s="257"/>
+      <c r="I134" s="230"/>
     </row>
     <row r="135" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I135" s="257"/>
+      <c r="I135" s="230"/>
     </row>
     <row r="136" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I136" s="257"/>
+      <c r="I136" s="230"/>
     </row>
     <row r="137" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I137" s="257"/>
+      <c r="I137" s="230"/>
     </row>
     <row r="138" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I138" s="257"/>
+      <c r="I138" s="230"/>
     </row>
     <row r="139" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I139" s="257"/>
+      <c r="I139" s="230"/>
     </row>
     <row r="140" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I140" s="257"/>
+      <c r="I140" s="230"/>
     </row>
     <row r="141" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I141" s="257"/>
+      <c r="I141" s="230"/>
     </row>
     <row r="142" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I142" s="257"/>
+      <c r="I142" s="230"/>
     </row>
     <row r="143" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I143" s="257"/>
+      <c r="I143" s="230"/>
     </row>
     <row r="144" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I144" s="257"/>
+      <c r="I144" s="230"/>
     </row>
     <row r="145" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I145" s="257"/>
+      <c r="I145" s="230"/>
     </row>
     <row r="146" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I146" s="257"/>
+      <c r="I146" s="230"/>
     </row>
     <row r="147" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I147" s="257"/>
+      <c r="I147" s="230"/>
     </row>
     <row r="148" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I148" s="257"/>
+      <c r="I148" s="230"/>
     </row>
     <row r="149" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I149" s="257"/>
+      <c r="I149" s="230"/>
     </row>
     <row r="150" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I150" s="257"/>
+      <c r="I150" s="230"/>
     </row>
     <row r="151" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I151" s="257"/>
+      <c r="I151" s="230"/>
     </row>
     <row r="152" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I152" s="257"/>
+      <c r="I152" s="230"/>
     </row>
     <row r="153" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I153" s="257"/>
+      <c r="I153" s="230"/>
     </row>
     <row r="154" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I154" s="257"/>
+      <c r="I154" s="230"/>
     </row>
     <row r="155" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I155" s="257"/>
+      <c r="I155" s="230"/>
     </row>
     <row r="156" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I156" s="257"/>
+      <c r="I156" s="230"/>
     </row>
     <row r="157" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I157" s="257"/>
+      <c r="I157" s="230"/>
     </row>
     <row r="158" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I158" s="257"/>
+      <c r="I158" s="230"/>
     </row>
     <row r="159" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I159" s="257"/>
+      <c r="I159" s="230"/>
     </row>
     <row r="160" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I160" s="257"/>
+      <c r="I160" s="230"/>
     </row>
     <row r="161" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I161" s="257"/>
+      <c r="I161" s="230"/>
     </row>
     <row r="162" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I162" s="257"/>
+      <c r="I162" s="230"/>
     </row>
     <row r="163" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I163" s="257"/>
+      <c r="I163" s="230"/>
     </row>
     <row r="164" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I164" s="257"/>
+      <c r="I164" s="230"/>
     </row>
     <row r="165" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I165" s="257"/>
+      <c r="I165" s="230"/>
     </row>
     <row r="166" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I166" s="257"/>
+      <c r="I166" s="230"/>
     </row>
     <row r="167" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I167" s="257"/>
+      <c r="I167" s="230"/>
     </row>
     <row r="168" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I168" s="257"/>
+      <c r="I168" s="230"/>
     </row>
     <row r="169" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I169" s="257"/>
+      <c r="I169" s="230"/>
     </row>
     <row r="170" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I170" s="257"/>
+      <c r="I170" s="230"/>
     </row>
     <row r="171" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I171" s="257"/>
+      <c r="I171" s="230"/>
     </row>
     <row r="172" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I172" s="257"/>
+      <c r="I172" s="230"/>
     </row>
     <row r="173" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I173" s="257"/>
+      <c r="I173" s="230"/>
     </row>
     <row r="174" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I174" s="257"/>
+      <c r="I174" s="230"/>
     </row>
     <row r="175" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I175" s="257"/>
+      <c r="I175" s="230"/>
     </row>
     <row r="176" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I176" s="257"/>
+      <c r="I176" s="230"/>
     </row>
     <row r="177" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I177" s="257"/>
+      <c r="I177" s="230"/>
     </row>
     <row r="178" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I178" s="257"/>
+      <c r="I178" s="230"/>
     </row>
     <row r="179" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I179" s="257"/>
+      <c r="I179" s="230"/>
     </row>
     <row r="180" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I180" s="257"/>
+      <c r="I180" s="230"/>
     </row>
     <row r="181" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I181" s="257"/>
+      <c r="I181" s="230"/>
     </row>
     <row r="182" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I182" s="257"/>
+      <c r="I182" s="230"/>
     </row>
     <row r="183" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I183" s="257"/>
+      <c r="I183" s="230"/>
     </row>
     <row r="184" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I184" s="257"/>
+      <c r="I184" s="230"/>
     </row>
     <row r="185" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I185" s="257"/>
+      <c r="I185" s="230"/>
     </row>
     <row r="186" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I186" s="257"/>
+      <c r="I186" s="230"/>
     </row>
     <row r="187" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I187" s="257"/>
+      <c r="I187" s="230"/>
     </row>
     <row r="188" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I188" s="257"/>
+      <c r="I188" s="230"/>
     </row>
     <row r="189" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I189" s="257"/>
+      <c r="I189" s="230"/>
     </row>
     <row r="190" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I190" s="257"/>
+      <c r="I190" s="230"/>
     </row>
     <row r="191" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I191" s="257"/>
+      <c r="I191" s="230"/>
     </row>
     <row r="192" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I192" s="257"/>
+      <c r="I192" s="230"/>
     </row>
     <row r="193" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I193" s="257"/>
+      <c r="I193" s="230"/>
     </row>
     <row r="194" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I194" s="257"/>
+      <c r="I194" s="230"/>
     </row>
     <row r="195" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I195" s="257"/>
+      <c r="I195" s="230"/>
     </row>
     <row r="196" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I196" s="257"/>
+      <c r="I196" s="230"/>
     </row>
     <row r="197" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I197" s="257"/>
+      <c r="I197" s="230"/>
     </row>
     <row r="198" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I198" s="257"/>
+      <c r="I198" s="230"/>
     </row>
     <row r="199" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I199" s="257"/>
+      <c r="I199" s="230"/>
     </row>
     <row r="200" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I200" s="257"/>
+      <c r="I200" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14564,13 +14505,13 @@
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="N4:T4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6:V151">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ISBLANK($D6)=FALSE,ISBLANK($F6)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="C6:V151">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND(ISBLANK($D6)=FALSE,ISBLANK($F6)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16070,16 +16011,16 @@
   <sheetData>
     <row r